--- a/static/output/analysis_results.xlsx
+++ b/static/output/analysis_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,179 +483,179 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nasher Miles Bag</t>
+          <t>Samsung Galaxy S25 Ultra</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"product_id": "B0DNQV9LKB?th=1&amp;psc=1", "product_url": "https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1", "summary": {"total_reviews": 2, "average_rating": 4.0, "sentiment_breakdown": {"positive": 2, "neutral": 0, "negative": 0}, "overall_sentiment": "positive", "accuracy_score": 100.0}, "reviews": [{"author": "Nitesh", "rating": "4.0", "date": "20 Mar 2025", "text": "Bag is quite sturdy and compact size not too big not too small .. Good fit for daily office usage.Material used for the bag looks premium only downside is bag should have side compartment to keep the water bottle.. But apart from this loving this product..", "product_id": "B0DNQV9LKB?th=1&amp;psc=1", "link": "https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1", "sentiment": "positive"}, {"author": "Nitesh", "rating": "4.0", "date": "20 Mar 2025", "text": "Bag is quite sturdy and compact size not too big not too small .. Good fit for daily office usage.Material used for the bag looks premium only downside is bag should have side compartment to keep the water bottle.. But apart from this loving this product..", "product_id": "B0DNQV9LKB?th=1&amp;psc=1", "link": "https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1", "sentiment": "positive"}]}</t>
+          <t>{\"product_id\": \"B0DSKMKJV5\", \"product_name\": \"Samsung Galaxy S25 Ultra 5G AI Smartphone (Titanium Black, 12GB RAM, 512GB Storage), 200MP Camera, S Pen Included, Long Battery Life\", \"product_url\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"negative\": 6, \"positive\": 6, \"neutral\": 4}, \"overall_sentiment\": \"negative\", \"accuracy_score\": 37.5}, \"reviews\": [{\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1</t>
+          <t>https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ugreen Charger</t>
+          <t>vivo X200 Pro</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"product_id": "B0CQ2F185Z", "product_url": "https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3", "summary": {"total_reviews": 2, "average_rating": 1.0, "sentiment_breakdown": {"positive": 0, "neutral": 0, "negative": 2}, "overall_sentiment": "negative", "accuracy_score": 100.0}, "reviews": [{"author": "Placeholder", "rating": "1.0", "date": "05 Feb 2025", "text": "Spending almost 5K for a charger and getting 200Rs charger pin quality. Not sure if it is only for Indian units.", "product_id": "B0CQ2F185Z", "link": "https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3", "sentiment": "negative"}, {"author": "Placeholder", "rating": "1.0", "date": "05 Feb 2025", "text": "Spending almost 5K for a charger and getting 200Rs charger pin quality. Not sure if it is only for Indian units.", "product_id": "B0CQ2F185Z", "link": "https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3", "sentiment": "negative"}]}</t>
+          <t>{\"product_id\": \"B07WDJMX16\", \"product_name\": \"Vivo X200 Pro 5G (Titanium Grey, 16GB RAM, 512GB Storage) with No Cost EMI/Additional Exchange Offers\", \"product_url\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"negative\": 4, \"positive\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 60.0}, \"reviews\": [{\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3</t>
+          <t>https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Iphone !6e</t>
+          <t>Xiaomi 15 Ultra</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.14%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"product_id": "B0DXQH1DBS", "product_url": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "summary": {"total_reviews": 16, "average_rating": 4.12, "sentiment_breakdown": {"positive": 12, "neutral": 2, "negative": 2}, "overall_sentiment": "positive", "accuracy_score": 75.0}, "reviews": [{"author": "ashish", "rating": "5.0", "date": "29 Mar 2025", "text": "The iPhone 16e delivers exceptional performance with its powerful A18 chip and stunning 6.1-inch OLED display. The 48MP camera captures brilliant photos, and its impressive battery life ensures all-day usage.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "JAYARAM O P", "rating": "5.0", "date": "28 Mar 2025", "text": "Its been Close to 1 week and I am happy with the purchase. Got a good exchange offer with my old IPhone 8 and with the bank offer, the price came down to around 45K for 128GB model.Battery backup is very good.Light Weight and build quality is good.Camera is good to the levell what we are paying.Except wide angle camera, getting everything what IPhone 16 has to offer.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "md sahanul islam", "rating": "5.0", "date": "03 Apr 2025", "text": "Good Good", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "sharatchandra khuman", "rating": "1.0", "date": "25 Mar 2025", "text": "Battery draining very fast\u2026.not suggested those planning to buy 16 e\u2026..", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "negative"}, {"author": "Gajendra", "rating": "4.0", "date": "14 Mar 2025", "text": "Very Nice Phone.Reliable and Durable.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "Amazon Customer", "rating": "5.0", "date": "29 Mar 2025", "text": "Practically perfect. All day battery with power performance.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "KRISHNA KUMAR", "rating": "3.0", "date": "16 Mar 2025", "text": "Good one but not worth for money", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "neutral"}, {"author": "Santhoshkumaran", "rating": "5.0", "date": "05 Apr 2025", "text": "Love it", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "ashish", "rating": "5.0", "date": "29 Mar 2025", "text": "The iPhone 16e delivers exceptional performance with its powerful A18 chip and stunning 6.1-inch OLED display. The 48MP camera captures brilliant photos, and its impressive battery life ensures all-day usage.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "JAYARAM O P", "rating": "5.0", "date": "28 Mar 2025", "text": "Its been Close to 1 week and I am happy with the purchase. Got a good exchange offer with my old IPhone 8 and with the bank offer, the price came down to around 45K for 128GB model.Battery backup is very good.Light Weight and build quality is good.Camera is good to the levell what we are paying.Except wide angle camera, getting everything what IPhone 16 has to offer.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "md sahanul islam", "rating": "5.0", "date": "03 Apr 2025", "text": "Good Good", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "sharatchandra khuman", "rating": "1.0", "date": "25 Mar 2025", "text": "Battery draining very fast\u2026.not suggested those planning to buy 16 e\u2026..", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "negative"}, {"author": "Gajendra", "rating": "4.0", "date": "14 Mar 2025", "text": "Very Nice Phone.Reliable and Durable.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "Amazon Customer", "rating": "5.0", "date": "29 Mar 2025", "text": "Practically perfect. All day battery with power performance.", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}, {"author": "KRISHNA KUMAR", "rating": "3.0", "date": "16 Mar 2025", "text": "Good one but not worth for money", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "neutral"}, {"author": "Santhoshkumaran", "rating": "5.0", "date": "05 Apr 2025", "text": "Love it", "product_id": "B0DXQH1DBS", "link": "https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3", "sentiment": "positive"}]}</t>
+          <t>{\"product_id\": \"B0DYV4177R\", \"product_name\": \"Xiaomi 15 Ultra (Silver Chrome, 16GB/512GB)| 200 MP Leica-Quad Camera | SD 8 Elite | WQHD+ Quad Curve AMOLED | Hyper AI\", \"product_url\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"summary\": {\"total_reviews\": 14, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 6, \"negative\": 8}, \"overall_sentiment\": \"negative\", \"accuracy_score\": 57.14}, \"reviews\": [{\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3</t>
+          <t>https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S24 Ultra 5G</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.38</v>
+        <v>4.83</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"product_id": "B0CS5XW6TN", "product_url": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "summary": {"total_reviews": 16, "average_rating": 4.38, "sentiment_breakdown": {"positive": 14, "neutral": 0, "negative": 2}, "overall_sentiment": "positive", "accuracy_score": 87.5}, "reviews": [{"author": "Anand", "rating": "5.0", "date": "29 Mar 2025", "text": "Simply Superb and Awesome..!!!S24 Ultra is the best Andriod available out there. Overall Styling, Top notch Camera, Premium feel, Titanium body, Super Advanced Processor, 12GB RAM, Vast Storage capacity (starting from 256GB), Best in class Battery backup, Reliable brand are the key USP's one should consider in this phone. I use IP15 Pro as my Primary phone and after this in hand, honestly iPhone 15 Pro feels outdated..!! Guys, if you are thinking of this phone, then just go for it..! No second thoughts.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Rahul", "rating": "5.0", "date": "05 Apr 2025", "text": "Excellent phone the camera quality is exceptional. Sound quality and battery life is good. Charging speed is fast.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Singhal", "rating": "1.0", "date": "17 Dec 2024", "text": "I did not have any inclination to buy a Samsung but looking at so many advertisements about the Samsung AI, I got inclined and when I got some offer, I bought a Samsung S24 Ultra. The phone worked fine but the face unlock was not accurate most of the time. It takes sometime to unlock which never happened with the phones I've used before. Secondly, there is a peculiar issue that I started noticing. Whenever, I use to get a call on WhatsApp, it does not ring and puts my volume to zero. Due to which, my normal calls also does not ring. Even after again making the sound to maximum, the WhatsApp call makes it to zero, making it so frustrating as I used to miss calls.I took it to the service centre 3 times and all they did was reset the settings, reinstall the OS etc. And after that they started telling that it's a issue in your WhatsApp. How can this be a WhatsApp issue when I've been using the same WhatsApp from so many years. They kept the phone for 4 days and ultimately returned saying that they could not replicate the issue.I would I do with a 1.1lakh phone if I'm not able to use a WhatsApp.I could have gone for Apple, which provides a stable OS atleast.Please look for alternatives.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "negative"}, {"author": "Hansel K.", "rating": "5.0", "date": "04 Nov 2024", "text": "I recently upgraded to the Samsung Galaxy S24 Ultra, and I couldn\u2019t be happier! From the moment I unboxed it, the sleek design and premium feel set a new standard. The screen is stunning \u2013 bright, vibrant, and incredibly responsive, making streaming and gaming a real pleasure.Performance-wise, this phone is a beast. Multitasking is a breeze, and apps open instantly, thanks to the top-tier processor. Battery life is also fantastic, easily lasting me a full day with heavy use, and fast charging means I\u2019m never stuck waiting long when I need a boost.The camera quality is next-level! Low-light photos come out crisp, the zoom is mind-blowing, and colors are captured beautifully. It\u2019s like having a professional camera in my pocket.Overall, the Galaxy S24 Ultra is worth every penny. It\u2019s a true flagship device that feels future-proof, and I\u2019d highly recommend it to anyone looking for a powerful, feature-packed smartphone!", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Mohammed Tameem", "rating": "4.0", "date": "13 Jan 2025", "text": "Amazing display, Great cam, charging speed, always cool.Cons:It doesn't maintain a steady video frame rate in low light.Wireless 15w charging is slowMy rant on AppleI was interested to get the Apple watch but was hesitant to get the iphone but finally gave in and... IT WAS HORROR...Worst part, during exchange, you don't have access to your iphone so say bye bye to your WhatsApp backup... I had to get an old iphone from a friend to get the data transfered...All that aside, S24 U has been just the right device for me...", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Mary iris", "rating": "5.0", "date": "28 Mar 2025", "text": "Works really well and good picture quality and Great zoom quality as well.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "kundan soren", "rating": "5.0", "date": "26 Mar 2025", "text": "Very good phone,display and camera superb, smoth processor", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Sanju Hazra", "rating": "5.0", "date": "28 Mar 2025", "text": "Good phone", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Anand", "rating": "5.0", "date": "29 Mar 2025", "text": "Simply Superb and Awesome..!!!S24 Ultra is the best Andriod available out there. Overall Styling, Top notch Camera, Premium feel, Titanium body, Super Advanced Processor, 12GB RAM, Vast Storage capacity (starting from 256GB), Best in class Battery backup, Reliable brand are the key USP's one should consider in this phone. I use IP15 Pro as my Primary phone and after this in hand, honestly iPhone 15 Pro feels outdated..!! Guys, if you are thinking of this phone, then just go for it..! No second thoughts.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Rahul", "rating": "5.0", "date": "05 Apr 2025", "text": "Excellent phone the camera quality is exceptional. Sound quality and battery life is good. Charging speed is fast.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Singhal", "rating": "1.0", "date": "17 Dec 2024", "text": "I did not have any inclination to buy a Samsung but looking at so many advertisements about the Samsung AI, I got inclined and when I got some offer, I bought a Samsung S24 Ultra. The phone worked fine but the face unlock was not accurate most of the time. It takes sometime to unlock which never happened with the phones I've used before. Secondly, there is a peculiar issue that I started noticing. Whenever, I use to get a call on WhatsApp, it does not ring and puts my volume to zero. Due to which, my normal calls also does not ring. Even after again making the sound to maximum, the WhatsApp call makes it to zero, making it so frustrating as I used to miss calls.I took it to the service centre 3 times and all they did was reset the settings, reinstall the OS etc. And after that they started telling that it's a issue in your WhatsApp. How can this be a WhatsApp issue when I've been using the same WhatsApp from so many years. They kept the phone for 4 days and ultimately returned saying that they could not replicate the issue.I would I do with a 1.1lakh phone if I'm not able to use a WhatsApp.I could have gone for Apple, which provides a stable OS atleast.Please look for alternatives.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "negative"}, {"author": "Hansel K.", "rating": "5.0", "date": "04 Nov 2024", "text": "I recently upgraded to the Samsung Galaxy S24 Ultra, and I couldn\u2019t be happier! From the moment I unboxed it, the sleek design and premium feel set a new standard. The screen is stunning \u2013 bright, vibrant, and incredibly responsive, making streaming and gaming a real pleasure.Performance-wise, this phone is a beast. Multitasking is a breeze, and apps open instantly, thanks to the top-tier processor. Battery life is also fantastic, easily lasting me a full day with heavy use, and fast charging means I\u2019m never stuck waiting long when I need a boost.The camera quality is next-level! Low-light photos come out crisp, the zoom is mind-blowing, and colors are captured beautifully. It\u2019s like having a professional camera in my pocket.Overall, the Galaxy S24 Ultra is worth every penny. It\u2019s a true flagship device that feels future-proof, and I\u2019d highly recommend it to anyone looking for a powerful, feature-packed smartphone!", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Mohammed Tameem", "rating": "4.0", "date": "13 Jan 2025", "text": "Amazing display, Great cam, charging speed, always cool.Cons:It doesn't maintain a steady video frame rate in low light.Wireless 15w charging is slowMy rant on AppleI was interested to get the Apple watch but was hesitant to get the iphone but finally gave in and... IT WAS HORROR...Worst part, during exchange, you don't have access to your iphone so say bye bye to your WhatsApp backup... I had to get an old iphone from a friend to get the data transfered...All that aside, S24 U has been just the right device for me...", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Mary iris", "rating": "5.0", "date": "28 Mar 2025", "text": "Works really well and good picture quality and Great zoom quality as well.", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "kundan soren", "rating": "5.0", "date": "26 Mar 2025", "text": "Very good phone,display and camera superb, smoth processor", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}, {"author": "Sanju Hazra", "rating": "5.0", "date": "28 Mar 2025", "text": "Good phone", "product_id": "B0CS5XW6TN", "link": "https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1", "sentiment": "positive"}]}</t>
+          <t>{\"product_id\": \"B0DQ8MJYXF\", \"product_name\": \"OnePlus 13 | Smarter AI | Lifetime Display Warranty (16GB RAM, 512GB Storage Midnight Ocean)\", \"product_url\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"summary\": {\"total_reviews\": 12, \"average_rating\": 4.83, \"sentiment_breakdown\": {\"negative\": 6, \"positive\": 6}, \"overall_sentiment\": \"negative\", \"accuracy_score\": 50.0}, \"reviews\": [{\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1</t>
+          <t>https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OnePlus Nord 4 5G (Obsidian Midnight, 8GB RAM, 256GB Storage)</t>
+          <t>Motorola Razr 60 Ultra</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -677,16 +677,142 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"product_id": "B0D7VKMLGD", "product_url": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "summary": {"total_reviews": 8, "average_rating": 4.5, "sentiment_breakdown": {"positive": 4, "neutral": 0, "negative": 0}, "overall_sentiment": "positive", "accuracy_score": 100.0}, "reviews": [{"author": "KalimKalim", "rating": "5.05.0", "date": "23 Mar 2025", "text": "I've been using the OnePlus Nord 4 for about 2 weeks and I can say this phone is a great but for this pricePros: Almost everything,1. The display is gorgeous but it is not dynamic, meaning it stays at 120Hz all the time even when set to auto2. The battery life is also really damn good, coming from an iPhone X, this is great and 100W in the box charger charges it while a small break,3. Build quality is top notch, I like the metal back but the looks is bad, I suggested a family member this phone but it looks so bad, it was dismissed but for me it is alright (side note: you get a transparent TPU case and not a high quality one which funnily enough you get in the CE 4)Performance is great too, 7+ gen 3 is one of the better choiceCons:Camera: while main camera is ok, selfie and ultrawide are preety midVideo: only the main camera can do 4K 60FPS, other cameras are capped at 1080p 30FPS. So while you can record in 4K, you cannot change perspectives.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "unknown"}, {"author": "Sahil kumar", "rating": "4.0", "date": "08 Feb 2025", "text": "Writing this Review After 20 days use and I can say this phone doesn't disappoint.Pros :-1. Metal build phone which feels premium and a notch above the rest of its competitors. Design is just pleasant to look at.2. Software after Android 15 and Oxygen os 15 update has become even more smooth and snappy which makes everyday use more refined and premium.3. With snapdragon 7+ gen 3 this phone is fast and feels like a flagship. Played games like BGMI and COD at 90 fps without any frames drop.4. Battery backup is amazing and it easily gives me 8 hrs plus SOT on day to day balanced use and 7+ hrs on a heavy use. I charge ones a day and next day I am still left with few more minutes before charging. Plus 100W superfast charger is cherry on top5. Haptics are just exceptioal and performs better than many flagship phones.6. The long software and security support also gives this phone a better chance to retain its resale value for longer period than its competitors.7. Clean software experience though it came with few bloatwares with its own app market but after deleting those apps and disabling the app market the experience has been overall great.8. This comes with flat screen which is great considering many good phone under this price segment have curve screens.Cons:-1. Camera is good but could have been better. Not a camera guy so it works for me but may not for the ones who want best camera for their buck.2. The front glass is not from the Corning thus should be handled with care and a screen tempered glass is must for this one.So in the end this is currently amongst the best balanced phone one could buy for this price and can experience a great phone at such low price.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "positive"}, {"author": "Gaurav K GauravGaurav K Gaurav", "rating": "5.05.0", "date": "10 Mar 2025", "text": "Okay this review is going to be long so have some popcorn with you.Quality :- phone quality is awesome it's metal building (Aluminium) back and the colour is amazing, I prefer black but my mother choose this colour so I prefer my mother's choice over mine and bought this one. \u2b50 9/10Processor :- I have been using for a week till now I didn't faced any lag or phone hanging issue phone is very smooth.  \u2b50 9/10Battery :- It gives preety good backup nearly 9 to 10hrs if you browser or watch videos. I didn't play games on it so don't know much about gaming performance.Charging :- charging is super fast that it charges 20 to 80 in just 15 to 20 mints. Till now I did not faced heating issue in phone during charging. Phone heats somewhat but not too much which does affect its functionality. \u2b50 9.5 /10Display :- display quality is also very good, its soo smooth and it's brightness is also good in external condition. Fingerprint sensor is also very fast but if you apply tempered glass on your phone please make sure you must remove the film which is pre applied on mobile otherwise it will affect the fingerprint scanning. \u2b50 9/10Overall no Phone hanging issue no any complaint till now in a week. I am satisfied with my purchase, I will update my review later.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "unknown"}, {"author": "Amazon Customer", "rating": "5.0", "date": "12 Feb 2025", "text": "Nord 4 Phone is excellent ,offering a compelling blend of high-end features and mid-range affordability. Its standout feature is undoubtedly the impressive camera system, boasting a 50MP main sensor that captures stunningly detailed photos and videos. The vibrant and responsive AMOLED display provides a visually immersive experience, perfect for streaming content or gaming. Performance is buttery smooth thanks to the powerful processor and ample RAM, ensuring lag-free multitasking and app usage. Battery life is another strong suit, easily lasting a full day on a single charge, even with heavy usage. While some users might find the lack of expandable storage a drawback, the Nord 4 compensates with its generous base storage option. Overall, the Nord 4 is an exceptional value proposition for budget-conscious consumers who don't want to compromise on performance or features.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "positive"}, {"author": "KalimKalim", "rating": "5.05.0", "date": "23 Mar 2025", "text": "I've been using the OnePlus Nord 4 for about 2 weeks and I can say this phone is a great but for this pricePros: Almost everything,1. The display is gorgeous but it is not dynamic, meaning it stays at 120Hz all the time even when set to auto2. The battery life is also really damn good, coming from an iPhone X, this is great and 100W in the box charger charges it while a small break,3. Build quality is top notch, I like the metal back but the looks is bad, I suggested a family member this phone but it looks so bad, it was dismissed but for me it is alright (side note: you get a transparent TPU case and not a high quality one which funnily enough you get in the CE 4)Performance is great too, 7+ gen 3 is one of the better choiceCons:Camera: while main camera is ok, selfie and ultrawide are preety midVideo: only the main camera can do 4K 60FPS, other cameras are capped at 1080p 30FPS. So while you can record in 4K, you cannot change perspectives.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "unknown"}, {"author": "Sahil kumar", "rating": "4.0", "date": "08 Feb 2025", "text": "Writing this Review After 20 days use and I can say this phone doesn't disappoint.Pros :-1. Metal build phone which feels premium and a notch above the rest of its competitors. Design is just pleasant to look at.2. Software after Android 15 and Oxygen os 15 update has become even more smooth and snappy which makes everyday use more refined and premium.3. With snapdragon 7+ gen 3 this phone is fast and feels like a flagship. Played games like BGMI and COD at 90 fps without any frames drop.4. Battery backup is amazing and it easily gives me 8 hrs plus SOT on day to day balanced use and 7+ hrs on a heavy use. I charge ones a day and next day I am still left with few more minutes before charging. Plus 100W superfast charger is cherry on top5. Haptics are just exceptioal and performs better than many flagship phones.6. The long software and security support also gives this phone a better chance to retain its resale value for longer period than its competitors.7. Clean software experience though it came with few bloatwares with its own app market but after deleting those apps and disabling the app market the experience has been overall great.8. This comes with flat screen which is great considering many good phone under this price segment have curve screens.Cons:-1. Camera is good but could have been better. Not a camera guy so it works for me but may not for the ones who want best camera for their buck.2. The front glass is not from the Corning thus should be handled with care and a screen tempered glass is must for this one.So in the end this is currently amongst the best balanced phone one could buy for this price and can experience a great phone at such low price.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "positive"}, {"author": "Gaurav K GauravGaurav K Gaurav", "rating": "5.05.0", "date": "10 Mar 2025", "text": "Okay this review is going to be long so have some popcorn with you.Quality :- phone quality is awesome it's metal building (Aluminium) back and the colour is amazing, I prefer black but my mother choose this colour so I prefer my mother's choice over mine and bought this one. \u2b50 9/10Processor :- I have been using for a week till now I didn't faced any lag or phone hanging issue phone is very smooth.  \u2b50 9/10Battery :- It gives preety good backup nearly 9 to 10hrs if you browser or watch videos. I didn't play games on it so don't know much about gaming performance.Charging :- charging is super fast that it charges 20 to 80 in just 15 to 20 mints. Till now I did not faced heating issue in phone during charging. Phone heats somewhat but not too much which does affect its functionality. \u2b50 9.5 /10Display :- display quality is also very good, its soo smooth and it's brightness is also good in external condition. Fingerprint sensor is also very fast but if you apply tempered glass on your phone please make sure you must remove the film which is pre applied on mobile otherwise it will affect the fingerprint scanning. \u2b50 9/10Overall no Phone hanging issue no any complaint till now in a week. I am satisfied with my purchase, I will update my review later.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "unknown"}, {"author": "Amazon Customer", "rating": "5.0", "date": "12 Feb 2025", "text": "Nord 4 Phone is excellent ,offering a compelling blend of high-end features and mid-range affordability. Its standout feature is undoubtedly the impressive camera system, boasting a 50MP main sensor that captures stunningly detailed photos and videos. The vibrant and responsive AMOLED display provides a visually immersive experience, perfect for streaming content or gaming. Performance is buttery smooth thanks to the powerful processor and ample RAM, ensuring lag-free multitasking and app usage. Battery life is another strong suit, easily lasting a full day on a single charge, even with heavy usage. While some users might find the lack of expandable storage a drawback, the Nord 4 compensates with its generous base storage option. Overall, the Nord 4 is an exceptional value proposition for budget-conscious consumers who don't want to compromise on performance or features.", "product_id": "B0D7VKMLGD", "link": "https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45", "sentiment": "positive"}]}</t>
+          <t>{\"product_id\": \"B0F5HVFVKH\", \"product_name\": \"Motorola razr 60 Ultra (Pantone Scarab, 16 GB RAM, 512 GB Storage) | Moto AI | Snapdragon® 8 Elite Mobile Platform | 6.9\\" AMOLED 165Hz Display | 50 MP + 50 MP + 50MP Triple Camera\", \"product_url\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"summary\": {\"total_reviews\": 2, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45</t>
+          <t>https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nothing Phone 3a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DZNP1MN3\", \"product_name\": \"Nothing Phone (3A) 5G (White, 8GB RAM, 256GB Storage)\", \"product_url\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 4, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"neutral\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"neutral\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Samsung S24 FE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DHL7YT5S\", \"product_name\": \"Samsung Galaxy S24 FE 5G AI Smartphone (Graphite, 8GB RAM, 128GB Storage)\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.12, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijit\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"Don\'t fall for this trap. Phone looks good and camera is also pretty decent. Battery also OK for my kind of usage. But it has HEATING ISSUES...No matter whether you close all the apps or what kind of usage you do, it heats up. I don\'t play games, normal browsing also you can feel on your palms despite using a Spigen cover. Without cover it feels even more.DONT GO FOR IT. Buy Iqoo 12 or one plus 13R or Vivo V40 or any other phone...\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijit\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"Don\'t fall for this trap. Phone looks good and camera is also pretty decent. Battery also OK for my kind of usage. But it has HEATING ISSUES...No matter whether you close all the apps or what kind of usage you do, it heats up. I don\'t play games, normal browsing also you can feel on your palms despite using a Spigen cover. Without cover it feels even more.DONT GO FOR IT. Buy Iqoo 12 or one plus 13R or Vivo V40 or any other phone...\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sony PlayStation®5 Digital Edition (slim) Console Video Game</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CY5QW186\", \"product_name\": \"Sony PlayStation®5 Digital Edition (slim) Console Video Game\", \"product_url\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.88, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Shivshankar\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    First time getting a PS5 as GTA VI soon, and honestly the console experience is nice. You pick up the controller and just play. Overall amazing experience, that’s coming from a long time PC gamer.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajay\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"It is perfect and got it for a great price. Playstation plus membership is highly recommended with it.PS: It may not work on inverter if there is a power outage as its wattage is over 100 watts. So don\'t worry, once the power comes back on, you are good to go 😎\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhanashree\", \"rating\": \"5.0\", \"date\": \"12 May 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"ADI\", \"rating\": \"5.0\", \"date\": \"23 Aug 2024\", \"text\": \"I finally got my hands on the Sony PlayStation®5 Digital Edition, and it has exceeded all my expectations! The only downside was the delayed delivery, which was frustrating, but once it arrived, it was absolutely worth the wait.Performance:The PS5 is a powerhouse. The speed and performance are on another level, with games loading almost instantly thanks to the SSD. The graphics are stunning, bringing an immersive experience that I’ve never felt before. Playing games in 4K with ray tracing truly makes a difference, and everything runs incredibly smoothly.Design:The design of the PS5 Digital Edition is sleek and modern. It looks great in my entertainment setup and feels like a premium piece of technology. Even though it’s a bit large, the futuristic design makes it a centerpiece rather than just a console.Digital Experience:I was initially concerned about going all-digital, but the PS5 Digital Edition has made me a believer. The PlayStation Store is easy to navigate, and downloading games is quick and hassle-free. Plus, without the need for discs, everything feels more streamlined and clutter-free.DualSense Controller:The new DualSense controller is a game-changer. The haptic feedback and adaptive triggers add a whole new dimension to gaming, making it feel more immersive and responsive. It’s comfortable to hold, and the battery life is impressive.Overall:Despite the delayed delivery, I couldn’t be happier with my PS5 Digital Edition. The performance, design, and overall gaming experience are phenomenal. If you’re considering making the leap to next-gen gaming, the PS5 Digital Edition is definitely the way to go.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Mayank Saluja\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"Really worth it at the cost I have got this gaming console . Playing it digital is also fun . Playstation Plus subscription is suggested to take to enjoy online gaming fun too . Graphics and gaming experience is really worth it . If anyone has a 4K smart tv then it will be more fun to enjoy. Wish if could have got 2 remotes instead of only 1 wid dis gaming console oderwise the its fun to enjoy .\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhrubajyoti Baishya\", \"rating\": \"4.0\", \"date\": \"19 Apr 2025\", \"text\": \"Got delivered in one day. Excellent service, excellent packaging. But the product built quality could be better. I have a feeling that the hdmi port will break if you keep putting it on and off. Plastic quality feels like something you get in a non branded console apart from the side panel and the front side. The main unit doesn\'t feel that good as compared to the controller. It feels cheap. But the performance is top notch. Power consumption is low if you compare it to a gaming pc setup with that much performance.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"30 Apr 2025\", \"text\": \"The item was delivered in appropriate packaging. Functions as expected, no issues at all.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Navdeep k.\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"A really good product for gamers.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Shivshankar\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    First time getting a PS5 as GTA VI soon, and honestly the console experience is nice. You pick up the controller and just play. Overall amazing experience, that’s coming from a long time PC gamer.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajay\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"It is perfect and got it for a great price. Playstation plus membership is highly recommended with it.PS: It may not work on inverter if there is a power outage as its wattage is over 100 watts. So don\'t worry, once the power comes back on, you are good to go 😎\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhanashree\", \"rating\": \"5.0\", \"date\": \"12 May 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"ADI\", \"rating\": \"5.0\", \"date\": \"23 Aug 2024\", \"text\": \"I finally got my hands on the Sony PlayStation®5 Digital Edition, and it has exceeded all my expectations! The only downside was the delayed delivery, which was frustrating, but once it arrived, it was absolutely worth the wait.Performance:The PS5 is a powerhouse. The speed and performance are on another level, with games loading almost instantly thanks to the SSD. The graphics are stunning, bringing an immersive experience that I’ve never felt before. Playing games in 4K with ray tracing truly makes a difference, and everything runs incredibly smoothly.Design:The design of the PS5 Digital Edition is sleek and modern. It looks great in my entertainment setup and feels like a premium piece of technology. Even though it’s a bit large, the futuristic design makes it a centerpiece rather than just a console.Digital Experience:I was initially concerned about going all-digital, but the PS5 Digital Edition has made me a believer. The PlayStation Store is easy to navigate, and downloading games is quick and hassle-free. Plus, without the need for discs, everything feels more streamlined and clutter-free.DualSense Controller:The new DualSense controller is a game-changer. The haptic feedback and adaptive triggers add a whole new dimension to gaming, making it feel more immersive and responsive. It’s comfortable to hold, and the battery life is impressive.Overall:Despite the delayed delivery, I couldn’t be happier with my PS5 Digital Edition. The performance, design, and overall gaming experience are phenomenal. If you’re considering making the leap to next-gen gaming, the PS5 Digital Edition is definitely the way to go.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Mayank Saluja\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"Really worth it at the cost I have got this gaming console . Playing it digital is also fun . Playstation Plus subscription is suggested to take to enjoy online gaming fun too . Graphics and gaming experience is really worth it . If anyone has a 4K smart tv then it will be more fun to enjoy. Wish if could have got 2 remotes instead of only 1 wid dis gaming console oderwise the its fun to enjoy .\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhrubajyoti Baishya\", \"rating\": \"4.0\", \"date\": \"19 Apr 2025\", \"text\": \"Got delivered in one day. Excellent service, excellent packaging. But the product built quality could be better. I have a feeling that the hdmi port will break if you keep putting it on and off. Plastic quality feels like something you get in a non branded console apart from the side panel and the front side. The main unit doesn\'t feel that good as compared to the controller. It feels cheap. But the performance is top notch. Power consumption is low if you compare it to a gaming pc setup with that much performance.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"30 Apr 2025\", \"text\": \"The item was delivered in appropriate packaging. Functions as expected, no issues at all.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Navdeep k.\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"A really good product for gamers.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1</t>
         </is>
       </c>
     </row>

--- a/static/output/analysis_results.xlsx
+++ b/static/output/analysis_results.xlsx
@@ -491,29 +491,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>16</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DSKMKJV5\", \"product_name\": \"Samsung Galaxy S25 Ultra 5G AI Smartphone (Titanium Black, 12GB RAM, 512GB Storage), 200MP Camera, S Pen Included, Long Battery Life\", \"product_url\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"negative\": 6, \"positive\": 6, \"neutral\": 4}, \"overall_sentiment\": \"negative\", \"accuracy_score\": 37.5}, \"reviews\": [{\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0DSKMKJV5\", \"product_name\": \"Samsung Galaxy S25 Ultra 5G AI Smartphone (Titanium Black, 12GB RAM, 512GB Storage), 200MP Camera, S Pen Included, Long Battery Life\", \"product_url\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 2, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,24 +538,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B07WDJMX16\", \"product_name\": \"Vivo X200 Pro 5G (Titanium Grey, 16GB RAM, 512GB Storage) with No Cost EMI/Additional Exchange Offers\", \"product_url\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"negative\": 4, \"positive\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 60.0}, \"reviews\": [{\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
+          <t>{\"product_id\": \"B07WDJMX16\", \"product_name\": \"Vivo X200 Pro 5G (Titanium Grey, 16GB RAM, 512GB Storage) with No Cost EMI/Additional Exchange Offers\", \"product_url\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -575,29 +575,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.14%</t>
+          <t>71.43%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DYV4177R\", \"product_name\": \"Xiaomi 15 Ultra (Silver Chrome, 16GB/512GB)| 200 MP Leica-Quad Camera | SD 8 Elite | WQHD+ Quad Curve AMOLED | Hyper AI\", \"product_url\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"summary\": {\"total_reviews\": 14, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 6, \"negative\": 8}, \"overall_sentiment\": \"negative\", \"accuracy_score\": 57.14}, \"reviews\": [{\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
+          <t>{\"product_id\": \"B0DYV4177R\", \"product_name\": \"Xiaomi 15 Ultra (Silver Chrome, 16GB/512GB)| 200 MP Leica-Quad Camera | SD 8 Elite | WQHD+ Quad Curve AMOLED | Hyper AI\", \"product_url\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"summary\": {\"total_reviews\": 14, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 71.43}, \"reviews\": [{\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -617,29 +617,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DQ8MJYXF\", \"product_name\": \"OnePlus 13 | Smarter AI | Lifetime Display Warranty (16GB RAM, 512GB Storage Midnight Ocean)\", \"product_url\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"summary\": {\"total_reviews\": 12, \"average_rating\": 4.83, \"sentiment_breakdown\": {\"negative\": 6, \"positive\": 6}, \"overall_sentiment\": \"negative\", \"accuracy_score\": 50.0}, \"reviews\": [{\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
+          <t>{\"product_id\": \"B0DQ8MJYXF\", \"product_name\": \"OnePlus 13 | Smarter AI | Lifetime Display Warranty (16GB RAM, 512GB Storage Midnight Ocean)\", \"product_url\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"summary\": {\"total_reviews\": 12, \"average_rating\": 4.83, \"sentiment_breakdown\": {\"positive\": 12}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -655,21 +655,21 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
@@ -677,11 +677,11 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0F5HVFVKH\", \"product_name\": \"Motorola razr 60 Ultra (Pantone Scarab, 16 GB RAM, 512 GB Storage) | Moto AI | Snapdragon® 8 Elite Mobile Platform | 6.9\\" AMOLED 165Hz Display | 50 MP + 50 MP + 50MP Triple Camera\", \"product_url\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"summary\": {\"total_reviews\": 2, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0F5HVFVKH\", \"product_name\": \"Motorola razr 60 Ultra (Pantone Scarab, 16 GB RAM, 512 GB Storage) | Moto AI | Snapdragon® 8 Elite Mobile Platform | 6.9\\" AMOLED 165Hz Display | 50 MP + 50 MP + 50MP Triple Camera\", \"product_url\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"summary\": {\"total_reviews\": 4, \"average_rating\": 4.5, \"sentiment_breakdown\": {\"positive\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijeet Chinchole\", \"rating\": \"5.0\", \"date\": \"28 May 2025\", \"text\": \"This is my very first smartphone, and after using the Moto Razr 60 Ultra for a week, I can confidently say I’m impressed! The design is sleek and premium, and the flip form factor adds a cool, nostalgic touch while still feeling modern.Performance has been smooth so far – apps open quickly, multitasking is easy, and the external display is actually very handy for quick glances or controls without unfolding the phone. The inner screen is vibrant and responsive, making everyday use a joy.Battery life could be better – it gets me through the day, but not much more. That’s the only area where I feel there’s room for improvement.Overall, it’s a fantastic flip phone for anyone who wants something unique yet functional. I’m really enjoying the experience!\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijeet Chinchole\", \"rating\": \"5.0\", \"date\": \"28 May 2025\", \"text\": \"This is my very first smartphone, and after using the Moto Razr 60 Ultra for a week, I can confidently say I’m impressed! The design is sleek and premium, and the flip form factor adds a cool, nostalgic touch while still feeling modern.Performance has been smooth so far – apps open quickly, multitasking is easy, and the external display is actually very handy for quick glances or controls without unfolding the phone. The inner screen is vibrant and responsive, making everyday use a joy.Battery life could be better – it gets me through the day, but not much more. That’s the only area where I feel there’s room for improvement.Overall, it’s a fantastic flip phone for anyone who wants something unique yet functional. I’m really enjoying the experience!\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DZNP1MN3\", \"product_name\": \"Nothing Phone (3A) 5G (White, 8GB RAM, 256GB Storage)\", \"product_url\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 4, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"neutral\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"neutral\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0DZNP1MN3\", \"product_name\": \"Nothing Phone (3A) 5G (White, 8GB RAM, 256GB Storage)\", \"product_url\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.12</v>
+        <v>4.38</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -748,24 +748,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>16</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DHL7YT5S\", \"product_name\": \"Samsung Galaxy S24 FE 5G AI Smartphone (Graphite, 8GB RAM, 128GB Storage)\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.12, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijit\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"Don\'t fall for this trap. Phone looks good and camera is also pretty decent. Battery also OK for my kind of usage. But it has HEATING ISSUES...No matter whether you close all the apps or what kind of usage you do, it heats up. I don\'t play games, normal browsing also you can feel on your palms despite using a Spigen cover. Without cover it feels even more.DONT GO FOR IT. Buy Iqoo 12 or one plus 13R or Vivo V40 or any other phone...\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijit\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"Don\'t fall for this trap. Phone looks good and camera is also pretty decent. Battery also OK for my kind of usage. But it has HEATING ISSUES...No matter whether you close all the apps or what kind of usage you do, it heats up. I don\'t play games, normal browsing also you can feel on your palms despite using a Spigen cover. Without cover it feels even more.DONT GO FOR IT. Buy Iqoo 12 or one plus 13R or Vivo V40 or any other phone...\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
+          <t>{\"product_id\": \"B0DHL7YT5S\", \"product_name\": \"Samsung Galaxy S24 FE 5G AI Smartphone (Graphite, 8GB RAM, 128GB Storage)\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"Awesome phone. Quality make and good looking too.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"Awesome phone. Quality make and good looking too.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">

--- a/static/output/analysis_results.xlsx
+++ b/static/output/analysis_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,11 +483,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Samsung Galaxy S25 Ultra</t>
+          <t>Nasher Miles Bag</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.38</v>
+        <v>2.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -496,40 +496,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DSKMKJV5\", \"product_name\": \"Samsung Galaxy S25 Ultra 5G AI Smartphone (Titanium Black, 12GB RAM, 512GB Storage), 200MP Camera, S Pen Included, Long Battery Life\", \"product_url\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 2, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0DNQV9LKB?th=1&amp;psc=1\", \"product_name\": \"Nasher Miles Staten Passenger Workpack 29 Liters Water Resistant, Padded, Premium Reversed Polyester Laptop Backpack | Number Lock with USB charging| Unisex| Ideal For Office\", \"product_url\": \"https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1\", \"summary\": {\"total_reviews\": 4, \"average_rating\": 2.5, \"sentiment_breakdown\": {\"positive\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Mayur kalkar\", \"rating\": \"4.0\", \"date\": \"23 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Product is very good as shown but only thing is charging port is not working\n  \nRead more\", \"product_id\": \"B0DNQV9LKB?th=1&amp;psc=1\", \"link\": \"https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"NiteshNitesh\", \"rating\": \"1.0\", \"date\": \"20 Mar 2025\", \"text\": \"Bag is quite sturdy and compact size not too big not too small .. Good fit for daily office usage.Material used for the bag looks premiumChanging my review post using for a month - - after keeping one laptop and one office diary stitches came loose.. Bag quality is absolutely rubbish and top is their customer service. It\'s useless though product is in warranty customer service is saying they won\'t be able to replace the product with new item and will repair the same.. I agree with this but to pick up simple bag that too from Mumbai is not possible for them.. Since last 8 days I am waiting for pick up but it\'s not happening.. If pick up is so bad imagine the efforts I need to put to get my repaired productThis is waste brand and not at all trustworthy.. Avoid this brand if you can.\n  \nRead more\", \"product_id\": \"B0DNQV9LKB?th=1&amp;psc=1\", \"link\": \"https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mayur kalkar\", \"rating\": \"4.0\", \"date\": \"23 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Product is very good as shown but only thing is charging port is not working\n  \nRead more\", \"product_id\": \"B0DNQV9LKB?th=1&amp;psc=1\", \"link\": \"https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"NiteshNitesh\", \"rating\": \"1.0\", \"date\": \"20 Mar 2025\", \"text\": \"Bag is quite sturdy and compact size not too big not too small .. Good fit for daily office usage.Material used for the bag looks premiumChanging my review post using for a month - - after keeping one laptop and one office diary stitches came loose.. Bag quality is absolutely rubbish and top is their customer service. It\'s useless though product is in warranty customer service is saying they won\'t be able to replace the product with new item and will repair the same.. I agree with this but to pick up simple bag that too from Mumbai is not possible for them.. Since last 8 days I am waiting for pick up but it\'s not happening.. If pick up is so bad imagine the efforts I need to put to get my repaired productThis is waste brand and not at all trustworthy.. Avoid this brand if you can.\n  \nRead more\", \"product_id\": \"B0DNQV9LKB?th=1&amp;psc=1\", \"link\": \"https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3</t>
+          <t>https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vivo X200 Pro</t>
+          <t>Ugreen Charger</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -551,27 +551,27 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B07WDJMX16\", \"product_name\": \"Vivo X200 Pro 5G (Titanium Grey, 16GB RAM, 512GB Storage) with No Cost EMI/Additional Exchange Offers\", \"product_url\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0CQ2F185Z\", \"product_name\": \"UGREEN Nexode RG USB C Charger 65W RobotGaN Charger USB C Power Supply 3 Port Fast Charger Robot Compatible with MacBook Pro/Air, iPad, iPhone 15 Pro Max, Galaxy S24 Ultra, Dell XPS (Black)\", \"product_url\": \"https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3\", \"summary\": {\"total_reviews\": 4, \"average_rating\": 2.5, \"sentiment_breakdown\": {\"positive\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Waseem SomjeeWaseem Somjee\", \"rating\": \"4.0\", \"date\": \"27 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    It’s good and does what it advertises to do but very frankly way bigger than I thought it would be. Moreover the cost is very high as the spigen one 70W does the same thing. Overall happy if you would like some quality but compactness is not upto the mark!\n  \nRead more\", \"product_id\": \"B0CQ2F185Z\", \"link\": \"https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"1.0\", \"date\": \"05 Feb 2025\", \"text\": \"Spending almost 5K for a charger and getting 200Rs charger pin quality. Not sure if it is only for Indian units.\n  \nRead more\", \"product_id\": \"B0CQ2F185Z\", \"link\": \"https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Waseem SomjeeWaseem Somjee\", \"rating\": \"4.0\", \"date\": \"27 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    It’s good and does what it advertises to do but very frankly way bigger than I thought it would be. Moreover the cost is very high as the spigen one 70W does the same thing. Overall happy if you would like some quality but compactness is not upto the mark!\n  \nRead more\", \"product_id\": \"B0CQ2F185Z\", \"link\": \"https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"1.0\", \"date\": \"05 Feb 2025\", \"text\": \"Spending almost 5K for a charger and getting 200Rs charger pin quality. Not sure if it is only for Indian units.\n  \nRead more\", \"product_id\": \"B0CQ2F185Z\", \"link\": \"https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3</t>
+          <t>https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xiaomi 15 Ultra</t>
+          <t>Iphone !6e</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -580,11 +580,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>71.43%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -593,27 +593,27 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DYV4177R\", \"product_name\": \"Xiaomi 15 Ultra (Silver Chrome, 16GB/512GB)| 200 MP Leica-Quad Camera | SD 8 Elite | WQHD+ Quad Curve AMOLED | Hyper AI\", \"product_url\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"summary\": {\"total_reviews\": 14, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 71.43}, \"reviews\": [{\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Agniva Pal\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Xiaomi has taken strides this time to make sure the camera works. I\'ve been using samsung s22 ultra for 3.5 years before this and the immediate jump was highly visible.The main camera is amazing and works in every condition. I was surprised to see that night videos come out without noise and there are no luminous colorful noise dots on the video. The pictures you shoot are really good and after 3.5 years I\'ve managed to take images of pets without the need to hold them still. The fastshot mode actually works. The 1.5x crop and 2x crop was magical. Since the sensor is big, these crops make it feel like it\'s being shot with an actual 1.5 and 2x lens.The 3x tele, even if reviewers have always said is not good enough, is actually good and shoots really good portrait. Actually all the lenses shoot really good portrait. The videos are also pretty balanced.The 4.3x is a literally a superbbbbb lens and you can literally shoot at 20 to 30x and find usable results. I was surprised at what this \'ai\' tele can do! This is really good if you\'re 20 to 30 metres away from birds/animals. You can use this to shoot nice pics / videos.Please be warned that pictures come out like a mirrorless camera and the color science isn\'t like phones. That is a major reason you\'ll find most reviews to prefer vivo with their polished look. Highlights on skin are supposed to stay if you shoot in direct sun and the sun isn\'t supposed to look round if you shoot it above 45 degrees. I love the fact that computational photography has been dialled down in this phone. You can always do those things in post with any good software. I hate the over processed look and this suffices for my case.Leaving the camera aside, I\'d say this is a really good battery for a flagship. I end the day with around 40 to 50 percent at times, and I\'m a heavy user. I use a lot of camera; like a lot of it. I use a lot of youtube and instagram. I edit photos. I also listen to music at least 3 hours in a day while working. All thing combined I\'m getting a screen on time of more than 8 hours.The phone is absolutely smooth and no complaints there. It\'s been a month and I\'ve not faced even one stutter. I sold off my mi 11 ultra after 2 months of use due to multiple issues. It\'s not the case anymore. I don\'t see any polish difference between samsung and this phone. I can\'t relate to the fact that samsung makes a better experience. People keep talking about it, but I\'m not sure I can relate. But yes, there are things I miss like samsung pay (google pay works on this one though), ultra wide band to search for my smart watch (i just let it ring now), a night mode on the camera (i think xiaomi has been over confident and has not included a night mode. I agree that shots come out really good even without one but including one would be good. And please include an astrophotography mode as well. All it has is auto night mode now. There\'s no dedicated mode).I can\'t find any other deterrents as of now. It\'s good for the price\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Soham S.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Apart from the software experience, this is a phone worth he \\"ultra\\" tag. It gets all the basics right and enhances the experience with several positives:1. The phone build quality is great and it has the heft that brings a premium experience. But this is strictly for big hands.2. The phone performance and smoothness is top of the line with no heating issues and unusual battery drain. Infact battery life has been great with more than 1 day\'s battery with my usage.3. The photography experience with the added accesories is superb and it redefines the phrase \\"The best camera is the one you always have on you\\". Photography with this phone is a joy and a convenience that makes me ditch my Sony camera on short trips.4. No complaints on the connectivity end as well.Overall, this the the most value for money \\"Ultra\\" phone that money can buy in India right now and it leaves behind the iphones and samsungs by a huge leap.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"js\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Don\'t buy this mobile. Something is loose inside the phone after use of 8  days. Now, amazon also don\'t exchange it. Also there is heating issue.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"nidhin\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"The Xiaomi 15 Ultra delivers outstanding performance, with one of the best cameras in the flagship segment. It captures detailed, vibrant photos, and its low-light capabilities are impressive. The device handles heavy apps and multitasking smoothly, and the gaming experience is excellent thanks to its powerful chipset and high refresh rate display.However, there\'s a minor lag when switching between camera modes, which could be improved with future updates. Also, the large camera bump on the back makes the phone wobble on flat surfaces—so it\'s definitely a good idea to use a protective case for better grip and stability.Overall, the Xiaomi 15 Ultra is a powerhouse with premium features, ideal for photography enthusiasts and gamers alike.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"SENTHIL KUMARAN\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"1) one of the best mobile.2) touch is very smoothly3) camera quality is marvelous.4) battery backup is super 💯\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"MANISH PANCHAL\", \"rating\": \"3.0\", \"date\": \"17 May 2025\", \"text\": \"The Xiaomi 15 Ultra undoubtedly makes a strong statement with its superb camera quality, delivering stunning photos and videos with impressive detail and dynamic range. However, it\'s not without its drawbacks. Videographers might be disappointed by the lower bitrate in Log video, potentially limiting flexibility in post-production. Furthermore, the poor noise cancellation in video recording could be a significant issue for capturing clean audio in noisy environments. The inability to connect the DJI Mic mini via Bluetooth is another frustrating limitation for content creators relying on wireless audio solutions. Finally, reports of battery and heating issues raise concerns about sustained performance and user comfort. While the camera prowess is undeniable, these other aspects need serious consideration.\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"drtechNNo\", \"rating\": \"4.0\", \"date\": \"04 May 2025\", \"text\": \"I came from Vivo X200 Pro just to see if xiaomi did it better in camera this year compared to vivo.  Sadly it falls sorry in everything except UI.UI of vivo(fun touch) is very bland but rest all parameters like camera,  battery,  etc are 10_20 percent better on vivo.Very sad to have spent this much on xiaomi and absolutely no sorry by the company to provide sodas updates to improve anything.The xiaomi hardware may be better but in this age of AI and computational photography it sorely falls behind the race\n  \nRead more\", \"product_id\": \"B0DYV4177R\", \"link\": \"https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3\", \"sentiment\": \"negative\"}]}</t>
+          <t>{\"product_id\": \"B0DXQH1DBS\", \"product_name\": \"iPhone 16e 128 GB: Built for Apple Intelligence, A18 Chip, Supersized Battery Life, 48MP Fusion. Camera, 15.40 cm (6.1″) Super Retina XDR Display; Black\", \"product_url\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Ravali\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Great value for money. Extended battery life.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Himanshu k.\", \"rating\": \"5.0\", \"date\": \"12 Apr 2025\", \"text\": \"This is awesome 😎 battery back up , screen, AI feature. Camera, must buy. No regerat.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Mitanshu meena\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"Better then iPhone 15 and 16 , if you just want to use this phone as your daily driver , and if you have already used iPhone 11,12,13 and you are fine with them this is the best choose for this price range.  best battery, good display, fast and smooth, good 5g modern better then iphone 16 and pro\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Gajendra\", \"rating\": \"4.0\", \"date\": \"14 Mar 2025\", \"text\": \"Very Nice Phone.Reliable and Durable.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"JITENDRA PRATAP SINGH\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"As someone who’s been riding the Android wave from Galaxy S3 to S24, I wasn’t expecting to be this impressed—but the iPhone 16e blew me away.• Battery? I’ve gone 3 days without charging.• Performance? The A18 chip is buttery smooth—no lags, no stutters.• Camera? The 48MP fusion system takes stunning, true-to-life shots.• Display? That Super Retina XDR screen makes everything look cinematic.Now I find myself wondering why I didn’t make the switch earlier. Everything just works—and works beautifully. This one’s a keeper.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ejaz Shaik\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Pls don’t buy. Slowest phone\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Gourav Pandey\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"Iphone 16e all over is good. Sound quality, charging speed and value for money.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"JAYARAM O P\", \"rating\": \"5.0\", \"date\": \"28 Mar 2025\", \"text\": \"Its been Close to 1 week and I am happy with the purchase. Got a good exchange offer with my old IPhone 8 and with the bank offer, the price came down to around 45K for 128GB model.Battery backup is very good.Light Weight and build quality is good.Camera is good to the levell what we are paying.Except wide angle camera, getting everything what IPhone 16 has to offer.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Ravali\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Great value for money. Extended battery life.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Himanshu k.\", \"rating\": \"5.0\", \"date\": \"12 Apr 2025\", \"text\": \"This is awesome 😎 battery back up , screen, AI feature. Camera, must buy. No regerat.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Mitanshu meena\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"Better then iPhone 15 and 16 , if you just want to use this phone as your daily driver , and if you have already used iPhone 11,12,13 and you are fine with them this is the best choose for this price range.  best battery, good display, fast and smooth, good 5g modern better then iphone 16 and pro\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Gajendra\", \"rating\": \"4.0\", \"date\": \"14 Mar 2025\", \"text\": \"Very Nice Phone.Reliable and Durable.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"JITENDRA PRATAP SINGH\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"As someone who’s been riding the Android wave from Galaxy S3 to S24, I wasn’t expecting to be this impressed—but the iPhone 16e blew me away.• Battery? I’ve gone 3 days without charging.• Performance? The A18 chip is buttery smooth—no lags, no stutters.• Camera? The 48MP fusion system takes stunning, true-to-life shots.• Display? That Super Retina XDR screen makes everything look cinematic.Now I find myself wondering why I didn’t make the switch earlier. Everything just works—and works beautifully. This one’s a keeper.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ejaz Shaik\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Pls don’t buy. Slowest phone\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Gourav Pandey\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"Iphone 16e all over is good. Sound quality, charging speed and value for money.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"JAYARAM O P\", \"rating\": \"5.0\", \"date\": \"28 Mar 2025\", \"text\": \"Its been Close to 1 week and I am happy with the purchase. Got a good exchange offer with my old IPhone 8 and with the bank offer, the price came down to around 45K for 128GB model.Battery backup is very good.Light Weight and build quality is good.Camera is good to the levell what we are paying.Except wide angle camera, getting everything what IPhone 16 has to offer.\n  \nRead more\", \"product_id\": \"B0DXQH1DBS\", \"link\": \"https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3</t>
+          <t>https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Samsung Galaxy S24 Ultra 5G</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.83</v>
+        <v>4.38</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -622,40 +622,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DQ8MJYXF\", \"product_name\": \"OnePlus 13 | Smarter AI | Lifetime Display Warranty (16GB RAM, 512GB Storage Midnight Ocean)\", \"product_url\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"summary\": {\"total_reviews\": 12, \"average_rating\": 4.83, \"sentiment_breakdown\": {\"positive\": 12}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Dhruthu Meghadooth\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Everything you could want in a high end phone. It gives you premium build, reliable battery life over a day and half, super fast charging, awesome display and a pretty reliable camera although I did find a bit of over processing in some shots, I do feel like it\'s value for money for what I paid for it which comes around 50k with exchange a steal for that price. Go for it wholeheartedly.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nirangkush DasNirangkush Das\", \"rating\": \"5.0\", \"date\": \"30 Mar 2025\", \"text\": \"Disclaimer: My previous android was the realme X2 which I had used since 2019. Hence, I have limited knowledge regarding other android devices/OS. This review is for those people who want to enjoy the experience of a flagship rather than the game-buffs or the photography enthusiasts.Coming to the phone,Performance: Buttery-smooth. Snapdragon 8 Elite is a premium chip. Transitioning between the apps seems so smooth quite like my iphone 13 if not better which I have been using for the last 2 years. I have played Call of Duty in the max settings and the gameplay is very smooth in both Multiplayer and Battle Royal modes. Camera is awesome though I have not used it much.Battery: I have attached battery SS for reference. The silicone battery gives excellent back-up.Build quality: Build quality is very good, quite like a flagship. The screen seems so premium and fluidy.Storage capacity: I have got the 12 GB + 256 GB variant. System &amp; OS takes around 19 GB. One general photo takes around 8-9 MB space.Connectivity: Have found it good particularly the Wifi as compared to my previous phone. It can catch onto weak wifi signal very strongly.OS: Oxygen OS is awesome. The dual tone color looks good.Verdict: Can easily go for it if you need a flagship device on budget when compared to other brand’s flagships (I got it at 65k).\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Joseph kv\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"Title: Flagship Killer! ★★★★★The OnePlus 13 is a powerhouse!✔ Design &amp; Build: Premium feel with a sleek aluminum frame and vegan leather back. IP68/IP69 rated for durability.✔ Display: Stunning 6.82” QHD+ OLED with a 1-120Hz refresh rate—smooth and vibrant.✔ Performance: Snapdragon 8 Elite + advanced cooling = zero lags, even with heavy multitasking.✔ Battery: 6,000mAh lasts 1.5-2 days. 100W fast charging fills up in ~35 minutes!✔ Camera: 50MP triple-camera with Hasselblad tuning—crisp, natural photos.✔ Software: OxygenOS 15 is smooth, with 4 years of updates.Cons: Slightly pricier than previous models; some pre-installed apps can’t be removed.Verdict: A premium flagship with top-tier performance, battery, and cameras. Worth every penny!\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kedar\", \"rating\": \"4.0\", \"date\": \"05 Feb 2025\", \"text\": \"I had a OnePlus 8 Pro for four and half years. It was a very nice phone having IP 68, wireless charging and Dolby Atmos.The OnePlus 13 stands out as a top-tier Android smartphone, offering a blend of performance, design, and innovation. Its 6.8-inch QHD+ AMOLED display delivers vibrant visuals with a smooth 120Hz refresh rate, ensuring an immersive viewing experience. Powered by Qualcomm\'s Snapdragon 8 Elite processor and up to 16GB of RAM, the device handles multitasking and demanding applications with ease. The triple 50MP rear camera system, developed in collaboration with Hasselblad, captures detailed and color-accurate photos across various lighting conditions. A substantial 6,000mAh battery provides impressive longevity, and with 100W wired fast charging, the phone reaches a full charge swiftly. The inclusion of IP68 and IP69 water resistance, along with MagSafe support, adds to its premium appeal. Running on OxygenOS 15 based on Android 15, the OnePlus 13 offers a clean and responsive user interface. Overall, it presents a compelling package for those seeking a high-end smartphone experience.I am definitely missing Dolby Atmos in this device for sure. Rest everything is fine.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Shubham S.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Very Great device. Been using this from last 2 months.Performance:Snapdragon 8 elite provides amazing performance.The performance has been top notch, zero lags, hangs and crashes.Camera:The cameras are good, they are almost as good as a flagship.Build:Already stopped phone a few times, it had the factory case, but nothing happened, not even a scratch.Charging:Charging speeds are amazing as well. Both wired and wireless.Display:The display is the out of this world. It is better in all aspects than s25 ultras display except for the anti glare coating.But the display becomes so bright that Idid not even miss the anti glare coating.I have played games during very bright day outdoors on it and I could see the screen like I was indoor.Connectivity:Had zero issues with connectivity. Amazing 5G speeds and coverage compared to my old device.Found few minor bugs in system such as auto brigness does not work sometimes.Camera zoom over modifies the image using AI.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"PJ.PJ.\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Given the spec, I found this one overall great phone in android space. Great overall performance so far - fast, smooth, easy cloud sync backup, big battery, robust privacy and security. I had to give a shot to Midnight ocean - the only OP13 which comes with eco leatherette back, as I had bad experience with back glass iphone. Transfer of data was tricky from iphone to android, however using cable it was a breeze in an hour. The only issue I faced in the few days since I got it in my hands was that the animation effects were laggy with first software update but it got fixed with second software update.\n  \nRead more\", \"product_id\": \"B0DQ8MJYXF\", \"link\": \"https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0CS5XW6TN\", \"product_name\": \"Samsung Galaxy S24 Ultra 5G AI Smartphone with Galaxy AI (Titanium Gray, 12GB, 256GB Storage), Snapdragon 8 Gen 3, 200 MP Camera with ProVisual Engine and 5000mAh Battery\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Balajisingh\", \"rating\": \"5.0\", \"date\": \"24 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Absolutely worth to buy and has many features comparing to other android phones\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kamruz ZamanKamruz Zaman\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Shifted from Iphone 14 to s24 ultra.Fully satisfied with the device.Display is the best among all the smartphones.Battery life and camera performance is also awesome. Lots of useful AI features.Bought at 85k. Proper bang for buck 👌\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jithu\", \"rating\": \"1.0\", \"date\": \"11 Apr 2025\", \"text\": \"The phone itself myt be one of thr best phones I have used till date but the problem is that the phone I received is of a different region(software) and not India so it\'s got defective issues. On contacting amazon service center and samsung service center I keep getting no solutions to my problem and will not allow a replacement since it\'s a software issue that cannot be solved. Samsung service center keeps holding my phone till the validity of return period and also saying they won\'t be able to give me the documents to return phone via amazon since their validity of the giving the documents have ended as it was counted from invoice date (date of ordering ) I received the phone after 5 days and have contacted both service centres within 2 days. I\'m pretty much helpless now.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Tamajit BoseTamajit Bose\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"The best phone made by Samsung, friends, believe me, I\'m telling you, you can buy this phone without any hesitation.Pros:1.Displays2.Camera3.processor4.S-Pen5.UI Experience6.Battery7.Network Connectivity8.Charging Speed With 45watt adapter and 5A cable9.Believe me ONE UI 7.0 is awesome10.Build Quality11.Anti Reflective Coating and few more…Cons:1. Slight distortion in the speaker at full volume2. It doesn\'t support Dolby Vision, but that\'s not a big deal because its display is great.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"abhayabhay\", \"rating\": \"4.0\", \"date\": \"17 May 2025\", \"text\": \"Best camera in segmentUltimate featuresBut something is missing\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Delwar hossain\", \"rating\": \"5.0\", \"date\": \"27 May 2025\", \"text\": \"It\'s a very nice phone at affordable price now\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Laxi\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"Ohh my these year big purchase and it is really a power house. Display, features, camera is totally amazing.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajay Thakur\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"This product offers excellent value for money. It delivers reliable performance and quality features at an affordable price point, making it a practical choice for budget-conscious buyers. Overall, it meets expectations and provides great satisfaction for the cost.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Balajisingh\", \"rating\": \"5.0\", \"date\": \"24 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Absolutely worth to buy and has many features comparing to other android phones\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kamruz ZamanKamruz Zaman\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Shifted from Iphone 14 to s24 ultra.Fully satisfied with the device.Display is the best among all the smartphones.Battery life and camera performance is also awesome. Lots of useful AI features.Bought at 85k. Proper bang for buck 👌\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jithu\", \"rating\": \"1.0\", \"date\": \"11 Apr 2025\", \"text\": \"The phone itself myt be one of thr best phones I have used till date but the problem is that the phone I received is of a different region(software) and not India so it\'s got defective issues. On contacting amazon service center and samsung service center I keep getting no solutions to my problem and will not allow a replacement since it\'s a software issue that cannot be solved. Samsung service center keeps holding my phone till the validity of return period and also saying they won\'t be able to give me the documents to return phone via amazon since their validity of the giving the documents have ended as it was counted from invoice date (date of ordering ) I received the phone after 5 days and have contacted both service centres within 2 days. I\'m pretty much helpless now.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Tamajit BoseTamajit Bose\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"The best phone made by Samsung, friends, believe me, I\'m telling you, you can buy this phone without any hesitation.Pros:1.Displays2.Camera3.processor4.S-Pen5.UI Experience6.Battery7.Network Connectivity8.Charging Speed With 45watt adapter and 5A cable9.Believe me ONE UI 7.0 is awesome10.Build Quality11.Anti Reflective Coating and few more…Cons:1. Slight distortion in the speaker at full volume2. It doesn\'t support Dolby Vision, but that\'s not a big deal because its display is great.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"abhayabhay\", \"rating\": \"4.0\", \"date\": \"17 May 2025\", \"text\": \"Best camera in segmentUltimate featuresBut something is missing\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Delwar hossain\", \"rating\": \"5.0\", \"date\": \"27 May 2025\", \"text\": \"It\'s a very nice phone at affordable price now\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Laxi\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"Ohh my these year big purchase and it is really a power house. Display, features, camera is totally amazing.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajay Thakur\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"This product offers excellent value for money. It delivers reliable performance and quality features at an affordable price point, making it a practical choice for budget-conscious buyers. Overall, it meets expectations and provides great satisfaction for the cost.\n  \nRead more\", \"product_id\": \"B0CS5XW6TN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3</t>
+          <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motorola Razr 60 Ultra</t>
+          <t>OnePlus Nord 4 5G (Obsidian Midnight, 8GB RAM, 256GB Storage)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -677,27 +677,27 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0F5HVFVKH\", \"product_name\": \"Motorola razr 60 Ultra (Pantone Scarab, 16 GB RAM, 512 GB Storage) | Moto AI | Snapdragon® 8 Elite Mobile Platform | 6.9\\" AMOLED 165Hz Display | 50 MP + 50 MP + 50MP Triple Camera\", \"product_url\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"summary\": {\"total_reviews\": 4, \"average_rating\": 4.5, \"sentiment_breakdown\": {\"positive\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijeet Chinchole\", \"rating\": \"5.0\", \"date\": \"28 May 2025\", \"text\": \"This is my very first smartphone, and after using the Moto Razr 60 Ultra for a week, I can confidently say I’m impressed! The design is sleek and premium, and the flip form factor adds a cool, nostalgic touch while still feeling modern.Performance has been smooth so far – apps open quickly, multitasking is easy, and the external display is actually very handy for quick glances or controls without unfolding the phone. The inner screen is vibrant and responsive, making everyday use a joy.Battery life could be better – it gets me through the day, but not much more. That’s the only area where I feel there’s room for improvement.Overall, it’s a fantastic flip phone for anyone who wants something unique yet functional. I’m really enjoying the experience!\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijeet Chinchole\", \"rating\": \"5.0\", \"date\": \"28 May 2025\", \"text\": \"This is my very first smartphone, and after using the Moto Razr 60 Ultra for a week, I can confidently say I’m impressed! The design is sleek and premium, and the flip form factor adds a cool, nostalgic touch while still feeling modern.Performance has been smooth so far – apps open quickly, multitasking is easy, and the external display is actually very handy for quick glances or controls without unfolding the phone. The inner screen is vibrant and responsive, making everyday use a joy.Battery life could be better – it gets me through the day, but not much more. That’s the only area where I feel there’s room for improvement.Overall, it’s a fantastic flip phone for anyone who wants something unique yet functional. I’m really enjoying the experience!\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0D7VKMLGD\", \"product_name\": \"OnePlus Nord 4 5G (Obsidian Midnight, 8GB RAM, 256GB Storage) | Lifetime Display Warranty | Qualcomm® Snapdragon™ 7 Plus Gen 3 | ANTUTU Score 1.5Mn AI\", \"product_url\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Savitha K C\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Using it for 4 months now. It\'s been almost a year since it\'s launch and it is still a good buy. Decent cameras, cameras is not it\'s strength, in the same price range you get other phones for better cameras. Battery, fast charging, UI UX , Software, Display, build quality, performance are all really good. It is the best all rounder phone to buy under 25k. Highly recommend it. I was considering to buy 13R for 40k but I feel Nord 4 is better value for money.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"Pragyesh pandeyPragyesh pandey\", \"rating\": \"4.0\", \"date\": \"11 May 2025\", \"text\": \"Now let me share review of this phone. After using the phone for almost a week, I find the phone good as per the price. I bought it for 24999 by using available discount through HDFC card. Now charging is not too fast, but it\'s fine as it\'s charging the phone in 40 mins from 20 to 100 percent. Battery backup is ok ok as it\'s lasting for less than a day with moderate use. Camera is fine and good as per price. Performancewise it\'s good phone as the use is smooth and the display is rich. The looks are premium but once u place back cover, it\'s not looking an elite one. Over all a value buy for those who uses the phone moderately. For heavy using, i would say ..better phone\'s are available in same price range.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"KalimKalim\", \"rating\": \"5.0\", \"date\": \"23 Mar 2025\", \"text\": \"I\'ve been using the OnePlus Nord 4 for about 2 weeks and I can say this phone is a great but for this pricePros: Almost everything,1. The display is gorgeous but it is not dynamic, meaning it stays at 120Hz all the time even when set to auto2. The battery life is also really damn good, coming from an iPhone X, this is great and 100W in the box charger charges it while a small break,3. Build quality is top notch, I like the metal back but the looks is bad, I suggested a family member this phone but it looks so bad, it was dismissed but for me it is alright (side note: you get a transparent TPU case and not a high quality one which funnily enough you get in the CE 4)Performance is great too, 7+ gen 3 is one of the better choiceCons:Camera: while main camera is ok, selfie and ultrawide are preety midVideo: only the main camera can do 4K 60FPS, other cameras are capped at 1080p 30FPS. So while you can record in 4K, you cannot change perspectives.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"Harihara Mallar SV\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"Been using this phone for 2 days now. The first thing that stood out is how light it feels in the hand, the build quality is sleek and solid, almost mimicking an iPhone-level finish. It has a premium touch without the premium price.Performance-wise, it’s smooth and responsive. Apps open quickly, multitasking is a breeze, and there’s been no lag so far. The 8GB RAM with 256GB storage is more than enough for my daily use — whether it\'s gaming, streaming, or work. The indisplay Fingerprint sensor is so fast and soo cool.The screen size is perfect. Not too big, not too small, just right for comfortable viewing, typing, and media consumption. Colors are good, and brightness is on point, even outdoors.Obsidian Black looks stunning, clean, classy, and minimal. Overall, for the price point, the OnePlus Nord 4 is delivering way more than expected.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"YaduYadu\", \"rating\": \"5.0\", \"date\": \"21 Nov 2024\", \"text\": \"I am writing this review after 1 month of using the Oneplus Nord 4. It is one of the best midrange phone that you can blindly buy without any confusion. I bought this phone during Great Indian festival after so much research and doubts. I was not sure which phone will be the best in 30000 segment. I was looking for a balanced phone which has everything like good performance, good design, good battery and good camera. I don\'t want to compromise in any one thing. So after lot of research i was having confusion between nord 4 and realme gt 6t. But in realme gt 6t the display is curved which i don\'t prefer at all. Curved display is waste of money and feels like gimmick so i avoided it and bought nord 4. Now i feel it was the best decision.Best features of this Nord 4 are-Design - I literally loved the mercurian silver metel design which looks so much premium. I thought metel might be heavier but in daily use its not a problem at all. It cools down so fast and does not have any heating issues at all.Performance - It has the best performance and able to play BGMI so smoothly. Flat screen helps so much in games also.Battery -  If you use normally the battery will last more than 1 day easily and it charges the phone within 25mins.Camera - I felt the main camera is so good and it takes very decent photos. 50mp camera performs above average. If camera is your main priority then its better to go for realme, vivo, Samsung or Iphone which are camera centric. But then other areas you have to compromise. Trust me below 30k this phone takes very good photos.Network - Being a metel phone i am getting 5g network always without any problem. Never felt any Issues at all.Display - It has best display and content viewing experience is top notch with minimum bezzels.This review is genuine and trust me if you want a balanced midrange phone you can go for Oneplus Nord 4 for sure. Greenline is coming in all the brands so no need to get back from this phone because of this reason....(If any problems comes in future then i will update the review for sure)\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"Savitha K C\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Using it for 4 months now. It\'s been almost a year since it\'s launch and it is still a good buy. Decent cameras, cameras is not it\'s strength, in the same price range you get other phones for better cameras. Battery, fast charging, UI UX , Software, Display, build quality, performance are all really good. It is the best all rounder phone to buy under 25k. Highly recommend it. I was considering to buy 13R for 40k but I feel Nord 4 is better value for money.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"Pragyesh pandeyPragyesh pandey\", \"rating\": \"4.0\", \"date\": \"11 May 2025\", \"text\": \"Now let me share review of this phone. After using the phone for almost a week, I find the phone good as per the price. I bought it for 24999 by using available discount through HDFC card. Now charging is not too fast, but it\'s fine as it\'s charging the phone in 40 mins from 20 to 100 percent. Battery backup is ok ok as it\'s lasting for less than a day with moderate use. Camera is fine and good as per price. Performancewise it\'s good phone as the use is smooth and the display is rich. The looks are premium but once u place back cover, it\'s not looking an elite one. Over all a value buy for those who uses the phone moderately. For heavy using, i would say ..better phone\'s are available in same price range.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"KalimKalim\", \"rating\": \"5.0\", \"date\": \"23 Mar 2025\", \"text\": \"I\'ve been using the OnePlus Nord 4 for about 2 weeks and I can say this phone is a great but for this pricePros: Almost everything,1. The display is gorgeous but it is not dynamic, meaning it stays at 120Hz all the time even when set to auto2. The battery life is also really damn good, coming from an iPhone X, this is great and 100W in the box charger charges it while a small break,3. Build quality is top notch, I like the metal back but the looks is bad, I suggested a family member this phone but it looks so bad, it was dismissed but for me it is alright (side note: you get a transparent TPU case and not a high quality one which funnily enough you get in the CE 4)Performance is great too, 7+ gen 3 is one of the better choiceCons:Camera: while main camera is ok, selfie and ultrawide are preety midVideo: only the main camera can do 4K 60FPS, other cameras are capped at 1080p 30FPS. So while you can record in 4K, you cannot change perspectives.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"Harihara Mallar SV\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"Been using this phone for 2 days now. The first thing that stood out is how light it feels in the hand, the build quality is sleek and solid, almost mimicking an iPhone-level finish. It has a premium touch without the premium price.Performance-wise, it’s smooth and responsive. Apps open quickly, multitasking is a breeze, and there’s been no lag so far. The 8GB RAM with 256GB storage is more than enough for my daily use — whether it\'s gaming, streaming, or work. The indisplay Fingerprint sensor is so fast and soo cool.The screen size is perfect. Not too big, not too small, just right for comfortable viewing, typing, and media consumption. Colors are good, and brightness is on point, even outdoors.Obsidian Black looks stunning, clean, classy, and minimal. Overall, for the price point, the OnePlus Nord 4 is delivering way more than expected.\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}, {\"author\": \"YaduYadu\", \"rating\": \"5.0\", \"date\": \"21 Nov 2024\", \"text\": \"I am writing this review after 1 month of using the Oneplus Nord 4. It is one of the best midrange phone that you can blindly buy without any confusion. I bought this phone during Great Indian festival after so much research and doubts. I was not sure which phone will be the best in 30000 segment. I was looking for a balanced phone which has everything like good performance, good design, good battery and good camera. I don\'t want to compromise in any one thing. So after lot of research i was having confusion between nord 4 and realme gt 6t. But in realme gt 6t the display is curved which i don\'t prefer at all. Curved display is waste of money and feels like gimmick so i avoided it and bought nord 4. Now i feel it was the best decision.Best features of this Nord 4 are-Design - I literally loved the mercurian silver metel design which looks so much premium. I thought metel might be heavier but in daily use its not a problem at all. It cools down so fast and does not have any heating issues at all.Performance - It has the best performance and able to play BGMI so smoothly. Flat screen helps so much in games also.Battery -  If you use normally the battery will last more than 1 day easily and it charges the phone within 25mins.Camera - I felt the main camera is so good and it takes very decent photos. 50mp camera performs above average. If camera is your main priority then its better to go for realme, vivo, Samsung or Iphone which are camera centric. But then other areas you have to compromise. Trust me below 30k this phone takes very good photos.Network - Being a metel phone i am getting 5g network always without any problem. Never felt any Issues at all.Display - It has best display and content viewing experience is top notch with minimum bezzels.This review is genuine and trust me if you want a balanced midrange phone you can go for Oneplus Nord 4 for sure. Greenline is coming in all the brands so no need to get back from this phone because of this reason....(If any problems comes in future then i will update the review for sure)\n  \nRead more\", \"product_id\": \"B0D7VKMLGD\", \"link\": \"https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3</t>
+          <t>https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nothing Phone 3a</t>
+          <t>Samsung Galaxy 45W Charging Adapter</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -706,40 +706,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DZNP1MN3\", \"product_name\": \"Nothing Phone (3A) 5G (White, 8GB RAM, 256GB Storage)\", \"product_url\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Shashwat Shashwat\", \"rating\": \"5.0\", \"date\": \"20 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Ordered this for my younger sister, Well i was very curious at first as all the sellers were new &amp; selling at slightly cheaper rates than official, but I checked everything thoroughly, packing was top notch, checked the device on nothing\'s website by IMEI if it was pre activated or what, but fortunately everything was fine. Phone is also nice, decent cameras, Nice UI, but I feel like it get\'s little warm to touch sometimes don\'t know why, Battery is okay too, not very good though but overall seriously it\'s a value for money indeed but yes you need to get a charger seperately as it doesn\'t come with one so keep that in mind, although my sister is very happy.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Farhan\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Excellent productsExcellent quality of phoneCamera is so clean and awesomeBudget phonePackaging is low but excellent\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Rajan Thakur\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Overall a great phone with smooth performance and a premium look. Display is crisp, but I found the screen lighting color a bit different compared to Samsung—takes a little time to adjust. Battery and camera are good, and it\'s definitely worth the price. Just a few small things from making it perfect!\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Dhiman\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Worst decision.Better to buy a brick at this price.Guys trust me the battery wont last u even 4 hours.overnight the battery is going to drain at least 15 percent.Go for motorala edge 60 fusion.Donot repeat my mistake.Tried nothing for the first time.Pathetic brand.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"negative\"}, {\"author\": \"sunilkumarnella\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"200%  satisfied\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Eren Yeager Eren Yeager\", \"rating\": \"5.0\", \"date\": \"09 Apr 2025\", \"text\": \"It\'s slick and beautiful tons of minimal features.... I prefer to use a back cover or tempered glass at back.... And you can trust amazon no damages and battery life is also best\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Sudhir waman\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Excellent specs\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}, {\"author\": \"Deep B.\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good, reasonably fast, cleanly designed phone. The battery isn\'t best in class, but enough for a daily driver.Not for gaming or high intensity usage. Bit large especially with a case, but I prefer that.\n  \nRead more\", \"product_id\": \"B0DZNP1MN3\", \"link\": \"https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"B0DT9N6BC6\", \"product_name\": \"Samsung Galaxy 45W Charging Adapter Ultra Fast Charging Charger for S25/S25 plus/S25 Ultra/S24 Ultra/S24 Plus/S24/S23 Plus/S23 Ultra/S23/S23 FE/S22 Ultra/Z Fold/Z Flip 5/4/3/A55/M55 USB-C Port Black\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.2, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"MD Ameer\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Supports Type C to TypeC cable only. Enables Super fast charging for your mobile phones.\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"KSK\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Super fast charging 2.0 blue color animation is coming which matches with original samsung adapter\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"SHIVAM SHARMA\", \"rating\": \"1.0\", \"date\": \"24 May 2025\", \"text\": \"Not satisfied ..There is no home replacement facility despite mentioning in this product. Local supplied .Not working\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"T.M.VENU\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"Good product\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"Gandharva bhatia\", \"rating\": \"5.0\", \"date\": \"22 Mar 2025\", \"text\": \"nice product very usefull\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"MD Ameer\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Supports Type C to TypeC cable only. Enables Super fast charging for your mobile phones.\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"KSK\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Super fast charging 2.0 blue color animation is coming which matches with original samsung adapter\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"SHIVAM SHARMA\", \"rating\": \"1.0\", \"date\": \"24 May 2025\", \"text\": \"Not satisfied ..There is no home replacement facility despite mentioning in this product. Local supplied .Not working\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"T.M.VENU\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"Good product\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}, {\"author\": \"Gandharva bhatia\", \"rating\": \"5.0\", \"date\": \"22 Mar 2025\", \"text\": \"nice product very usefull\n  \nRead more\", \"product_id\": \"B0DT9N6BC6\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2</t>
+          <t>https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Samsung S24 FE</t>
+          <t xml:space="preserve">KZ Castor Pro IEM </t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -765,54 +765,3540 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{\"product_id\": \"B0DHL7YT5S\", \"product_name\": \"Samsung Galaxy S24 FE 5G AI Smartphone (Graphite, 8GB RAM, 128GB Storage)\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"Awesome phone. Quality make and good looking too.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Gangadhar\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Exceptional photo quality great processerBest in the segment display most optimized software  value got money in this price range.Great fast charging no noticeable heating issues but gets temperature\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Thomas\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Bought it for 35kTotally worth it for 35k a phone with flagship features camera is very nice you get 4k recording on all 4 camera for this price it\'s pretty rare but on one UI 6.1 it had some heating issue but after updating to oneui7 it stopped heating so much it has far far better heat mangement than s23fe and also chin is slightly thick but most of the time you won\'t notice it gaming is smooth and I get 60fps most of the time you get extrem plus on bgmi\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhishek katoch\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Device is really good . The only issue is heating\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Annappa\", \"rating\": \"1.0\", \"date\": \"22 May 2025\", \"text\": \"Please don\'t buy these expensive mobiles from Amazon, After paying hell amount of money, you need to run behind service centres for new phone service.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Ramiz mariner\", \"rating\": \"5.0\", \"date\": \"04 Mar 2025\", \"text\": \"Writing the review after 10 days of usage.Phone Quality - quality is just awesome, looks premium.Size- this matters person to person, honestly I love to have phone size of 5.5 or even 5.0, but know you don\'t get such small size Phone. Coming back to this, I am 5.10 ft, so for my hand this mobile looks big, unable to use with one hand.Performance- have played games continously, watched champions trophy.. Performance is very good...Battery life - it good enough to survive for all day.Weight- again this comes person to person, I l9ve the weight of this cell phone, quiet heavy....\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"RAAZ PATHAN\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"awesome smoothness to new galaxy ai feautersall package this phoneVALU FOR MONEYI DONT HAVE ANY WORDS\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Vilas N Patil\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Nice product and received all items as required\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"Awesome phone. Quality make and good looking too.\n  \nRead more\", \"product_id\": \"B0DHL7YT5S\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+          <t>{\"product_id\": \"unknown\", \"product_name\": \"KZ Castor Pro IEM with HD Mic, Dual 10mm Dynamic Driver, Harman Target Improved Bass for Hi-Res Audio Quality, 4 Tuning Switch, Oxygen Free Copper Flat Cable, 0.78mm 2Pin &amp; 3.5mm Plug Compatible\", \"product_url\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Shamik M.Shamik M.\", \"rating\": \"5.0\", \"date\": \"21 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I was sceptical before buying the pair but after getting hands on it bangggg! This is the product that i was looking for long time.Lossless high resolution audio with low bidget price tag. It provides snug fit with different size eartips. Feels really sturdy and premium with its metal and resin build. You will absolutely loves its design. Now coming to its functionality and sound signature1. Bulit in mic is clear2. You have equaliser switches built in with both the buds. You can tweak it as per your choice.3. Lows mids and highs are clearly audible and crystal clear. Bass is thumpy ( bassheads go for it) mids are clear not muddy and highs are also lossless.4. Musicians mainly drummers and bass guitarist this thing is made for you guys.5. You can hear each and every instrument in a song individually good for every musician.My verdict is clear you will not regret after buying them. These pair sounds better than earphones 5 times costly than these.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Debjeet Debjeet\", \"rating\": \"4.0\", \"date\": \"28 Feb 2025\", \"text\": \"This iem has perfect balanced sound and pretty much a jack of all trades product. However the bass is a little shallow , though the pristine sound quality kind of makes up for it.Only one thing to note for new buyers , if you don\'t have a setup that gives a clean noiseless output or a cheap and bad dac which is not at least 24-bit supporting , then these headphones will sound really really terrible. You will need a good driver and clean signal to get the proper sound quality that these headphones produce.Overall these are a good buy and 9/10 chances you will not be disappointed.Some pros:-1. Comfortable to wear2. Design is really interesting3. Mic works well4. Easy to use , bonus if you know your way around Equalizer settings.5. Fits perfectly for the most part.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Karan KapurKaran Kapur\", \"rating\": \"5.0\", \"date\": \"11 Mar 2025\", \"text\": \"These are high performing earbuds with a great balanced soundtage. I got the model without the mic to ensure cable integrity over the long term as my only usage for these is Hi Res audio from my Iphone lightning DAC.  The buds take at least half an hour of audio at high volume to \\" break in \\" and i would recommend keeping them off your ears and break them in before listening ing to them. It is a giant difference between when they are new, and after the sound drivers are broken in.  Cant comment on durability as i just got these but absolutlely delighted with comfort and audio quality for this pricepoint. All the spend in in bud quality and not packaging or marketing, and that is the best possible value a discerning listener wants.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Krishna Rao\", \"rating\": \"5.0\", \"date\": \"01 Mar 2025\", \"text\": \"A WARNING FOR THOSE WHO WANT TO USE THIS WITH A GAMING PC.These IEMS sound wonderful. BUT, please check the ports of your PC before buying these IEMs. These IEMs use a single \\"TRRS\\" jack. If your PC, like mine, has two \\"TRS\\" ports namley one port for sound and one port for the mic, the TRRS jack of these IEMs will only give you the sound and the mic will be useless. This is because you would have plugged it into the TRS audio port. Alternatively the audio will get disabled and only the mic will work, if you plug it into the TRS mic port. Why? because you are plugging in a TRRS jack into TRS port wherein the latter is capable of handling only one feature i.e. either the sound or the mic BUT NOT BOTH AT THE SAME TIME.Thus you will be constained to buy a TRRS to TRS splitter (which is also available on Amazon). BUT, this will cause \\"audio leakage\\" from the mic into the speakers. In other words, you will hear an echo of whatever you say on the mic and also hear an echo of whatever you hear through the earphones! So be very careful and do enough research before taking the plunge.Personally it was a disaster for me as far as gaming is concerned and hence I am getting a TRRS to lightning jack to use it with my Iphone.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rohit lodhi\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Posting this review after using it for one month:-The mic is practically unusable for official meetings. It sounds like the speaker is too far from the mic, making communication unclear. And today the mic has stopped working.-If you\'re a bass lover, this product will disappoint you. The bass is very average and doesn\'t justify the price at all.Overall, I wouldn’t recommend buying this at this price point.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhilip K\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"Sounds amazing but now within one week right side bud getting little bit crackling sound during calls and songs at high volumesWhat should I do now\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SOUMYAJIT MALLICK\", \"rating\": \"4.0\", \"date\": \"12 May 2025\", \"text\": \"1.Quality is good...2.Design is awesome3.Comfort is not at par...felt heavy this can\'t use for long time4. Cable quality should be betterOverall more than average...\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Krish Raghuwanshi\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Very good product if you are using headphones than trust me the bass is much better than Headphone\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shamik M.Shamik M.\", \"rating\": \"5.0\", \"date\": \"21 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I was sceptical before buying the pair but after getting hands on it bangggg! This is the product that i was looking for long time.Lossless high resolution audio with low bidget price tag. It provides snug fit with different size eartips. Feels really sturdy and premium with its metal and resin build. You will absolutely loves its design. Now coming to its functionality and sound signature1. Bulit in mic is clear2. You have equaliser switches built in with both the buds. You can tweak it as per your choice.3. Lows mids and highs are clearly audible and crystal clear. Bass is thumpy ( bassheads go for it) mids are clear not muddy and highs are also lossless.4. Musicians mainly drummers and bass guitarist this thing is made for you guys.5. You can hear each and every instrument in a song individually good for every musician.My verdict is clear you will not regret after buying them. These pair sounds better than earphones 5 times costly than these.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Debjeet Debjeet\", \"rating\": \"4.0\", \"date\": \"28 Feb 2025\", \"text\": \"This iem has perfect balanced sound and pretty much a jack of all trades product. However the bass is a little shallow , though the pristine sound quality kind of makes up for it.Only one thing to note for new buyers , if you don\'t have a setup that gives a clean noiseless output or a cheap and bad dac which is not at least 24-bit supporting , then these headphones will sound really really terrible. You will need a good driver and clean signal to get the proper sound quality that these headphones produce.Overall these are a good buy and 9/10 chances you will not be disappointed.Some pros:-1. Comfortable to wear2. Design is really interesting3. Mic works well4. Easy to use , bonus if you know your way around Equalizer settings.5. Fits perfectly for the most part.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Karan KapurKaran Kapur\", \"rating\": \"5.0\", \"date\": \"11 Mar 2025\", \"text\": \"These are high performing earbuds with a great balanced soundtage. I got the model without the mic to ensure cable integrity over the long term as my only usage for these is Hi Res audio from my Iphone lightning DAC.  The buds take at least half an hour of audio at high volume to \\" break in \\" and i would recommend keeping them off your ears and break them in before listening ing to them. It is a giant difference between when they are new, and after the sound drivers are broken in.  Cant comment on durability as i just got these but absolutlely delighted with comfort and audio quality for this pricepoint. All the spend in in bud quality and not packaging or marketing, and that is the best possible value a discerning listener wants.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Krishna Rao\", \"rating\": \"5.0\", \"date\": \"01 Mar 2025\", \"text\": \"A WARNING FOR THOSE WHO WANT TO USE THIS WITH A GAMING PC.These IEMS sound wonderful. BUT, please check the ports of your PC before buying these IEMs. These IEMs use a single \\"TRRS\\" jack. If your PC, like mine, has two \\"TRS\\" ports namley one port for sound and one port for the mic, the TRRS jack of these IEMs will only give you the sound and the mic will be useless. This is because you would have plugged it into the TRS audio port. Alternatively the audio will get disabled and only the mic will work, if you plug it into the TRS mic port. Why? because you are plugging in a TRRS jack into TRS port wherein the latter is capable of handling only one feature i.e. either the sound or the mic BUT NOT BOTH AT THE SAME TIME.Thus you will be constained to buy a TRRS to TRS splitter (which is also available on Amazon). BUT, this will cause \\"audio leakage\\" from the mic into the speakers. In other words, you will hear an echo of whatever you say on the mic and also hear an echo of whatever you hear through the earphones! So be very careful and do enough research before taking the plunge.Personally it was a disaster for me as far as gaming is concerned and hence I am getting a TRRS to lightning jack to use it with my Iphone.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rohit lodhi\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Posting this review after using it for one month:-The mic is practically unusable for official meetings. It sounds like the speaker is too far from the mic, making communication unclear. And today the mic has stopped working.-If you\'re a bass lover, this product will disappoint you. The bass is very average and doesn\'t justify the price at all.Overall, I wouldn’t recommend buying this at this price point.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhilip K\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"Sounds amazing but now within one week right side bud getting little bit crackling sound during calls and songs at high volumesWhat should I do now\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SOUMYAJIT MALLICK\", \"rating\": \"4.0\", \"date\": \"12 May 2025\", \"text\": \"1.Quality is good...2.Design is awesome3.Comfort is not at par...felt heavy this can\'t use for long time4. Cable quality should be betterOverall more than average...\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Krish Raghuwanshi\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Very good product if you are using headphones than trust me the bass is much better than Headphone\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3</t>
+          <t>https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sony PlayStation®5 Digital Edition (slim) Console Video Game</t>
+          <t>Samsung Galaxy S25 5G</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DSBVGKVF\", \"product_name\": \"Samsung Galaxy S25 5G AI Smartphone (Icyblue, 12GB RAM, 256GB Storage), 50MP Camera with Galaxy AI\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Chaitanya tawarChaitanya tawar\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Great phone with processor and camera!Really enjoyed software which is ultra smooth on 120hz display! Color brightness is as expected in sunlight. Fingerprint sensor dynamic fast. Only thing which i felt is little downside is battery. Battery drains very fast. In this price segment samsung could have offered 5000 mah.All good. Premium feel.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Dr.SR\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Great phone with great pic quality…very smooth..performance is fantastic..charging speed is good enough…light weight..battery life is average…camera quality is better than s24 and s23…This phone is Value for money…Buy without any hesitation…\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sudipto\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"The phone is very compact and feels premium. Flagship level performance and camera. No complaints.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"ANKIT BADNOREANKIT BADNORE\", \"rating\": \"4.0\", \"date\": \"11 May 2025\", \"text\": \"Firstly talk about delivery experience, whi h was not smooth as I have exchanged my old phone. Delivery agent didn\'t accepts the notification light at the bottom of the screen. And demands 800 Rs for the damage. Literally amazon is playing game.I have to pay since I got the good deal.However there\'s no damage as such.Talk about the device. It looks Truely premium and compets the IPhone build.Display Is 6 star.Sound 4.5Heptics 4.5Camera 4.2Figure print sensor 6 starSuperfast functionalityCons. quite expensive as far as 8 elite phones in the market are concerned.Charging speed\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Sumedh\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Super Fast!!!!!!!!Go blindly it, iphone is no way near to it,Iphones are Overhyped and overpricedYou will not regret after buying this.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Pijush Konar\", \"rating\": \"5.0\", \"date\": \"09 Feb 2025\", \"text\": \"I recently upgraded from the Galaxy S22 to the S25, and the difference is significant. The S22 used to heat up even with simple tasks (Thanks to the chipset), but the S25 remains cool even during high-end usage. The display is top-notch, and while the camera setup is the same as last year, the improved processing makes a visible difference—photos are better than the S24.Battery life is solid, it\'s averaging around 6 hours 30 minutes with heavy usage and over 7 hours for normal tasks. However, Samsung still needs to improve its charging speed, which is the only con I’ve noticed so far.One UI 7 is a fantastic upgrade from One UI 6—smooth, feature-rich, and far superior to Oxygen OS (read, Color OS). It enhances daily usability in meaningful ways.I highly recommend this phone for anyone looking for a compact flagship that doesn’t feel like a mini tablet in their pocket. A great upgrade overall!\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kaushal Kumar\", \"rating\": \"1.0\", \"date\": \"02 May 2025\", \"text\": \"Cons:The phone heats a lot even if you just use normal app like whatsapp. It\'s so hot that it\'s unccomfortable to hold more than 10 mins of normal use. Charging is slow. The UI is very slow for a flagship model. My previous phone S20 FE was faster than this when it was new. On the same wifi other phone shows automatically shows 1080p but on this it show 360P video auto.It\'s definatly not worth even half of it\'s price. Looks like lots of fake reviewer are out there to sell this phone. Wasn\'t expecting this from Samsung.Pros:Phone looks good and handy. Camera is good.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Sumit Arya\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"Amazing phone with samsung features and knox security. Minor concern is with is battery but If you can manage the usage of your phone battery may last upto 48hrs else 24hrs.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Chaitanya tawarChaitanya tawar\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Great phone with processor and camera!Really enjoyed software which is ultra smooth on 120hz display! Color brightness is as expected in sunlight. Fingerprint sensor dynamic fast. Only thing which i felt is little downside is battery. Battery drains very fast. In this price segment samsung could have offered 5000 mah.All good. Premium feel.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Dr.SR\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Great phone with great pic quality…very smooth..performance is fantastic..charging speed is good enough…light weight..battery life is average…camera quality is better than s24 and s23…This phone is Value for money…Buy without any hesitation…\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"sudipto\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"The phone is very compact and feels premium. Flagship level performance and camera. No complaints.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"ANKIT BADNOREANKIT BADNORE\", \"rating\": \"4.0\", \"date\": \"11 May 2025\", \"text\": \"Firstly talk about delivery experience, whi h was not smooth as I have exchanged my old phone. Delivery agent didn\'t accepts the notification light at the bottom of the screen. And demands 800 Rs for the damage. Literally amazon is playing game.I have to pay since I got the good deal.However there\'s no damage as such.Talk about the device. It looks Truely premium and compets the IPhone build.Display Is 6 star.Sound 4.5Heptics 4.5Camera 4.2Figure print sensor 6 starSuperfast functionalityCons. quite expensive as far as 8 elite phones in the market are concerned.Charging speed\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Sumedh\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Super Fast!!!!!!!!Go blindly it, iphone is no way near to it,Iphones are Overhyped and overpricedYou will not regret after buying this.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Pijush Konar\", \"rating\": \"5.0\", \"date\": \"09 Feb 2025\", \"text\": \"I recently upgraded from the Galaxy S22 to the S25, and the difference is significant. The S22 used to heat up even with simple tasks (Thanks to the chipset), but the S25 remains cool even during high-end usage. The display is top-notch, and while the camera setup is the same as last year, the improved processing makes a visible difference—photos are better than the S24.Battery life is solid, it\'s averaging around 6 hours 30 minutes with heavy usage and over 7 hours for normal tasks. However, Samsung still needs to improve its charging speed, which is the only con I’ve noticed so far.One UI 7 is a fantastic upgrade from One UI 6—smooth, feature-rich, and far superior to Oxygen OS (read, Color OS). It enhances daily usability in meaningful ways.I highly recommend this phone for anyone looking for a compact flagship that doesn’t feel like a mini tablet in their pocket. A great upgrade overall!\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kaushal Kumar\", \"rating\": \"1.0\", \"date\": \"02 May 2025\", \"text\": \"Cons:The phone heats a lot even if you just use normal app like whatsapp. It\'s so hot that it\'s unccomfortable to hold more than 10 mins of normal use. Charging is slow. The UI is very slow for a flagship model. My previous phone S20 FE was faster than this when it was new. On the same wifi other phone shows automatically shows 1080p but on this it show 360P video auto.It\'s definatly not worth even half of it\'s price. Looks like lots of fake reviewer are out there to sell this phone. Wasn\'t expecting this from Samsung.Pros:Phone looks good and handy. Camera is good.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Sumit Arya\", \"rating\": \"5.0\", \"date\": \"04 May 2025\", \"text\": \"Amazing phone with samsung features and knox security. Minor concern is with is battery but If you can manage the usage of your phone battery may last upto 48hrs else 24hrs.\n  \nRead more\", \"product_id\": \"B0DSBVGKVF\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>iPhone 16 Pro Max 256 GB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DGHYPFYB\", \"product_name\": \"iPhone 16 Pro Max 256 GB: 5G Mobile Phone with Camera Control, 4K 120 fps Dolby Vision and a Huge Leap in Battery Life. Works with AirPods; Natural Titanium\", \"product_url\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Nikhil\", \"rating\": \"5.0\", \"date\": \"01 Nov 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'ve been using the iPhone 16 Pro Max for over a month, and I\'m blown away by its sheer performance, stunning display, and revolutionary camera capabilities. Apple has truly outdone themselves with this flagship device.*Pros:*1. *Breathtaking Display*: The 6.9-inch Super Retina XDR display is mesmerizing, with vibrant colors and an immersive viewing experience.2. *Camera Revolution*: The 48MP Pro camera system is incredible, capturing life-like images with ease. Night mode portraits and advanced features take mobile photography to new heights.3. *Lightning-Fast Performance*: The A18 Pro chip delivers seamless multitasking, graphics-intensive gaming, and effortless navigation.4. *All-Day Battery Life*: With up to 33 hours of video playback, I no longer worry about running out of juice.5. *Sleek Design*: The titanium build and textured matte glass back exude premium quality and durability.*Additional Highlights:*- Dynamic Island and Always-On display provide an intuitive experience- ProMotion technology with adaptive refresh rates up to 120Hz ensures silky-smooth visuals- Fast charging and wireless charging (MagSafe and Qi) make powering up convenient- IP68 rating ensures peace of mind against accidental water exposure*Verdict:*The iPhone 16 Pro Max is an exceptional device that justifies its premium price. If you\'re seeking the best iPhone experience, look no further. Apple\'s attention to detail, innovative features, and commitment to quality make this device a game-changer.*Rating Breakdown:*- Display: 5/5- Camera: 5/5- Performance: 5/5- Battery Life: 5/5- Design: 5/5- Value: 4.5/5*Recommendation:*If you\'re due for an upgrade or seeking the ultimate smartphone experience, the iPhone 16 Pro Max is the perfect choice.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"P.jayarani\", \"rating\": \"5.0\", \"date\": \"24 Apr 2025\", \"text\": \"Very good quality. I trust Amazon delivery.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SarthakSarthak\", \"rating\": \"5.0\", \"date\": \"22 Oct 2024\", \"text\": \"Excellent phone, Apple Intelligence is amazing, the battery life is mind blowing and comes with the best camera. If you have a 13 Pro Max or older, go for it. If you have a 14 Pro Max, the only difference you are going to see is Apple Intelligence, better battery life and slightly better cameras. Otherwise it\'s going to feel like the exact same phone if you use it without a case as the rounded eges in 16 Pro Max are better to use without cases. Skip and save money if you have the 15 Pro Max because the difference is negligible. The black titanium color looks gorgeous and the only good color in the current series. It\'s a shame they removed the Blue Titanium color. Also costs 15-20k less than the launch price of 15 Pro Max so that is a huge plus.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Alpha Lion\", \"rating\": \"1.0\", \"date\": \"14 May 2025\", \"text\": \"Android users switching to iphone for the first time will regret it! 1. Phone is heavy 2. Can\'t really keep up with the operating system as it lacks basic swipe gestures, notification access etc.. 3. Has touch issues mainly around the corners ( not sure if this is specific to indian made) as per the news i read about horrible quality checks done! Touch response is horrible compared to previous iphones. You have to literally press hard while typing!! 4. Many apps hang in the middle of operation and cannot go back but the only option is to close the app and reopen. 5. User friendly-ness is  not even close to android, forget it. Really not worth the money!!Finally sold it after 5 months of usage with horrible experience. Now I\'m back to android and feeling great about my decision!\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Virendra PandeyVirendra Pandey\", \"rating\": \"5.0\", \"date\": \"22 Oct 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I love the iPhone 16 Pro Max. It\'s big, powerful, and up for anything. Yes, I play a console-level game on it without any issue. It takes lovely photos that, even if you choose not to try out the new styles and undertones, are clear and color-accurate.Key SpecsApple iPhone 16 Pro MaxRAM 8 GBProcessor Apple A18 ProRear Camera 48 MP + 48 MP + 12 MPFront Camera 12 MPBattery 4685 mAhDisplay 6.9 inches (17.53 cm)Pros:*Larger screens/thinner bezels*4K slo-mo, OMG*Powerful processor*Camera control for instant camera access*Good performance &amp; battery life*Excellent cameras &amp; useful Photo Styles*Video capabilities &amp; Audio Mix*Apple IntelligenceCons:*No 8K video recording*Slow charging*Pricey\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Devmallya KararDevmallya Karar\", \"rating\": \"5.0\", \"date\": \"28 Oct 2024\", \"text\": \"Upgrading to the iPhone 16 Pro Max was a game-changer. The enhanced Apple Intelligence will take daily tasks to a whole new level—faster, smarter, and more intuitive. The camera\'s quality is stunning, capturing every detail effortlessly, and the display feels like a visual treat with vibrant colors. Battery life comfortably lasts all day, even with heavy use. The sleek design is the cherry on top. If you’re already an iPhone user, this is a must-have upgrade for those looking to stay at the forefront of tech!\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"..:: m a n i ::..\", \"rating\": \"4.0\", \"date\": \"30 Nov 2024\", \"text\": \"I did not like it at first. Its my first iPhone. I have used Samsung, Oneplus and Xiaomi phones. 16 Pro Max has many flaws. Android is much better now. But iOS is very smooth.Things I liked:1. Speakers are amazing.2. Battery life is good.3. Overall smoothness.4. Camera is great.Things I did not like:1. All the Web Browsers (Safari or others) are limited to 60hz.2. No option for menu bar navigation (android has both gestures and bar).3. Display / Screen color is fixed at Natural tone (no option for Vivid etc).4. Restricted files/folder access and many other UI limitations.5. Managing Whatsapp media is a mess (its much simpler on android).6. Telephoto 5X images are too soft.7. No separate Camera folder in Photos app for the photos you take with your phone.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"BIJIMATHEW\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nikhil\", \"rating\": \"5.0\", \"date\": \"01 Nov 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'ve been using the iPhone 16 Pro Max for over a month, and I\'m blown away by its sheer performance, stunning display, and revolutionary camera capabilities. Apple has truly outdone themselves with this flagship device.*Pros:*1. *Breathtaking Display*: The 6.9-inch Super Retina XDR display is mesmerizing, with vibrant colors and an immersive viewing experience.2. *Camera Revolution*: The 48MP Pro camera system is incredible, capturing life-like images with ease. Night mode portraits and advanced features take mobile photography to new heights.3. *Lightning-Fast Performance*: The A18 Pro chip delivers seamless multitasking, graphics-intensive gaming, and effortless navigation.4. *All-Day Battery Life*: With up to 33 hours of video playback, I no longer worry about running out of juice.5. *Sleek Design*: The titanium build and textured matte glass back exude premium quality and durability.*Additional Highlights:*- Dynamic Island and Always-On display provide an intuitive experience- ProMotion technology with adaptive refresh rates up to 120Hz ensures silky-smooth visuals- Fast charging and wireless charging (MagSafe and Qi) make powering up convenient- IP68 rating ensures peace of mind against accidental water exposure*Verdict:*The iPhone 16 Pro Max is an exceptional device that justifies its premium price. If you\'re seeking the best iPhone experience, look no further. Apple\'s attention to detail, innovative features, and commitment to quality make this device a game-changer.*Rating Breakdown:*- Display: 5/5- Camera: 5/5- Performance: 5/5- Battery Life: 5/5- Design: 5/5- Value: 4.5/5*Recommendation:*If you\'re due for an upgrade or seeking the ultimate smartphone experience, the iPhone 16 Pro Max is the perfect choice.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"P.jayarani\", \"rating\": \"5.0\", \"date\": \"24 Apr 2025\", \"text\": \"Very good quality. I trust Amazon delivery.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SarthakSarthak\", \"rating\": \"5.0\", \"date\": \"22 Oct 2024\", \"text\": \"Excellent phone, Apple Intelligence is amazing, the battery life is mind blowing and comes with the best camera. If you have a 13 Pro Max or older, go for it. If you have a 14 Pro Max, the only difference you are going to see is Apple Intelligence, better battery life and slightly better cameras. Otherwise it\'s going to feel like the exact same phone if you use it without a case as the rounded eges in 16 Pro Max are better to use without cases. Skip and save money if you have the 15 Pro Max because the difference is negligible. The black titanium color looks gorgeous and the only good color in the current series. It\'s a shame they removed the Blue Titanium color. Also costs 15-20k less than the launch price of 15 Pro Max so that is a huge plus.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Alpha Lion\", \"rating\": \"1.0\", \"date\": \"14 May 2025\", \"text\": \"Android users switching to iphone for the first time will regret it! 1. Phone is heavy 2. Can\'t really keep up with the operating system as it lacks basic swipe gestures, notification access etc.. 3. Has touch issues mainly around the corners ( not sure if this is specific to indian made) as per the news i read about horrible quality checks done! Touch response is horrible compared to previous iphones. You have to literally press hard while typing!! 4. Many apps hang in the middle of operation and cannot go back but the only option is to close the app and reopen. 5. User friendly-ness is  not even close to android, forget it. Really not worth the money!!Finally sold it after 5 months of usage with horrible experience. Now I\'m back to android and feeling great about my decision!\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Virendra PandeyVirendra Pandey\", \"rating\": \"5.0\", \"date\": \"22 Oct 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I love the iPhone 16 Pro Max. It\'s big, powerful, and up for anything. Yes, I play a console-level game on it without any issue. It takes lovely photos that, even if you choose not to try out the new styles and undertones, are clear and color-accurate.Key SpecsApple iPhone 16 Pro MaxRAM 8 GBProcessor Apple A18 ProRear Camera 48 MP + 48 MP + 12 MPFront Camera 12 MPBattery 4685 mAhDisplay 6.9 inches (17.53 cm)Pros:*Larger screens/thinner bezels*4K slo-mo, OMG*Powerful processor*Camera control for instant camera access*Good performance &amp; battery life*Excellent cameras &amp; useful Photo Styles*Video capabilities &amp; Audio Mix*Apple IntelligenceCons:*No 8K video recording*Slow charging*Pricey\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Devmallya KararDevmallya Karar\", \"rating\": \"5.0\", \"date\": \"28 Oct 2024\", \"text\": \"Upgrading to the iPhone 16 Pro Max was a game-changer. The enhanced Apple Intelligence will take daily tasks to a whole new level—faster, smarter, and more intuitive. The camera\'s quality is stunning, capturing every detail effortlessly, and the display feels like a visual treat with vibrant colors. Battery life comfortably lasts all day, even with heavy use. The sleek design is the cherry on top. If you’re already an iPhone user, this is a must-have upgrade for those looking to stay at the forefront of tech!\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"..:: m a n i ::..\", \"rating\": \"4.0\", \"date\": \"30 Nov 2024\", \"text\": \"I did not like it at first. Its my first iPhone. I have used Samsung, Oneplus and Xiaomi phones. 16 Pro Max has many flaws. Android is much better now. But iOS is very smooth.Things I liked:1. Speakers are amazing.2. Battery life is good.3. Overall smoothness.4. Camera is great.Things I did not like:1. All the Web Browsers (Safari or others) are limited to 60hz.2. No option for menu bar navigation (android has both gestures and bar).3. Display / Screen color is fixed at Natural tone (no option for Vivid etc).4. Restricted files/folder access and many other UI limitations.5. Managing Whatsapp media is a mess (its much simpler on android).6. Telephoto 5X images are too soft.7. No separate Camera folder in Photos app for the photos you take with your phone.\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"BIJIMATHEW\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0DGHYPFYB\", \"link\": \"https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Google Pixel 8a</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DTKDW6XN\", \"product_name\": \"Google Pixel 8a (Obsidian, 128, GB, 8, GB)\", \"product_url\": \"https://www.amazon.in/Google-Pixel-8a-Obsidian-128/dp/B0DTKDW6XN/ref=sr_1_7?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-7\", \"summary\": {\"total_reviews\": 4, \"average_rating\": 3.0, \"sentiment_breakdown\": {\"positive\": 2, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 50.0}, \"reviews\": [{\"author\": \"Shaikh Mushtaque Ahmed\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent\n  \nRead more\", \"product_id\": \"B0DTKDW6XN\", \"link\": \"https://www.amazon.in/Google-Pixel-8a-Obsidian-128/dp/B0DTKDW6XN/ref=sr_1_7?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-7\", \"sentiment\": \"positive\"}, {\"author\": \"Ankit\", \"rating\": \"1.0\", \"date\": \"02 May 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Extremely disappointed with the Pixel 8a. Here\'s why:🔥 Overheats like crazy – 20 minutes of Call of Duty and it feels like holding a hot brick. Totally unusable for gaming.🔋 Battery is a joke – Drains fast even on standby. Can’t last a full day without touching it.🔒 Fingerprint sensor is garbage – Fails to recognize prints most of the time. Basic unlocking becomes frustrating.💸 Totally overpriced – Phones under ₹22,000 perform miles better.🛑 Overall experience? Pathetic – Feels like a rushed, poorly optimized device.Verdict: Google seriously dropped the ball. Do NOT waste your money on this phone.\n  \nRead more\", \"product_id\": \"B0DTKDW6XN\", \"link\": \"https://www.amazon.in/Google-Pixel-8a-Obsidian-128/dp/B0DTKDW6XN/ref=sr_1_7?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-7\", \"sentiment\": \"negative\"}, {\"author\": \"Shaikh Mushtaque Ahmed\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent\n  \nRead more\", \"product_id\": \"B0DTKDW6XN\", \"link\": \"https://www.amazon.in/Google-Pixel-8a-Obsidian-128/dp/B0DTKDW6XN/ref=sr_1_7?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-7\", \"sentiment\": \"positive\"}, {\"author\": \"Ankit\", \"rating\": \"1.0\", \"date\": \"02 May 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Extremely disappointed with the Pixel 8a. Here\'s why:🔥 Overheats like crazy – 20 minutes of Call of Duty and it feels like holding a hot brick. Totally unusable for gaming.🔋 Battery is a joke – Drains fast even on standby. Can’t last a full day without touching it.🔒 Fingerprint sensor is garbage – Fails to recognize prints most of the time. Basic unlocking becomes frustrating.💸 Totally overpriced – Phones under ₹22,000 perform miles better.🛑 Overall experience? Pathetic – Feels like a rushed, poorly optimized device.Verdict: Google seriously dropped the ball. Do NOT waste your money on this phone.\n  \nRead more\", \"product_id\": \"B0DTKDW6XN\", \"link\": \"https://www.amazon.in/Google-Pixel-8a-Obsidian-128/dp/B0DTKDW6XN/ref=sr_1_7?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-7\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Google-Pixel-8a-Obsidian-128/dp/B0DTKDW6XN/ref=sr_1_7?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>iQOO Z10 5G</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0F2HCGXTB\", \"product_name\": \"iQOO Z10 5G (Silver, 8GB RAM, 128GB Stroage) | India\'s Biggest Ever 7300 mAh Battery | Snapdragon 7s Gen 3 Processor | Brightest Quad Curved AMOLED Display in The Segment\", \"product_url\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.5, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Sanket Deshpande\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Bought this phone for my mother, and she absolutely loves it! The large AMOLED curved display is very bright and easy on the eyes, which is great for reading and watching videos. The performance is super smooth with 12GB RAM—no lags at all during daily use. The battery life is a standout feature—lasts almost two full days with normal use, thanks to the massive 7300 mAh battery. Camera quality is also impressive. A great pick for anyone looking for a powerful and stylish phone at a good price!\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"kumar shivamkumar shivam\", \"rating\": \"4.0\", \"date\": \"07 May 2025\", \"text\": \"Pros of iQOO Z10 5G:Excellent 7,300mAh battery life90W fast chargingBright 6.77\\" AMOLED 120Hz displaySnapdragon 7s Gen 3 processorIP65 and MIL-STD-810H certified durabilityDecent 50MP main and 32MP selfie cameras4K video recording on both camerasCons of iQOO Z10 5G:No ultrawide cameraNo stereo speakersNo NFC supportBattery, display very good5g+ support speed good,Speaker sound could be betterBgmi performance averageCamera average\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"pratha\", \"rating\": \"5.0\", \"date\": \"30 Apr 2025\", \"text\": \"the phone is sleak and feels premium in handscreen is bright and interface is snappy,already got a software update on startup,cpu and camera performance are as advertisedthe best feature of this phone is that the battery charges quickly in an hour or so and lasts very long (3+days ) if you are a regular usersingle speaker is a bit underwhelmingnetworking works great calling , 5g , wifi and bluetooth quick share etc all work without issueall in all one of the best offerings in this price point!only place iQOO could be better if they remove pre-installed bloatware, but they can be easily disabled by their permissions removed during setup\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amita C.\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Pros:Overall value for money phone. Performance is very good. No heating issue while charging or watching videos. Camera is good. Its capturing good portraite pics. Battary backup is amazing (last for 1.5 days despite watching videos and WhatsApp video calls). Sound quality is fair. Display is also smooth. I don\'t do gaming so not tested that.Cons:Fingure print sensor is bit slow but no big deal.Sound quality could have been better.\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sharda kumari\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Writing this review after one month uses ,Awesome phone ,Decent battery,pic great, superfast processer,super performance Super features no heating issue till now..\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Karthi\", \"rating\": \"3.0\", \"date\": \"14 May 2025\", \"text\": \"I am using the phone for last 10 days.Battery and processor performance is pretty awesome,charge last for two days in ideal usage.Rear camera photos were looking nice, selfie is not worth, over all build quality is OK,  charging speed is fast, I am looking for normal tempered glass but no luck to find it only UV tempered glass is available.for this budget sound quality is low.I played pubg for 3 hrs continuously no heating issues and responsive rate is high as it is Powered by a 120 Hz Refresh rate. Overall if it is placed at less than 17k it is quite good.\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Alwin\", \"rating\": \"4.0\", \"date\": \"07 May 2025\", \"text\": \"Pros-good amoled display,good perfomnce,good battery backupCons-no cooling system,heating issue while gaming,average camera,single speaker.\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mayank\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Battery backup is so good ,light in weight,hand comfort is good, display quality is good, gaming performance much better, everything is good ,no hiting face during in summer while playing a high performance gam like a BGMI and cars simulator\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sanket Deshpande\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Bought this phone for my mother, and she absolutely loves it! The large AMOLED curved display is very bright and easy on the eyes, which is great for reading and watching videos. The performance is super smooth with 12GB RAM—no lags at all during daily use. The battery life is a standout feature—lasts almost two full days with normal use, thanks to the massive 7300 mAh battery. Camera quality is also impressive. A great pick for anyone looking for a powerful and stylish phone at a good price!\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"kumar shivamkumar shivam\", \"rating\": \"4.0\", \"date\": \"07 May 2025\", \"text\": \"Pros of iQOO Z10 5G:Excellent 7,300mAh battery life90W fast chargingBright 6.77\\" AMOLED 120Hz displaySnapdragon 7s Gen 3 processorIP65 and MIL-STD-810H certified durabilityDecent 50MP main and 32MP selfie cameras4K video recording on both camerasCons of iQOO Z10 5G:No ultrawide cameraNo stereo speakersNo NFC supportBattery, display very good5g+ support speed good,Speaker sound could be betterBgmi performance averageCamera average\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"pratha\", \"rating\": \"5.0\", \"date\": \"30 Apr 2025\", \"text\": \"the phone is sleak and feels premium in handscreen is bright and interface is snappy,already got a software update on startup,cpu and camera performance are as advertisedthe best feature of this phone is that the battery charges quickly in an hour or so and lasts very long (3+days ) if you are a regular usersingle speaker is a bit underwhelmingnetworking works great calling , 5g , wifi and bluetooth quick share etc all work without issueall in all one of the best offerings in this price point!only place iQOO could be better if they remove pre-installed bloatware, but they can be easily disabled by their permissions removed during setup\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amita C.\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Pros:Overall value for money phone. Performance is very good. No heating issue while charging or watching videos. Camera is good. Its capturing good portraite pics. Battary backup is amazing (last for 1.5 days despite watching videos and WhatsApp video calls). Sound quality is fair. Display is also smooth. I don\'t do gaming so not tested that.Cons:Fingure print sensor is bit slow but no big deal.Sound quality could have been better.\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sharda kumari\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Writing this review after one month uses ,Awesome phone ,Decent battery,pic great, superfast processer,super performance Super features no heating issue till now..\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Karthi\", \"rating\": \"3.0\", \"date\": \"14 May 2025\", \"text\": \"I am using the phone for last 10 days.Battery and processor performance is pretty awesome,charge last for two days in ideal usage.Rear camera photos were looking nice, selfie is not worth, over all build quality is OK,  charging speed is fast, I am looking for normal tempered glass but no luck to find it only UV tempered glass is available.for this budget sound quality is low.I played pubg for 3 hrs continuously no heating issues and responsive rate is high as it is Powered by a 120 Hz Refresh rate. Overall if it is placed at less than 17k it is quite good.\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Alwin\", \"rating\": \"4.0\", \"date\": \"07 May 2025\", \"text\": \"Pros-good amoled display,good perfomnce,good battery backupCons-no cooling system,heating issue while gaming,average camera,single speaker.\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mayank\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Battery backup is so good ,light in weight,hand comfort is good, display quality is good, gaming performance much better, everything is good ,no hiting face during in summer while playing a high performance gam like a BGMI and cars simulator\n  \nRead more\", \"product_id\": \"B0F2HCGXTB\", \"link\": \"https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iQOO Neo 10R 5G </t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DW47XR3X\", \"product_name\": \"iQOO Neo 10R 5G (Raging Blue, 8GB RAM, 128GB Storage) | Snapdragon 8s Gen 3 Processor | India\'s Slimmest 6400mAh Battery Smartphone | Segment\'s Most Stable 90FPS for 5 Hours\", \"product_url\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"manikandan\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The iQOO Neo 10 R delivers flagship-level performance at an unbeatable price. Powered by a high-end Snapdragon chipset, it handles multitasking, gaming, and heavy applications effortlessly. The AMOLED display is sharp and smooth, with an excellent refresh rate that enhances the user experience.Battery life is reliable, easily lasting a full day, and the fast charging is incredibly efficient—100% in around 25 minutes. The design feels premium and modern, and the camera system performs very well in good lighting conditions.However, the one downside is the Funtouch OS. It\'s functional but lacks the polish and refinement of Origin OS, which would’ve taken the experience to the next level. If iQOO brings Origin OS globally, it could truly set a new benchmark in this segment.Still, if you’re looking for performance, fast charging, and great hardware at a competitive price, the Neo 10 R is a fantastic choice.\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Eswar\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"I am college student . Who use device more as router and gaming .Performance: the processer is very powerful. It can handle all tasks and mid-level graphics with higher fps gaming . Overall all best for performance.Display: the display is also good, viewings angles and outdoor brightness is also good , you can use in direct sunlight also . And one thing it is excellent only when you like flat display. Which is you personally prefrence. Overall is good for the price .Cameras : the camera is ok but if we compare with others is very worst in ultra wide or in video stability which leads to noise in some scenarios . If you only use for photos with main camera and only in good light then it good . Night photos are good , but while using night mode you should not shake your hand little bit also then the photo would have less noise .Battery and charging: battery is good and it gives me overall 1 day ( 5-6 hr screen time with gaming of 1hr ) . Charging is also good , but you need to on the fast charging in settings.Ram and Rom (8/256): guys this is first time i am using ufs 4.1 . I have got around 100-120 mbps transfer speed from my laptop to phone for a movie ( using FTP ) . And Ram management is also excellent sometimes it takes time to open the previous apps which are opened at staring but it loads where we were left .UI : it is as expected. But personally i like fun touch os , so it ok for me .Heating is normal . One thing i need to say that if the phone heats at 45-46 degrees also you don\'t feel so warm as other device , it feels like 43 around.The only that I didn\'t like is the NFC is not available.Guys this review is rewritten after 20 days usages . This is my experience after 20 days usage .\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Himadri sarkarHimadri sarkar\", \"rating\": \"4.0\", \"date\": \"21 May 2025\", \"text\": \"Product is very good. Performance is top notch. Sound quality and camara quality also impressive and massive battery backup. Display quality is out of the world But heating issue is having it need to be resolved with software update. Price range is high.\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kanit Habib Chowdhury\", \"rating\": \"5.0\", \"date\": \"27 Apr 2025\", \"text\": \"Dear Tech Enthusiast,I recently had the pleasure of experiencing a gaming phone that falls comfortably under the ₹30,000 price bracket, and I felt compelled to share my impressions. In a market flooded with options, finding a device that balances performance and affordability can be a daunting task. However, this particular contender has genuinely impressed me with its capabilities.The phone I\'m referring to is the iQOO Neo 10R. Priced competitively at around ₹26,999 for the base variant, it stands out as a strong contender for gamers on a budget.Here\'s a breakdown of my experience:Performance: At the heart of this device lies the Snapdragon 8s Gen 3 chipset. This powerful processor, coupled with 8GB of RAM, ensures smooth and lag-free gaming even on demanding titles like BGMI and COD Mobile at high settings. I was particularly impressed by the consistent frame rates and the minimal heating during extended gaming sessions. The AnTuTu GPU score of 4,99,035 speaks volumes about its graphical prowess.Display: The 6.78-inch AMOLED display with a 144Hz refresh rate offers a vibrant and fluid visual experience. The colors are rich, and the fast refresh rate makes gameplay feel incredibly responsive. While the resolution is adequate, a slightly higher resolution could have elevated the visual fidelity further, but at this price point, it\'s a minor compromise.Gaming Features: iQOO has clearly focused on the gaming experience with the Neo 10R. It boasts dedicated gaming features like a built-in FPS meter, an e-sports mode, and a \'Monster Mode\' that optimizes the phone for peak gaming performance. The inclusion of bypass charging is a thoughtful addition, allowing you to game for extended periods without significantly heating the battery.Battery: The 6400mAh battery is a significant highlight. It easily lasted me through a full day of moderate use, including several hours of gaming. Even after intense gaming sessions, I was left with enough power to get through the rest of the day.Other Notable Aspects:* The phone supports 5G connectivity, ensuring future-proof network capabilities.* It features a decent camera setup, although it\'s not the primary focus of this device. The 50MP main camera captures good quality images in daylight.* The software experience is clean and optimized for performance.Areas for Potential Improvement:* While the polycarbonate build feels sturdy, it might not feel as premium as some of the glass-backed competitors.* The camera performance, while adequate, could be better, especially in low-light conditions.Overall:The iQOO Neo 10R offers an exceptional gaming experience without breaking the bank. Its powerful processor, high refresh rate display, dedicated gaming features, and long-lasting battery make it a compelling choice for budget-conscious gamers. While there are a few minor compromises, the overall package delivers excellent value for its price. If gaming is your priority and you\'re looking for a phone under ₹30,000, the iQOO Neo 10R deserves a serious look.Sincerely,A Satisfied Mobile Gamer.\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mukesh.M\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"If you want a beast under 30k just go for it. To be honest great battery backup great camera and even great gameplay. But the 120fps is a bit unstable when the phone starts heating. Does have slight heating issues when gaming for a very long period of time. But totally a beast and king of the segment for sure 💯. 8/256 is great. No doubt. Also very light weight and great display with rich colours. Good peak brightness. Huge screen 💯\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"manikandan\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The iQOO Neo 10 R delivers flagship-level performance at an unbeatable price. Powered by a high-end Snapdragon chipset, it handles multitasking, gaming, and heavy applications effortlessly. The AMOLED display is sharp and smooth, with an excellent refresh rate that enhances the user experience.Battery life is reliable, easily lasting a full day, and the fast charging is incredibly efficient—100% in around 25 minutes. The design feels premium and modern, and the camera system performs very well in good lighting conditions.However, the one downside is the Funtouch OS. It\'s functional but lacks the polish and refinement of Origin OS, which would’ve taken the experience to the next level. If iQOO brings Origin OS globally, it could truly set a new benchmark in this segment.Still, if you’re looking for performance, fast charging, and great hardware at a competitive price, the Neo 10 R is a fantastic choice.\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Eswar\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"I am college student . Who use device more as router and gaming .Performance: the processer is very powerful. It can handle all tasks and mid-level graphics with higher fps gaming . Overall all best for performance.Display: the display is also good, viewings angles and outdoor brightness is also good , you can use in direct sunlight also . And one thing it is excellent only when you like flat display. Which is you personally prefrence. Overall is good for the price .Cameras : the camera is ok but if we compare with others is very worst in ultra wide or in video stability which leads to noise in some scenarios . If you only use for photos with main camera and only in good light then it good . Night photos are good , but while using night mode you should not shake your hand little bit also then the photo would have less noise .Battery and charging: battery is good and it gives me overall 1 day ( 5-6 hr screen time with gaming of 1hr ) . Charging is also good , but you need to on the fast charging in settings.Ram and Rom (8/256): guys this is first time i am using ufs 4.1 . I have got around 100-120 mbps transfer speed from my laptop to phone for a movie ( using FTP ) . And Ram management is also excellent sometimes it takes time to open the previous apps which are opened at staring but it loads where we were left .UI : it is as expected. But personally i like fun touch os , so it ok for me .Heating is normal . One thing i need to say that if the phone heats at 45-46 degrees also you don\'t feel so warm as other device , it feels like 43 around.The only that I didn\'t like is the NFC is not available.Guys this review is rewritten after 20 days usages . This is my experience after 20 days usage .\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Himadri sarkarHimadri sarkar\", \"rating\": \"4.0\", \"date\": \"21 May 2025\", \"text\": \"Product is very good. Performance is top notch. Sound quality and camara quality also impressive and massive battery backup. Display quality is out of the world But heating issue is having it need to be resolved with software update. Price range is high.\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kanit Habib Chowdhury\", \"rating\": \"5.0\", \"date\": \"27 Apr 2025\", \"text\": \"Dear Tech Enthusiast,I recently had the pleasure of experiencing a gaming phone that falls comfortably under the ₹30,000 price bracket, and I felt compelled to share my impressions. In a market flooded with options, finding a device that balances performance and affordability can be a daunting task. However, this particular contender has genuinely impressed me with its capabilities.The phone I\'m referring to is the iQOO Neo 10R. Priced competitively at around ₹26,999 for the base variant, it stands out as a strong contender for gamers on a budget.Here\'s a breakdown of my experience:Performance: At the heart of this device lies the Snapdragon 8s Gen 3 chipset. This powerful processor, coupled with 8GB of RAM, ensures smooth and lag-free gaming even on demanding titles like BGMI and COD Mobile at high settings. I was particularly impressed by the consistent frame rates and the minimal heating during extended gaming sessions. The AnTuTu GPU score of 4,99,035 speaks volumes about its graphical prowess.Display: The 6.78-inch AMOLED display with a 144Hz refresh rate offers a vibrant and fluid visual experience. The colors are rich, and the fast refresh rate makes gameplay feel incredibly responsive. While the resolution is adequate, a slightly higher resolution could have elevated the visual fidelity further, but at this price point, it\'s a minor compromise.Gaming Features: iQOO has clearly focused on the gaming experience with the Neo 10R. It boasts dedicated gaming features like a built-in FPS meter, an e-sports mode, and a \'Monster Mode\' that optimizes the phone for peak gaming performance. The inclusion of bypass charging is a thoughtful addition, allowing you to game for extended periods without significantly heating the battery.Battery: The 6400mAh battery is a significant highlight. It easily lasted me through a full day of moderate use, including several hours of gaming. Even after intense gaming sessions, I was left with enough power to get through the rest of the day.Other Notable Aspects:* The phone supports 5G connectivity, ensuring future-proof network capabilities.* It features a decent camera setup, although it\'s not the primary focus of this device. The 50MP main camera captures good quality images in daylight.* The software experience is clean and optimized for performance.Areas for Potential Improvement:* While the polycarbonate build feels sturdy, it might not feel as premium as some of the glass-backed competitors.* The camera performance, while adequate, could be better, especially in low-light conditions.Overall:The iQOO Neo 10R offers an exceptional gaming experience without breaking the bank. Its powerful processor, high refresh rate display, dedicated gaming features, and long-lasting battery make it a compelling choice for budget-conscious gamers. While there are a few minor compromises, the overall package delivers excellent value for its price. If gaming is your priority and you\'re looking for a phone under ₹30,000, the iQOO Neo 10R deserves a serious look.Sincerely,A Satisfied Mobile Gamer.\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mukesh.M\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"If you want a beast under 30k just go for it. To be honest great battery backup great camera and even great gameplay. But the 120fps is a bit unstable when the phone starts heating. Does have slight heating issues when gaming for a very long period of time. But totally a beast and king of the segment for sure 💯. 8/256 is great. No doubt. Also very light weight and great display with rich colours. Good peak brightness. Huge screen 💯\n  \nRead more\", \"product_id\": \"B0DW47XR3X\", \"link\": \"https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samsung Galaxy Z Fold6 </t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DH7226XN\", \"product_name\": \"Samsung Galaxy Z Fold6 5G AI Smartphone (Silver Shadow, 12GB RAM, 256GB Storage) Without Offer\", \"product_url\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 3.62, \"sentiment_breakdown\": {\"neutral\": 8, \"positive\": 6, \"negative\": 2}, \"overall_sentiment\": \"neutral\", \"accuracy_score\": 50.0}, \"reviews\": [{\"author\": \"Garry\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good phone\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Abhishek\", \"rating\": \"1.0\", \"date\": \"19 May 2025\", \"text\": \"Amazon se koi v mobile mt lena ye refurbished mobile sell krta h samsung service centre pe jake check krwaye h fir v nhi mann rha h amazon ka technician v bola fir v nhi mnn rha h proof diye service centre se lake fir v nhi man rha h Koi v phone Mt Lena\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"mahesh reddii\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Thanks to my friend who reminded me I had a extra kidney ,sold the spare one immediately and bought the phone . Absolutely worth it\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sameer\", \"rating\": \"5.0\", \"date\": \"15 Jan 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Isha SinhalIsha Sinhal\", \"rating\": \"1.0\", \"date\": \"09 Oct 2024\", \"text\": \"It\'s a scam\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Placeholder\", \"rating\": \"2.0\", \"date\": \"20 May 2025\", \"text\": \"ToAs far as I am aware, purchasing a foldable phone is just dumb. We can dare to purchase an iPhone, which is incredibly worthy, in lieu of a foldable phone. I would advise against purchasing a foldable phone.\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"SatishSatish\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"Been using Samsung Fold6 daily for over sometime now, and the first thing I noticed was how sturdy it feels. The hinge opens and shuts smoothly, and the screen protector holds up well even with constant usage. It’s gone through the usual bumps in my bag and pockets, and still looks as good as new.\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kabita ChoudharyKabita Choudhary\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"After switching from iPhone 12 to Fold6 about 8 months ago, I don’t think I can go back to a standard phone. The big screen is a game-changer. I use it to read e-books, browse spreadsheets, and watch Netflix. Perfect for both work and entertainment.\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Garry\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good phone\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Abhishek\", \"rating\": \"1.0\", \"date\": \"19 May 2025\", \"text\": \"Amazon se koi v mobile mt lena ye refurbished mobile sell krta h samsung service centre pe jake check krwaye h fir v nhi mann rha h amazon ka technician v bola fir v nhi mnn rha h proof diye service centre se lake fir v nhi man rha h Koi v phone Mt Lena\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"mahesh reddii\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Thanks to my friend who reminded me I had a extra kidney ,sold the spare one immediately and bought the phone . Absolutely worth it\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sameer\", \"rating\": \"5.0\", \"date\": \"15 Jan 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Isha SinhalIsha Sinhal\", \"rating\": \"1.0\", \"date\": \"09 Oct 2024\", \"text\": \"It\'s a scam\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Placeholder\", \"rating\": \"2.0\", \"date\": \"20 May 2025\", \"text\": \"ToAs far as I am aware, purchasing a foldable phone is just dumb. We can dare to purchase an iPhone, which is incredibly worthy, in lieu of a foldable phone. I would advise against purchasing a foldable phone.\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"SatishSatish\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"Been using Samsung Fold6 daily for over sometime now, and the first thing I noticed was how sturdy it feels. The hinge opens and shuts smoothly, and the screen protector holds up well even with constant usage. It’s gone through the usual bumps in my bag and pockets, and still looks as good as new.\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kabita ChoudharyKabita Choudhary\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"After switching from iPhone 12 to Fold6 about 8 months ago, I don’t think I can go back to a standard phone. The big screen is a game-changer. I use it to read e-books, browse spreadsheets, and watch Netflix. Perfect for both work and entertainment.\n  \nRead more\", \"product_id\": \"B0DH7226XN\", \"link\": \"https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Microsoft New Surface Pro</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D926JN5N\", \"product_name\": \"Microsoft New Surface Pro (11Th Edition) - Windows 11 Home Copilot + Pc - 13\\" LCD Pixelsense Touchscreen - Qualcomm Snapdragon X Plus (10 Core,Wi-Fi) - 16Gb Ram - 256Gb Ssd - Platinum - Zhx-00014\", \"product_url\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 8, \"neutral\": 6, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 50.0}, \"reviews\": [{\"author\": \"JAYA PRAKASH JAYA PRAKASH\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The quality of product is good. Latest product (Feb 2025 manifactured) was sent &amp; amazing packing. All genuine accessories.  Delivery was on time. All softwares are preloaded, enhancing the performance. Perfect for day use and battery life is the best.  Value for money.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Peace1402\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Always liked it. This is my third surface.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"neutral\"}, {\"author\": \"vikrant pandita\", \"rating\": \"5.0\", \"date\": \"08 Apr 2025\", \"text\": \"It\'s perfect . Best laptop\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"3.0\", \"date\": \"25 Dec 2024\", \"text\": \"No SIM SLOT\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"neutral\"}, {\"author\": \"Ravi ShekharRavi Shekhar\", \"rating\": \"5.0\", \"date\": \"04 Oct 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Good performance, display quality is also good and excellent Battery life. Bit pricey.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Laxmi Patil\", \"rating\": \"1.0\", \"date\": \"17 Mar 2025\", \"text\": \"Product not turning ON.Amazon denied to provide replacement or return.Microsoft not having authorised service centre in India.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"negative\"}, {\"author\": \"Ashwani parikAshwani parik\", \"rating\": \"5.0\", \"date\": \"21 Jan 2025\", \"text\": \"This is my Second Microsoft Surface Pro 11, I am very happy with battery life, elite style and face recognition feature.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"neutral\"}, {\"author\": \"Vishal Juneja\", \"rating\": \"5.0\", \"date\": \"08 Jan 2025\", \"text\": \"Looking for the best AI PC and tablet? Look no further, just get Surface Pro 11.  Best Windows PC ever with maximum portability, and touch screen.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"JAYA PRAKASH JAYA PRAKASH\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The quality of product is good. Latest product (Feb 2025 manifactured) was sent &amp; amazing packing. All genuine accessories.  Delivery was on time. All softwares are preloaded, enhancing the performance. Perfect for day use and battery life is the best.  Value for money.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Peace1402\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Always liked it. This is my third surface.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"neutral\"}, {\"author\": \"vikrant pandita\", \"rating\": \"5.0\", \"date\": \"08 Apr 2025\", \"text\": \"It\'s perfect . Best laptop\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"3.0\", \"date\": \"25 Dec 2024\", \"text\": \"No SIM SLOT\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"neutral\"}, {\"author\": \"Ravi ShekharRavi Shekhar\", \"rating\": \"5.0\", \"date\": \"04 Oct 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Good performance, display quality is also good and excellent Battery life. Bit pricey.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Laxmi Patil\", \"rating\": \"1.0\", \"date\": \"17 Mar 2025\", \"text\": \"Product not turning ON.Amazon denied to provide replacement or return.Microsoft not having authorised service centre in India.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"negative\"}, {\"author\": \"Ashwani parikAshwani parik\", \"rating\": \"5.0\", \"date\": \"21 Jan 2025\", \"text\": \"This is my Second Microsoft Surface Pro 11, I am very happy with battery life, elite style and face recognition feature.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"neutral\"}, {\"author\": \"Vishal Juneja\", \"rating\": \"5.0\", \"date\": \"08 Jan 2025\", \"text\": \"Looking for the best AI PC and tablet? Look no further, just get Surface Pro 11.  Best Windows PC ever with maximum portability, and touch screen.\n  \nRead more\", \"product_id\": \"B0D926JN5N\", \"link\": \"https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Motorola razr 60 Ultra</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0F5HVFVKH\", \"product_name\": \"Motorola razr 60 Ultra (Pantone Scarab, 16 GB RAM, 512 GB Storage) | Moto AI | Snapdragon® 8 Elite Mobile Platform | 6.9\\" AMOLED 165Hz Display | 50 MP + 50 MP + 50MP Triple Camera\", \"product_url\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"summary\": {\"total_reviews\": 4, \"average_rating\": 4.5, \"sentiment_breakdown\": {\"positive\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijeet Chinchole\", \"rating\": \"5.0\", \"date\": \"28 May 2025\", \"text\": \"This is my very first smartphone, and after using the Moto Razr 60 Ultra for a week, I can confidently say I’m impressed! The design is sleek and premium, and the flip form factor adds a cool, nostalgic touch while still feeling modern.Performance has been smooth so far – apps open quickly, multitasking is easy, and the external display is actually very handy for quick glances or controls without unfolding the phone. The inner screen is vibrant and responsive, making everyday use a joy.Battery life could be better – it gets me through the day, but not much more. That’s the only area where I feel there’s room for improvement.Overall, it’s a fantastic flip phone for anyone who wants something unique yet functional. I’m really enjoying the experience!\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Kamal Kundu\", \"rating\": \"4.0\", \"date\": \"25 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Phone is awesome but eSim option is not active in India. Let me know if there are ways to activate eSim for it.\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Abhijeet Chinchole\", \"rating\": \"5.0\", \"date\": \"28 May 2025\", \"text\": \"This is my very first smartphone, and after using the Moto Razr 60 Ultra for a week, I can confidently say I’m impressed! The design is sleek and premium, and the flip form factor adds a cool, nostalgic touch while still feeling modern.Performance has been smooth so far – apps open quickly, multitasking is easy, and the external display is actually very handy for quick glances or controls without unfolding the phone. The inner screen is vibrant and responsive, making everyday use a joy.Battery life could be better – it gets me through the day, but not much more. That’s the only area where I feel there’s room for improvement.Overall, it’s a fantastic flip phone for anyone who wants something unique yet functional. I’m really enjoying the experience!\n  \nRead more\", \"product_id\": \"B0F5HVFVKH\", \"link\": \"https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HQW3GZ/ref=sr_1_1_sspa?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S25 Ultra</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DSKMKJV5\", \"product_name\": \"Samsung Galaxy S25 Ultra 5G AI Smartphone (Titanium Black, 12GB RAM, 512GB Storage), 200MP Camera, S Pen Included, Long Battery Life\", \"product_url\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 2, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Nihir Shah\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Samsung Galaxy S25 Ultra continues the Ultra legacy with a device that’s powerful, polished, and packed with cutting-edge features. It’s clear Samsung aimed to solidify its position at the top of the premium smartphone market—and it mostly succeeds.Design and DisplayThe S25 Ultra features a 6.9-inch Dynamic AMOLED 2X display with a 120Hz adaptive refresh rate, offering vibrant colors, deep blacks, and smooth scrolling.The display has a resolution of 3120 x 1440 pixels.It is protected by Corning Gorilla Glass Armor 2, which provides enhanced durability.The phone has a titanium frame and an IP68 rating for dust and water resistance.It also includes an embedded S Pen stylus.Software &amp; FeaturesRunning One UI 7.1 based on Android 15, the user experience is smooth and customizable. Samsung’s commitment to 7 years of software updates gives it an edge over most Android competitors. The integration of Galaxy AI, such as real-time translation, generative photo editing, and productivity enhancements in Samsung Notes, brings genuinely useful features to the everyday experience.CameraThe S25 Ultra has a quad-camera setup:200MP wide-angle primary camera50MP ultra-wide-angle camera10MP telephoto camera (3x optical zoom)50MP periscope telephoto camera (5x optical zoom)The front-facing camera is 12MP.The camera system supports 8K video recording, HDR, and various professional features.Performance and HardwareThe S25 Ultra is powered by the Snapdragon 8 Elite processor.It comes with 12GB or 16GB of RAM.Storage options include 256GB, 512GB, and 1TB.The phone runs on Android 15 with Samsung\'s One UI 7.BatteryThe S25 Ultra has a 5000mAh battery.It supports 45W wired fast charging and 15W wireless charging.Other FeaturesThe phone supports 5G connectivity.It has an ultrasonic in-display fingerprint sensor.It includes Wi-Fi 7, Bluetooth 5.3, NFC, and USB Type-C.SummaryThe Samsung Galaxy S25 Ultra is a premium smartphone with a top-of-the-line display, powerful performance, a versatile camera system, and a long-lasting battery. It also has an S Pen, which is useful for productivity and creativity.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I\'ve been using the Galaxy S25 Ultra for over two months now, having upgraded from the S22 Ultra — and I couldn’t be more satisfied. The display is absolutely stunning, offering crisp visuals and vibrant colors that enhance every viewing experience. The camera is top-notch, particularly excelling in low-light photography — easily the best in the industry.Battery life is another strong point; despite my heavy usage, it easily lasts a full day without needing a recharge. Performance-wise, the phone runs incredibly smooth with no lags or slowdowns. Overall, the S25 Ultra is a powerful, well-rounded upgrade that delivers on all front.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Avishek DeyAvishek Dey\", \"rating\": \"5.0\", \"date\": \"05 Feb 2025\", \"text\": \"I switched to the Galaxy S25 Ultra after using the iPhone 12 Pro Max for 4 years. The display is absolutely stunning, super bright and the colours pop out. S25 Ultra is very snappy, apps open instantly and higher refresh rate makes the animations very smooth. Camera is decent too. Overall a very worthy upgrade from my current phone\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Deepansh J.\", \"rating\": \"4.0\", \"date\": \"03 May 2025\", \"text\": \"Phone is nice.Performance and speed is good.Little heavy in weight.But battery can be improved to 6000 mah.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"neutral\"}, {\"author\": \"PRADEEP N.\", \"rating\": \"1.0\", \"date\": \"04 Apr 2025\", \"text\": \"Be very careful before ordering expensive phones at seemingly attractive discounts - you might be in for a shock. They might send you a used/second hand set. Which is what happened in my case. I received it on March 27th but it had already been activated on 11th February. Was lucky to find out because I happened to get the warranty checked from a authorised Samsung store. However, to their credit, Amazon agreed to take it back immediately and issue a refund. Now in the process....Disappointed\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"negative\"}, {\"author\": \"Kushagra M.\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"The design, look and feel of the UI, battery, display, multi-tasking and AI functionality is top-notch. Camera, gaming experience, S-pen support is pretty good too. One of the best flagship phone, if not the best one.\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Aman\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Superb\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}, {\"author\": \"Arun Ganesh\", \"rating\": \"5.0\", \"date\": \"26 Mar 2025\", \"text\": \"I was initially hesitant to purchase the S25 Ultra, but after 2 weeks of use, I\'m thrilled to share my overwhelmingly positive experience!The battery life has been a standout feature for me, consistently lasting a full day and often stretching into the next with moderate to heavy use.The phone\'s overall performance has been seamless, with lightning-fast app loading, effortless multitasking, and silky-smooth graphics.The display is stunning, with vibrant colors and crisp details that make every visual experience a joy.I\'ve also been impressed with the camera\'s capabilities, delivering crisp, high-quality photos and videos in a variety of conditions.Overall, the S25 Ultra has exceeded my expectations and truly lives up to its reputation as an Android powerhouse. If you\'re in the market for a new flagship device, I highly recommend giving this one a serious look!\n  \nRead more\", \"product_id\": \"B0DSKMKJV5\", \"link\": \"https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DSKNVWK7/ref=sspa_dk_detail_5?pd_rd_i=B0DSKNVWK7&amp;pd_rd_w=5bWOT&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=0ETXZXDS4EWRAA11T15X&amp;pd_rd_wg=A7avg&amp;pd_rd_r=1a644a6d-1c0c-4741-9e61-835460064a2a&amp;s=electronics&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Nothing Phone (3a)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DZTMFWDB\", \"product_name\": \"Nothing Phone (3a) 5G (8GB RAM + 128GB Storage) (White)\", \"product_url\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 3.25, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Amandeep singh\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good product\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Naveen\", \"rating\": \"1.0\", \"date\": \"26 May 2025\", \"text\": \"Battery life is not good\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Shabnam\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Great product\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Prashant Tripathi\", \"rating\": \"3.0\", \"date\": \"27 May 2025\", \"text\": \"Heating issue....Not for gamers.. for day to day task it\'s good..camera is good processor is also good ..No lag\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"rameshchalilrameshchalil\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"The good phone charge is a long time standing and good speed responses\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Syam Tatineni\", \"rating\": \"5.0\", \"date\": \"22 Apr 2025\", \"text\": \"Better than OnePlusBrilliant displayBest android software experienceGood photos..better than my previous OnePlus 10RGreat value for moneyLooks good ..best in the budget..not going to other android brands any time soonOnly company that seems to have been investing time , brains and money in innovation in android segment\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Suresh Kumar saini\", \"rating\": \"1.0\", \"date\": \"19 May 2025\", \"text\": \"Not working sim card port and not supported charge\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"neutral\"}, {\"author\": \"KIRAN KUMAR (Raju)\", \"rating\": \"1.0\", \"date\": \"09 Apr 2025\", \"text\": \"बहुत बेकार mobile हे ऑटो switch ओफ़ हो जाता हे or amazon पर सेल के लिए registered hi nahi h nothing service centre wale bolte h वेस्ट ओफ़ मनी.!😂\n  \n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"neutral\"}, {\"author\": \"Amandeep singh\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good product\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Naveen\", \"rating\": \"1.0\", \"date\": \"26 May 2025\", \"text\": \"Battery life is not good\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Shabnam\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Great product\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Prashant Tripathi\", \"rating\": \"3.0\", \"date\": \"27 May 2025\", \"text\": \"Heating issue....Not for gamers.. for day to day task it\'s good..camera is good processor is also good ..No lag\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"rameshchalilrameshchalil\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"The good phone charge is a long time standing and good speed responses\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Syam Tatineni\", \"rating\": \"5.0\", \"date\": \"22 Apr 2025\", \"text\": \"Better than OnePlusBrilliant displayBest android software experienceGood photos..better than my previous OnePlus 10RGreat value for moneyLooks good ..best in the budget..not going to other android brands any time soonOnly company that seems to have been investing time , brains and money in innovation in android segment\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"positive\"}, {\"author\": \"Suresh Kumar saini\", \"rating\": \"1.0\", \"date\": \"19 May 2025\", \"text\": \"Not working sim card port and not supported charge\n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"neutral\"}, {\"author\": \"KIRAN KUMAR (Raju)\", \"rating\": \"1.0\", \"date\": \"09 Apr 2025\", \"text\": \"बहुत बेकार mobile हे ऑटो switch ओफ़ हो जाता हे or amazon पर सेल के लिए registered hi nahi h nothing service centre wale bolte h वेस्ट ओफ़ मनी.!😂\n  \n  \nRead more\", \"product_id\": \"B0DZTMFWDB\", \"link\": \"https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Motorola Edge 50 Fusion 5G</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D4JNVVHH\", \"product_name\": \"Motorola Edge 50 Fusion 5G (Hot Pink, 12GB RAM, 256GB Storage)\", \"product_url\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 2, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Bharat Shrivastava\", \"rating\": \"5.0\", \"date\": \"27 Jul 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    ⭐⭐⭐⭐⭐ A Stellar Smartphone Experience with the Moto Edge 50 Fusion!I recently purchased the Moto Edge 50 Fusion, and I must say, it has exceeded all my expectations! From the moment I unboxed it, I was impressed by its sleek design and premium build quality. Here’s a breakdown of my experience:Performance: The Moto Edge 50 Fusion delivers top-notch performance, handling multitasking and demanding apps with ease. The processor is incredibly fast, and there’s no noticeable lag even with intensive usage. It’s perfect for both everyday tasks and more demanding applications.Camera: The camera system is nothing short of fantastic. Photos come out crisp and vibrant, with excellent detail and color accuracy. Whether it’s capturing landscapes or close-ups, the Moto Edge 50 Fusion’s camera performs exceptionally well in various lighting conditions. The night mode is particularly impressive, delivering clear and bright photos even in low light.Battery Life: Battery life has been outstanding. I comfortably get through a full day of heavy use without needing a recharge. The battery optimization is top-tier, ensuring that the phone lasts longer between charges.Overall Performance: The Moto Edge 50 Fusion has proven to be a reliable and high-performing device. The user interface is smooth and intuitive, and the phone handles everything I throw at it effortlessly.In summary, the Moto Edge 50 Fusion is a remarkable smartphone that combines great performance, an excellent camera, and impressive battery life. If you’re in the market for a new phone, I highly recommend giving this one a try. It offers exceptional value and a premium experience without breaking the bank.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"B R C.\", \"rating\": \"4.0\", \"date\": \"15 May 2025\", \"text\": \"Nice !\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"30 Dec 2024\", \"text\": \"I was facing issues with network, disturbance in calling &amp; internet speed in my poco X6 5G smartphone since day one! I was literally feeling harassed with these problems during past six months. A 5G phone with a 5G sim, a 5G plan &amp; mobile tower hardly a 50 meters away from my location, It was like a useless decision to buy poco X6! Battery also drained fast due to buffering &amp; searching the network. Swiped the sims with another 5G phones also to get the accurate solution which got positively correct. The ringtone volume also goes zero automatically &amp; I was not able to hear the ringtone only to see several missed calls! Hence I decided to go for Moto edge 50 fusion.. BELIEVE ME friends, all my problems &amp; complaints got solved. Writing this review after 60 days of experience. Also, Moto\'s build quality is excellent, 144Hz curved glass display, vegan leather back finish, weight, minimal blotware, user friendly interface, camera with Sony lenses, future sequrity updates makes this phone- the best flagship brand in this segment. One more thing I want to mention here is that, the phone &amp; its charging accessories have a soothing fragrance which gives you a fresh feel. Vegan leather back finish is just awesome. It gives you a non slippery handling no matter its in your hand or on the dashboard of your car. I didn\'t find any lags during past two months of use with the snapdragon processor. Speed, accuracy and functionality is great if compared with poco X6, redmi, vivo or any other similar samsung galaxy phones. Totally peace of mind purchase I must say. Thanks Motorola for such a beautiful experience &amp; thanks Amazon for the best deal.👍\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Akshara\", \"rating\": \"1.0\", \"date\": \"14 Mar 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Motorola Edge 50 Fusion 5G from Amazon, and unfortunately, on the first day of purchase, the device has a hardware issue—the flash remains on and keeps blinking, with no option to turn it off. I contacted Amazon customer support, followed by Motorola customer support, who confirmed that it is likely a hardware defect and advised me to visit the nearest service center for a replacement.However, upon visiting the Motorola service center, I was informed that they would only repair the device instead of providing a replacement. The repair process would take 5 to 7 days, which is completely unacceptable for a brand-new phone. If a newly purchased device is faulty, it should be replaced, not repaired.Furthermore, when I attempted to return the product via Amazon, I was redirected to customer support, where my return request was denied, despite the 10-day return policy. As a regular customer, I am extremely disappointed with Amazon’s handling of this issue. I do not intend to use a repaired phone when I paid for a brand-new one. This has been one of the worst shopping experiences, and due to such poor service, I will no longer use Amazon for future purchases.I expect a proper resolution, preferably a replacement or a full refund, as per standard consumer rights.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Balamurali\", \"rating\": \"5.0\", \"date\": \"01 Apr 2025\", \"text\": \"I\'ve been using the Motorola Edge 50 for about two weeks now, and I\'m generally impressed, but it\'s not without its flaws. The design is absolutely stunning – the curved display and vegan leather back feel premium and look fantastic. The display itself is vibrant and smooth, perfect for watching videos and browsing.Performance-wise, it handles everyday tasks and moderate gaming with ease. The processor is snappy, and I haven\'t experienced any significant lag. The camera system is decent, producing good photos in daylight, although low-light performance could be better. The software is clean and near-stock Android, which I appreciate. Motorola\'s \'Ready For\' feature is also a nice addition, allowing for desktop-like functionality.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KNP NairKNP Nair\", \"rating\": \"5.0\", \"date\": \"11 Apr 2025\", \"text\": \"Wonderful mobile phone. I like its performance. Battery life is super. Nice looking and elegant.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kindle Customer\", \"rating\": \"3.0\", \"date\": \"20 Apr 2025\", \"text\": \"Good phone, only issue with speaker sometimes it\'s not working and need to restart. Camera is very good. Battery also good .\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Avi\", \"rating\": \"4.0\", \"date\": \"05 Apr 2025\", \"text\": \"Photo quality : Very goodAudio : PerfectProfessor: slow as compared to oneplus\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Bharat Shrivastava\", \"rating\": \"5.0\", \"date\": \"27 Jul 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    ⭐⭐⭐⭐⭐ A Stellar Smartphone Experience with the Moto Edge 50 Fusion!I recently purchased the Moto Edge 50 Fusion, and I must say, it has exceeded all my expectations! From the moment I unboxed it, I was impressed by its sleek design and premium build quality. Here’s a breakdown of my experience:Performance: The Moto Edge 50 Fusion delivers top-notch performance, handling multitasking and demanding apps with ease. The processor is incredibly fast, and there’s no noticeable lag even with intensive usage. It’s perfect for both everyday tasks and more demanding applications.Camera: The camera system is nothing short of fantastic. Photos come out crisp and vibrant, with excellent detail and color accuracy. Whether it’s capturing landscapes or close-ups, the Moto Edge 50 Fusion’s camera performs exceptionally well in various lighting conditions. The night mode is particularly impressive, delivering clear and bright photos even in low light.Battery Life: Battery life has been outstanding. I comfortably get through a full day of heavy use without needing a recharge. The battery optimization is top-tier, ensuring that the phone lasts longer between charges.Overall Performance: The Moto Edge 50 Fusion has proven to be a reliable and high-performing device. The user interface is smooth and intuitive, and the phone handles everything I throw at it effortlessly.In summary, the Moto Edge 50 Fusion is a remarkable smartphone that combines great performance, an excellent camera, and impressive battery life. If you’re in the market for a new phone, I highly recommend giving this one a try. It offers exceptional value and a premium experience without breaking the bank.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"B R C.\", \"rating\": \"4.0\", \"date\": \"15 May 2025\", \"text\": \"Nice !\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"30 Dec 2024\", \"text\": \"I was facing issues with network, disturbance in calling &amp; internet speed in my poco X6 5G smartphone since day one! I was literally feeling harassed with these problems during past six months. A 5G phone with a 5G sim, a 5G plan &amp; mobile tower hardly a 50 meters away from my location, It was like a useless decision to buy poco X6! Battery also drained fast due to buffering &amp; searching the network. Swiped the sims with another 5G phones also to get the accurate solution which got positively correct. The ringtone volume also goes zero automatically &amp; I was not able to hear the ringtone only to see several missed calls! Hence I decided to go for Moto edge 50 fusion.. BELIEVE ME friends, all my problems &amp; complaints got solved. Writing this review after 60 days of experience. Also, Moto\'s build quality is excellent, 144Hz curved glass display, vegan leather back finish, weight, minimal blotware, user friendly interface, camera with Sony lenses, future sequrity updates makes this phone- the best flagship brand in this segment. One more thing I want to mention here is that, the phone &amp; its charging accessories have a soothing fragrance which gives you a fresh feel. Vegan leather back finish is just awesome. It gives you a non slippery handling no matter its in your hand or on the dashboard of your car. I didn\'t find any lags during past two months of use with the snapdragon processor. Speed, accuracy and functionality is great if compared with poco X6, redmi, vivo or any other similar samsung galaxy phones. Totally peace of mind purchase I must say. Thanks Motorola for such a beautiful experience &amp; thanks Amazon for the best deal.👍\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Akshara\", \"rating\": \"1.0\", \"date\": \"14 Mar 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Motorola Edge 50 Fusion 5G from Amazon, and unfortunately, on the first day of purchase, the device has a hardware issue—the flash remains on and keeps blinking, with no option to turn it off. I contacted Amazon customer support, followed by Motorola customer support, who confirmed that it is likely a hardware defect and advised me to visit the nearest service center for a replacement.However, upon visiting the Motorola service center, I was informed that they would only repair the device instead of providing a replacement. The repair process would take 5 to 7 days, which is completely unacceptable for a brand-new phone. If a newly purchased device is faulty, it should be replaced, not repaired.Furthermore, when I attempted to return the product via Amazon, I was redirected to customer support, where my return request was denied, despite the 10-day return policy. As a regular customer, I am extremely disappointed with Amazon’s handling of this issue. I do not intend to use a repaired phone when I paid for a brand-new one. This has been one of the worst shopping experiences, and due to such poor service, I will no longer use Amazon for future purchases.I expect a proper resolution, preferably a replacement or a full refund, as per standard consumer rights.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Balamurali\", \"rating\": \"5.0\", \"date\": \"01 Apr 2025\", \"text\": \"I\'ve been using the Motorola Edge 50 for about two weeks now, and I\'m generally impressed, but it\'s not without its flaws. The design is absolutely stunning – the curved display and vegan leather back feel premium and look fantastic. The display itself is vibrant and smooth, perfect for watching videos and browsing.Performance-wise, it handles everyday tasks and moderate gaming with ease. The processor is snappy, and I haven\'t experienced any significant lag. The camera system is decent, producing good photos in daylight, although low-light performance could be better. The software is clean and near-stock Android, which I appreciate. Motorola\'s \'Ready For\' feature is also a nice addition, allowing for desktop-like functionality.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KNP NairKNP Nair\", \"rating\": \"5.0\", \"date\": \"11 Apr 2025\", \"text\": \"Wonderful mobile phone. I like its performance. Battery life is super. Nice looking and elegant.\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kindle Customer\", \"rating\": \"3.0\", \"date\": \"20 Apr 2025\", \"text\": \"Good phone, only issue with speaker sometimes it\'s not working and need to restart. Camera is very good. Battery also good .\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Avi\", \"rating\": \"4.0\", \"date\": \"05 Apr 2025\", \"text\": \"Photo quality : Very goodAudio : PerfectProfessor: slow as compared to oneplus\n  \nRead more\", \"product_id\": \"B0D4JNVVHH\", \"link\": \"https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>realme GT 6T 5G</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D3J8HYDD\", \"product_name\": \"realme GT 6T 5G (Fluid Silver,12GB RAM+256GB Storage) | India\'s 1st 7+ Gen 3 Flagship Chipset | 1.5M + AnTuTu Score | 5500mAh+120W | The World\'s Brightest Flagship Display\", \"product_url\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"appuflee\", \"rating\": \"5.0\", \"date\": \"24 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent phoneGood battery backupNo lagsThere was heating issue while initially installing the apps, once it was updated to android 15, no heating at all.Camera does the jobEdge screen is awesomeWe need to use a case for sure, as the back is glossy, fingerprints easily destroy the look.Overall it\'s a killer for this budget.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ishan mahajan\", \"rating\": \"4.0\", \"date\": \"28 Sep 2024\", \"text\": \"I was using Samsung M51 from past 4 years and was looking for a new phone in 25-30k budget, couldn\'t find any Samsung phone in this budget which had better specifications than my ongoing M51.I started looking for another brands, since i naver used any other brand than Samsung i was bit hesitant in using RealMe, just took feedback from a friend who was using RealMe from last 4 years and purchased GT 6T.I am a normal user, not a gaming or photography guy. So far experience of using GT 6T has been good, not very great but good enough.Display of phone is very good feels better than my M51 which also have AMOLED, sound is very good, haptic feedback is good not like OnePlus but just upto the mark.Camera is ok. More or less similar to M51 there are multiple features but not used any of them till now.Issues I observed1. I was Not able to take calls when it is connected to car via bluetooth or Android auto, though it shows that sound is playing via car Audio but there was not sound, inhad to change something settings in USB debugging and it is working fine now.2. I was playing music via Amazon music and then started YouTube, YouTube video started but phone was still playing music from Amazon music instead of YouTube.This got fixed on its own.Phone never hanged, never falled off my hands so not sure about durability, i have not applied any screen guard since it has victus glass. m51 had just gorrila glass and it survived multiple falls in last 4 year hoping same for this phone.Battery backup is good for my usage, M51 had 7000 mah battery this one had 5500 but charging speed is very good. Even if it can hold 80 % battery capacity by next year i would be happy since it takes just 30 mins to charge to 100% by supplied charger.I will update this thread with time. This was my feedback of using this phone in last two weeks.Update 10-oct-2024I observed that phone does not ring some times and i directly get miss call notification, observed it 3 times in 20 days. No other issue till date.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shyamal BhattacharjeeShyamal Bhattacharjee\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"\\"I\'ve been using the Realme GT 6T for almost a week now, and I\'m thoroughly impressed. The performance is top-notch - I can play BGMI on 90fps with Ultra HDR and Ultra FPS without any issues. CarX Street runs smoothly on max graphics at 50fps, and Delta Force Mobile is solid on ultimate graphics at 40fps. Fortnite is buttery smooth at 80fps on low graphics. Thanks to Snapdragon 7+ Gen 3 , UFS 4.0 storage and LPDDR5X ram.The camera is another highlight - it captures amazing photos, even in low light. I love the Street mode feature, and 4K video recording at 60fps is a bonus. The Pro mode is also really good, giving me more control over my shots and the color profiles are nice too.The Curve display is simply impressive, with vibrant colors and great brightness. The phone also comes with an IR blaster, which is super convenient for controlling my TV and AC.The audio experience is immersive thanks to spatial sound, which makes gaming and watching videos even more engaging.The 120W SUPERVOC charging is blazing fast. The battery is good as well.The phone itself has a impressive design.Here are some pictures that I took with my phone.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Basudev GoraiBasudev Gorai\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"Really great phone under this price, chargeing super fast, battry long lasting, performance after realme ui 6 just extraordinaryDslr mode is great of this camera but quality and color is decent\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"20 Aug 2024\", \"text\": \"This is post 3 days of using of phone and simply couldn\'t resist myself from writing this review. Got the Razor Green 12 GB 512 GB for 32K post Bank discount. Adding some context before diving into my experience. I was an S22 Ultra user and ditched the same for OnePlus 12 SD8G3. I wanted an add on phone for office use and for gaming (BGMI &amp; MKX). Got this one post going through round of comparisons against IQOOs out there. Not I just had one sim in the phone as I was using it. So coming straight to how I rate this phone. It is a 5/5 for me.Looks: 4/5 ✌️✌️✌️✌️Display: 5/5 🤩🤩🤩🤩🤩Touch Response: 5/5 🧈🧈🧈🧈🧈Performance: 5/5 ✨✨✨✨✨Gaming performance: 5/5 👍👍👍👍👍Speaker Output: 5/5 ( very decent)Battery: 10/5 ( Simply marvellous)Charging speed: 15/5 (no comments)Camera: 4/5 (boosted this up from 3 to 4 based off overall happiness with the phone and considering the price factor)OS: 4/5 (-1 because of few preloaded apps)Finger print scanner: 5/5So what I loved: Display and performance crisp and buttery smooth. OS is clean too to the most. SD7+G3 takes on any tasks thrown on it with ease. No hassles in multitasking. Got July security patch as of yesterday so all good on that front too. Now speaking about what I\'m in love with - Being an S22 Ultra user I must say the biggest pain point has been battery since day 1. Max gaming time 3.5 Hrs. in the initial days which reduced to 1.5 over a span of 2 years. Stand-by was crazy bad too on S22 Ultra. This Lil gizmo GT 6T is a dream in this case. 3 days of game play BGMI 5 Hrs. each day and was left with 22% of juice still remaining each time. And post sleep of 6 hrs. the phone still retained 17% of charge. This already is insane in my perspective.Now coming to the charging aspect, this is unimaginable. Lightning fast... 17% - 100% in 22 minutes. Speechless in this front. Sammy used to take like 1 hr and 10 mins. in the initial days and post an year and half I really don\'t know. Gaming done without gtmode. Frame rate was set to auto adaptive. BGMI played in Smooth Extreme+. Brightness at ~45%. No throttling or heating. It got slightly warm at a point (really no where close to be called as heating) and then cooled too which is 😍😍😍.WhatsApp, FB, Insta, Gmail, O365, Teams and all other apps on the background. So you can go for this one blindfolded if you are looking for a phone with great backup and performance (gaming performance). I hope this is helpful.What I didn\'t like: Given all of above a 3.5 mm slot was expected. And sound output in headphones could have been better. I used Sony WH1000XM3 for gaming and Wf1000XM4 for listening to music and watching movie to test the output. Again you can hear all the footsteps and minute details and same applies to music if not all details but covers 90% of it but somewhere lacks the loudness factor by a bit and no Dolby Atmos so less to mention there.Lastly, I didn\'t cover anything on cam perspective because I was really not looking at this phone from that aspect and me sharing my experience on that front will definitely make no sense as the comparison will be against S22 Ultra here and this reaches no where close to it which is completely fine given it is not even 1/4th of the price for which I had bought S22 Ultra. That said both front and rear cam are decent is all I can say from price point perspective.Overall this is a bang on deal from my perspective and would definitely recommend going for it if you are not cam centric and looking for a great performer!\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"appuflee\", \"rating\": \"5.0\", \"date\": \"24 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent phoneGood battery backupNo lagsThere was heating issue while initially installing the apps, once it was updated to android 15, no heating at all.Camera does the jobEdge screen is awesomeWe need to use a case for sure, as the back is glossy, fingerprints easily destroy the look.Overall it\'s a killer for this budget.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ishan mahajan\", \"rating\": \"4.0\", \"date\": \"28 Sep 2024\", \"text\": \"I was using Samsung M51 from past 4 years and was looking for a new phone in 25-30k budget, couldn\'t find any Samsung phone in this budget which had better specifications than my ongoing M51.I started looking for another brands, since i naver used any other brand than Samsung i was bit hesitant in using RealMe, just took feedback from a friend who was using RealMe from last 4 years and purchased GT 6T.I am a normal user, not a gaming or photography guy. So far experience of using GT 6T has been good, not very great but good enough.Display of phone is very good feels better than my M51 which also have AMOLED, sound is very good, haptic feedback is good not like OnePlus but just upto the mark.Camera is ok. More or less similar to M51 there are multiple features but not used any of them till now.Issues I observed1. I was Not able to take calls when it is connected to car via bluetooth or Android auto, though it shows that sound is playing via car Audio but there was not sound, inhad to change something settings in USB debugging and it is working fine now.2. I was playing music via Amazon music and then started YouTube, YouTube video started but phone was still playing music from Amazon music instead of YouTube.This got fixed on its own.Phone never hanged, never falled off my hands so not sure about durability, i have not applied any screen guard since it has victus glass. m51 had just gorrila glass and it survived multiple falls in last 4 year hoping same for this phone.Battery backup is good for my usage, M51 had 7000 mah battery this one had 5500 but charging speed is very good. Even if it can hold 80 % battery capacity by next year i would be happy since it takes just 30 mins to charge to 100% by supplied charger.I will update this thread with time. This was my feedback of using this phone in last two weeks.Update 10-oct-2024I observed that phone does not ring some times and i directly get miss call notification, observed it 3 times in 20 days. No other issue till date.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shyamal BhattacharjeeShyamal Bhattacharjee\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"\\"I\'ve been using the Realme GT 6T for almost a week now, and I\'m thoroughly impressed. The performance is top-notch - I can play BGMI on 90fps with Ultra HDR and Ultra FPS without any issues. CarX Street runs smoothly on max graphics at 50fps, and Delta Force Mobile is solid on ultimate graphics at 40fps. Fortnite is buttery smooth at 80fps on low graphics. Thanks to Snapdragon 7+ Gen 3 , UFS 4.0 storage and LPDDR5X ram.The camera is another highlight - it captures amazing photos, even in low light. I love the Street mode feature, and 4K video recording at 60fps is a bonus. The Pro mode is also really good, giving me more control over my shots and the color profiles are nice too.The Curve display is simply impressive, with vibrant colors and great brightness. The phone also comes with an IR blaster, which is super convenient for controlling my TV and AC.The audio experience is immersive thanks to spatial sound, which makes gaming and watching videos even more engaging.The 120W SUPERVOC charging is blazing fast. The battery is good as well.The phone itself has a impressive design.Here are some pictures that I took with my phone.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Basudev GoraiBasudev Gorai\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"Really great phone under this price, chargeing super fast, battry long lasting, performance after realme ui 6 just extraordinaryDslr mode is great of this camera but quality and color is decent\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"20 Aug 2024\", \"text\": \"This is post 3 days of using of phone and simply couldn\'t resist myself from writing this review. Got the Razor Green 12 GB 512 GB for 32K post Bank discount. Adding some context before diving into my experience. I was an S22 Ultra user and ditched the same for OnePlus 12 SD8G3. I wanted an add on phone for office use and for gaming (BGMI &amp; MKX). Got this one post going through round of comparisons against IQOOs out there. Not I just had one sim in the phone as I was using it. So coming straight to how I rate this phone. It is a 5/5 for me.Looks: 4/5 ✌️✌️✌️✌️Display: 5/5 🤩🤩🤩🤩🤩Touch Response: 5/5 🧈🧈🧈🧈🧈Performance: 5/5 ✨✨✨✨✨Gaming performance: 5/5 👍👍👍👍👍Speaker Output: 5/5 ( very decent)Battery: 10/5 ( Simply marvellous)Charging speed: 15/5 (no comments)Camera: 4/5 (boosted this up from 3 to 4 based off overall happiness with the phone and considering the price factor)OS: 4/5 (-1 because of few preloaded apps)Finger print scanner: 5/5So what I loved: Display and performance crisp and buttery smooth. OS is clean too to the most. SD7+G3 takes on any tasks thrown on it with ease. No hassles in multitasking. Got July security patch as of yesterday so all good on that front too. Now speaking about what I\'m in love with - Being an S22 Ultra user I must say the biggest pain point has been battery since day 1. Max gaming time 3.5 Hrs. in the initial days which reduced to 1.5 over a span of 2 years. Stand-by was crazy bad too on S22 Ultra. This Lil gizmo GT 6T is a dream in this case. 3 days of game play BGMI 5 Hrs. each day and was left with 22% of juice still remaining each time. And post sleep of 6 hrs. the phone still retained 17% of charge. This already is insane in my perspective.Now coming to the charging aspect, this is unimaginable. Lightning fast... 17% - 100% in 22 minutes. Speechless in this front. Sammy used to take like 1 hr and 10 mins. in the initial days and post an year and half I really don\'t know. Gaming done without gtmode. Frame rate was set to auto adaptive. BGMI played in Smooth Extreme+. Brightness at ~45%. No throttling or heating. It got slightly warm at a point (really no where close to be called as heating) and then cooled too which is 😍😍😍.WhatsApp, FB, Insta, Gmail, O365, Teams and all other apps on the background. So you can go for this one blindfolded if you are looking for a phone with great backup and performance (gaming performance). I hope this is helpful.What I didn\'t like: Given all of above a 3.5 mm slot was expected. And sound output in headphones could have been better. I used Sony WH1000XM3 for gaming and Wf1000XM4 for listening to music and watching movie to test the output. Again you can hear all the footsteps and minute details and same applies to music if not all details but covers 90% of it but somewhere lacks the loudness factor by a bit and no Dolby Atmos so less to mention there.Lastly, I didn\'t cover anything on cam perspective because I was really not looking at this phone from that aspect and me sharing my experience on that front will definitely make no sense as the comparison will be against S22 Ultra here and this reaches no where close to it which is completely fine given it is not even 1/4th of the price for which I had bought S22 Ultra. That said both front and rear cam are decent is all I can say from price point perspective.Overall this is a bang on deal from my perspective and would definitely recommend going for it if you are not cam centric and looking for a great performer!\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OnePlus Nord 4 5G </t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D7VGZS69\", \"product_name\": \"OnePlus Nord 4 5G (Oasis Green, 8GB RAM, 256GB Storage) | Lifetime Display Warranty | Qualcomm® Snapdragon™ 7 Plus Gen 3 | ANTUTU Score 1.5Mn AI\", \"product_url\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Savitha K C\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Using it for 4 months now. It\'s been almost a year since it\'s launch and it is still a good buy. Decent cameras, cameras is not it\'s strength, in the same price range you get other phones for better cameras. Battery, fast charging, UI UX , Software, Display, build quality, performance are all really good. It is the best all rounder phone to buy under 25k. Highly recommend it. I was considering to buy 13R for 40k but I feel Nord 4 is better value for money.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pragyesh pandeyPragyesh pandey\", \"rating\": \"4.0\", \"date\": \"11 May 2025\", \"text\": \"Now let me share review of this phone. After using the phone for almost a week, I find the phone good as per the price. I bought it for 24999 by using available discount through HDFC card. Now charging is not too fast, but it\'s fine as it\'s charging the phone in 40 mins from 20 to 100 percent. Battery backup is ok ok as it\'s lasting for less than a day with moderate use. Camera is fine and good as per price. Performancewise it\'s good phone as the use is smooth and the display is rich. The looks are premium but once u place back cover, it\'s not looking an elite one. Over all a value buy for those who uses the phone moderately. For heavy using, i would say ..better phone\'s are available in same price range.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KalimKalim\", \"rating\": \"5.0\", \"date\": \"23 Mar 2025\", \"text\": \"I\'ve been using the OnePlus Nord 4 for about 2 weeks and I can say this phone is a great but for this pricePros: Almost everything,1. The display is gorgeous but it is not dynamic, meaning it stays at 120Hz all the time even when set to auto2. The battery life is also really damn good, coming from an iPhone X, this is great and 100W in the box charger charges it while a small break,3. Build quality is top notch, I like the metal back but the looks is bad, I suggested a family member this phone but it looks so bad, it was dismissed but for me it is alright (side note: you get a transparent TPU case and not a high quality one which funnily enough you get in the CE 4)Performance is great too, 7+ gen 3 is one of the better choiceCons:Camera: while main camera is ok, selfie and ultrawide are preety midVideo: only the main camera can do 4K 60FPS, other cameras are capped at 1080p 30FPS. So while you can record in 4K, you cannot change perspectives.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Harihara Mallar SV\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"Been using this phone for 2 days now. The first thing that stood out is how light it feels in the hand, the build quality is sleek and solid, almost mimicking an iPhone-level finish. It has a premium touch without the premium price.Performance-wise, it’s smooth and responsive. Apps open quickly, multitasking is a breeze, and there’s been no lag so far. The 8GB RAM with 256GB storage is more than enough for my daily use — whether it\'s gaming, streaming, or work. The indisplay Fingerprint sensor is so fast and soo cool.The screen size is perfect. Not too big, not too small, just right for comfortable viewing, typing, and media consumption. Colors are good, and brightness is on point, even outdoors.Obsidian Black looks stunning, clean, classy, and minimal. Overall, for the price point, the OnePlus Nord 4 is delivering way more than expected.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"YaduYadu\", \"rating\": \"5.0\", \"date\": \"21 Nov 2024\", \"text\": \"I am writing this review after 1 month of using the Oneplus Nord 4. It is one of the best midrange phone that you can blindly buy without any confusion. I bought this phone during Great Indian festival after so much research and doubts. I was not sure which phone will be the best in 30000 segment. I was looking for a balanced phone which has everything like good performance, good design, good battery and good camera. I don\'t want to compromise in any one thing. So after lot of research i was having confusion between nord 4 and realme gt 6t. But in realme gt 6t the display is curved which i don\'t prefer at all. Curved display is waste of money and feels like gimmick so i avoided it and bought nord 4. Now i feel it was the best decision.Best features of this Nord 4 are-Design - I literally loved the mercurian silver metel design which looks so much premium. I thought metel might be heavier but in daily use its not a problem at all. It cools down so fast and does not have any heating issues at all.Performance - It has the best performance and able to play BGMI so smoothly. Flat screen helps so much in games also.Battery -  If you use normally the battery will last more than 1 day easily and it charges the phone within 25mins.Camera - I felt the main camera is so good and it takes very decent photos. 50mp camera performs above average. If camera is your main priority then its better to go for realme, vivo, Samsung or Iphone which are camera centric. But then other areas you have to compromise. Trust me below 30k this phone takes very good photos.Network - Being a metel phone i am getting 5g network always without any problem. Never felt any Issues at all.Display - It has best display and content viewing experience is top notch with minimum bezzels.This review is genuine and trust me if you want a balanced midrange phone you can go for Oneplus Nord 4 for sure. Greenline is coming in all the brands so no need to get back from this phone because of this reason....(If any problems comes in future then i will update the review for sure)\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Savitha K C\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Using it for 4 months now. It\'s been almost a year since it\'s launch and it is still a good buy. Decent cameras, cameras is not it\'s strength, in the same price range you get other phones for better cameras. Battery, fast charging, UI UX , Software, Display, build quality, performance are all really good. It is the best all rounder phone to buy under 25k. Highly recommend it. I was considering to buy 13R for 40k but I feel Nord 4 is better value for money.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pragyesh pandeyPragyesh pandey\", \"rating\": \"4.0\", \"date\": \"11 May 2025\", \"text\": \"Now let me share review of this phone. After using the phone for almost a week, I find the phone good as per the price. I bought it for 24999 by using available discount through HDFC card. Now charging is not too fast, but it\'s fine as it\'s charging the phone in 40 mins from 20 to 100 percent. Battery backup is ok ok as it\'s lasting for less than a day with moderate use. Camera is fine and good as per price. Performancewise it\'s good phone as the use is smooth and the display is rich. The looks are premium but once u place back cover, it\'s not looking an elite one. Over all a value buy for those who uses the phone moderately. For heavy using, i would say ..better phone\'s are available in same price range.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KalimKalim\", \"rating\": \"5.0\", \"date\": \"23 Mar 2025\", \"text\": \"I\'ve been using the OnePlus Nord 4 for about 2 weeks and I can say this phone is a great but for this pricePros: Almost everything,1. The display is gorgeous but it is not dynamic, meaning it stays at 120Hz all the time even when set to auto2. The battery life is also really damn good, coming from an iPhone X, this is great and 100W in the box charger charges it while a small break,3. Build quality is top notch, I like the metal back but the looks is bad, I suggested a family member this phone but it looks so bad, it was dismissed but for me it is alright (side note: you get a transparent TPU case and not a high quality one which funnily enough you get in the CE 4)Performance is great too, 7+ gen 3 is one of the better choiceCons:Camera: while main camera is ok, selfie and ultrawide are preety midVideo: only the main camera can do 4K 60FPS, other cameras are capped at 1080p 30FPS. So while you can record in 4K, you cannot change perspectives.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Harihara Mallar SV\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"Been using this phone for 2 days now. The first thing that stood out is how light it feels in the hand, the build quality is sleek and solid, almost mimicking an iPhone-level finish. It has a premium touch without the premium price.Performance-wise, it’s smooth and responsive. Apps open quickly, multitasking is a breeze, and there’s been no lag so far. The 8GB RAM with 256GB storage is more than enough for my daily use — whether it\'s gaming, streaming, or work. The indisplay Fingerprint sensor is so fast and soo cool.The screen size is perfect. Not too big, not too small, just right for comfortable viewing, typing, and media consumption. Colors are good, and brightness is on point, even outdoors.Obsidian Black looks stunning, clean, classy, and minimal. Overall, for the price point, the OnePlus Nord 4 is delivering way more than expected.\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"YaduYadu\", \"rating\": \"5.0\", \"date\": \"21 Nov 2024\", \"text\": \"I am writing this review after 1 month of using the Oneplus Nord 4. It is one of the best midrange phone that you can blindly buy without any confusion. I bought this phone during Great Indian festival after so much research and doubts. I was not sure which phone will be the best in 30000 segment. I was looking for a balanced phone which has everything like good performance, good design, good battery and good camera. I don\'t want to compromise in any one thing. So after lot of research i was having confusion between nord 4 and realme gt 6t. But in realme gt 6t the display is curved which i don\'t prefer at all. Curved display is waste of money and feels like gimmick so i avoided it and bought nord 4. Now i feel it was the best decision.Best features of this Nord 4 are-Design - I literally loved the mercurian silver metel design which looks so much premium. I thought metel might be heavier but in daily use its not a problem at all. It cools down so fast and does not have any heating issues at all.Performance - It has the best performance and able to play BGMI so smoothly. Flat screen helps so much in games also.Battery -  If you use normally the battery will last more than 1 day easily and it charges the phone within 25mins.Camera - I felt the main camera is so good and it takes very decent photos. 50mp camera performs above average. If camera is your main priority then its better to go for realme, vivo, Samsung or Iphone which are camera centric. But then other areas you have to compromise. Trust me below 30k this phone takes very good photos.Network - Being a metel phone i am getting 5g network always without any problem. Never felt any Issues at all.Display - It has best display and content viewing experience is top notch with minimum bezzels.This review is genuine and trust me if you want a balanced midrange phone you can go for Oneplus Nord 4 for sure. Greenline is coming in all the brands so no need to get back from this phone because of this reason....(If any problems comes in future then i will update the review for sure)\n  \nRead more\", \"product_id\": \"B0D7VGZS69\", \"link\": \"https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tecno Phantom V Fold 2</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>71.43%</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>14</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"product_name\": \"Tecno Phantom V Fold 2 (Rippling Blue, 12GB+512GB) | Strongest Fold Ever | Largest Battery in Fold Segment-5750mAh | Segment Largest Display | Rear - Triple 50MP Camera with OIS | 70W Fast Charger\", \"product_url\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"summary\": {\"total_reviews\": 14, \"average_rating\": 3.29, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 71.43}, \"reviews\": [{\"author\": \"Rudraprakash\", \"rating\": \"5.0\", \"date\": \"25 Dec 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Phantom V Fold 2 is a powerhouse device with a stunning 7.85\\" foldable display.Its sleek design and robust hinge make it a joy to use.With a long-lasting 5000mAh battery and fast charging, you\'ll stay powered up all day.The device also boasts impressive cameras and seamless performance. Looks, feels designed amazing complete packsge of a premium phone,No such a fold phone in maket now like Tecno v fold.  Overall, the Phantom V Fold 2 is a top-notch choice for those seeking a premium foldable smartphone.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"S P.\", \"rating\": \"1.0\", \"date\": \"24 Feb 2025\", \"text\": \"Bought this phone on 31st dec. Got a dead pixel on 18th Jan. Phone was replaced by 1stFeb. Today is 24th Feb, the phone doesn\'t unfold. The phone is great but it\'s not worth risking a lakh of rupees. Every month one can\'t spend 15 days in customer care. So it\'s not worth it unless build quality is proven.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kuldeep Gupta.\", \"rating\": \"5.0\", \"date\": \"15 Dec 2024\", \"text\": \"- *Multitasking Master*: The phone\'s large inner display and intuitive UI make multitasking a breeze. You can easily run multiple apps side-by-side, and the phone\'s powerful processor ensures smooth performance ¹.- *Camera Capabilities*: The Phantom V Fold 2\'s main camera takes excellent photos, and the phone\'s AI-powered features, such as object eraser and AI-generated artwork, are impressive ¹.- *Battery Life*: With a massive 5750mAh battery, the phone can last for days on a single charge. Plus, the 70W fast charging feature ensures you can quickly top up your battery ¹.- *Affordability*: The Phantom V Fold 2 is significantly cheaper than other large foldable phones on the market, making it an attractive option for those looking for a premium experience without the hefty price tag ¹.- *Great In-Hand Feel*: Reviewers have praised the phone\'s design, saying it feels great in the hand, with plenty of grip ².- *Well-Optimized Software*: The phone\'s software is well-optimized, looks nice, and provides a seamless user experience ².Overall, the TECNO Phantom V Fold 2 seems like an excellent choice for anyone looking for a powerful, feature-packed, and affordable large foldable phone\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"GNG\", \"rating\": \"1.0\", \"date\": \"03 Jan 2025\", \"text\": \"I never though I would give 1 star to this phone.. As I was literally waiting for this phone to be released. I\'ve already used tecno phantom fold first version.. I was so impressed with that phone that even though it\'s display went dead suddenly after 1 year of purchase, I still decided to buy this fold 2 considering how good fold 1 was.. That was my big mistake.. Since the day of purchase, I.e ,20th Dec 2024,the hinge seemed somewhat tight... Unlike fold 1 which was so easy to open.. I thought may be because it\'s a new one.. It\'s tighter.. And I hardly unfolded the phone these past few days as I was very busy with my work.. Yesterday I was trying to unfold it as wanted to use 2 screens.. It was tighter.. I gave a but more pressure and suddenly heard a Crack sound and flickering of display of mainscreen.. I was immediately reminded of the sudden dead screen of my first tecno fold one.. That one lasted atleast 1 Yr.. This one hardly lasted 15 days.. I tool it to nearby carlcare Centre.. That guy was saying you should have escalated this hinge problem immediately before the screen broke.i don\'t know if I can do anything now. Or you have to pay 56000 rs for main screen replacement.Imagine the pain when a device which you bought with so much anticipation at a price of 80k.. Again costing 56k for repair..Hope the tecno team will sort this out without me spending huge money from my pocket. If I have to pay 56k for it.. I would rather keep it aside and buy some other phone..Amazon has accepted to take the product back and issue refund.. I have returned the product but after few days Amazon was denting refund saying that wrong item was sent.. When I\'ve contacted them, they told me product received was same but their is mismatch in some serial number..when I have asked them to show proof they are not showing. And moreover they are refusing to return the product back. The pickup boy has confirmed everything during pick up.. Worst customer service by Amazon.. They are not issuing refund and also not returning the phone back.. Pathetic service from Amazon. I have bought atleast 15 mobiles from Amazon and shop atleast 15k to 20k every month from Amazon.. Yet their customer service is worst..\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Raghunath N Rao\", \"rating\": \"5.0\", \"date\": \"21 Dec 2024\", \"text\": \"I recently purchased the TECNO Phantom V Fold 2 in Rippling Blue, and I must say, it\'s an impressive device that delivers on most of its promises. Here\'s my experience1. Build Quality: The phone feels sturdy, and the hinge mechanism is smooth. TECNO\'s \\"strongest fold ever\\" claim seems justified so far.2. Battery: The massive 5750mAh battery is a game-changer! I easily get a full day of use, even with heavy multitasking and media consumption.3. Display: The large, vibrant display is perfect for watching videos and multitasking. It’s a joy to use in unfolded mode.4. Camera: The triple 50MP camera setup delivers excellent photos, especially in good lighting. OIS helps stabilize videos, which is great for content creation.5. Performance: The 12GB RAM ensures smooth performance, and 512GB of storage is more than enough for apps,  photos and files\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jatinder karir\", \"rating\": \"1.0\", \"date\": \"22 Apr 2025\", \"text\": \"Don\'t Buy....After just four months, the internal screen broke even though I hadn\'t unfolded the phone for several days. When I attempted to open it, the screen was already damaged. Upon consulting the service agent, I was informed that such problems are quite common with this model, and the screen replacement would cost  of 48,000 rupees. Also, the agent showed me another phone with a similar issue as mine.Given these experiences, I would not recommend buying flip or fold phones, as they seem to be prone to issues and require costly maintenance.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Pravin K.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Strong in built quality.Almost no crease on display.Display fold does not stop at places in between.Fast processor for normal office use.Display quality is excellent.Sound is comparably low.Looks premium.Feels tough.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rudraprakash\", \"rating\": \"5.0\", \"date\": \"25 Dec 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Phantom V Fold 2 is a powerhouse device with a stunning 7.85\\" foldable display.Its sleek design and robust hinge make it a joy to use.With a long-lasting 5000mAh battery and fast charging, you\'ll stay powered up all day.The device also boasts impressive cameras and seamless performance. Looks, feels designed amazing complete packsge of a premium phone,No such a fold phone in maket now like Tecno v fold.  Overall, the Phantom V Fold 2 is a top-notch choice for those seeking a premium foldable smartphone.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"S P.\", \"rating\": \"1.0\", \"date\": \"24 Feb 2025\", \"text\": \"Bought this phone on 31st dec. Got a dead pixel on 18th Jan. Phone was replaced by 1stFeb. Today is 24th Feb, the phone doesn\'t unfold. The phone is great but it\'s not worth risking a lakh of rupees. Every month one can\'t spend 15 days in customer care. So it\'s not worth it unless build quality is proven.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kuldeep Gupta.\", \"rating\": \"5.0\", \"date\": \"15 Dec 2024\", \"text\": \"- *Multitasking Master*: The phone\'s large inner display and intuitive UI make multitasking a breeze. You can easily run multiple apps side-by-side, and the phone\'s powerful processor ensures smooth performance ¹.- *Camera Capabilities*: The Phantom V Fold 2\'s main camera takes excellent photos, and the phone\'s AI-powered features, such as object eraser and AI-generated artwork, are impressive ¹.- *Battery Life*: With a massive 5750mAh battery, the phone can last for days on a single charge. Plus, the 70W fast charging feature ensures you can quickly top up your battery ¹.- *Affordability*: The Phantom V Fold 2 is significantly cheaper than other large foldable phones on the market, making it an attractive option for those looking for a premium experience without the hefty price tag ¹.- *Great In-Hand Feel*: Reviewers have praised the phone\'s design, saying it feels great in the hand, with plenty of grip ².- *Well-Optimized Software*: The phone\'s software is well-optimized, looks nice, and provides a seamless user experience ².Overall, the TECNO Phantom V Fold 2 seems like an excellent choice for anyone looking for a powerful, feature-packed, and affordable large foldable phone\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"GNG\", \"rating\": \"1.0\", \"date\": \"03 Jan 2025\", \"text\": \"I never though I would give 1 star to this phone.. As I was literally waiting for this phone to be released. I\'ve already used tecno phantom fold first version.. I was so impressed with that phone that even though it\'s display went dead suddenly after 1 year of purchase, I still decided to buy this fold 2 considering how good fold 1 was.. That was my big mistake.. Since the day of purchase, I.e ,20th Dec 2024,the hinge seemed somewhat tight... Unlike fold 1 which was so easy to open.. I thought may be because it\'s a new one.. It\'s tighter.. And I hardly unfolded the phone these past few days as I was very busy with my work.. Yesterday I was trying to unfold it as wanted to use 2 screens.. It was tighter.. I gave a but more pressure and suddenly heard a Crack sound and flickering of display of mainscreen.. I was immediately reminded of the sudden dead screen of my first tecno fold one.. That one lasted atleast 1 Yr.. This one hardly lasted 15 days.. I tool it to nearby carlcare Centre.. That guy was saying you should have escalated this hinge problem immediately before the screen broke.i don\'t know if I can do anything now. Or you have to pay 56000 rs for main screen replacement.Imagine the pain when a device which you bought with so much anticipation at a price of 80k.. Again costing 56k for repair..Hope the tecno team will sort this out without me spending huge money from my pocket. If I have to pay 56k for it.. I would rather keep it aside and buy some other phone..Amazon has accepted to take the product back and issue refund.. I have returned the product but after few days Amazon was denting refund saying that wrong item was sent.. When I\'ve contacted them, they told me product received was same but their is mismatch in some serial number..when I have asked them to show proof they are not showing. And moreover they are refusing to return the product back. The pickup boy has confirmed everything during pick up.. Worst customer service by Amazon.. They are not issuing refund and also not returning the phone back.. Pathetic service from Amazon. I have bought atleast 15 mobiles from Amazon and shop atleast 15k to 20k every month from Amazon.. Yet their customer service is worst..\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Raghunath N Rao\", \"rating\": \"5.0\", \"date\": \"21 Dec 2024\", \"text\": \"I recently purchased the TECNO Phantom V Fold 2 in Rippling Blue, and I must say, it\'s an impressive device that delivers on most of its promises. Here\'s my experience1. Build Quality: The phone feels sturdy, and the hinge mechanism is smooth. TECNO\'s \\"strongest fold ever\\" claim seems justified so far.2. Battery: The massive 5750mAh battery is a game-changer! I easily get a full day of use, even with heavy multitasking and media consumption.3. Display: The large, vibrant display is perfect for watching videos and multitasking. It’s a joy to use in unfolded mode.4. Camera: The triple 50MP camera setup delivers excellent photos, especially in good lighting. OIS helps stabilize videos, which is great for content creation.5. Performance: The 12GB RAM ensures smooth performance, and 512GB of storage is more than enough for apps,  photos and files\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jatinder karir\", \"rating\": \"1.0\", \"date\": \"22 Apr 2025\", \"text\": \"Don\'t Buy....After just four months, the internal screen broke even though I hadn\'t unfolded the phone for several days. When I attempted to open it, the screen was already damaged. Upon consulting the service agent, I was informed that such problems are quite common with this model, and the screen replacement would cost  of 48,000 rupees. Also, the agent showed me another phone with a similar issue as mine.Given these experiences, I would not recommend buying flip or fold phones, as they seem to be prone to issues and require costly maintenance.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Pravin K.\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"Strong in built quality.Almost no crease on display.Display fold does not stop at places in between.Fast processor for normal office use.Display quality is excellent.Sound is comparably low.Looks premium.Feels tough.\n  \nRead more\", \"product_id\": \"B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"link\": \"https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vivo X200 Pro 5G </t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B07WDJMX16\", \"product_name\": \"Vivo X200 Pro 5G (Titanium Grey, 16GB RAM, 512GB Storage) with No Cost EMI/Additional Exchange Offers\", \"product_url\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Bappa royBappa roy\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Pros:- 1. telephoto lense : captures stunning portrait2. Macro shots: The best in the industry of smartphones within the range3. Battery backup: With heavy usage lasts 1day with min 25% charge remaining for useWith standard usage lasts for 1.5 days with ease.4. Fingerprint &amp; face unlock: The smoothest among all used devices till now and best thing is face unlock even works in low light and dark consitions alao.5. Processor: the best in terms of performance in gaming &amp; other tasks.6. RAM management: The best as keeps in the same page while  opened after 3 days in \\"eFootball 2024\\" and many ithers apps.Cons:-1. Bulky: Seems to the bulkiest phone compared to previusly used ones.2. Difficult to hold: The phone is difficult to hold due to huge camera bump and it always feels that is will fall from hand anytime. One hand use has limited excess to whole screen.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AbhilashAbhilash\", \"rating\": \"5.0\", \"date\": \"04 Feb 2025\", \"text\": \"Camera: Best in the market, significantly better than my previous Samsung S21 Ultra. The 10x, 5x, and 3x zoom are excellent.AI Features: Not on the level of Samsung S24/S25 Ultra.Design: Looks good, but the camera bump doesn’t feel very practical. Still getting used to it after a month.Display: Great quality, no complaints.Sound: Good and clear.UI: A major drawback. Samsung’s One UI is far better in terms of experience.Gaming: Performs well with smooth gameplay.Battery: Good battery life, lasts well through the day.Build &amp; Feel: Slim, compact, and feels premium in hand.IR Blaster: Placed in the camera module instead of on top, but having it is still better than not.Processor: Was initially nervous about the Dimensity chip, but it turned out to be really capable.Social Media Camera Integration: Needs improvement. Vivo should work on better integration like Apple does with Instagram and Snapchat.Overall: Not a perfect phone, but a well-balanced one with the best camera in the market. Haven’t faced any issues so far.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Riyas M\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"This is phone is really good. I upgraded from an s22 ultra.UI is really not that bad as everyone say. It could be better but it\'s really good on the basics like animation, customisation etc but not on par with oneui 7.The display is also good. Plenty bright and dims very well. Personally not a fan of the color saturation but no complaints here.The sound is good. Rich and loud but the volume levels are not linear.Camera is great ofcourse. Both main and the telephoto. Stunning photos and videos. Vivo has nailed the balance between true to life and rich vibrant colours.Ultra wide is average. Selfie camera is trash.The battery life is not on par with the capacity. This could be improved through updates and the charging speed is acceptable.The Bulld quality isn\'t as great but nothing bad. It doesn\'t feel like a tank when you hold it.Performance is really great. Everything runs without a hassle. Mediatek is better than snappy in terms of sustained performance but this doesn\'t give peak like 8 elite.Vibration motor is okish. Button are also okish. Fingerprint scanner is best in class.Overall pretty good phone with few little downsides.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vikas MahajanVikas Mahajan\", \"rating\": \"5.0\", \"date\": \"19 Dec 2024\", \"text\": \"Outstanding Phone with DSLR-Like Camera Quality!I recently upgraded to the Vivo X200 Pro, and I couldn’t be happier with my choice. This phone is a complete powerhouse!Pros:Display: The OLED display is vibrant, with excellent brightness and crisp resolution. It’s a treat for watching videos or scrolling through content.Performance: The processor is incredibly fast, handling multitasking and gaming effortlessly without any lags.Camera: The camera quality is phenomenal! It clicks real DSLR-like photos with stunning detail and natural colors, even in low-light conditions. It’s a game-changer for photography enthusiasts.Battery Life: The battery lasts all day, even with heavy usage, and the fast charging is a lifesaver.Design: The sleek and premium design feels great in the hand. It’s stylish yet sturdy.If you’re looking for a top-tier smartphone experience with outstanding camera performance, the Vivo X200 Pro is worth every penny!\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"sunilsunil\", \"rating\": \"5.0\", \"date\": \"17 Jan 2025\", \"text\": \"If you want a smartphone for complete camera you won\'t get better one than thisIf you want a smartphone for best battery life you won\'t get better one than thisThe image processing, photo optimization, battery optimisation are far better than what I expectedThe dimensity 9400 Chip is tuned for efficiency more than perfomance you won\'t find any ui lags, u don\'t get any heating issues evening in heavy tasksThis is a battery beast no smartphone in segment can beat the battery life of this phone including S24 ultra and Iphone 16 pro MaxFor 95k this is complete value for money phonePeak Camera 📸, Peak durability, Peak Battery 🔋Worth every pennyConsider buying this if you are a photography geek like me.\n  \nRead more\", \"product_id\": \"B07WDJMX16\", \"link\": \"https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vivo V50 5G</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>16</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DTHTDGH7\", \"product_name\": \"Vivo V50 5G (Titanium Grey, 8GB RAM, 128GB Storage) with No Cost EMI/Additional Exchange Offers\", \"product_url\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.62, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Nikunj Dhameliya\", \"rating\": \"5.0\", \"date\": \"02 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'ve been using the Vivo V50 5G for a while now, and I\'m genuinely impressed with its performance. One of the biggest highlights is the long-lasting battery – I only need to charge it once, and it easily runs for a day and a half with regular usage. This is a huge plus for anyone who doesn’t want to keep reaching for a charger.Network connectivity is also very reliable. Whether I\'m on a call or browsing, I haven’t faced any major drops or signal issues. The 5G capability gives it a future-ready edge too.The AI features in the camera are quite decent. It enhances photos subtly and smartly, especially in portrait and low-light shots. It\'s not overdone, which I appreciate.Overall, I’m really happy with the performance of this phone. It handles daily tasks smoothly, has a clean UI, and gives excellent value for money. If you\'re looking for a dependable 5G phone with strong battery life and good performance, the Vivo V50 is worth considering.\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"WOONNA GOVINDA RAJULU\", \"rating\": \"4.0\", \"date\": \"21 May 2025\", \"text\": \"Product all are good.  Charging good.  Battery performance are good\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AparnaAparna\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"Everything is top notch I was so excited to get my new phone and it fulfiled all my expectations1. Battery life is pretty good can use for whole day if you use constantly....2. Sound quality amazing try to use on 95-97% volume so it will be good3. Value for money definetly it worth every penny spend on it4. Camera quality is amazingggggg...Everything is smooth and perfect in short\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sk Ershad\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Camera quality is goodBattery time is ok but push to upgrade as per demandSound quality is goodSmoothnessWeight is ok\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Ashitha MBAshitha MB\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Compared to other phones, the front and rear cameras od this phone can take good photos. It has a good battery backup. It can last up to two days on a charge.IssuesBut price is  high.Small heating issue.\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Momo\", \"rating\": \"4.0\", \"date\": \"05 May 2025\", \"text\": \"Good phone with great features. I miss the 3.5 mm jack. The earphones one buys gets outdated when one upgrades a phone. The phone companies must give a headphone/earphone set.\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Suman C.Suman C.\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Undoubtedly the best smartphone in the price segment.The camera quality is simply wow..\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AnkitAnkit\", \"rating\": \"4.0\", \"date\": \"31 Mar 2025\", \"text\": \"This phone is one of the best mid-range options, but the price is a little too high. However, its sound quality is amazing, the performance is good, and the battery life is also good.\\"\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nikunj Dhameliya\", \"rating\": \"5.0\", \"date\": \"02 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'ve been using the Vivo V50 5G for a while now, and I\'m genuinely impressed with its performance. One of the biggest highlights is the long-lasting battery – I only need to charge it once, and it easily runs for a day and a half with regular usage. This is a huge plus for anyone who doesn’t want to keep reaching for a charger.Network connectivity is also very reliable. Whether I\'m on a call or browsing, I haven’t faced any major drops or signal issues. The 5G capability gives it a future-ready edge too.The AI features in the camera are quite decent. It enhances photos subtly and smartly, especially in portrait and low-light shots. It\'s not overdone, which I appreciate.Overall, I’m really happy with the performance of this phone. It handles daily tasks smoothly, has a clean UI, and gives excellent value for money. If you\'re looking for a dependable 5G phone with strong battery life and good performance, the Vivo V50 is worth considering.\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"WOONNA GOVINDA RAJULU\", \"rating\": \"4.0\", \"date\": \"21 May 2025\", \"text\": \"Product all are good.  Charging good.  Battery performance are good\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AparnaAparna\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"Everything is top notch I was so excited to get my new phone and it fulfiled all my expectations1. Battery life is pretty good can use for whole day if you use constantly....2. Sound quality amazing try to use on 95-97% volume so it will be good3. Value for money definetly it worth every penny spend on it4. Camera quality is amazingggggg...Everything is smooth and perfect in short\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sk Ershad\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Camera quality is goodBattery time is ok but push to upgrade as per demandSound quality is goodSmoothnessWeight is ok\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Ashitha MBAshitha MB\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Compared to other phones, the front and rear cameras od this phone can take good photos. It has a good battery backup. It can last up to two days on a charge.IssuesBut price is  high.Small heating issue.\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Momo\", \"rating\": \"4.0\", \"date\": \"05 May 2025\", \"text\": \"Good phone with great features. I miss the 3.5 mm jack. The earphones one buys gets outdated when one upgrades a phone. The phone companies must give a headphone/earphone set.\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Suman C.Suman C.\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Undoubtedly the best smartphone in the price segment.The camera quality is simply wow..\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AnkitAnkit\", \"rating\": \"4.0\", \"date\": \"31 Mar 2025\", \"text\": \"This phone is one of the best mid-range options, but the price is a little too high. However, its sound quality is amazing, the performance is good, and the battery life is also good.\\"\n  \nRead more\", \"product_id\": \"B0DTHTDGH7\", \"link\": \"https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Vivo Y300 5G</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B07WDKLBLZ\", \"product_name\": \"Vivo Y300 5G (Titanium Silver, 8GB RAM, 128GB Storage) with No Cost EMI/Additional Exchange Offers\", \"product_url\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"U Suresh\", \"rating\": \"5.0\", \"date\": \"07 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good phone with smooth screen and soft key pad. Excellent camera and long battery life. It is value for money and its audio sound quality is good.\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"Nice phone\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Deepak kushwaha\", \"rating\": \"4.0\", \"date\": \"16 Apr 2025\", \"text\": \"As expected , this is good phone under this price .. display quality is good … 👍. The thing which i like most about this phone is it’s design which overpowers the phone 👍👍… value for money👍\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"vivek\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Nice design best camera quality\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Dileep Kumar\", \"rating\": \"1.0\", \"date\": \"10 May 2025\", \"text\": \"Very Good Product. Value for money, remarkable display quality, good battery life.\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rahul kumar\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"Good Mobile\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ashish patil\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"Good phone\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SYED RAYAN.\", \"rating\": \"4.0\", \"date\": \"19 May 2025\", \"text\": \"Nice and sleek design\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"U Suresh\", \"rating\": \"5.0\", \"date\": \"07 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good phone with smooth screen and soft key pad. Excellent camera and long battery life. It is value for money and its audio sound quality is good.\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"Nice phone\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Deepak kushwaha\", \"rating\": \"4.0\", \"date\": \"16 Apr 2025\", \"text\": \"As expected , this is good phone under this price .. display quality is good … 👍. The thing which i like most about this phone is it’s design which overpowers the phone 👍👍… value for money👍\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"vivek\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Nice design best camera quality\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Dileep Kumar\", \"rating\": \"1.0\", \"date\": \"10 May 2025\", \"text\": \"Very Good Product. Value for money, remarkable display quality, good battery life.\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rahul kumar\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"Good Mobile\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ashish patil\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"Good phone\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SYED RAYAN.\", \"rating\": \"4.0\", \"date\": \"19 May 2025\", \"text\": \"Nice and sleek design\n  \nRead more\", \"product_id\": \"B07WDKLBLZ\", \"link\": \"https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Microsoft New Surface Laptop</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D926W4YN\", \"product_name\": \"Microsoft New Surface Laptop (7th Edition) - Windows 11 Home Copilot + PC - 13.8” LCD PixelSense Touchscreen - Qualcomm Snapdragon X Elite (12 Core) - 16GB RAM - 512GB SSD - Graphite - ZGP-00059\", \"product_url\": \"https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m\", \"summary\": {\"total_reviews\": 6, \"average_rating\": 5.0, \"sentiment_breakdown\": {\"positive\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"HEMANT GARG\", \"rating\": \"5.0\", \"date\": \"19 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    My search for Laptop Ends Finally I write here detailed recommendationsScreen - Amazing Quality Pixels Fast Responsive TouchAudio - Very Good Quality Audio Speakers Nice SoundProcessor - Switching from Intel to Qualcomm was easy for me however I try to take chance after lots of reviews available on Youtube Now I am happy its good processor for Multitasking and GamingBattery - Nice Backup However Brand Claim upto 20 Hours Backup But I found it for 13 may be depends on my usage also charges with both Type C and Magnate ChargerUI and Software - Switching from Windows 10 to 11 is very Critical depends on User choice I don\'t like Windows 11Overall A good recommendation In this range of laptop thin and Light laptop\n  \nRead more\", \"product_id\": \"B0D926W4YN\", \"link\": \"https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m\", \"sentiment\": \"positive\"}, {\"author\": \"Mahendra Bilagi\", \"rating\": \"5.0\", \"date\": \"30 Sep 2024\", \"text\": \"Qualcomm entered this market and given tough competition to Intel and AMD. Overall very good laptop with on device AI capabilities. Battery life is excellent.\n  \nRead more\", \"product_id\": \"B0D926W4YN\", \"link\": \"https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m\", \"sentiment\": \"positive\"}, {\"author\": \"yerubandi s.\", \"rating\": \"5.0\", \"date\": \"07 Aug 2024\", \"text\": \"Excellent product with AI.. qulacomm did best job...it would be good,  if all the application supports. Future  laptops with fast charging option\n  \nRead more\", \"product_id\": \"B0D926W4YN\", \"link\": \"https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m\", \"sentiment\": \"positive\"}, {\"author\": \"HEMANT GARG\", \"rating\": \"5.0\", \"date\": \"19 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    My search for Laptop Ends Finally I write here detailed recommendationsScreen - Amazing Quality Pixels Fast Responsive TouchAudio - Very Good Quality Audio Speakers Nice SoundProcessor - Switching from Intel to Qualcomm was easy for me however I try to take chance after lots of reviews available on Youtube Now I am happy its good processor for Multitasking and GamingBattery - Nice Backup However Brand Claim upto 20 Hours Backup But I found it for 13 may be depends on my usage also charges with both Type C and Magnate ChargerUI and Software - Switching from Windows 10 to 11 is very Critical depends on User choice I don\'t like Windows 11Overall A good recommendation In this range of laptop thin and Light laptop\n  \nRead more\", \"product_id\": \"B0D926W4YN\", \"link\": \"https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m\", \"sentiment\": \"positive\"}, {\"author\": \"Mahendra Bilagi\", \"rating\": \"5.0\", \"date\": \"30 Sep 2024\", \"text\": \"Qualcomm entered this market and given tough competition to Intel and AMD. Overall very good laptop with on device AI capabilities. Battery life is excellent.\n  \nRead more\", \"product_id\": \"B0D926W4YN\", \"link\": \"https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m\", \"sentiment\": \"positive\"}, {\"author\": \"yerubandi s.\", \"rating\": \"5.0\", \"date\": \"07 Aug 2024\", \"text\": \"Excellent product with AI.. qulacomm did best job...it would be good,  if all the application supports. Future  laptops with fast charging option\n  \nRead more\", \"product_id\": \"B0D926W4YN\", \"link\": \"https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lenovo Yoga Slim 7 Intel Core Ultra 7 155H</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>16</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CTMQDLQX\", \"product_name\": \"Lenovo Yoga Slim 7 Intel Core Ultra 7 155H Built-in AI 14\\"(35.5cm) WUXGA-OLED 400Nits Laptop (32GB/1TB SSD/100% DCI-P3/FHD+IR Camera/Win11/MSO 21/1Yr ADP Free/3Mon. Game Pass/Grey/1.39Kg), 83CV002DIN\", \"product_url\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 8, \"negative\": 6, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 50.0}, \"reviews\": [{\"author\": \"Lawrence\", \"rating\": \"5.0\", \"date\": \"22 Aug 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Compact, light weight, great build quality and premium. I mostly work on Office 365 apps. Love the speed. Battery life exceeded my expectations.  I charge only once in a day. It lasts more than 12 hours. Thanks to Lenovo for not putting nagging preinstalled apps.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}, {\"author\": \"Ranjan Chand\", \"rating\": \"5.0\", \"date\": \"24 Oct 2024\", \"text\": \"Working well for last 2 weeks. Doesn’t slow down with amazing battery life.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}, {\"author\": \"Thunder Rolls\", \"rating\": \"5.0\", \"date\": \"13 Dec 2024\", \"text\": \"Laptop is fast. Only issue is the power on button is on the right side of the laptop facing you. So chances of pressing it accidentally is more.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"negative\"}, {\"author\": \"E Services\", \"rating\": \"4.0\", \"date\": \"14 May 2025\", \"text\": \"I received one that had only 6.months warranty left.Thankfully I could return it as I checked the next day after purchase. The serial number did not match the Invoice and the Packing slip had yet another serial, making it impossible to establish purchase date with Lenovo support.I\'m not sure how many others have bought and not realized the problem till it was too late\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"negative\"}, {\"author\": \"Koshlendra P. SinghKoshlendra P. Singh\", \"rating\": \"1.0\", \"date\": \"08 Dec 2024\", \"text\": \"Used product send, o have raise a return request which will take 3 days after investigation and approval. Don\'t go for this.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"neutral\"}, {\"author\": \"Aniruddha RoychowdhuryAniruddha Roychowdhury\", \"rating\": \"3.0\", \"date\": \"05 Sep 2024\", \"text\": \"Display resolution poor. No fingerprint sensor.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"negative\"}, {\"author\": \"Nischit\", \"rating\": \"5.0\", \"date\": \"25 Jul 2024\", \"text\": \"Best for college\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}, {\"author\": \"Manoj naik\", \"rating\": \"4.0\", \"date\": \"09 Apr 2024\", \"text\": \"It has good display and performance.4 star because of one issue. Laptop heats very much when doing some above average tasks like installing, playing average games, hence the fan activates with a average noise.Other than this the laptop is pretty good\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}, {\"author\": \"Lawrence\", \"rating\": \"5.0\", \"date\": \"22 Aug 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Compact, light weight, great build quality and premium. I mostly work on Office 365 apps. Love the speed. Battery life exceeded my expectations.  I charge only once in a day. It lasts more than 12 hours. Thanks to Lenovo for not putting nagging preinstalled apps.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}, {\"author\": \"Ranjan Chand\", \"rating\": \"5.0\", \"date\": \"24 Oct 2024\", \"text\": \"Working well for last 2 weeks. Doesn’t slow down with amazing battery life.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}, {\"author\": \"Thunder Rolls\", \"rating\": \"5.0\", \"date\": \"13 Dec 2024\", \"text\": \"Laptop is fast. Only issue is the power on button is on the right side of the laptop facing you. So chances of pressing it accidentally is more.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"negative\"}, {\"author\": \"E Services\", \"rating\": \"4.0\", \"date\": \"14 May 2025\", \"text\": \"I received one that had only 6.months warranty left.Thankfully I could return it as I checked the next day after purchase. The serial number did not match the Invoice and the Packing slip had yet another serial, making it impossible to establish purchase date with Lenovo support.I\'m not sure how many others have bought and not realized the problem till it was too late\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"negative\"}, {\"author\": \"Koshlendra P. SinghKoshlendra P. Singh\", \"rating\": \"1.0\", \"date\": \"08 Dec 2024\", \"text\": \"Used product send, o have raise a return request which will take 3 days after investigation and approval. Don\'t go for this.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"neutral\"}, {\"author\": \"Aniruddha RoychowdhuryAniruddha Roychowdhury\", \"rating\": \"3.0\", \"date\": \"05 Sep 2024\", \"text\": \"Display resolution poor. No fingerprint sensor.\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"negative\"}, {\"author\": \"Nischit\", \"rating\": \"5.0\", \"date\": \"25 Jul 2024\", \"text\": \"Best for college\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}, {\"author\": \"Manoj naik\", \"rating\": \"4.0\", \"date\": \"09 Apr 2024\", \"text\": \"It has good display and performance.4 star because of one issue. Laptop heats very much when doing some above average tasks like installing, playing average games, hence the fan activates with a average noise.Other than this the laptop is pretty good\n  \nRead more\", \"product_id\": \"B0CTMQDLQX\", \"link\": \"https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Apple iPad Pro 13″ (M4)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D3J873LP\", \"product_name\": \"Apple iPad Pro 13″ (M4): Ultra Retina XDR Display, 256GB, Landscape 12MP Front Camera / 12MP Back Camera, LiDAR Scanner, Wi-Fi 6E, Face ID, All-Day Battery Life, Standard Glass — Space Black\", \"product_url\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.5, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 2, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Riddhi Acharya\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The iPad Pro 13” M4 is everything I expected from Apple—smooth, fast, and beautifully designed. The sleek design gives it a premium feel, and the performance is top-notch, handling everything I throw at it effortlessly.I purchased it a few months ago and I’m still discovering new ways to make the most of its capabilities. It has definitely made my daily tasks more efficient, and it’s also a fantastic device for watching movies with its large, stunning display.Overall, a solid investment for both productivity and entertainment. Apple delivers once again.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pratyaksh YadavPratyaksh Yadav\", \"rating\": \"5.0\", \"date\": \"14 Jun 2024\", \"text\": \"iPad is just like a tablet, which is just fully loaded with the power of M4 and it is having 4.4 ghz processor which is really very powerful and unleashed processor and it was my dream to buy an iPad as it is having a very nice ecosystem with my iPhone, my Apple Watch and my AirPods Pro, which is really really really nice and you might think that it is very very very useful to you when you are searching something when you’re watching it, all it is really crispy and very awesome to look really value for money as but sometimes you think that it doesn’t give something is just like small things like you can see there is no WhatsApp for this iPad OS, which is really sucks, but the weight it’s it’s really light and it is very thin. It is having 5.1 MM thickness which is really thinner than my iPhone as well as my other android phones which have I bought in the past, which is very nice thing, but and a strong quality is a very very very good is having a quad, which is having a probability to beat all at most and make this surround sound better to hear the movies to watch movies to watch your YouTube videos to hear the music and lot of stuff on you can do it. There is just all of the world you can play games. You can play games and focus resolution like a resident evil evil and we can really run a PS5 game on it which is a really nice thing is just like a PC processor in a tablet, but small and compact and thin factor . I really like it.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"VIPIN CHAUDHARY\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Amazing\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mohammad Imran Khan\", \"rating\": \"5.0\", \"date\": \"28 Oct 2024\", \"text\": \"Insanely powerful. I had been using M1 ipad pro for last three years. Got this newly launched M4 in the great Indian festival sale on amazon. The product is a major upgrade from its predecessor.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sunil KatochSunil Katoch\", \"rating\": \"5.0\", \"date\": \"11 Oct 2024\", \"text\": \"Highly satisfied with the product with everything bigger and display or sound or computing everything to my satisfaction. I am mainly using it for entertainment purposes rather than computing. Got good discounts during mega sale. Got the original product no flaws at all. But little advice if your pocket permits than only go for it otherwise don’t purchase it on loan.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shrey Bond\", \"rating\": \"1.0\", \"date\": \"06 Feb 2025\", \"text\": \"S10 Ultra is way better...don\'t waste your money on it.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Pacific\", \"rating\": \"5.0\", \"date\": \"14 Jun 2024\", \"text\": \"Pros- Oled is just nice, speakers, usb c, thin n light, super smooth, waiting for Apple intel features, large interface perfect for reading, making notes, wasting life in videos, reels and social media.Cons - Ripoff. Pen is costly. Keyboard is costly which I\'m not gonna use.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sukesh M.\", \"rating\": \"5.0\", \"date\": \"28 May 2024\", \"text\": \"Nothing can be slimmer than this\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Riddhi Acharya\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The iPad Pro 13” M4 is everything I expected from Apple—smooth, fast, and beautifully designed. The sleek design gives it a premium feel, and the performance is top-notch, handling everything I throw at it effortlessly.I purchased it a few months ago and I’m still discovering new ways to make the most of its capabilities. It has definitely made my daily tasks more efficient, and it’s also a fantastic device for watching movies with its large, stunning display.Overall, a solid investment for both productivity and entertainment. Apple delivers once again.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pratyaksh YadavPratyaksh Yadav\", \"rating\": \"5.0\", \"date\": \"14 Jun 2024\", \"text\": \"iPad is just like a tablet, which is just fully loaded with the power of M4 and it is having 4.4 ghz processor which is really very powerful and unleashed processor and it was my dream to buy an iPad as it is having a very nice ecosystem with my iPhone, my Apple Watch and my AirPods Pro, which is really really really nice and you might think that it is very very very useful to you when you are searching something when you’re watching it, all it is really crispy and very awesome to look really value for money as but sometimes you think that it doesn’t give something is just like small things like you can see there is no WhatsApp for this iPad OS, which is really sucks, but the weight it’s it’s really light and it is very thin. It is having 5.1 MM thickness which is really thinner than my iPhone as well as my other android phones which have I bought in the past, which is very nice thing, but and a strong quality is a very very very good is having a quad, which is having a probability to beat all at most and make this surround sound better to hear the movies to watch movies to watch your YouTube videos to hear the music and lot of stuff on you can do it. There is just all of the world you can play games. You can play games and focus resolution like a resident evil evil and we can really run a PS5 game on it which is a really nice thing is just like a PC processor in a tablet, but small and compact and thin factor . I really like it.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"VIPIN CHAUDHARY\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Amazing\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mohammad Imran Khan\", \"rating\": \"5.0\", \"date\": \"28 Oct 2024\", \"text\": \"Insanely powerful. I had been using M1 ipad pro for last three years. Got this newly launched M4 in the great Indian festival sale on amazon. The product is a major upgrade from its predecessor.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sunil KatochSunil Katoch\", \"rating\": \"5.0\", \"date\": \"11 Oct 2024\", \"text\": \"Highly satisfied with the product with everything bigger and display or sound or computing everything to my satisfaction. I am mainly using it for entertainment purposes rather than computing. Got good discounts during mega sale. Got the original product no flaws at all. But little advice if your pocket permits than only go for it otherwise don’t purchase it on loan.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shrey Bond\", \"rating\": \"1.0\", \"date\": \"06 Feb 2025\", \"text\": \"S10 Ultra is way better...don\'t waste your money on it.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Pacific\", \"rating\": \"5.0\", \"date\": \"14 Jun 2024\", \"text\": \"Pros- Oled is just nice, speakers, usb c, thin n light, super smooth, waiting for Apple intel features, large interface perfect for reading, making notes, wasting life in videos, reels and social media.Cons - Ripoff. Pen is costly. Keyboard is costly which I\'m not gonna use.\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sukesh M.\", \"rating\": \"5.0\", \"date\": \"28 May 2024\", \"text\": \"Nothing can be slimmer than this\n  \nRead more\", \"product_id\": \"B0D3J873LP\", \"link\": \"https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Redmi Note 14 5G</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DPFVDFT3\", \"product_name\": \"Redmi Note 14 5G (Titan Black, 8GB RAM 256GB Storage) | Global Debut MTK Dimensity 7025 Ultra | 2100 nits Segment Brightest 120Hz AMOLED | 50MP Sony LYT 600 OIS+EIS Triple Camera\", \"product_url\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 3.62, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 4, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Sudip sen\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Nice build quality and battery backup at this range. Camera quality may be improved.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shailesh Tomar\", \"rating\": \"1.0\", \"date\": \"30 Dec 2024\", \"text\": \"I don’t have words to explain the quality of camera, only can say it is pathetic, poor, disgusting etc. I have connected with their team also and they told me that they can’t do any thing as camera will provide this type of pic only. I will suggest please don’t buy Redmi Note 14 mobile it is totally wastage of money and they are fooling by saying it is 50mp camera; however my old mobile provide better pic. I am going to request to Amazon also please don’t keep these type of low standard product which are costing so much. I am never going to buy electronic product from Amazon because if quality of product is not good u can’t return it and ur hard earned money will go to waste and will suggest my family and friends also not to buy electronic product from Amazon.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"omkar kamble\", \"rating\": \"4.0\", \"date\": \"20 May 2025\", \"text\": \"Value for money | great build and speed\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"vishwas vinayak garud\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Good quality &amp; value for money sound, picture quality display is too good and efficient charging &amp; very quick\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Arnab Chakraborty\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Improved camera, touch and performance from redmi note 12\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"ketan r solanki\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"Superb phone in under 20000 value with Sony camera\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Gary\", \"rating\": \"3.0\", \"date\": \"23 Apr 2025\", \"text\": \"Slow processing. Below average camera. Heating issues.Display, looks are good. Sound is fine. Average battery life on normal use. Not for multi tasking.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Any\", \"rating\": \"1.0\", \"date\": \"31 Mar 2025\", \"text\": \"Worst phone, touch does not work, phone hangs continuously. And not able to exchange also as name of this phone does not appear in exchange list. I am stuck don\'t know what to do. I bought it in month of January 2025. Even my previous phone redmi note 9 pro Max was good as compared to this one which I bought in dec 2020.Worst phone worst experience. Mi quality degrading day by day.Buy any other company phones not mi.Hanging issue.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Sudip sen\", \"rating\": \"5.0\", \"date\": \"26 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Nice build quality and battery backup at this range. Camera quality may be improved.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shailesh Tomar\", \"rating\": \"1.0\", \"date\": \"30 Dec 2024\", \"text\": \"I don’t have words to explain the quality of camera, only can say it is pathetic, poor, disgusting etc. I have connected with their team also and they told me that they can’t do any thing as camera will provide this type of pic only. I will suggest please don’t buy Redmi Note 14 mobile it is totally wastage of money and they are fooling by saying it is 50mp camera; however my old mobile provide better pic. I am going to request to Amazon also please don’t keep these type of low standard product which are costing so much. I am never going to buy electronic product from Amazon because if quality of product is not good u can’t return it and ur hard earned money will go to waste and will suggest my family and friends also not to buy electronic product from Amazon.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"omkar kamble\", \"rating\": \"4.0\", \"date\": \"20 May 2025\", \"text\": \"Value for money | great build and speed\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"vishwas vinayak garud\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Good quality &amp; value for money sound, picture quality display is too good and efficient charging &amp; very quick\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Arnab Chakraborty\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Improved camera, touch and performance from redmi note 12\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"ketan r solanki\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"Superb phone in under 20000 value with Sony camera\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Gary\", \"rating\": \"3.0\", \"date\": \"23 Apr 2025\", \"text\": \"Slow processing. Below average camera. Heating issues.Display, looks are good. Sound is fine. Average battery life on normal use. Not for multi tasking.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Any\", \"rating\": \"1.0\", \"date\": \"31 Mar 2025\", \"text\": \"Worst phone, touch does not work, phone hangs continuously. And not able to exchange also as name of this phone does not appear in exchange list. I am stuck don\'t know what to do. I bought it in month of January 2025. Even my previous phone redmi note 9 pro Max was good as compared to this one which I bought in dec 2020.Worst phone worst experience. Mi quality degrading day by day.Buy any other company phones not mi.Hanging issue.\n  \nRead more\", \"product_id\": \"B0DPFVDFT3\", \"link\": \"https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>OnePlus Nord CE4 Lite 5G</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D5YCYS1G\", \"product_name\": \"OnePlus Nord CE4 Lite 5G (Super Silver, 8GB RAM, 128GB Storage) | Lifetime Display Warranty | 5500 mAh Battery, 80W SUPERVOOC and Reverse Charging | 50MP Camera with OIS | 120Hz AMOLED Display\", \"product_url\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"summary\": {\"total_reviews\": 8, \"average_rating\": 4.75, \"sentiment_breakdown\": {\"positive\": 6, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Raju kumtekar\", \"rating\": \"5.0\", \"date\": \"02 Sep 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the OnePlus Nord CE 4 Lite, and it has truly exceeded my expectations, deserving a solid 5-star rating. Here’s a detailed breakdown of why this phone is an excellent choice:Design and Build Quality: The OnePlus Nord CE 4 Lite boasts a sleek, modern design with a premium feel. The materials used are top-notch, giving it a solid and durable build. Its slim profile and lightweight nature make it comfortable to hold and use for extended periods.Display: The phone features a stunning AMOLED display with vibrant colors and sharp resolution. Whether watching videos, playing games, or browsing the web, the visuals are crisp and clear. The high refresh rate adds to the smoothness of the experience, making every interaction buttery smooth.Performance: Powered by the Qualcomm Snapdragon 695 SoC, the OnePlus Nord CE 4 Lite handles everything with ease. From multitasking to running graphic-intensive games, it performs without a hitch. While the processor might not be the latest, it still delivers reliable performance for daily use.Camera: The camera setup is impressive, especially the 50MP main sensor, which captures detailed and vibrant photos even in low light. The wide-angle lens adds versatility, allowing for creative shots. The video recording quality is also top-notch, with stable and clear footage. However, low-light photography could use some improvement.Battery Life: Battery life is outstanding, easily lasting a full day with moderate to heavy use. The 5,500mAh battery ensures you won’t run out of juice during the day. The fast charging feature is a lifesaver, allowing you to quickly top up the battery when needed.Additional Features: The phone has an official IP54 certification for protection against water splashes and dust. The design, inspired by minimalist tones and patterns, gives it a premium look. The 3.5mm audio jack is a bonus for wired earphone users.In conclusion, the OnePlus Nord CE 4 Lite is an excellent smartphone in its price segment. Its design, display, performance, and battery life make it a worthy contender. While it could benefit from a newer processor and improved low-light camera performance, it still offers great value for money. For daily usage, the Nord CE 4 Lite will not disappoint.\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Adv. Y. P. Kaushal\", \"rating\": \"4.0\", \"date\": \"10 Oct 2024\", \"text\": \"My review :Performance [ 4/5 ] - Gaming Performance good but you\'ll see some frame drops and lag somewhere while using but a great gaming experience at this price.Camera [ 3/5 ] - Very limit features in camera app and quality is also not good and you\'ll find better options in market at 20k.Battery [ 5/5 ] - Awesome battery life and 80w fast charging is crazy and will take about 40m-60m for 0-100%.Display [ 4.5/5 ] - Good display quality in this price segment.Software [ 4/5 ] - Somewhere a decent ui experience but if you are looking for a good ui then Samsung ofc will be the best option.Conclusion - If you are looking for a phone for normal use and don\'t use camera that much then it\'s a great choice but OnePlus as a company is not offering you something special  if you buy at by seeing their brand value and it\'s quite similar to Realme Mobiles.\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhanraj restaurant\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Looks and feels premiumWorth the money\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Chandan\", \"rating\": \"5.0\", \"date\": \"31 Jul 2024\", \"text\": \"I recently purchased the OnePlus Nord CE 4 Lite, and it has truly exceeded my expectations, deserving a solid 5-star rating. Here’s a detailed breakdown of why this phone is an excellent choice:Design and Build Quality: The OnePlus Nord CE 4 Lite boasts a sleek, modern design with a premium feel. The materials used are top-notch, giving it a solid and durable build. Its slim profile and lightweight nature make it comfortable to hold and use for extended periods.Display: The phone features a stunning AMOLED display with vibrant colors and sharp resolution. Whether watching videos, playing games, or browsing the web, the visuals are crisp and clear. The high refresh rate adds to the smoothness of the experience, making every interaction buttery smooth.Performance: Powered by the Qualcomm Snapdragon 695 SoC, the OnePlus Nord CE 4 Lite handles everything with ease. From multitasking to running graphic-intensive games, it performs without a hitch. While the processor might not be the latest, it still delivers reliable performance for daily use.Camera: The camera setup is impressive, especially the 50MP main sensor, which captures detailed and vibrant photos even in low light. The wide-angle lens adds versatility, allowing for creative shots. The video recording quality is also top-notch, with stable and clear footage. However, low-light photography could use some improvement.Battery Life: Battery life is outstanding, easily lasting a full day with moderate to heavy use. The 5,500mAh battery ensures you won’t run out of juice during the day. The fast charging feature is a lifesaver, allowing you to quickly top up the battery when needed.Additional Features: The phone has an official IP54 certification for protection against water splashes and dust. The design, inspired by minimalist tones and patterns, gives it a premium look. The 3.5mm audio jack is a bonus for wired earphone users.In conclusion, the OnePlus Nord CE 4 Lite is an excellent smartphone in its price segment. Its design, display, performance, and battery life make it a worthy contender. While it could benefit from a newer processor and improved low-light camera performance, it still offers great value for money. For daily usage, the Nord CE 4 Lite will not disappoint.\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Raju kumtekar\", \"rating\": \"5.0\", \"date\": \"02 Sep 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the OnePlus Nord CE 4 Lite, and it has truly exceeded my expectations, deserving a solid 5-star rating. Here’s a detailed breakdown of why this phone is an excellent choice:Design and Build Quality: The OnePlus Nord CE 4 Lite boasts a sleek, modern design with a premium feel. The materials used are top-notch, giving it a solid and durable build. Its slim profile and lightweight nature make it comfortable to hold and use for extended periods.Display: The phone features a stunning AMOLED display with vibrant colors and sharp resolution. Whether watching videos, playing games, or browsing the web, the visuals are crisp and clear. The high refresh rate adds to the smoothness of the experience, making every interaction buttery smooth.Performance: Powered by the Qualcomm Snapdragon 695 SoC, the OnePlus Nord CE 4 Lite handles everything with ease. From multitasking to running graphic-intensive games, it performs without a hitch. While the processor might not be the latest, it still delivers reliable performance for daily use.Camera: The camera setup is impressive, especially the 50MP main sensor, which captures detailed and vibrant photos even in low light. The wide-angle lens adds versatility, allowing for creative shots. The video recording quality is also top-notch, with stable and clear footage. However, low-light photography could use some improvement.Battery Life: Battery life is outstanding, easily lasting a full day with moderate to heavy use. The 5,500mAh battery ensures you won’t run out of juice during the day. The fast charging feature is a lifesaver, allowing you to quickly top up the battery when needed.Additional Features: The phone has an official IP54 certification for protection against water splashes and dust. The design, inspired by minimalist tones and patterns, gives it a premium look. The 3.5mm audio jack is a bonus for wired earphone users.In conclusion, the OnePlus Nord CE 4 Lite is an excellent smartphone in its price segment. Its design, display, performance, and battery life make it a worthy contender. While it could benefit from a newer processor and improved low-light camera performance, it still offers great value for money. For daily usage, the Nord CE 4 Lite will not disappoint.\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Adv. Y. P. Kaushal\", \"rating\": \"4.0\", \"date\": \"10 Oct 2024\", \"text\": \"My review :Performance [ 4/5 ] - Gaming Performance good but you\'ll see some frame drops and lag somewhere while using but a great gaming experience at this price.Camera [ 3/5 ] - Very limit features in camera app and quality is also not good and you\'ll find better options in market at 20k.Battery [ 5/5 ] - Awesome battery life and 80w fast charging is crazy and will take about 40m-60m for 0-100%.Display [ 4.5/5 ] - Good display quality in this price segment.Software [ 4/5 ] - Somewhere a decent ui experience but if you are looking for a good ui then Samsung ofc will be the best option.Conclusion - If you are looking for a phone for normal use and don\'t use camera that much then it\'s a great choice but OnePlus as a company is not offering you something special  if you buy at by seeing their brand value and it\'s quite similar to Realme Mobiles.\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhanraj restaurant\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Looks and feels premiumWorth the money\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Chandan\", \"rating\": \"5.0\", \"date\": \"31 Jul 2024\", \"text\": \"I recently purchased the OnePlus Nord CE 4 Lite, and it has truly exceeded my expectations, deserving a solid 5-star rating. Here’s a detailed breakdown of why this phone is an excellent choice:Design and Build Quality: The OnePlus Nord CE 4 Lite boasts a sleek, modern design with a premium feel. The materials used are top-notch, giving it a solid and durable build. Its slim profile and lightweight nature make it comfortable to hold and use for extended periods.Display: The phone features a stunning AMOLED display with vibrant colors and sharp resolution. Whether watching videos, playing games, or browsing the web, the visuals are crisp and clear. The high refresh rate adds to the smoothness of the experience, making every interaction buttery smooth.Performance: Powered by the Qualcomm Snapdragon 695 SoC, the OnePlus Nord CE 4 Lite handles everything with ease. From multitasking to running graphic-intensive games, it performs without a hitch. While the processor might not be the latest, it still delivers reliable performance for daily use.Camera: The camera setup is impressive, especially the 50MP main sensor, which captures detailed and vibrant photos even in low light. The wide-angle lens adds versatility, allowing for creative shots. The video recording quality is also top-notch, with stable and clear footage. However, low-light photography could use some improvement.Battery Life: Battery life is outstanding, easily lasting a full day with moderate to heavy use. The 5,500mAh battery ensures you won’t run out of juice during the day. The fast charging feature is a lifesaver, allowing you to quickly top up the battery when needed.Additional Features: The phone has an official IP54 certification for protection against water splashes and dust. The design, inspired by minimalist tones and patterns, gives it a premium look. The 3.5mm audio jack is a bonus for wired earphone users.In conclusion, the OnePlus Nord CE 4 Lite is an excellent smartphone in its price segment. Its design, display, performance, and battery life make it a worthy contender. While it could benefit from a newer processor and improved low-light camera performance, it still offers great value for money. For daily usage, the Nord CE 4 Lite will not disappoint.\n  \nRead more\", \"product_id\": \"B0D5YCYS1G\", \"link\": \"https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>realme NARZO 70 Turbo 5G</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>14</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>14</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DDTXW9WH\", \"product_name\": \"realme NARZO 70 Turbo 5G (Turbo Green,6GB RAM,128GB Storage) | Segment\'s Fastest Dimensity 7300 Energy 5G Chipset | Motorsports Inspired Design\", \"product_url\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"summary\": {\"total_reviews\": 14, \"average_rating\": 4.43, \"sentiment_breakdown\": {\"positive\": 14}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"PRAVEEN.PS\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    One of the best phone in 15 k price range. Display Good, Camera good, can record 4k 30fps videos using rear camera. Front camera is ok. Missing AI features which is available in other phones in the price range. Expandable memory, 3.5 mm audio jack, dual speakers available. Gaming also have good response without lag. Battery backup is ok. Only drawback I noticed is that this phone is in Android 14.2 android updates available\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Aditya JatwaAditya Jatwa\", \"rating\": \"4.0\", \"date\": \"17 May 2025\", \"text\": \"If you want performance and don\'t care about anything else then this is itBgmi 90fps is for tdmIn classic mode you get average 70 to 75fps in intense fights and it has 3.5mm jack which is bonus as of today now even it\'s successor narzo 80 pro don\'t have 3.5mm jack i also updated on realme ui 6.0 and the experience is too good, animations are very smooth and fast. I get 7.5hr screen on time including gaming Internet surfing YouTube and offline movie on 120hz. And on 60hz you get extra 1hr. Brightness is enough in outdoor mode. It has O-reality audio but not dolby atmos which is slight drawback i guessBut it\'s only effective if you are using any high res audio file and headphones like sony sennheiser bose etc. Otherwise doesn\'t matter. Haptic motor are worse, cameras are not that great but it\'s main cam takes fine pictures in daylight in lowlight it sucks.And remember once you boot the device simply off the all features like app marketAnd Get recommendations in settings appSo you don\'t see any ads in. File manager.I purchased the 12/256 gb in 17490 without any bank offer. Bcoz in future games and apps will require more resources and storage. But if you are on tight budget then purchase 6/128gb which comes around under 14k in sale.\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Siuli Hait\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"The phone is amazing in this prize range. It\'s working good. Speed is excellent. I am fully satisfied with it. Go for it without any second thought. Look is good. Screen is broad. After working,the set is not hot. It is very slim and it will guide you properly for the next step. It\'s user friendly.\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"NirmalaNirmala\", \"rating\": \"5.0\", \"date\": \"06 Nov 2024\", \"text\": \"My ratings 4.45/5⭐Okay! I\'m writing this review after one month of usage. I played BGMI and FF, ran antutu test and cpu throttling too..Pros:-1) Gaming:-  No doubt that this is the best phone for gaming at this price segment, I played both FF and BGMI on this device, the dimensity 7300 processor runs so smoothly so that you can experience a lag free gaming even in high graphics/resolution. (To experience true 90FPS gaming you need to turn on the GT mode).2)Performance:- Gaming phones generally do perform well on normal usage too, same here, the processor was good enough and runs smoothly even on multitasking. (Can give a max of 120hz refresh rate). Performance wise no doubt, you will be satisfied!3)Design and display: The 6.67 inch OLED display was really good and appreciable!4)Camera:- Although primarily this was not a camera phone but still the picture quality was fine and good, with a 50mp back camera and 16mp front camera (Back camera was better though).5)Battery:- Battery backup was good, comes with a 45W supervoc UF inbox charger, Takes almost 1 hr 20 mins to charge fully from zero. Can give a full working day backup on normal usage.6) Sound quality:- Sound quality was fine, The stereo speakers are loud and clear, For calls they\'ve included clear voice(ENC) feature too.(There was no Dolby Atmos BTW, should \'ve included it! :)7) Comfort in hand: Trust me, this mobile is really comfortable in hand while holding and gaming. You don\'t feel any slipperiness.Cons:-1) The main problem i personally experienced is \'overheating\', like wtf man it goes till 42.5°C while charging and 41°C while gaming at a room temperature of 30 degrees!!2) Too much bloatware from the app market (although you can clear it).3) build quality/looks:-  The built quality can be improved, both frame and back comes with a plastic material and No Gorrila glass too:)4) Should also have included NFC tap to pay or Gorrila glass as most phone\'s at this price are providing any one of them.5) Antutu scores: When I ran antutu test, it scored nearly 670k (BTW they\'ve said 750k)👎🏻. Although 670k was a good score, it was much lesser than what they\'ve said(750k).Final verdict: This phone was mainly focused on gaming and performance, if you are a mobile gamer or need a good performance mobile, you can go for it. If you prefer good camera and build quality/design this  might not be a better choice for you!!This phone worked well for me!! I advice you to check other reviews too:)\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sandeep singhSandeep singh\", \"rating\": \"4.0\", \"date\": \"09 Mar 2025\", \"text\": \"So far is good. I do face some problem during going back sometimes it\'s don\'t work. Although I knew about how it\'s focused on processor but front camera is really disappointed. I\'m not talking about quality but it\'s beaut filter option it\'s so annoying I don\'t know how to turn it off or whether you can. Anyway gaming experience was good. Back camera is also good enough. Look is okay. Camera is kinda big compare to it\'s actual ability anyway I think it\'s worth the money\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Santosh Pandey\", \"rating\": \"3.0\", \"date\": \"10 Apr 2025\", \"text\": \"First of all the phone is good. The specs it have is good as compared to other phones come in this segment. But it have some issues I am facing and itProsComes with latest technologiesDual mode video support (like GoPro)Attractive features like dynamic island, torch level, customization, etc.ConsFace lagingPhone hangingEven get stuck sometime and need to click power button then turn off the screen and again need to unlock to remove hangMinor heatingCamera is not that good\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"MahendranMahendran\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"📸 Best cameraBest performance ⚡Best battery backup 🔋 👌🏻❣️Overall best smartphone in that budget 15k 💸Mind-blowing purchase✨\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"PRAVEEN.PS\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    One of the best phone in 15 k price range. Display Good, Camera good, can record 4k 30fps videos using rear camera. Front camera is ok. Missing AI features which is available in other phones in the price range. Expandable memory, 3.5 mm audio jack, dual speakers available. Gaming also have good response without lag. Battery backup is ok. Only drawback I noticed is that this phone is in Android 14.2 android updates available\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Aditya JatwaAditya Jatwa\", \"rating\": \"4.0\", \"date\": \"17 May 2025\", \"text\": \"If you want performance and don\'t care about anything else then this is itBgmi 90fps is for tdmIn classic mode you get average 70 to 75fps in intense fights and it has 3.5mm jack which is bonus as of today now even it\'s successor narzo 80 pro don\'t have 3.5mm jack i also updated on realme ui 6.0 and the experience is too good, animations are very smooth and fast. I get 7.5hr screen on time including gaming Internet surfing YouTube and offline movie on 120hz. And on 60hz you get extra 1hr. Brightness is enough in outdoor mode. It has O-reality audio but not dolby atmos which is slight drawback i guessBut it\'s only effective if you are using any high res audio file and headphones like sony sennheiser bose etc. Otherwise doesn\'t matter. Haptic motor are worse, cameras are not that great but it\'s main cam takes fine pictures in daylight in lowlight it sucks.And remember once you boot the device simply off the all features like app marketAnd Get recommendations in settings appSo you don\'t see any ads in. File manager.I purchased the 12/256 gb in 17490 without any bank offer. Bcoz in future games and apps will require more resources and storage. But if you are on tight budget then purchase 6/128gb which comes around under 14k in sale.\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Siuli Hait\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"The phone is amazing in this prize range. It\'s working good. Speed is excellent. I am fully satisfied with it. Go for it without any second thought. Look is good. Screen is broad. After working,the set is not hot. It is very slim and it will guide you properly for the next step. It\'s user friendly.\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"NirmalaNirmala\", \"rating\": \"5.0\", \"date\": \"06 Nov 2024\", \"text\": \"My ratings 4.45/5⭐Okay! I\'m writing this review after one month of usage. I played BGMI and FF, ran antutu test and cpu throttling too..Pros:-1) Gaming:-  No doubt that this is the best phone for gaming at this price segment, I played both FF and BGMI on this device, the dimensity 7300 processor runs so smoothly so that you can experience a lag free gaming even in high graphics/resolution. (To experience true 90FPS gaming you need to turn on the GT mode).2)Performance:- Gaming phones generally do perform well on normal usage too, same here, the processor was good enough and runs smoothly even on multitasking. (Can give a max of 120hz refresh rate). Performance wise no doubt, you will be satisfied!3)Design and display: The 6.67 inch OLED display was really good and appreciable!4)Camera:- Although primarily this was not a camera phone but still the picture quality was fine and good, with a 50mp back camera and 16mp front camera (Back camera was better though).5)Battery:- Battery backup was good, comes with a 45W supervoc UF inbox charger, Takes almost 1 hr 20 mins to charge fully from zero. Can give a full working day backup on normal usage.6) Sound quality:- Sound quality was fine, The stereo speakers are loud and clear, For calls they\'ve included clear voice(ENC) feature too.(There was no Dolby Atmos BTW, should \'ve included it! :)7) Comfort in hand: Trust me, this mobile is really comfortable in hand while holding and gaming. You don\'t feel any slipperiness.Cons:-1) The main problem i personally experienced is \'overheating\', like wtf man it goes till 42.5°C while charging and 41°C while gaming at a room temperature of 30 degrees!!2) Too much bloatware from the app market (although you can clear it).3) build quality/looks:-  The built quality can be improved, both frame and back comes with a plastic material and No Gorrila glass too:)4) Should also have included NFC tap to pay or Gorrila glass as most phone\'s at this price are providing any one of them.5) Antutu scores: When I ran antutu test, it scored nearly 670k (BTW they\'ve said 750k)👎🏻. Although 670k was a good score, it was much lesser than what they\'ve said(750k).Final verdict: This phone was mainly focused on gaming and performance, if you are a mobile gamer or need a good performance mobile, you can go for it. If you prefer good camera and build quality/design this  might not be a better choice for you!!This phone worked well for me!! I advice you to check other reviews too:)\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sandeep singhSandeep singh\", \"rating\": \"4.0\", \"date\": \"09 Mar 2025\", \"text\": \"So far is good. I do face some problem during going back sometimes it\'s don\'t work. Although I knew about how it\'s focused on processor but front camera is really disappointed. I\'m not talking about quality but it\'s beaut filter option it\'s so annoying I don\'t know how to turn it off or whether you can. Anyway gaming experience was good. Back camera is also good enough. Look is okay. Camera is kinda big compare to it\'s actual ability anyway I think it\'s worth the money\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Santosh Pandey\", \"rating\": \"3.0\", \"date\": \"10 Apr 2025\", \"text\": \"First of all the phone is good. The specs it have is good as compared to other phones come in this segment. But it have some issues I am facing and itProsComes with latest technologiesDual mode video support (like GoPro)Attractive features like dynamic island, torch level, customization, etc.ConsFace lagingPhone hangingEven get stuck sometime and need to click power button then turn off the screen and again need to unlock to remove hangMinor heatingCamera is not that good\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"MahendranMahendran\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"📸 Best cameraBest performance ⚡Best battery backup 🔋 👌🏻❣️Overall best smartphone in that budget 15k 💸Mind-blowing purchase✨\n  \nRead more\", \"product_id\": \"B0DDTXW9WH\", \"link\": \"https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>16</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>16</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CHX1W1XY\", \"product_name\": \"Apple iPhone 15 (128 GB) - Black\", \"product_url\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.75, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"NIDHI SOMANI\", \"rating\": \"5.0\", \"date\": \"21 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the iPhone 15 in Pink from Amazon, and I couldn’t be happier with my decision! From the moment I unboxed it, the sleek design and soft pastel pink color caught my attention—it looks even better in person than in pictures. Phone is lightweight aluminum and glass build, making the phone feel premium yet comfortable to hold. The pink shade is elegant and subtle, perfect for anyone who loves a touch of sophistication. The 6.1-inch Super Retina XDR display is bright, sharp, and offers vibrant colors. Whether watching videos or scrolling through social media, the experience is smooth and immersive. The 48MP main camera and 12MP ultra-wide lens take incredible photos, even in low light. The details, sharpness, and colors are truly impressive. Portrait mode works beautifully, capturing professional-looking shots effortlessly. The front camera is equally good for selfies and FaceTime. Charging with the USB-C port is much more convenient than before, and fast charging is a plus. The delivery was fast and secure, with the iPhone arriving in perfect condition. The packaging was intact, and setting up the phone was a breeze. If you\'re looking for a stylish, powerful, and reliable phone, the iPhone 15 in Pink is a fantastic choice.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"TheBOt2.9TheBOt2.9\", \"rating\": \"5.0\", \"date\": \"03 Apr 2025\", \"text\": \"The iPhone 15 has truly surpassed all my expectations. Its elegant design, breathtaking display, and remarkably swift performance establish it as a premier device within the smartphone arena. The camera\'s exceptional quality allows for the capture of every moment with astonishing detail and clarity. Furthermore, the battery life is notably robust, effortlessly sustaining me through an entire day\'s use. Securing the iPhone 15 from Amazon, especially with the advantageous deal and discount, felt like an absolute bargain.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abhi Harshe\", \"rating\": \"5.0\", \"date\": \"20 Apr 2025\", \"text\": \"Got my iPhone 15 from Amazon, and honestly, 10/10 on the unboxing vibes. Packing was neat, no dents, no drama. Delivery guy showed up right on time like he had a GPS tracker on my excitement.The phone? 100% original – not one of those “iPhoney” deals. It runs super smooth, apps load faster than my brain in the morning, and the camera? Oh man, it makes my average face look Hollywood-ready. Portrait mode is basically magic.Now for the tiny hiccup – the battery. Let’s just say it gets tired quickly. You blink, and it’s already asking for a nap. But hey, with great power comes… slightly faster charging breaks.Overall, loving it. Just keep a charger nearby and you’re golden.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sahil Arora\", \"rating\": \"4.0\", \"date\": \"26 May 2025\", \"text\": \"The iPhone 15 is a noticeable step up from previous models. The design feels premium, and the new green color is subtle yet refreshing. Performance is smooth — apps launch instantly, and multitasking is seamless. The camera system is excellent, especially in low light, and photos come out crisp and vibrant. Battery life easily lasts a full day, even with heavy use. The display is bright and clear, perfect for watching videos or browsing. If you\'re upgrading from an older iPhone, the iPhone 15 feels like a worthy investment. It’s reliable, fast, and beautifully designed.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"HINDUSTAN ELECTRICALSHINDUSTAN ELECTRICALS\", \"rating\": \"5.0\", \"date\": \"06 Oct 2023\", \"text\": \"DesignOne of the most noticeable changes to the iPhone 15 is its new design. The phone now has rounded edges, which makes it feel more comfortable in the hand. It also has a new camera bump that is less pronounced than the one on the iPhone 14.DisplayThe iPhone 15 has the same 6.1-inch Super Retina XDR display as the iPhone 14. However, the new display is brighter and has better contrast. It also supports HDR10 and Dolby Vision.PerformanceThe iPhone 15 is powered by the new A16 Bionic chip, which is the fastest mobile chip on the market. The A16 Bionic chip is up to 20% faster than the A15 Bionic chip in the iPhone 14.CameraThe iPhone 15 has a new 48-megapixel main camera. The new camera sensor is larger than the one in the iPhone 14, and it has better low-light performance. The iPhone 15 also has a new 12-megapixel ultrawide camera and a new 12-megapixel telephoto camera.Battery lifeThe iPhone 15 has the same battery life as the iPhone 14. This means that you can expect to get around a day of use on a single charge.  Overall  The iPhone 15 is a solid upgrade over the iPhone 14.ProsNew design with rounded edgesMore powerful A16 Bionic chip found in 14 proNew 48-megapixel main cameraBrighter display with upto 2000 nits brightnessUSB C can be used for anythingDynamic IslandConsNo 120hz displayNo Macro photography\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Madhusudan GoswamiMadhusudan Goswami\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Good Product.Smoothly workingCamera is excellent.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Talib ahmad\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"Nice phone\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shani\", \"rating\": \"4.0\", \"date\": \"24 May 2025\", \"text\": \"Goood phone for the price if u into apple . Great cameras it’s nice to have a proper 2x zoom on normal variant and not loosing much quality and it also nice to have usb c and it charge okey speed . But whenever I play games it heats up (not soo hot but hot enough to know) fast that’s the only issue I faced using this phone\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"NIDHI SOMANI\", \"rating\": \"5.0\", \"date\": \"21 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the iPhone 15 in Pink from Amazon, and I couldn’t be happier with my decision! From the moment I unboxed it, the sleek design and soft pastel pink color caught my attention—it looks even better in person than in pictures. Phone is lightweight aluminum and glass build, making the phone feel premium yet comfortable to hold. The pink shade is elegant and subtle, perfect for anyone who loves a touch of sophistication. The 6.1-inch Super Retina XDR display is bright, sharp, and offers vibrant colors. Whether watching videos or scrolling through social media, the experience is smooth and immersive. The 48MP main camera and 12MP ultra-wide lens take incredible photos, even in low light. The details, sharpness, and colors are truly impressive. Portrait mode works beautifully, capturing professional-looking shots effortlessly. The front camera is equally good for selfies and FaceTime. Charging with the USB-C port is much more convenient than before, and fast charging is a plus. The delivery was fast and secure, with the iPhone arriving in perfect condition. The packaging was intact, and setting up the phone was a breeze. If you\'re looking for a stylish, powerful, and reliable phone, the iPhone 15 in Pink is a fantastic choice.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"TheBOt2.9TheBOt2.9\", \"rating\": \"5.0\", \"date\": \"03 Apr 2025\", \"text\": \"The iPhone 15 has truly surpassed all my expectations. Its elegant design, breathtaking display, and remarkably swift performance establish it as a premier device within the smartphone arena. The camera\'s exceptional quality allows for the capture of every moment with astonishing detail and clarity. Furthermore, the battery life is notably robust, effortlessly sustaining me through an entire day\'s use. Securing the iPhone 15 from Amazon, especially with the advantageous deal and discount, felt like an absolute bargain.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abhi Harshe\", \"rating\": \"5.0\", \"date\": \"20 Apr 2025\", \"text\": \"Got my iPhone 15 from Amazon, and honestly, 10/10 on the unboxing vibes. Packing was neat, no dents, no drama. Delivery guy showed up right on time like he had a GPS tracker on my excitement.The phone? 100% original – not one of those “iPhoney” deals. It runs super smooth, apps load faster than my brain in the morning, and the camera? Oh man, it makes my average face look Hollywood-ready. Portrait mode is basically magic.Now for the tiny hiccup – the battery. Let’s just say it gets tired quickly. You blink, and it’s already asking for a nap. But hey, with great power comes… slightly faster charging breaks.Overall, loving it. Just keep a charger nearby and you’re golden.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sahil Arora\", \"rating\": \"4.0\", \"date\": \"26 May 2025\", \"text\": \"The iPhone 15 is a noticeable step up from previous models. The design feels premium, and the new green color is subtle yet refreshing. Performance is smooth — apps launch instantly, and multitasking is seamless. The camera system is excellent, especially in low light, and photos come out crisp and vibrant. Battery life easily lasts a full day, even with heavy use. The display is bright and clear, perfect for watching videos or browsing. If you\'re upgrading from an older iPhone, the iPhone 15 feels like a worthy investment. It’s reliable, fast, and beautifully designed.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"HINDUSTAN ELECTRICALSHINDUSTAN ELECTRICALS\", \"rating\": \"5.0\", \"date\": \"06 Oct 2023\", \"text\": \"DesignOne of the most noticeable changes to the iPhone 15 is its new design. The phone now has rounded edges, which makes it feel more comfortable in the hand. It also has a new camera bump that is less pronounced than the one on the iPhone 14.DisplayThe iPhone 15 has the same 6.1-inch Super Retina XDR display as the iPhone 14. However, the new display is brighter and has better contrast. It also supports HDR10 and Dolby Vision.PerformanceThe iPhone 15 is powered by the new A16 Bionic chip, which is the fastest mobile chip on the market. The A16 Bionic chip is up to 20% faster than the A15 Bionic chip in the iPhone 14.CameraThe iPhone 15 has a new 48-megapixel main camera. The new camera sensor is larger than the one in the iPhone 14, and it has better low-light performance. The iPhone 15 also has a new 12-megapixel ultrawide camera and a new 12-megapixel telephoto camera.Battery lifeThe iPhone 15 has the same battery life as the iPhone 14. This means that you can expect to get around a day of use on a single charge.  Overall  The iPhone 15 is a solid upgrade over the iPhone 14.ProsNew design with rounded edgesMore powerful A16 Bionic chip found in 14 proNew 48-megapixel main cameraBrighter display with upto 2000 nits brightnessUSB C can be used for anythingDynamic IslandConsNo 120hz displayNo Macro photography\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Madhusudan GoswamiMadhusudan Goswami\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Good Product.Smoothly workingCamera is excellent.\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Talib ahmad\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"Nice phone\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shani\", \"rating\": \"4.0\", \"date\": \"24 May 2025\", \"text\": \"Goood phone for the price if u into apple . Great cameras it’s nice to have a proper 2x zoom on normal variant and not loosing much quality and it also nice to have usb c and it charge okey speed . But whenever I play games it heats up (not soo hot but hot enough to know) fast that’s the only issue I faced using this phone\n  \nRead more\", \"product_id\": \"B0CHX1W1XY\", \"link\": \"https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HONOR X9b 5G</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CSDQ434W\", \"product_name\": \"HONOR X9b 5G (Midnight Black, 8GB + 256GB) | India\'s First Ultra-Bounce Anti-Drop Curved AMOLED Display | 5800mAh Battery | 108MP Primary Camera | Without Charger\", \"product_url\": \"https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8\", \"summary\": {\"total_reviews\": 6, \"average_rating\": 3.33, \"sentiment_breakdown\": {\"positive\": 4, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 66.67}, \"reviews\": [{\"author\": \"Vinit Gupta\", \"rating\": \"5.0\", \"date\": \"01 Mar 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently got my hands on the HONOR X9b during a fantastic deal, and I must say, it has been a delightful experience.Mentioning the experience after using the phone for more then a week.Display: The screen on the HONOR X9b is truly impressive. The colors are vibrant, and the display is crisp, providing a visually stunning experience for watching videos and browsing through photos and most importantly my eyes are safe. It\'s a visual treat that adds a whole new dimension to my smartphone experience.Performance: Zero issues with hanging or lagging. The HONOR X9b handles multitasking seamlessly, and switching between apps is a breeze. It has proven to be a reliable companion for all my daily tasks, making every interaction smooth and efficient. Also, being a moderate gamer, I feel its a great device to handle games on high settings.Battery Life: I\'m pleasantly surprised by the battery life. With normal usage, I can easily go through a full day, and there\'s still some juice left at the end. It\'s reassuring not to worry about constantly searching for a charger – a definite plus for a busy lifestyle.Design and Comfort: The sleek design of the HONOR X9b adds a touch of elegance, and it\'s comfortable to hold. The phone strikes the right balance in terms of weight. I always question myself how it comes with a 5800mAh massive battery? Making it a joy to use for extended periods without causing any discomfort.Camera: The camera on the HONOR X9b is outstanding. It captures sharp and vivid photos. Selfies come out looking great, and the overall camera performance adds a lot to the phone\'s appeal.In summary, my experience with the HONOR X9b has exceeded my expectations. From the stunning display to the reliable battery life and impressive camera performance, it\'s a device that offers great value. If you\'re considering an upgrade, the HONOR X9b is definitely worth considering – a smartphone that delivers on both style and substance. Highly recommended!\n  \nRead more\", \"product_id\": \"B0CSDQ434W\", \"link\": \"https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8\", \"sentiment\": \"positive\"}, {\"author\": \"Manoj Kumar VSManoj Kumar VS\", \"rating\": \"1.0\", \"date\": \"17 Jul 2024\", \"text\": \"### Expert Review: Honor X9b 5G Anti-Drop Curved Display-Dont Buy**Purchased Date**: May 7, 2024**Reviewed Date**: July 17, 2024and Updated on December 7 2024---Honor X9b 5G: Terrible Service, Spare Parts Delays, Display, and Signal IssuesReview:I purchased the HONOR X9b 5G (Sunrise Orange, 8GB + 256GB) on May 7, 2024, expecting a premium product with reliable after-sales service. However, this experience has been an absolute disappointment on multiple fronts.After an accidental fall, the phone’s glass broke, and a large black patch appeared on the display, making it unusable. When I contacted Honor’s service centers, I was informed that sourcing spare parts was a persistent issue. Despite submitting my phone for repair at a larger service center, even seven months later, the required parts have not arrived, leaving my phone unrepaired.To make matters worse, after a software update, the phone developed green and pink lines on the display—an issue widely reported online as being linked to faulty software. These lines often worsen over time, and with no replacement parts available, the phone remains inoperable.Additionally, the device suffers from poor signal reception. Despite being marketed as a 5G phone, it struggles to maintain consistent network connectivity, even in areas where other devices perform perfectly. This affects basic usability like calls, browsing, and app functionality, which is unacceptable for a phone in this price range.Attempts to seek assistance from Amazon were futile, as they redirected me to Honor, stating post-sale responsibility lies with the manufacturer. Honor\'s lack of accountability, unreliable software updates, unavailability of parts, and subpar network performance have made this the worst smartphone purchase I’ve ever made.I regret choosing Honor and strongly advise others to avoid this brand. If you value reliable service, quality hardware, and consistent network performance, look elsewhere. Honor does not deserve your money or trust.---\n  \nRead more\", \"product_id\": \"B0CSDQ434W\", \"link\": \"https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8\", \"sentiment\": \"negative\"}, {\"author\": \"Vimal\", \"rating\": \"4.0\", \"date\": \"23 Oct 2024\", \"text\": \"After Using this phone for last 3 months and here are obervations. First thing I did after getting the phone is turn OFF all software update due to fear of getting Green Line issue as reported by many users. Second Do Not put any back cover or use any tempered glass as it blocks the heat tranfer which Is also one of the main cause of green line. Lastly do not use any fast charger as the phone is capable of recieving only 2 amp during charging and slows down charging due to heat generated during charging. . I am using only 1 amp charger. Also set screen refresh rate to 60hz. The battery life of this phone is very good but battery is producing lot of heat and this phone does not have any cooling system and poor heat managment.  I also have iqoo Z9X in our family which has same SNAPDRAGON 6 GEN 1 chipset and bigger battery but it runs very Cool.  Huawei needs to work on heat management in their phone as nobody wants to spend 12k on new display. There is no call recording by default but you can use third party app like \\"Cube ACR\\" for call recording.Camera is ok but has really good night mode but no OIS which not acceptable at this price point. Overall it\'s good phone but I am not sure if this phone will survice hot Indian summer but So far it\'s working good.\n  \nRead more\", \"product_id\": \"B0CSDQ434W\", \"link\": \"https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8\", \"sentiment\": \"positive\"}, {\"author\": \"Vinit Gupta\", \"rating\": \"5.0\", \"date\": \"01 Mar 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently got my hands on the HONOR X9b during a fantastic deal, and I must say, it has been a delightful experience.Mentioning the experience after using the phone for more then a week.Display: The screen on the HONOR X9b is truly impressive. The colors are vibrant, and the display is crisp, providing a visually stunning experience for watching videos and browsing through photos and most importantly my eyes are safe. It\'s a visual treat that adds a whole new dimension to my smartphone experience.Performance: Zero issues with hanging or lagging. The HONOR X9b handles multitasking seamlessly, and switching between apps is a breeze. It has proven to be a reliable companion for all my daily tasks, making every interaction smooth and efficient. Also, being a moderate gamer, I feel its a great device to handle games on high settings.Battery Life: I\'m pleasantly surprised by the battery life. With normal usage, I can easily go through a full day, and there\'s still some juice left at the end. It\'s reassuring not to worry about constantly searching for a charger – a definite plus for a busy lifestyle.Design and Comfort: The sleek design of the HONOR X9b adds a touch of elegance, and it\'s comfortable to hold. The phone strikes the right balance in terms of weight. I always question myself how it comes with a 5800mAh massive battery? Making it a joy to use for extended periods without causing any discomfort.Camera: The camera on the HONOR X9b is outstanding. It captures sharp and vivid photos. Selfies come out looking great, and the overall camera performance adds a lot to the phone\'s appeal.In summary, my experience with the HONOR X9b has exceeded my expectations. From the stunning display to the reliable battery life and impressive camera performance, it\'s a device that offers great value. If you\'re considering an upgrade, the HONOR X9b is definitely worth considering – a smartphone that delivers on both style and substance. Highly recommended!\n  \nRead more\", \"product_id\": \"B0CSDQ434W\", \"link\": \"https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8\", \"sentiment\": \"positive\"}, {\"author\": \"Manoj Kumar VSManoj Kumar VS\", \"rating\": \"1.0\", \"date\": \"17 Jul 2024\", \"text\": \"### Expert Review: Honor X9b 5G Anti-Drop Curved Display-Dont Buy**Purchased Date**: May 7, 2024**Reviewed Date**: July 17, 2024and Updated on December 7 2024---Honor X9b 5G: Terrible Service, Spare Parts Delays, Display, and Signal IssuesReview:I purchased the HONOR X9b 5G (Sunrise Orange, 8GB + 256GB) on May 7, 2024, expecting a premium product with reliable after-sales service. However, this experience has been an absolute disappointment on multiple fronts.After an accidental fall, the phone’s glass broke, and a large black patch appeared on the display, making it unusable. When I contacted Honor’s service centers, I was informed that sourcing spare parts was a persistent issue. Despite submitting my phone for repair at a larger service center, even seven months later, the required parts have not arrived, leaving my phone unrepaired.To make matters worse, after a software update, the phone developed green and pink lines on the display—an issue widely reported online as being linked to faulty software. These lines often worsen over time, and with no replacement parts available, the phone remains inoperable.Additionally, the device suffers from poor signal reception. Despite being marketed as a 5G phone, it struggles to maintain consistent network connectivity, even in areas where other devices perform perfectly. This affects basic usability like calls, browsing, and app functionality, which is unacceptable for a phone in this price range.Attempts to seek assistance from Amazon were futile, as they redirected me to Honor, stating post-sale responsibility lies with the manufacturer. Honor\'s lack of accountability, unreliable software updates, unavailability of parts, and subpar network performance have made this the worst smartphone purchase I’ve ever made.I regret choosing Honor and strongly advise others to avoid this brand. If you value reliable service, quality hardware, and consistent network performance, look elsewhere. Honor does not deserve your money or trust.---\n  \nRead more\", \"product_id\": \"B0CSDQ434W\", \"link\": \"https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8\", \"sentiment\": \"negative\"}, {\"author\": \"Vimal\", \"rating\": \"4.0\", \"date\": \"23 Oct 2024\", \"text\": \"After Using this phone for last 3 months and here are obervations. First thing I did after getting the phone is turn OFF all software update due to fear of getting Green Line issue as reported by many users. Second Do Not put any back cover or use any tempered glass as it blocks the heat tranfer which Is also one of the main cause of green line. Lastly do not use any fast charger as the phone is capable of recieving only 2 amp during charging and slows down charging due to heat generated during charging. . I am using only 1 amp charger. Also set screen refresh rate to 60hz. The battery life of this phone is very good but battery is producing lot of heat and this phone does not have any cooling system and poor heat managment.  I also have iqoo Z9X in our family which has same SNAPDRAGON 6 GEN 1 chipset and bigger battery but it runs very Cool.  Huawei needs to work on heat management in their phone as nobody wants to spend 12k on new display. There is no call recording by default but you can use third party app like \\"Cube ACR\\" for call recording.Camera is ok but has really good night mode but no OIS which not acceptable at this price point. Overall it\'s good phone but I am not sure if this phone will survice hot Indian summer but So far it\'s working good.\n  \nRead more\", \"product_id\": \"B0CSDQ434W\", \"link\": \"https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HONOR 200 5G</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D6VJ6FYG\", \"product_name\": \"HONOR 200 5G (8GB+256GB, Black) – 50MP+50MP+12MP Triple Camera with Dual OIS | 50MP Selfie | Quad-Curved AMOLED Display | AI-Powered MagicOS 9.0 | Without Charger\", \"product_url\": \"https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1\", \"summary\": {\"total_reviews\": 6, \"average_rating\": 4.67, \"sentiment_breakdown\": {\"positive\": 4, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 66.67}, \"reviews\": [{\"author\": \"Iam happy to buy the phone but Due to no after sales service provided by brand, iam returning the item. Iam happy to buy the phone but Due to no after sales service provided by brand, iam returning the item.\", \"rating\": \"5.0\", \"date\": \"13 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Such a superb device packed with bundle of very needful features that are helpful in every day work.I LOVE HONOR!!! The honor devices comes always with great features. Previously i used honor 4X it was  went for more than 4 years then switched to realme and now again after 5 years came to Honor. Honor devices are too good in camera quality than any other phones. Here are detailed review of honor 200 after using 4 months.1. Camera (4.7) :- its not a camera its an AI camera which is too smart that can detect type of image you are taking and prompt you accordingly. Crisp clear quality images it will generate with different modes. Especially the portrait mode was excellent. Front and back camera both support 50 megapixels perfectly.  You can see the images too that i uploaded.Super macro mode, night mode, slow motion, etc are available. However zoom quality beyond 10X is not upto the mark and upto 50X zoom it shakes too much but to overcome this problem you can switch to high resolution mode which captures full details in brighter environment. Overall its. Great Camera phone...2. Screen (4.5) :- It\'s a quad curved display with 120Hz ulta smooth refresh rate which gives you very comfortable to scroll anything. Also screen brightness is good enough to use in sunlight as well. But one thing company didn\'t mentioned is screen protection. Yes weird but screen protection is not upto the mark. One should definitely use screen protector like UV Glass otherwise you might get scratches and other problems.3. Battery (5) :- 5200 mAh silicon carbon battery is too good to handle dialy work without any worry. Battery is well optimized and can last upto 2 days from normal to heavy usage.  Except one thing that  while taking photos it can consume more battery then using any other apps which is quite surprising. Also the Honor supercharger charge the phone from 0 to 100% within 45 to 50 minutes. But however the box does not contain any charger I bought it separately which cost me around 2.5k with an offer.4. Ai Features(5) :- In this segment Honor absolutely worked well than any other brands witb its MagisOs. i have shown an images of Honor Ai which comes with lots a needful features like Ai eraser, magic capsule, magic text, magic portal, Ai subtitles, Ai translate.These are very useful features which save time for example you can directly copy text from images, you can directly take cutout from any image just by tapping on it and can use it somewhere where you need it. And lot more. Thanks to AI5 Other Features (4.5) :- It has dual Nano sim which also supports dual esim feature. Dual stereo speakers which gives impressive sound.IR Blaster also available. Also 5g speed is good i use jio which didn\'t bother me at all. Along with these it has Multi window mode, Favourite space, Ai noice cancellation etc.6. Os Updates (4.7) :- since from i bought this phone i got continuous monthly updates with some new features everytime.** Major Concern is that they told after sale service is not good and also you cannot get parts for this phone if unluckily phone is damaged by any how. In my case i never went to after sale for any of my phone which (honor  or realme ) till now. And i hope in future also i won\'t go for that.Overall its Great phone to use which i bought at 22k in offer.Thanks amazon and Thanks to the Honor...👍👍\n  \nRead more\", \"product_id\": \"B0D6VJ6FYG\", \"link\": \"https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Deepayan paulDeepayan paul\", \"rating\": \"4.0\", \"date\": \"29 Sep 2024\", \"text\": \"Pros -1. Superb speakers. it\'s doesn\'t have dolby but it can beat any other phone\'s speaker with Dolby.2. Back camera is Good but not the great Especially portrait mode is awesome.3. Ui/software experience is fluid. Doesn\'t lag or frezz. Although honor needs to implement much more features in the ui.4. No heating issues at all. Even with intensive task it goes maximum upto 41°overall day to day normal task will reach the device maximum upto 39°5. Insane battery backup in 120hz, the sot is 6.5-7 hours. If you use on 60hz will give you 8-9 hours sot.6. Lightweight device and slim.Cons -1. Front camera is 12 mp. With Hi-res capture it will take 50mp pictures but picture quality is not satisfictory, Skin tone issues, High contrast ,don\'t khow which sensor is this. even hardware info apps are not showing.Front camera is not well optimized.you will be disappointed in artificial indoor lighting photographs.. Low light photos are awful.sometimes skin tone got dark in artificial lighting.Also has the portrait mode lagging issues in camera ui.. Hope honor fixes the camera ui issues and skin tone issues with updates over time.overall got it @23749 with 5% cashback (amazonpayicicicard) Rs in Great Indian festival sale .totally value for money device.although didn\'t came with charger in the box.I have samsung 25watt pd charger which can fully charge the device within 1 hour.\n  \nRead more\", \"product_id\": \"B0D6VJ6FYG\", \"link\": \"https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"RAJESH PADAVALARAJESH PADAVALA\", \"rating\": \"5.0\", \"date\": \"05 Aug 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Been Using the Mighty Honor 200 from the Past 10 days &amp; I am spellbound by the Performance of the phone , awestruck with the Photos captured . The Visuals of the Display are vivid &amp; an eye feast to watch videos.The Best part is the camera of the phone ( 50MP Portrait  + 50MP Telephoto lens + 12MP Wide  &amp; 50MP Selfie camera ) . The best camera setup in the price segment. What I love the most is the Honor has collaborated with Studio Harcourt renewed for capturing Portraits of Hollywood Stars &amp; Celebrities. They together brought 3 stunning filters to capture studio level portraits. I have shared a few pictures captured using the Harcourt filters. The output is stunningly marvelous.  Posting them directly. No filters added &amp; no colour correction done.  Most importantly we don\'t  have any photography skills. It\'s all the magic of the Camera &amp; Harcourt Filters.If you are looking for the Phone to capture best Portraits , Honor200 is Undoubtedly the best choice.The Telephoto lens is outstanding . you could capture crisp photos even in 50X Zoom.The last 4 pictures , I have attached are captured from the same spot ( Ultrawide , 1X , 10X &amp; 50X Zoom )  You could see the names of the boards captured clearly in 50X zoom.Coming to the selfie camera , you could capture beautiful selfies with 50MP selfie camera.you could record 4K videos using both Rear &amp; Front camera . Dula video recording , slow motion video recording , Time lapse , Solo cut are the other camera options you could found.In Camera Department ,  Honor 200 is the complete package.Apart from the camera Yu can have the Honor Eye comfort Display with 3840Hz PWM Dimming for utmost eye care.Silicon -Carbob Battery with 5200mAh with 100W Wired charging .The UI is so smooth with Magic OS 8.0. The best part with Magic OS is , it pefectly synchronizes with the Hardware of the phone &amp; you will never faces any issue with performance.I have been using Honor20 from the past 5 years &amp; it still working like a charm , not even once I faced an issue like phone lagging . Thanks to Magic OS.There are so many Ai features that could make your life so easier with daily tasks. .I am not a Hardcore gamer . You could smoothly play games &amp; the Graphics are loading good in BGMI.I haven\'t played for long hours to check the performance while gaming.Positives-----------1) camera2) Display3) Charging4) Beautiful Design5) Magic OSCons------Charger could have Included in the Box\n  \nRead more\", \"product_id\": \"B0D6VJ6FYG\", \"link\": \"https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Iam happy to buy the phone but Due to no after sales service provided by brand, iam returning the item. Iam happy to buy the phone but Due to no after sales service provided by brand, iam returning the item.\", \"rating\": \"5.0\", \"date\": \"13 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Such a superb device packed with bundle of very needful features that are helpful in every day work.I LOVE HONOR!!! The honor devices comes always with great features. Previously i used honor 4X it was  went for more than 4 years then switched to realme and now again after 5 years came to Honor. Honor devices are too good in camera quality than any other phones. Here are detailed review of honor 200 after using 4 months.1. Camera (4.7) :- its not a camera its an AI camera which is too smart that can detect type of image you are taking and prompt you accordingly. Crisp clear quality images it will generate with different modes. Especially the portrait mode was excellent. Front and back camera both support 50 megapixels perfectly.  You can see the images too that i uploaded.Super macro mode, night mode, slow motion, etc are available. However zoom quality beyond 10X is not upto the mark and upto 50X zoom it shakes too much but to overcome this problem you can switch to high resolution mode which captures full details in brighter environment. Overall its. Great Camera phone...2. Screen (4.5) :- It\'s a quad curved display with 120Hz ulta smooth refresh rate which gives you very comfortable to scroll anything. Also screen brightness is good enough to use in sunlight as well. But one thing company didn\'t mentioned is screen protection. Yes weird but screen protection is not upto the mark. One should definitely use screen protector like UV Glass otherwise you might get scratches and other problems.3. Battery (5) :- 5200 mAh silicon carbon battery is too good to handle dialy work without any worry. Battery is well optimized and can last upto 2 days from normal to heavy usage.  Except one thing that  while taking photos it can consume more battery then using any other apps which is quite surprising. Also the Honor supercharger charge the phone from 0 to 100% within 45 to 50 minutes. But however the box does not contain any charger I bought it separately which cost me around 2.5k with an offer.4. Ai Features(5) :- In this segment Honor absolutely worked well than any other brands witb its MagisOs. i have shown an images of Honor Ai which comes with lots a needful features like Ai eraser, magic capsule, magic text, magic portal, Ai subtitles, Ai translate.These are very useful features which save time for example you can directly copy text from images, you can directly take cutout from any image just by tapping on it and can use it somewhere where you need it. And lot more. Thanks to AI5 Other Features (4.5) :- It has dual Nano sim which also supports dual esim feature. Dual stereo speakers which gives impressive sound.IR Blaster also available. Also 5g speed is good i use jio which didn\'t bother me at all. Along with these it has Multi window mode, Favourite space, Ai noice cancellation etc.6. Os Updates (4.7) :- since from i bought this phone i got continuous monthly updates with some new features everytime.** Major Concern is that they told after sale service is not good and also you cannot get parts for this phone if unluckily phone is damaged by any how. In my case i never went to after sale for any of my phone which (honor  or realme ) till now. And i hope in future also i won\'t go for that.Overall its Great phone to use which i bought at 22k in offer.Thanks amazon and Thanks to the Honor...👍👍\n  \nRead more\", \"product_id\": \"B0D6VJ6FYG\", \"link\": \"https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Deepayan paulDeepayan paul\", \"rating\": \"4.0\", \"date\": \"29 Sep 2024\", \"text\": \"Pros -1. Superb speakers. it\'s doesn\'t have dolby but it can beat any other phone\'s speaker with Dolby.2. Back camera is Good but not the great Especially portrait mode is awesome.3. Ui/software experience is fluid. Doesn\'t lag or frezz. Although honor needs to implement much more features in the ui.4. No heating issues at all. Even with intensive task it goes maximum upto 41°overall day to day normal task will reach the device maximum upto 39°5. Insane battery backup in 120hz, the sot is 6.5-7 hours. If you use on 60hz will give you 8-9 hours sot.6. Lightweight device and slim.Cons -1. Front camera is 12 mp. With Hi-res capture it will take 50mp pictures but picture quality is not satisfictory, Skin tone issues, High contrast ,don\'t khow which sensor is this. even hardware info apps are not showing.Front camera is not well optimized.you will be disappointed in artificial indoor lighting photographs.. Low light photos are awful.sometimes skin tone got dark in artificial lighting.Also has the portrait mode lagging issues in camera ui.. Hope honor fixes the camera ui issues and skin tone issues with updates over time.overall got it @23749 with 5% cashback (amazonpayicicicard) Rs in Great Indian festival sale .totally value for money device.although didn\'t came with charger in the box.I have samsung 25watt pd charger which can fully charge the device within 1 hour.\n  \nRead more\", \"product_id\": \"B0D6VJ6FYG\", \"link\": \"https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"RAJESH PADAVALARAJESH PADAVALA\", \"rating\": \"5.0\", \"date\": \"05 Aug 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    Been Using the Mighty Honor 200 from the Past 10 days &amp; I am spellbound by the Performance of the phone , awestruck with the Photos captured . The Visuals of the Display are vivid &amp; an eye feast to watch videos.The Best part is the camera of the phone ( 50MP Portrait  + 50MP Telephoto lens + 12MP Wide  &amp; 50MP Selfie camera ) . The best camera setup in the price segment. What I love the most is the Honor has collaborated with Studio Harcourt renewed for capturing Portraits of Hollywood Stars &amp; Celebrities. They together brought 3 stunning filters to capture studio level portraits. I have shared a few pictures captured using the Harcourt filters. The output is stunningly marvelous.  Posting them directly. No filters added &amp; no colour correction done.  Most importantly we don\'t  have any photography skills. It\'s all the magic of the Camera &amp; Harcourt Filters.If you are looking for the Phone to capture best Portraits , Honor200 is Undoubtedly the best choice.The Telephoto lens is outstanding . you could capture crisp photos even in 50X Zoom.The last 4 pictures , I have attached are captured from the same spot ( Ultrawide , 1X , 10X &amp; 50X Zoom )  You could see the names of the boards captured clearly in 50X zoom.Coming to the selfie camera , you could capture beautiful selfies with 50MP selfie camera.you could record 4K videos using both Rear &amp; Front camera . Dula video recording , slow motion video recording , Time lapse , Solo cut are the other camera options you could found.In Camera Department ,  Honor 200 is the complete package.Apart from the camera Yu can have the Honor Eye comfort Display with 3840Hz PWM Dimming for utmost eye care.Silicon -Carbob Battery with 5200mAh with 100W Wired charging .The UI is so smooth with Magic OS 8.0. The best part with Magic OS is , it pefectly synchronizes with the Hardware of the phone &amp; you will never faces any issue with performance.I have been using Honor20 from the past 5 years &amp; it still working like a charm , not even once I faced an issue like phone lagging . Thanks to Magic OS.There are so many Ai features that could make your life so easier with daily tasks. .I am not a Hardcore gamer . You could smoothly play games &amp; the Graphics are loading good in BGMI.I haven\'t played for long hours to check the performance while gaming.Positives-----------1) camera2) Display3) Charging4) Beautiful Design5) Magic OSCons------Charger could have Included in the Box\n  \nRead more\", \"product_id\": \"B0D6VJ6FYG\", \"link\": \"https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>realme GT 6T 5G</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D3J8HYDD\", \"product_name\": \"realme GT 6T 5G (Fluid Silver,12GB RAM+256GB Storage) | India\'s 1st 7+ Gen 3 Flagship Chipset | 1.5M + AnTuTu Score | 5500mAh+120W | The World\'s Brightest Flagship Display\", \"product_url\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"appuflee\", \"rating\": \"5.0\", \"date\": \"24 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent phoneGood battery backupNo lagsThere was heating issue while initially installing the apps, once it was updated to android 15, no heating at all.Camera does the jobEdge screen is awesomeWe need to use a case for sure, as the back is glossy, fingerprints easily destroy the look.Overall it\'s a killer for this budget.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ishan mahajan\", \"rating\": \"4.0\", \"date\": \"28 Sep 2024\", \"text\": \"I was using Samsung M51 from past 4 years and was looking for a new phone in 25-30k budget, couldn\'t find any Samsung phone in this budget which had better specifications than my ongoing M51.I started looking for another brands, since i naver used any other brand than Samsung i was bit hesitant in using RealMe, just took feedback from a friend who was using RealMe from last 4 years and purchased GT 6T.I am a normal user, not a gaming or photography guy. So far experience of using GT 6T has been good, not very great but good enough.Display of phone is very good feels better than my M51 which also have AMOLED, sound is very good, haptic feedback is good not like OnePlus but just upto the mark.Camera is ok. More or less similar to M51 there are multiple features but not used any of them till now.Issues I observed1. I was Not able to take calls when it is connected to car via bluetooth or Android auto, though it shows that sound is playing via car Audio but there was not sound, inhad to change something settings in USB debugging and it is working fine now.2. I was playing music via Amazon music and then started YouTube, YouTube video started but phone was still playing music from Amazon music instead of YouTube.This got fixed on its own.Phone never hanged, never falled off my hands so not sure about durability, i have not applied any screen guard since it has victus glass. m51 had just gorrila glass and it survived multiple falls in last 4 year hoping same for this phone.Battery backup is good for my usage, M51 had 7000 mah battery this one had 5500 but charging speed is very good. Even if it can hold 80 % battery capacity by next year i would be happy since it takes just 30 mins to charge to 100% by supplied charger.I will update this thread with time. This was my feedback of using this phone in last two weeks.Update 10-oct-2024I observed that phone does not ring some times and i directly get miss call notification, observed it 3 times in 20 days. No other issue till date.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shyamal BhattacharjeeShyamal Bhattacharjee\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"\\"I\'ve been using the Realme GT 6T for almost a week now, and I\'m thoroughly impressed. The performance is top-notch - I can play BGMI on 90fps with Ultra HDR and Ultra FPS without any issues. CarX Street runs smoothly on max graphics at 50fps, and Delta Force Mobile is solid on ultimate graphics at 40fps. Fortnite is buttery smooth at 80fps on low graphics. Thanks to Snapdragon 7+ Gen 3 , UFS 4.0 storage and LPDDR5X ram.The camera is another highlight - it captures amazing photos, even in low light. I love the Street mode feature, and 4K video recording at 60fps is a bonus. The Pro mode is also really good, giving me more control over my shots and the color profiles are nice too.The Curve display is simply impressive, with vibrant colors and great brightness. The phone also comes with an IR blaster, which is super convenient for controlling my TV and AC.The audio experience is immersive thanks to spatial sound, which makes gaming and watching videos even more engaging.The 120W SUPERVOC charging is blazing fast. The battery is good as well.The phone itself has a impressive design.Here are some pictures that I took with my phone.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Basudev GoraiBasudev Gorai\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"Really great phone under this price, chargeing super fast, battry long lasting, performance after realme ui 6 just extraordinaryDslr mode is great of this camera but quality and color is decent\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"20 Aug 2024\", \"text\": \"This is post 3 days of using of phone and simply couldn\'t resist myself from writing this review. Got the Razor Green 12 GB 512 GB for 32K post Bank discount. Adding some context before diving into my experience. I was an S22 Ultra user and ditched the same for OnePlus 12 SD8G3. I wanted an add on phone for office use and for gaming (BGMI &amp; MKX). Got this one post going through round of comparisons against IQOOs out there. Not I just had one sim in the phone as I was using it. So coming straight to how I rate this phone. It is a 5/5 for me.Looks: 4/5 ✌️✌️✌️✌️Display: 5/5 🤩🤩🤩🤩🤩Touch Response: 5/5 🧈🧈🧈🧈🧈Performance: 5/5 ✨✨✨✨✨Gaming performance: 5/5 👍👍👍👍👍Speaker Output: 5/5 ( very decent)Battery: 10/5 ( Simply marvellous)Charging speed: 15/5 (no comments)Camera: 4/5 (boosted this up from 3 to 4 based off overall happiness with the phone and considering the price factor)OS: 4/5 (-1 because of few preloaded apps)Finger print scanner: 5/5So what I loved: Display and performance crisp and buttery smooth. OS is clean too to the most. SD7+G3 takes on any tasks thrown on it with ease. No hassles in multitasking. Got July security patch as of yesterday so all good on that front too. Now speaking about what I\'m in love with - Being an S22 Ultra user I must say the biggest pain point has been battery since day 1. Max gaming time 3.5 Hrs. in the initial days which reduced to 1.5 over a span of 2 years. Stand-by was crazy bad too on S22 Ultra. This Lil gizmo GT 6T is a dream in this case. 3 days of game play BGMI 5 Hrs. each day and was left with 22% of juice still remaining each time. And post sleep of 6 hrs. the phone still retained 17% of charge. This already is insane in my perspective.Now coming to the charging aspect, this is unimaginable. Lightning fast... 17% - 100% in 22 minutes. Speechless in this front. Sammy used to take like 1 hr and 10 mins. in the initial days and post an year and half I really don\'t know. Gaming done without gtmode. Frame rate was set to auto adaptive. BGMI played in Smooth Extreme+. Brightness at ~45%. No throttling or heating. It got slightly warm at a point (really no where close to be called as heating) and then cooled too which is 😍😍😍.WhatsApp, FB, Insta, Gmail, O365, Teams and all other apps on the background. So you can go for this one blindfolded if you are looking for a phone with great backup and performance (gaming performance). I hope this is helpful.What I didn\'t like: Given all of above a 3.5 mm slot was expected. And sound output in headphones could have been better. I used Sony WH1000XM3 for gaming and Wf1000XM4 for listening to music and watching movie to test the output. Again you can hear all the footsteps and minute details and same applies to music if not all details but covers 90% of it but somewhere lacks the loudness factor by a bit and no Dolby Atmos so less to mention there.Lastly, I didn\'t cover anything on cam perspective because I was really not looking at this phone from that aspect and me sharing my experience on that front will definitely make no sense as the comparison will be against S22 Ultra here and this reaches no where close to it which is completely fine given it is not even 1/4th of the price for which I had bought S22 Ultra. That said both front and rear cam are decent is all I can say from price point perspective.Overall this is a bang on deal from my perspective and would definitely recommend going for it if you are not cam centric and looking for a great performer!\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"appuflee\", \"rating\": \"5.0\", \"date\": \"24 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent phoneGood battery backupNo lagsThere was heating issue while initially installing the apps, once it was updated to android 15, no heating at all.Camera does the jobEdge screen is awesomeWe need to use a case for sure, as the back is glossy, fingerprints easily destroy the look.Overall it\'s a killer for this budget.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ishan mahajan\", \"rating\": \"4.0\", \"date\": \"28 Sep 2024\", \"text\": \"I was using Samsung M51 from past 4 years and was looking for a new phone in 25-30k budget, couldn\'t find any Samsung phone in this budget which had better specifications than my ongoing M51.I started looking for another brands, since i naver used any other brand than Samsung i was bit hesitant in using RealMe, just took feedback from a friend who was using RealMe from last 4 years and purchased GT 6T.I am a normal user, not a gaming or photography guy. So far experience of using GT 6T has been good, not very great but good enough.Display of phone is very good feels better than my M51 which also have AMOLED, sound is very good, haptic feedback is good not like OnePlus but just upto the mark.Camera is ok. More or less similar to M51 there are multiple features but not used any of them till now.Issues I observed1. I was Not able to take calls when it is connected to car via bluetooth or Android auto, though it shows that sound is playing via car Audio but there was not sound, inhad to change something settings in USB debugging and it is working fine now.2. I was playing music via Amazon music and then started YouTube, YouTube video started but phone was still playing music from Amazon music instead of YouTube.This got fixed on its own.Phone never hanged, never falled off my hands so not sure about durability, i have not applied any screen guard since it has victus glass. m51 had just gorrila glass and it survived multiple falls in last 4 year hoping same for this phone.Battery backup is good for my usage, M51 had 7000 mah battery this one had 5500 but charging speed is very good. Even if it can hold 80 % battery capacity by next year i would be happy since it takes just 30 mins to charge to 100% by supplied charger.I will update this thread with time. This was my feedback of using this phone in last two weeks.Update 10-oct-2024I observed that phone does not ring some times and i directly get miss call notification, observed it 3 times in 20 days. No other issue till date.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shyamal BhattacharjeeShyamal Bhattacharjee\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"\\"I\'ve been using the Realme GT 6T for almost a week now, and I\'m thoroughly impressed. The performance is top-notch - I can play BGMI on 90fps with Ultra HDR and Ultra FPS without any issues. CarX Street runs smoothly on max graphics at 50fps, and Delta Force Mobile is solid on ultimate graphics at 40fps. Fortnite is buttery smooth at 80fps on low graphics. Thanks to Snapdragon 7+ Gen 3 , UFS 4.0 storage and LPDDR5X ram.The camera is another highlight - it captures amazing photos, even in low light. I love the Street mode feature, and 4K video recording at 60fps is a bonus. The Pro mode is also really good, giving me more control over my shots and the color profiles are nice too.The Curve display is simply impressive, with vibrant colors and great brightness. The phone also comes with an IR blaster, which is super convenient for controlling my TV and AC.The audio experience is immersive thanks to spatial sound, which makes gaming and watching videos even more engaging.The 120W SUPERVOC charging is blazing fast. The battery is good as well.The phone itself has a impressive design.Here are some pictures that I took with my phone.\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Basudev GoraiBasudev Gorai\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"Really great phone under this price, chargeing super fast, battry long lasting, performance after realme ui 6 just extraordinaryDslr mode is great of this camera but quality and color is decent\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"20 Aug 2024\", \"text\": \"This is post 3 days of using of phone and simply couldn\'t resist myself from writing this review. Got the Razor Green 12 GB 512 GB for 32K post Bank discount. Adding some context before diving into my experience. I was an S22 Ultra user and ditched the same for OnePlus 12 SD8G3. I wanted an add on phone for office use and for gaming (BGMI &amp; MKX). Got this one post going through round of comparisons against IQOOs out there. Not I just had one sim in the phone as I was using it. So coming straight to how I rate this phone. It is a 5/5 for me.Looks: 4/5 ✌️✌️✌️✌️Display: 5/5 🤩🤩🤩🤩🤩Touch Response: 5/5 🧈🧈🧈🧈🧈Performance: 5/5 ✨✨✨✨✨Gaming performance: 5/5 👍👍👍👍👍Speaker Output: 5/5 ( very decent)Battery: 10/5 ( Simply marvellous)Charging speed: 15/5 (no comments)Camera: 4/5 (boosted this up from 3 to 4 based off overall happiness with the phone and considering the price factor)OS: 4/5 (-1 because of few preloaded apps)Finger print scanner: 5/5So what I loved: Display and performance crisp and buttery smooth. OS is clean too to the most. SD7+G3 takes on any tasks thrown on it with ease. No hassles in multitasking. Got July security patch as of yesterday so all good on that front too. Now speaking about what I\'m in love with - Being an S22 Ultra user I must say the biggest pain point has been battery since day 1. Max gaming time 3.5 Hrs. in the initial days which reduced to 1.5 over a span of 2 years. Stand-by was crazy bad too on S22 Ultra. This Lil gizmo GT 6T is a dream in this case. 3 days of game play BGMI 5 Hrs. each day and was left with 22% of juice still remaining each time. And post sleep of 6 hrs. the phone still retained 17% of charge. This already is insane in my perspective.Now coming to the charging aspect, this is unimaginable. Lightning fast... 17% - 100% in 22 minutes. Speechless in this front. Sammy used to take like 1 hr and 10 mins. in the initial days and post an year and half I really don\'t know. Gaming done without gtmode. Frame rate was set to auto adaptive. BGMI played in Smooth Extreme+. Brightness at ~45%. No throttling or heating. It got slightly warm at a point (really no where close to be called as heating) and then cooled too which is 😍😍😍.WhatsApp, FB, Insta, Gmail, O365, Teams and all other apps on the background. So you can go for this one blindfolded if you are looking for a phone with great backup and performance (gaming performance). I hope this is helpful.What I didn\'t like: Given all of above a 3.5 mm slot was expected. And sound output in headphones could have been better. I used Sony WH1000XM3 for gaming and Wf1000XM4 for listening to music and watching movie to test the output. Again you can hear all the footsteps and minute details and same applies to music if not all details but covers 90% of it but somewhere lacks the loudness factor by a bit and no Dolby Atmos so less to mention there.Lastly, I didn\'t cover anything on cam perspective because I was really not looking at this phone from that aspect and me sharing my experience on that front will definitely make no sense as the comparison will be against S22 Ultra here and this reaches no where close to it which is completely fine given it is not even 1/4th of the price for which I had bought S22 Ultra. That said both front and rear cam are decent is all I can say from price point perspective.Overall this is a bang on deal from my perspective and would definitely recommend going for it if you are not cam centric and looking for a great performer!\n  \nRead more\", \"product_id\": \"B0D3J8HYDD\", \"link\": \"https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-9&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>POCO M7 5G</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>66.67%</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0F135PGDX\", \"product_name\": \"POCO M7 5G, Ocean Blue (6GB, 128GB)\", \"product_url\": \"https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj\", \"summary\": {\"total_reviews\": 6, \"average_rating\": 2.67, \"sentiment_breakdown\": {\"neutral\": 4, \"positive\": 2}, \"overall_sentiment\": \"neutral\", \"accuracy_score\": 66.67}, \"reviews\": [{\"author\": \"Mohammad.Aamir\", \"rating\": \"3.0\", \"date\": \"23 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    poor touch\n  \nRead more\", \"product_id\": \"B0F135PGDX\", \"link\": \"https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj\", \"sentiment\": \"neutral\"}, {\"author\": \"sekar\", \"rating\": \"4.0\", \"date\": \"05 Apr 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0F135PGDX\", \"link\": \"https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj\", \"sentiment\": \"positive\"}, {\"author\": \"Santosh\", \"rating\": \"1.0\", \"date\": \"12 May 2025\", \"text\": \"Saste k chakkr me na fase bahut hi ghatiya kissam ka phon haiPlisse na kharido aap log acha hoga thoda 🙏\n  \nRead more\", \"product_id\": \"B0F135PGDX\", \"link\": \"https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj\", \"sentiment\": \"neutral\"}, {\"author\": \"Mohammad.Aamir\", \"rating\": \"3.0\", \"date\": \"23 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    poor touch\n  \nRead more\", \"product_id\": \"B0F135PGDX\", \"link\": \"https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj\", \"sentiment\": \"neutral\"}, {\"author\": \"sekar\", \"rating\": \"4.0\", \"date\": \"05 Apr 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0F135PGDX\", \"link\": \"https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj\", \"sentiment\": \"positive\"}, {\"author\": \"Santosh\", \"rating\": \"1.0\", \"date\": \"12 May 2025\", \"text\": \"Saste k chakkr me na fase bahut hi ghatiya kissam ka phon haiPlisse na kharido aap log acha hoga thoda 🙏\n  \nRead more\", \"product_id\": \"B0F135PGDX\", \"link\": \"https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lava Bold 5G</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>16</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0F1N1KN2K\", \"product_name\": \"Lava Bold 5G (Sapphire Blue, 6GB RAM, 128GB Storage) | 3D Curved FHD+ AMOLED Display | Mediatek Dimensity 6300 Processor | IP64 Water Resistance | 64MP Rear Sensor | Supports All Indian 5G Bands\", \"product_url\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.12, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 2, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"JP StuFFs\", \"rating\": \"5.0\", \"date\": \"24 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    For the brand like LAVA this is an unexpected product at unexpected price, since it has everything good and ticks all the boxes *except cameras* this could be better, rest all are good including- Stock Android experience which is smooth and not at all laggy- battery is solid for one day and sometimes more . It depends upon the usage- Curved Amoled display with 120 hz refresh rate for the price was major surprise ( this is the major highlight of this phone ) it\'s quality is too good for the price- Speaker could be better I felt.- 5G holds a good network- 128GB is more than enoughOverall a solid phone for the price\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rajesh reddy\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"Everyone who has seen this in my hand said it is worth more than 30k, so design is 100 out of 100Then comes the display again same the premium 120hz amoled curved screenThe performance is enough for a daily driverBattery life is amazing with normal calls and browsing apps it will last easily 3 days5g performance is great always strong signal than my previous phones and speed tooAlso it has VONR support and it is working greatFor the price its a great product\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sheikh Amin\", \"rating\": \"4.0\", \"date\": \"07 May 2025\", \"text\": \"Nice display, quick response in display unlock finger touch, quick face unlock, good battery backup, performance, design and functionality. Best brightness and clear font, good reading in the bright sun light. Go for it, nice deal and value for money.\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sujith\", \"rating\": \"1.0\", \"date\": \"07 May 2025\", \"text\": \"Very bad phone you cannot use the phone in sunlight as it gets heated and starts hanging and you have to restart your phone again and again. Wifi network is worst\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"bhuvan dave\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"Yes it\'s not the phone for  gaming ..!! but the way mediatec dimensity 6300 6nm processer handles all other personal and professional tasks including heavy multi tasking is realy appreciable.  Good for professional salaried, corporate employees, house wifes &amp; other day-to-day work.Good battery backup , Good looking , smoothe response of touch screen , Good Camara (lighting need to be adjusted while taking pics &amp; i hope lava will resoleve this by giving update)Overall It\'s good performance by Lava .\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vijay kumar\", \"rating\": \"3.0\", \"date\": \"07 May 2025\", \"text\": \"Average phone.\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"The product is super cool and efficient as well. Design too good 👍 value for money. No hanging problem. Speed I can say 4/5Display 5/5, Sound 5/5, No blotware. Overall best experience with lava.\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Bhanu pratap singh\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Front and back camera is good, back camera is very good, display quality, fingerprint both are very good, battery backup is also good, overall performance is very good,in this price segment phone is v v good you can go for it।\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"JP StuFFs\", \"rating\": \"5.0\", \"date\": \"24 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    For the brand like LAVA this is an unexpected product at unexpected price, since it has everything good and ticks all the boxes *except cameras* this could be better, rest all are good including- Stock Android experience which is smooth and not at all laggy- battery is solid for one day and sometimes more . It depends upon the usage- Curved Amoled display with 120 hz refresh rate for the price was major surprise ( this is the major highlight of this phone ) it\'s quality is too good for the price- Speaker could be better I felt.- 5G holds a good network- 128GB is more than enoughOverall a solid phone for the price\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rajesh reddy\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"Everyone who has seen this in my hand said it is worth more than 30k, so design is 100 out of 100Then comes the display again same the premium 120hz amoled curved screenThe performance is enough for a daily driverBattery life is amazing with normal calls and browsing apps it will last easily 3 days5g performance is great always strong signal than my previous phones and speed tooAlso it has VONR support and it is working greatFor the price its a great product\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sheikh Amin\", \"rating\": \"4.0\", \"date\": \"07 May 2025\", \"text\": \"Nice display, quick response in display unlock finger touch, quick face unlock, good battery backup, performance, design and functionality. Best brightness and clear font, good reading in the bright sun light. Go for it, nice deal and value for money.\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sujith\", \"rating\": \"1.0\", \"date\": \"07 May 2025\", \"text\": \"Very bad phone you cannot use the phone in sunlight as it gets heated and starts hanging and you have to restart your phone again and again. Wifi network is worst\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"bhuvan dave\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"Yes it\'s not the phone for  gaming ..!! but the way mediatec dimensity 6300 6nm processer handles all other personal and professional tasks including heavy multi tasking is realy appreciable.  Good for professional salaried, corporate employees, house wifes &amp; other day-to-day work.Good battery backup , Good looking , smoothe response of touch screen , Good Camara (lighting need to be adjusted while taking pics &amp; i hope lava will resoleve this by giving update)Overall It\'s good performance by Lava .\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vijay kumar\", \"rating\": \"3.0\", \"date\": \"07 May 2025\", \"text\": \"Average phone.\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"The product is super cool and efficient as well. Design too good 👍 value for money. No hanging problem. Speed I can say 4/5Display 5/5, Sound 5/5, No blotware. Overall best experience with lava.\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Bhanu pratap singh\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Front and back camera is good, back camera is very good, display quality, fingerprint both are very good, battery backup is also good, overall performance is very good,in this price segment phone is v v good you can go for it।\n  \nRead more\", \"product_id\": \"B0F1N1KN2K\", \"link\": \"https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Lava Agni 3 5G</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>14</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>16</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DGQMDVRV\", \"product_name\": \"Lava Agni 3 5G (Pristine Glass, 8GB+128GB) | India\'s 1st dual AMOLED | Dimensity 7300X | 50MP Triple AI Camera | 66W Fast Charge,5000 mAh Battery | Clean UI | Free Replacement @ Home | Without Charger\", \"product_url\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.75, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"GAURAV AGRAWAL\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Color quality is great and great design that makes it easy to carry. Moreover it is an excellent product, good battery performance, value for money, Great touch quality, Excellent performance.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"20 Apr 2025\", \"text\": \"Mobile under 25k with all the features loaded has premium look on your hand, just go for this. Battery backup is excellent I\'m a frequent user and it lasts up to 1.5 days solid and charges to 100% in just 30 to 40 min is quick charging for me.Camera is good but not great, I\'m not a camera person, still I use camera for selfie and other family events and I feel it gives you good shots. 120hz is cool, it works like a breeze, no lag have been seen so far of more than 1 month of use.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vijay Gir\", \"rating\": \"4.0\", \"date\": \"25 Jan 2025\", \"text\": \"I have been using the phone for the last 3 months. Battery backup is huge, you would not get such powerful battery in anyother phone, Inscreen fingerprint sensor is mind blowing. Performance is great, never faced any issue, does not hand, no lagging - be advised I do not play high graphic hungry games like CODM or any other battle royales. There is absolutely no heating issue. Touch quality is smooth. One crutial thing that Lava needs to work on is the camera. They have provided the wide angle camera which is great but the issue lies in the primary camera. For apparent no reasons the camera would go out of focus and even after trying for many minutes will not correct itself. Another thing is the zoom, as soon as you go above 2x, the quality will go towards bad and light capturing decreases.Apart from these issues, the phone is great. the mini screen in the back is a nice addition.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Subramanya\", \"rating\": \"5.0\", \"date\": \"17 Feb 2025\", \"text\": \"Loving it! Lava has done a tremendous job. After looking at reviews for good phone at 20k range between Motorola G85, Lava Blaze Duo, Samsung M35 and Lava Agni 3. I took more than 3 weeks to decide among these. I went across shopping platforms, websites, youtube videos to decide. After so much of tireless brainstorming practices finally selected lava agni 3 and luckily there was 2k discount from amazon side. Grabbed the discount and ordered Lava Agni 3. Mannnnnn! Loving this mobile so much. Yes Camera could be better but for a normal camera user it is still good camera. For camera pro\'s they may not like it. Loved features like dual screen, dolby atmos, Youtube background music. Also excited for 3 OS updated till android 17. Such a premium looking phone and also premium experience. We need to support indian brands like Lava especially after giving phones like agni 3. Love you LAVA. I was already a LAVA brand fan ever since I bought Lava Probuds 2 Ear buds due to their audio quality. Its been almost 3 years and am still loving it the same way for its experinece. Lava please do not change keep continue doing good work as you are doing.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"anuanu\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"This phone is awesome! High quality, fully featured and smooth operations. Gemini AI worked  seamlessly once I set it up. The mini screen is much more useful than I had imagined - I use the timer, camera, and music contols on mini screen. I wish there was a way to get the Gemini AI widget also on mini screen.I started with low expectations as I was only comparing specs with Samsung S25. I do miss the Samsung split screen feature which I often used. My take - Agni 3 is easily worth twice the price it is being sold for. I hope they won\'t raise the price once the brand gets established.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anita\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I am a lava Agni 2 user from last 1.5 years, and i am so happy to receive this upgrade. Model, the back screen is so useful and makes the overall look premium and outstanding in the crowdPicture quality has improved and is just right.Build quality is Awesome and 5 stars to itAnd the most important, It\'s the only Indian Brand to survive and able to match/outperform against Chinese competition.5***** &amp; + For being Value To Money\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Siva\", \"rating\": \"5.0\", \"date\": \"17 Apr 2025\", \"text\": \"I have been using this phone from oct 2024 and never felt bad about it. It\'s about 6 months now and I have no problem to complaint. Bgmi runs well, 5g connection is stable, never hanged, no over hearing, handy action key, super fast charging, more than 1.5 day battery back up.Missing mi IR blaster though. Previously had a  usb to 3.5 converter jack, using it for gaming headset.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Sanjay\", \"rating\": \"4.0\", \"date\": \"06 Nov 2024\", \"text\": \"I gave order under exchange but delivery man offered nothing on my old mobile so paid additional amount in his gpay account.Don\'t rely on exchange value shown on Amazon.Mobile looks good. Camera is average.. reddish pics . Good in day light. Battery Charges very fast..but charger has some dark spot..may be second hand supplied.Some minor bugs are there in mobile where background screen appears slightly..but tolerable. Nice curve display but toughn glass will cost 500 rs. Call quality good. Speaker good.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"GAURAV AGRAWAL\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Color quality is great and great design that makes it easy to carry. Moreover it is an excellent product, good battery performance, value for money, Great touch quality, Excellent performance.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"20 Apr 2025\", \"text\": \"Mobile under 25k with all the features loaded has premium look on your hand, just go for this. Battery backup is excellent I\'m a frequent user and it lasts up to 1.5 days solid and charges to 100% in just 30 to 40 min is quick charging for me.Camera is good but not great, I\'m not a camera person, still I use camera for selfie and other family events and I feel it gives you good shots. 120hz is cool, it works like a breeze, no lag have been seen so far of more than 1 month of use.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vijay Gir\", \"rating\": \"4.0\", \"date\": \"25 Jan 2025\", \"text\": \"I have been using the phone for the last 3 months. Battery backup is huge, you would not get such powerful battery in anyother phone, Inscreen fingerprint sensor is mind blowing. Performance is great, never faced any issue, does not hand, no lagging - be advised I do not play high graphic hungry games like CODM or any other battle royales. There is absolutely no heating issue. Touch quality is smooth. One crutial thing that Lava needs to work on is the camera. They have provided the wide angle camera which is great but the issue lies in the primary camera. For apparent no reasons the camera would go out of focus and even after trying for many minutes will not correct itself. Another thing is the zoom, as soon as you go above 2x, the quality will go towards bad and light capturing decreases.Apart from these issues, the phone is great. the mini screen in the back is a nice addition.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Subramanya\", \"rating\": \"5.0\", \"date\": \"17 Feb 2025\", \"text\": \"Loving it! Lava has done a tremendous job. After looking at reviews for good phone at 20k range between Motorola G85, Lava Blaze Duo, Samsung M35 and Lava Agni 3. I took more than 3 weeks to decide among these. I went across shopping platforms, websites, youtube videos to decide. After so much of tireless brainstorming practices finally selected lava agni 3 and luckily there was 2k discount from amazon side. Grabbed the discount and ordered Lava Agni 3. Mannnnnn! Loving this mobile so much. Yes Camera could be better but for a normal camera user it is still good camera. For camera pro\'s they may not like it. Loved features like dual screen, dolby atmos, Youtube background music. Also excited for 3 OS updated till android 17. Such a premium looking phone and also premium experience. We need to support indian brands like Lava especially after giving phones like agni 3. Love you LAVA. I was already a LAVA brand fan ever since I bought Lava Probuds 2 Ear buds due to their audio quality. Its been almost 3 years and am still loving it the same way for its experinece. Lava please do not change keep continue doing good work as you are doing.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"anuanu\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"This phone is awesome! High quality, fully featured and smooth operations. Gemini AI worked  seamlessly once I set it up. The mini screen is much more useful than I had imagined - I use the timer, camera, and music contols on mini screen. I wish there was a way to get the Gemini AI widget also on mini screen.I started with low expectations as I was only comparing specs with Samsung S25. I do miss the Samsung split screen feature which I often used. My take - Agni 3 is easily worth twice the price it is being sold for. I hope they won\'t raise the price once the brand gets established.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anita\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"I am a lava Agni 2 user from last 1.5 years, and i am so happy to receive this upgrade. Model, the back screen is so useful and makes the overall look premium and outstanding in the crowdPicture quality has improved and is just right.Build quality is Awesome and 5 stars to itAnd the most important, It\'s the only Indian Brand to survive and able to match/outperform against Chinese competition.5***** &amp; + For being Value To Money\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Siva\", \"rating\": \"5.0\", \"date\": \"17 Apr 2025\", \"text\": \"I have been using this phone from oct 2024 and never felt bad about it. It\'s about 6 months now and I have no problem to complaint. Bgmi runs well, 5g connection is stable, never hanged, no over hearing, handy action key, super fast charging, more than 1.5 day battery back up.Missing mi IR blaster though. Previously had a  usb to 3.5 converter jack, using it for gaming headset.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Sanjay\", \"rating\": \"4.0\", \"date\": \"06 Nov 2024\", \"text\": \"I gave order under exchange but delivery man offered nothing on my old mobile so paid additional amount in his gpay account.Don\'t rely on exchange value shown on Amazon.Mobile looks good. Camera is average.. reddish pics . Good in day light. Battery Charges very fast..but charger has some dark spot..may be second hand supplied.Some minor bugs are there in mobile where background screen appears slightly..but tolerable. Nice curve display but toughn glass will cost 500 rs. Call quality good. Speaker good.\n  \nRead more\", \"product_id\": \"B0DGQMDVRV\", \"link\": \"https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Infinix Note 50x+ 5G</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0F3V2TCLL\", \"product_name\": \"Infinix Note 50x+ 5G (Enchanted Purple, 8GB RAM, 128GB Storage) | MediaTek Dimensity 6100+ | 50MP Dual Rear Camera| 6.78\\" AMOLED Display | 5000mAh Battery | 33W Fast Charging | Upto 16GB RAM Expansion\", \"product_url\": \"https://www.amazon.in/Infinix-Enchanted-MediaTek-Dimensity-Expansion/dp/B0F3V2TCLL/ref=pd_ci_mcx_pspc_dp_d_2_t_2?pd_rd_w=I4e1H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=MY63V7KK31MQQQZESVD6&amp;pd_rd_wg=8dJAy&amp;pd_rd_r=877ba305-e7d9-4d3f-86b8-993add282ee4&amp;pd_rd_i=B0F3V2TCLL\", \"summary\": {\"total_reviews\": 2, \"average_rating\": 5.0, \"sentiment_breakdown\": {\"positive\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"goutham\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Best price phone Quality super 👌 looking also very nice camera quality Good So many options this mobile mobile speed download any videos\n  \nRead more\", \"product_id\": \"B0F3V2TCLL\", \"link\": \"https://www.amazon.in/Infinix-Enchanted-MediaTek-Dimensity-Expansion/dp/B0F3V2TCLL/ref=pd_ci_mcx_pspc_dp_d_2_t_2?pd_rd_w=I4e1H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=MY63V7KK31MQQQZESVD6&amp;pd_rd_wg=8dJAy&amp;pd_rd_r=877ba305-e7d9-4d3f-86b8-993add282ee4&amp;pd_rd_i=B0F3V2TCLL\", \"sentiment\": \"positive\"}, {\"author\": \"goutham\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Best price phone Quality super 👌 looking also very nice camera quality Good So many options this mobile mobile speed download any videos\n  \nRead more\", \"product_id\": \"B0F3V2TCLL\", \"link\": \"https://www.amazon.in/Infinix-Enchanted-MediaTek-Dimensity-Expansion/dp/B0F3V2TCLL/ref=pd_ci_mcx_pspc_dp_d_2_t_2?pd_rd_w=I4e1H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=MY63V7KK31MQQQZESVD6&amp;pd_rd_wg=8dJAy&amp;pd_rd_r=877ba305-e7d9-4d3f-86b8-993add282ee4&amp;pd_rd_i=B0F3V2TCLL\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Infinix-Enchanted-MediaTek-Dimensity-Expansion/dp/B0F3V2TCLL/ref=pd_ci_mcx_pspc_dp_d_2_t_2?pd_rd_w=I4e1H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=MY63V7KK31MQQQZESVD6&amp;pd_rd_wg=8dJAy&amp;pd_rd_r=877ba305-e7d9-4d3f-86b8-993add282ee4&amp;pd_rd_i=B0F3V2TCLL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy M35 5G</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D812DY6P\", \"product_name\": \"Samsung Galaxy M35 5G (Daybreak Blue,8GB RAM,256GB Storage)| Corning Gorilla Glass Victus+| AnTuTu Score 595K+ | Vapour Cooling Chamber | 6000mAh Battery | 120Hz Super AMOLED Display| Without Charger\", \"product_url\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"summary\": {\"total_reviews\": 12, \"average_rating\": 4.33, \"sentiment_breakdown\": {\"positive\": 12}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Kabeer Raj SinghKabeer Raj Singh\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'m having A55 as my personal primary phone and using this M35 as a secondary business phone. Looks wise it is a plain from behind as seen in the picture. Since I have 2 Samsung phones, I could mirror my office apps into this phone, without specially getting it setup by my IT team, as I faced issues in my old xiaomi phone. Battery life is solid, but charging feels slower as compared to my A55. It is understandable since A55 has a 5000mAh and this one having a 6000mAh battery. Fingerprint Sensor is located on side, which is faster and accurate than in display fingerprint. Also the best thing I like about this phone is its bass quality. I\'m not very sure about other people but I find that this phone has a bassier speaker, probably because the polycarbonate vibrates while producing bass, and I don\'t need to use an external speaker. The drawback of this phone is that it starts heating up after 30 min to 1 hr. It has knox security and a punch hole display at low budget, which is why I brought this model at 13,999. Cameras are decent in comparison to my A55. For this price the phone is a pretty great option.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"4.0\", \"date\": \"21 Mar 2025\", \"text\": \"I had recently ordered this phone and it\'s one of the best options under budget and for the people who do not use phone for prolonged durations. The functioning and screen is excellent . It has triple camera setup but the camera quality at this price is way above average seizing memories with exceptional sharpness and clarity. The battery life is decent but it gets a little heated when used for long duration but none the less it\'s not a bad option. The device features quick charging functionality. The display quality is good. During the initial time the processor was good but eventually it slowed down and phone gets hung often. The phone doesn\'t have an IP certification due to which contact with water might damage it. This purchase has truly exceeded my expectations and would highly recommend it to anyone seeking a premium smartphone experience at an affordable price.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ritesh\", \"rating\": \"5.0\", \"date\": \"02 Sep 2024\", \"text\": \"Pros:- Great battery backup. With moderate usage on WiFi, can easily last upto 2 days. Also, there is very less battery drain when idle, especially overnight. Definitely one of the best with 6000 mAh. One of my primary reasons to buy this phone.- Camera quality at this price is way above average.- Finally, punch hole display from Samsung for M series and at this price point.- One UI software is very stable and comes with plenty of customisations.- No issues in performance with multitasking involving streaming videos, music, social media apps, browser surfing, etc. Can\'t say about gaming as I am not a gamer.- Up to 4 gens of software updates which hardly any company provides even with flagship phones. But need to keep in mind that the product page on Samsung\'s website clearly states that this is not a promise but just their current plans, and it can be changed anytime at their own discretion.Cons:- Bulky (which is expected considering the massive battery), holding with one hand for extended period of time causes discomfort, specially if you are used to phones weighing below 175g.- Headphone jack missing. Considering the thickness of the phone, this could easily have been accommodated.- Phone does not come with any IP rating which is surprising, so any contact with water might potentially cause damage.- There is a noticeable battery drain with 5G network, but could be improved in future software updates.- Not specific to this phone but with all Samsung phones: Missing charging adaptor, back cover, and screen protector. So, need to shell out extra money for these.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Partha SenPartha Sen\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"An excellent phone in budget friendly price. Came loaded with Android 14. Updated to Android 15 and UI7. Smooth operation, good sound quality. Front and rear camera are fine. Perfect pictures. Videos are also clear. Easy to handle. But no headphone jack, no charger and back cover are provided. Hybrid SIM card slot. You can replace 2nd SIM with memory card. 6000mah battery is sufficient for whole day. 25W or 33W charger is to be procured seperately. No dust and water protection. Most important is software updates. Highest compared to other brands.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"doctor a\", \"rating\": \"3.0\", \"date\": \"18 May 2025\", \"text\": \"I bought this phone for my wife mainly because of its solid specs and large battery. While it performs well overall, there are a few things buyers should know before purchasing:✅ Pros:The 6000mAh battery is excellent – lasts easily more than a day with moderate usage.The screen quality is good for watching videos and using apps.Decent performance for daily tasks like calls, WhatsApp, YouTube, etc.⚠️ Cons:The phone is noticeably bulky and heavy. It feels tiring to hold in one hand for long, especially for users with smaller hands.Not ideal for someone looking for a lightweight or sleek design.Camera is average – not bad, but not exceptional in low light.📌 Bottom Line:If battery life is your top priority, this phone delivers. But if weight, comfort, and long one-handed use matter to you (or the person you\'re buying it for), you might want to look for a more compact alternative. I gave it 3 stars mainly due to the form factor and weight – performance-wise, it’s good for the price.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"BrijendraBrijendra\", \"rating\": \"4.0\", \"date\": \"26 May 2025\", \"text\": \"The Samsung Galaxy M35 impresses with its vibrant Super AMOLED display and rich stereo speakers, making it ideal for media consumption. Its camera setup delivers better-than-average results in daylight, though it\'s not flagship-level. The phone feels bulky in hand, likely due to its large battery, but this also translates to ok battery life. Samsung’s One UI software continues to be smooth, feature-rich, and reliable, ensuring a good user experience overall. A solid choice for those prioritizing display, sound, and battery over sleek design.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kabeer Raj SinghKabeer Raj Singh\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'m having A55 as my personal primary phone and using this M35 as a secondary business phone. Looks wise it is a plain from behind as seen in the picture. Since I have 2 Samsung phones, I could mirror my office apps into this phone, without specially getting it setup by my IT team, as I faced issues in my old xiaomi phone. Battery life is solid, but charging feels slower as compared to my A55. It is understandable since A55 has a 5000mAh and this one having a 6000mAh battery. Fingerprint Sensor is located on side, which is faster and accurate than in display fingerprint. Also the best thing I like about this phone is its bass quality. I\'m not very sure about other people but I find that this phone has a bassier speaker, probably because the polycarbonate vibrates while producing bass, and I don\'t need to use an external speaker. The drawback of this phone is that it starts heating up after 30 min to 1 hr. It has knox security and a punch hole display at low budget, which is why I brought this model at 13,999. Cameras are decent in comparison to my A55. For this price the phone is a pretty great option.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"4.0\", \"date\": \"21 Mar 2025\", \"text\": \"I had recently ordered this phone and it\'s one of the best options under budget and for the people who do not use phone for prolonged durations. The functioning and screen is excellent . It has triple camera setup but the camera quality at this price is way above average seizing memories with exceptional sharpness and clarity. The battery life is decent but it gets a little heated when used for long duration but none the less it\'s not a bad option. The device features quick charging functionality. The display quality is good. During the initial time the processor was good but eventually it slowed down and phone gets hung often. The phone doesn\'t have an IP certification due to which contact with water might damage it. This purchase has truly exceeded my expectations and would highly recommend it to anyone seeking a premium smartphone experience at an affordable price.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ritesh\", \"rating\": \"5.0\", \"date\": \"02 Sep 2024\", \"text\": \"Pros:- Great battery backup. With moderate usage on WiFi, can easily last upto 2 days. Also, there is very less battery drain when idle, especially overnight. Definitely one of the best with 6000 mAh. One of my primary reasons to buy this phone.- Camera quality at this price is way above average.- Finally, punch hole display from Samsung for M series and at this price point.- One UI software is very stable and comes with plenty of customisations.- No issues in performance with multitasking involving streaming videos, music, social media apps, browser surfing, etc. Can\'t say about gaming as I am not a gamer.- Up to 4 gens of software updates which hardly any company provides even with flagship phones. But need to keep in mind that the product page on Samsung\'s website clearly states that this is not a promise but just their current plans, and it can be changed anytime at their own discretion.Cons:- Bulky (which is expected considering the massive battery), holding with one hand for extended period of time causes discomfort, specially if you are used to phones weighing below 175g.- Headphone jack missing. Considering the thickness of the phone, this could easily have been accommodated.- Phone does not come with any IP rating which is surprising, so any contact with water might potentially cause damage.- There is a noticeable battery drain with 5G network, but could be improved in future software updates.- Not specific to this phone but with all Samsung phones: Missing charging adaptor, back cover, and screen protector. So, need to shell out extra money for these.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Partha SenPartha Sen\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"An excellent phone in budget friendly price. Came loaded with Android 14. Updated to Android 15 and UI7. Smooth operation, good sound quality. Front and rear camera are fine. Perfect pictures. Videos are also clear. Easy to handle. But no headphone jack, no charger and back cover are provided. Hybrid SIM card slot. You can replace 2nd SIM with memory card. 6000mah battery is sufficient for whole day. 25W or 33W charger is to be procured seperately. No dust and water protection. Most important is software updates. Highest compared to other brands.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"doctor a\", \"rating\": \"3.0\", \"date\": \"18 May 2025\", \"text\": \"I bought this phone for my wife mainly because of its solid specs and large battery. While it performs well overall, there are a few things buyers should know before purchasing:✅ Pros:The 6000mAh battery is excellent – lasts easily more than a day with moderate usage.The screen quality is good for watching videos and using apps.Decent performance for daily tasks like calls, WhatsApp, YouTube, etc.⚠️ Cons:The phone is noticeably bulky and heavy. It feels tiring to hold in one hand for long, especially for users with smaller hands.Not ideal for someone looking for a lightweight or sleek design.Camera is average – not bad, but not exceptional in low light.📌 Bottom Line:If battery life is your top priority, this phone delivers. But if weight, comfort, and long one-handed use matter to you (or the person you\'re buying it for), you might want to look for a more compact alternative. I gave it 3 stars mainly due to the form factor and weight – performance-wise, it’s good for the price.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"BrijendraBrijendra\", \"rating\": \"4.0\", \"date\": \"26 May 2025\", \"text\": \"The Samsung Galaxy M35 impresses with its vibrant Super AMOLED display and rich stereo speakers, making it ideal for media consumption. Its camera setup delivers better-than-average results in daylight, though it\'s not flagship-level. The phone feels bulky in hand, likely due to its large battery, but this also translates to ok battery life. Samsung’s One UI software continues to be smooth, feature-rich, and reliable, ensuring a good user experience overall. A solid choice for those prioritizing display, sound, and battery over sleek design.\n  \nRead more\", \"product_id\": \"B0D812DY6P\", \"link\": \"https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Samsung 9 kg, 5 Star,Washing Machine</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DS681G4K\", \"product_name\": \"Samsung 9 kg, 5 Star, AI Control, AI Ecobubble, Super Speed, Wi-Fi, Hygiene Steam with Inbuilt Heater, Digital Inverter, Fully-Automatic Front Load Washing Machine (WW90DG6U24ASTL, NAVY)\", \"product_url\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 4.8, \"sentiment_breakdown\": {\"positive\": 6, \"neutral\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 60.0}, \"reviews\": [{\"author\": \"PrajwalPrajwal\", \"rating\": \"5.0\", \"date\": \"01 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Samsung 9 kg, 5 Star, Eco Bubble Technology, AI Control, Wi-Fi, Digital Inverter Motor, Fully-Automatic Front Load Washing Machine (WW90T504DAN1TL, Hygiene Steam, Inox) from Amazon, and I must say, this machine has exceeded my expectations in every way.Performance and FeaturesThe washing machine is incredibly user-friendly and simple to operate. The AI Control feature is a game-changer, as it personalizes washing by remembering my habits, suggesting cycles, and displaying timely information. The Eco Bubble Technology ensures that detergent penetrates fabrics quickly, removing dirt effectively even at low temperatures. This not only saves energy but also protects the color and texture of my clothes.The washing quality is outstanding. Clothes come out looking fresh and clean, thanks to the Hygiene Steam feature, which eliminates 99.9% of bacteria and allergens. The Digital Inverter Motor is both powerful and quiet, providing a seamless washing experience without any noise disturbances.Connectivity and ConvenienceThe Wi-Fi connectivity allows me to control and monitor the washing machine remotely using the SmartThings app. This feature is incredibly convenient, especially when I’m multitasking or away from home. The machine’s 5 Star energy rating ensures that it is highly efficient, saving both water and electricity.Design and Build QualityThe washing machine has a sleek and modern design that fits perfectly in my laundry area. The Inox finish gives it a premium look, and the build quality is robust and durable. The 9 kg capacity is perfect for my family’s needs, handling large loads with ease.Delivery ExperienceWhile the product itself is fantastic, I did have a bad experience with the delivery agent. The delivery vehicle was not parked properly, and the driver seemed inexperienced. Unfortunately, he knocked over two bikes in our parking area and even caused minor damage to a wall. This was quite disappointing and added unnecessary stress to the otherwise smooth purchase process.ConclusionOverall, I am extremely satisfied with the Samsung 9 kg, 5 Star, Eco Bubble Technology, AI Control, Wi-Fi, Digital Inverter Motor, Fully-Automatic Front Load Washing Machine. Its advanced technology, excellent washing quality, and user-friendly features make it a top-notch appliance. However, the delivery experience could have been better. Despite this hiccup, I highly recommend this washing machine for anyone looking for a reliable and efficient laundry solution.\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vaibhav verma\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"the washing quality is superb. There is very less sound while running even less then table fan. Samsung has done a great job.AI support is also good.\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Babra Rashida\", \"rating\": \"4.0\", \"date\": \"01 Jan 2025\", \"text\": \"Washing abilities, Quality, Design and Features, Performance\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Anoop Venugopal\", \"rating\": \"5.0\", \"date\": \"03 Sep 2022\", \"text\": \"First of all, even though it says \\"black\\", it\'s 90% grey. Still looking very good. Just putting it out there.Had a bit of hassle with the Samsung team that called to schedule installation. On the scheduled date, even after 4pm they didn\'t came. I called them and understood that my installation request was not registered correctly, even though they said before they will come the said date. But, to my surprise, they sent a team within an hour after I called them at the late hour. Kudos to Samsung for that.This is my very first washing machine, so I have very little to compare to. But, I will say that this was a very good purchase.This machine provides very good cleaning results, provided you choose cleaning options like prewash, bubble soak, intensive wash, additional rinse cycles and higher temperature washes with respect to the degree of dirt in the clothes you put in. There is a lot of options. A good combination will surely do the magic. I would highly recommend to use liquid detergents only.Now, the spinning part. I have seen both noisy spins which will make one think the machine is damaged and super smooth spins which gave me another level of satisfaction. It comes as a result of the efficiency of pre spin where the load is distributed equally inside the drum. I have to say, it is less efficient that I would love it to be. When the load distribution is perfect, there is not a single vibration or noise during spinning. It\'s so good. It has been rare in my case. But it doesn\'t imply a faulty machine.And, another thing is that the WiFi reception strength is low. So, if you keep the machine a bit far from the router and behind multiple walls, like I had to, WiFi connectivity is basically useless. It failed everytime when I was trying to connect the machine to SmartThings.Still haven\'t received an electric bill after purchasing the machine, so I can\'t say much about the energy efficiency now. Will give an update once I have enough data to refer to.Overall, it\'s a very good machine if we use it correctly. I would surely recommend it.\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amit Mukhedkar\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Eco bubble wash feature cleans the clothes very nicelySeveral wash cyclesSturdy machine\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"PrajwalPrajwal\", \"rating\": \"5.0\", \"date\": \"01 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Samsung 9 kg, 5 Star, Eco Bubble Technology, AI Control, Wi-Fi, Digital Inverter Motor, Fully-Automatic Front Load Washing Machine (WW90T504DAN1TL, Hygiene Steam, Inox) from Amazon, and I must say, this machine has exceeded my expectations in every way.Performance and FeaturesThe washing machine is incredibly user-friendly and simple to operate. The AI Control feature is a game-changer, as it personalizes washing by remembering my habits, suggesting cycles, and displaying timely information. The Eco Bubble Technology ensures that detergent penetrates fabrics quickly, removing dirt effectively even at low temperatures. This not only saves energy but also protects the color and texture of my clothes.The washing quality is outstanding. Clothes come out looking fresh and clean, thanks to the Hygiene Steam feature, which eliminates 99.9% of bacteria and allergens. The Digital Inverter Motor is both powerful and quiet, providing a seamless washing experience without any noise disturbances.Connectivity and ConvenienceThe Wi-Fi connectivity allows me to control and monitor the washing machine remotely using the SmartThings app. This feature is incredibly convenient, especially when I’m multitasking or away from home. The machine’s 5 Star energy rating ensures that it is highly efficient, saving both water and electricity.Design and Build QualityThe washing machine has a sleek and modern design that fits perfectly in my laundry area. The Inox finish gives it a premium look, and the build quality is robust and durable. The 9 kg capacity is perfect for my family’s needs, handling large loads with ease.Delivery ExperienceWhile the product itself is fantastic, I did have a bad experience with the delivery agent. The delivery vehicle was not parked properly, and the driver seemed inexperienced. Unfortunately, he knocked over two bikes in our parking area and even caused minor damage to a wall. This was quite disappointing and added unnecessary stress to the otherwise smooth purchase process.ConclusionOverall, I am extremely satisfied with the Samsung 9 kg, 5 Star, Eco Bubble Technology, AI Control, Wi-Fi, Digital Inverter Motor, Fully-Automatic Front Load Washing Machine. Its advanced technology, excellent washing quality, and user-friendly features make it a top-notch appliance. However, the delivery experience could have been better. Despite this hiccup, I highly recommend this washing machine for anyone looking for a reliable and efficient laundry solution.\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vaibhav verma\", \"rating\": \"5.0\", \"date\": \"25 May 2025\", \"text\": \"the washing quality is superb. There is very less sound while running even less then table fan. Samsung has done a great job.AI support is also good.\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Babra Rashida\", \"rating\": \"4.0\", \"date\": \"01 Jan 2025\", \"text\": \"Washing abilities, Quality, Design and Features, Performance\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Anoop Venugopal\", \"rating\": \"5.0\", \"date\": \"03 Sep 2022\", \"text\": \"First of all, even though it says \\"black\\", it\'s 90% grey. Still looking very good. Just putting it out there.Had a bit of hassle with the Samsung team that called to schedule installation. On the scheduled date, even after 4pm they didn\'t came. I called them and understood that my installation request was not registered correctly, even though they said before they will come the said date. But, to my surprise, they sent a team within an hour after I called them at the late hour. Kudos to Samsung for that.This is my very first washing machine, so I have very little to compare to. But, I will say that this was a very good purchase.This machine provides very good cleaning results, provided you choose cleaning options like prewash, bubble soak, intensive wash, additional rinse cycles and higher temperature washes with respect to the degree of dirt in the clothes you put in. There is a lot of options. A good combination will surely do the magic. I would highly recommend to use liquid detergents only.Now, the spinning part. I have seen both noisy spins which will make one think the machine is damaged and super smooth spins which gave me another level of satisfaction. It comes as a result of the efficiency of pre spin where the load is distributed equally inside the drum. I have to say, it is less efficient that I would love it to be. When the load distribution is perfect, there is not a single vibration or noise during spinning. It\'s so good. It has been rare in my case. But it doesn\'t imply a faulty machine.And, another thing is that the WiFi reception strength is low. So, if you keep the machine a bit far from the router and behind multiple walls, like I had to, WiFi connectivity is basically useless. It failed everytime when I was trying to connect the machine to SmartThings.Still haven\'t received an electric bill after purchasing the machine, so I can\'t say much about the energy efficiency now. Will give an update once I have enough data to refer to.Overall, it\'s a very good machine if we use it correctly. I would surely recommend it.\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amit Mukhedkar\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Eco bubble wash feature cleans the clothes very nicelySeveral wash cyclesSturdy machine\n  \nRead more\", \"product_id\": \"B0DS681G4K\", \"link\": \"https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>G 7 Kg 5 Star Smart Inverter Technology Fully Automatic Top Load Washing Machine</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>16</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DPHT2HZL\", \"product_name\": \"LG 7 Kg 5 Star Smart Inverter Technology Fully Automatic Top Load Washing Machine (T70VBMB1Z, Auto Prewash, Turbodrum, Stainless Steel drum, LED Display, Smart Diagnosis Middle Black)\", \"product_url\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"vishalvishal\", \"rating\": \"5.0\", \"date\": \"22 Oct 2023\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I had to switch from a Samsung front load 5kg to this machine as the Samsung one gave up due to its age(12yrs) &amp; regular shifting of residence(5).My observations:PROS:1.Wash quality is good  2. i just put the clothes &amp; detergent powder inside.the machine does the rest for water intake,wash program selection &amp; time.  3.low sound levels.  4.lint filter is effective. 5.separate intake for softener  &amp; separate intake for descaling powder. 6.tub size is big. 7.cost of machine saved me 10-12k as compared a front load. 7.EB required is lower as motor is 230 watts but sufficient for 6.5 kgs load.  8.front load was a pain ,as family size increased, with respect to loading,capacity,machine used to dance like a pro,countless repairs.CONS:1,water required is much higher.  2. i bought water intake filter(400) ,extended outlet drain pipe(400) and washing machine cover(1000) from LG service person for 1850.no need of stand as drainage pipe is 1mtr+3mter long now. 3.build quality is just ok. 4,rat mesh is flimsy 5.lint filter is placed high up. 6.can wash max 17 clothes(shirts/trousers adult 5 kids 5 socks 4 others 2) in one go. 6.no heater  7.need to scrub collars seperately in case of heavy load.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"aditya\", \"rating\": \"4.0\", \"date\": \"11 Mar 2025\", \"text\": \"Performence is good, Wash is good, Everyday use\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Atul G.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Fabulous performance till date no problem detected, LG is really good brand.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mahesh\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Great product and quality.Used for 2-3 years\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"4.0\", \"date\": \"20 Jan 2023\", \"text\": \"We bought this model in 2013. On 9th year it started to make huge noise while washing. The service person (service charge is around Rs. 800) said suspension rods got rust and eroded, the service person told us this washing machine has 2 motors, one is which has stopped functioning is not covered by warranty, also he said there is some clutch is there which has stopped functioning as well. He said the repairing charge would be around Rs. 9000. Within few days we noticed that the sensor is not working as well. The machine is unable to take adequate water on its own. So we got no benefit from LG\'s ten years\'warranty. You should keep it in mind that their main motor is quite powerful but their suspension rods are not. This washing machine served us nine years without much hassle. Although clothes get badly tangled even in \'delicate\' mode. Clothes lost their lints very fast in this machine. You need to use wool balls for every wash. Also, you need to clean the the lint catcher regularly if you are not using wool balls. We are in Howrah, West Bengal, we use municipality water for our machine but we experienced that this machine needs to be clean every 4-5 months. Auto clean mode is not sufficient, it requires opening the bottom of the drum and manual cleaning. Otherwise some mud like objects get attached with washed clothes. I don\'t have good experience with the staffs of local LG service centre either.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Santanu\", \"rating\": \"5.0\", \"date\": \"22 Oct 2024\", \"text\": \"Best product in this offer price range but without a big discount it\'s a bit costly for middle class people. The machine clean, wash and dry your cloths properly. Proper usage of minimum detergent which we intentionally use more than enough in everyday use. Less electricity and less water consumption are really a good thing from. Very low sound or zero noise level while spining. LG creates really a good job in every aspects. A Samsung washing machine is also good and a big opponent in this price segment and both have a advantages more or less in every angle. And personally I really like both Samsung and LG products but before I buy I have searched a lot for a budget frindly good washing machine for a middle class people which has good for our environment also. So keep all those in my mind it\'s highly recommended. Save water, save energy and save the environment. And lastly thanks to flipkart to deliver the priduct at my village so fast.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"gopr\", \"rating\": \"3.0\", \"date\": \"24 Mar 2025\", \"text\": \"Quality of fiber  on the top lid and cover is cheap. I removed the plastic protection and it looks like an old machine even though it is 4 days since I started using it. Even after cleaning with mild soap it has scratches and patchesWash quality is good and machine is silent. Number of setting are good enough.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amulya Sri\", \"rating\": \"4.0\", \"date\": \"20 Apr 2025\", \"text\": \"LG washing machine has been a great addition to our home. It runs quietly, cleans clothes thoroughly, and has multiple wash settings to suit different fabrics. The touch controls are easy to use, and the overall design is sleek and modern. It also uses water and energy efficiently. Highly recommend for anyone looking for a reliable and smart washing machine.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"vishalvishal\", \"rating\": \"5.0\", \"date\": \"22 Oct 2023\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I had to switch from a Samsung front load 5kg to this machine as the Samsung one gave up due to its age(12yrs) &amp; regular shifting of residence(5).My observations:PROS:1.Wash quality is good  2. i just put the clothes &amp; detergent powder inside.the machine does the rest for water intake,wash program selection &amp; time.  3.low sound levels.  4.lint filter is effective. 5.separate intake for softener  &amp; separate intake for descaling powder. 6.tub size is big. 7.cost of machine saved me 10-12k as compared a front load. 7.EB required is lower as motor is 230 watts but sufficient for 6.5 kgs load.  8.front load was a pain ,as family size increased, with respect to loading,capacity,machine used to dance like a pro,countless repairs.CONS:1,water required is much higher.  2. i bought water intake filter(400) ,extended outlet drain pipe(400) and washing machine cover(1000) from LG service person for 1850.no need of stand as drainage pipe is 1mtr+3mter long now. 3.build quality is just ok. 4,rat mesh is flimsy 5.lint filter is placed high up. 6.can wash max 17 clothes(shirts/trousers adult 5 kids 5 socks 4 others 2) in one go. 6.no heater  7.need to scrub collars seperately in case of heavy load.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"aditya\", \"rating\": \"4.0\", \"date\": \"11 Mar 2025\", \"text\": \"Performence is good, Wash is good, Everyday use\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Atul G.\", \"rating\": \"5.0\", \"date\": \"15 May 2025\", \"text\": \"Fabulous performance till date no problem detected, LG is really good brand.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mahesh\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Great product and quality.Used for 2-3 years\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"4.0\", \"date\": \"20 Jan 2023\", \"text\": \"We bought this model in 2013. On 9th year it started to make huge noise while washing. The service person (service charge is around Rs. 800) said suspension rods got rust and eroded, the service person told us this washing machine has 2 motors, one is which has stopped functioning is not covered by warranty, also he said there is some clutch is there which has stopped functioning as well. He said the repairing charge would be around Rs. 9000. Within few days we noticed that the sensor is not working as well. The machine is unable to take adequate water on its own. So we got no benefit from LG\'s ten years\'warranty. You should keep it in mind that their main motor is quite powerful but their suspension rods are not. This washing machine served us nine years without much hassle. Although clothes get badly tangled even in \'delicate\' mode. Clothes lost their lints very fast in this machine. You need to use wool balls for every wash. Also, you need to clean the the lint catcher regularly if you are not using wool balls. We are in Howrah, West Bengal, we use municipality water for our machine but we experienced that this machine needs to be clean every 4-5 months. Auto clean mode is not sufficient, it requires opening the bottom of the drum and manual cleaning. Otherwise some mud like objects get attached with washed clothes. I don\'t have good experience with the staffs of local LG service centre either.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Santanu\", \"rating\": \"5.0\", \"date\": \"22 Oct 2024\", \"text\": \"Best product in this offer price range but without a big discount it\'s a bit costly for middle class people. The machine clean, wash and dry your cloths properly. Proper usage of minimum detergent which we intentionally use more than enough in everyday use. Less electricity and less water consumption are really a good thing from. Very low sound or zero noise level while spining. LG creates really a good job in every aspects. A Samsung washing machine is also good and a big opponent in this price segment and both have a advantages more or less in every angle. And personally I really like both Samsung and LG products but before I buy I have searched a lot for a budget frindly good washing machine for a middle class people which has good for our environment also. So keep all those in my mind it\'s highly recommended. Save water, save energy and save the environment. And lastly thanks to flipkart to deliver the priduct at my village so fast.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"gopr\", \"rating\": \"3.0\", \"date\": \"24 Mar 2025\", \"text\": \"Quality of fiber  on the top lid and cover is cheap. I removed the plastic protection and it looks like an old machine even though it is 4 days since I started using it. Even after cleaning with mild soap it has scratches and patchesWash quality is good and machine is silent. Number of setting are good enough.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amulya Sri\", \"rating\": \"4.0\", \"date\": \"20 Apr 2025\", \"text\": \"LG washing machine has been a great addition to our home. It runs quietly, cleans clothes thoroughly, and has multiple wash settings to suit different fabrics. The touch controls are easy to use, and the overall design is sleek and modern. It also uses water and energy efficiently. Highly recommend for anyone looking for a reliable and smart washing machine.\n  \nRead more\", \"product_id\": \"B0DPHT2HZL\", \"link\": \"https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Whirlpool 7 kg Magic Clean 5 Star Fully Automatic Top Load Washing Machine</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>16</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DSBRDRDV\", \"product_name\": \"Whirlpool 7 kg Magic Clean 5 Star Fully Automatic Top Load Washing Machine Grey (MAGIC CLEAN 7.0 GENX GREY 5YMW)\", \"product_url\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Ameer j.\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Iam happy\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shantanu VermaShantanu Verma\", \"rating\": \"4.0\", \"date\": \"13 Sep 2020\", \"text\": \"I chose this machine because it had fully auto hot water wash at a suitable price point. There is endless debate of top load vs front load. This uses more water than a front load machine but is quieter, clothes get damaged less, and you dont have to bend over. Its a great machine, I am happy to own it and use it, but here is the critique.Pros:Fully autoHot water washWhirlpool- known brand with decent serviceCost 17100/- purchased a whirlpool trolley with wheels for 1400/- from installer technician for rust protection amd easy water drainCons:No (separate) place to add softener/conditioner. Check out the photo. I am forced to open the lid at the end of first rinse cycle and add conditioner into the tub. This mars the fire and forget experience expected from a fully auto machine. The wife says: not adding softener/conditioner solves the problem though, and saves money in the process. Touché.Somewhere in the fine print it is probably mentioned that you require a 15 amp socket for the 15 amp plug of this machine. So keep the socket handy. The manual says the machine should not be installed in a bathroom/ near a source of moisture, amd extension cords are a no-no. Should have given a longer cord then.Spin cycle feels rather slow. (Less RPM) And I am upgrading from a semi auto machine. Clothes come out nearly as dry though.I feel a capacity of 6.5 is small for a family of 2 adults and 2 small kids. Go in for the larger variant, its not a con of the machine though.Uses a larger amount of water than a front load, but we already knew that.Machine cycle stops the moment you open the lid and restarts when you close it, though its not a con.Full load normal wash cycle is 1hr 30 mins plus. The timer pauses when water is being filled.The stainwash, anti bacterial other sophesticated programs run longer (2-3 hrs), and accept much less load (1.5-2 kg) to be effective. See photo.Express wash feature reduces cycle time by upto 40%, but at the cost of the second rinse cycle. Clothes MAY smell of detergent after completion of the cycle.Other issues:In my opinion, call the brand helpline, register the product and ask for their AMC and extended warranty, rather than prchasing it from online retailer. I have (only) a hunch that it is likely to give better results than the (much cheaper) online alternatives in the long run. I will not be able to prove anything though.\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Best washing machine\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Farsin ahammed\", \"rating\": \"1.0\", \"date\": \"01 May 2025\", \"text\": \"The senor got complaint within 9 months. Their service in Kerala is pathetic. It took 4 days for a technician to come and check the problem. Now I am being told to wait another 4-5 days for the new board to arrive and then get it fixed.\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Vihaan darak\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"Product is good washing machine work good but when you add more than 15 clothes lint is there in washing machine in clothes also\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"4.0\", \"date\": \"17 May 2025\", \"text\": \"Nice product but according to size 7 KG, it’s  bit small\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Adarsh Singh\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"Very nice and quality product\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Hans Raj Bhatt\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"This washing machine is just an average performer. Delivery was swift, within one day at Delhi however the machine had a dent on one of its side. I thought of getting it replaced by seeking help from amazon customer care but I was told that this being the last piece either I will have to keep or accept a refund. Dent being small I kept the machine though. Having used it for 2 months, I have listed the pros and cons of this machine.Pros1. I bought it for just above  Rs 13000, which is a good deal for 7 Kg segment2. It does its job of cleaning clothes well.3. Build quality is nice and doesnt make much noise.4. Fitments provided by company are adequate for you to start using the machine without spending any additional amount on any other accessories.Cons1. Lint filter is absolutely useless. In fact the company claims it to be unique but it doesn\'t do its basic work of removing lint from the fabric.2. ZPF is nothing and is a marketing gimmick. Machine has no additional motor. It just permits the water flow in if pressure is less, that\'s all3. Hard water wash option is also a marketing gimmick. The only difference in Hard water wash is, it lets in more amount of water. Else use chemical on your own.For me it has been value for money since I paid less amount. However, removing lint remains an important aspect for me which I feel I have been tricked into by the marketing jargons of company. Rest it does its job.\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ameer j.\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Iam happy\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shantanu VermaShantanu Verma\", \"rating\": \"4.0\", \"date\": \"13 Sep 2020\", \"text\": \"I chose this machine because it had fully auto hot water wash at a suitable price point. There is endless debate of top load vs front load. This uses more water than a front load machine but is quieter, clothes get damaged less, and you dont have to bend over. Its a great machine, I am happy to own it and use it, but here is the critique.Pros:Fully autoHot water washWhirlpool- known brand with decent serviceCost 17100/- purchased a whirlpool trolley with wheels for 1400/- from installer technician for rust protection amd easy water drainCons:No (separate) place to add softener/conditioner. Check out the photo. I am forced to open the lid at the end of first rinse cycle and add conditioner into the tub. This mars the fire and forget experience expected from a fully auto machine. The wife says: not adding softener/conditioner solves the problem though, and saves money in the process. Touché.Somewhere in the fine print it is probably mentioned that you require a 15 amp socket for the 15 amp plug of this machine. So keep the socket handy. The manual says the machine should not be installed in a bathroom/ near a source of moisture, amd extension cords are a no-no. Should have given a longer cord then.Spin cycle feels rather slow. (Less RPM) And I am upgrading from a semi auto machine. Clothes come out nearly as dry though.I feel a capacity of 6.5 is small for a family of 2 adults and 2 small kids. Go in for the larger variant, its not a con of the machine though.Uses a larger amount of water than a front load, but we already knew that.Machine cycle stops the moment you open the lid and restarts when you close it, though its not a con.Full load normal wash cycle is 1hr 30 mins plus. The timer pauses when water is being filled.The stainwash, anti bacterial other sophesticated programs run longer (2-3 hrs), and accept much less load (1.5-2 kg) to be effective. See photo.Express wash feature reduces cycle time by upto 40%, but at the cost of the second rinse cycle. Clothes MAY smell of detergent after completion of the cycle.Other issues:In my opinion, call the brand helpline, register the product and ask for their AMC and extended warranty, rather than prchasing it from online retailer. I have (only) a hunch that it is likely to give better results than the (much cheaper) online alternatives in the long run. I will not be able to prove anything though.\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Best washing machine\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Farsin ahammed\", \"rating\": \"1.0\", \"date\": \"01 May 2025\", \"text\": \"The senor got complaint within 9 months. Their service in Kerala is pathetic. It took 4 days for a technician to come and check the problem. Now I am being told to wait another 4-5 days for the new board to arrive and then get it fixed.\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Vihaan darak\", \"rating\": \"5.0\", \"date\": \"03 May 2025\", \"text\": \"Product is good washing machine work good but when you add more than 15 clothes lint is there in washing machine in clothes also\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"4.0\", \"date\": \"17 May 2025\", \"text\": \"Nice product but according to size 7 KG, it’s  bit small\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Adarsh Singh\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"Very nice and quality product\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Hans Raj Bhatt\", \"rating\": \"3.0\", \"date\": \"09 Apr 2025\", \"text\": \"This washing machine is just an average performer. Delivery was swift, within one day at Delhi however the machine had a dent on one of its side. I thought of getting it replaced by seeking help from amazon customer care but I was told that this being the last piece either I will have to keep or accept a refund. Dent being small I kept the machine though. Having used it for 2 months, I have listed the pros and cons of this machine.Pros1. I bought it for just above  Rs 13000, which is a good deal for 7 Kg segment2. It does its job of cleaning clothes well.3. Build quality is nice and doesnt make much noise.4. Fitments provided by company are adequate for you to start using the machine without spending any additional amount on any other accessories.Cons1. Lint filter is absolutely useless. In fact the company claims it to be unique but it doesn\'t do its basic work of removing lint from the fabric.2. ZPF is nothing and is a marketing gimmick. Machine has no additional motor. It just permits the water flow in if pressure is less, that\'s all3. Hard water wash option is also a marketing gimmick. The only difference in Hard water wash is, it lets in more amount of water. Else use chemical on your own.For me it has been value for money since I paid less amount. However, removing lint remains an important aspect for me which I feel I have been tricked into by the marketing jargons of company. Rest it does its job.\n  \nRead more\", \"product_id\": \"B0DSBRDRDV\", \"link\": \"https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Godrej 472 L 2 Star With AI Tech, 95%+ Food Surface Disinfection with Nano Shield Technology Inverter Frost Free Double Door Regalis Refrigerator</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>16</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DB63CFRM\", \"product_name\": \"Godrej 472 L 2 Star With AI Tech, 95%+ Food Surface Disinfection with Nano Shield Technology Inverter Frost Free Double Door Regalis Refrigerator (RF EON 474B RCI MT BK, Matt Black)\", \"product_url\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 3.62, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Vivek H.\", \"rating\": \"5.0\", \"date\": \"30 Sep 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Godrej 436 Litre refrigerator from Amazon, and I must say the experience has been flawless from start to finish!First off, the ordering process was extremely smooth. Amazon\'s interface made it easy to find exactly what I was looking for, with detailed product descriptions and user reviews helping me finalize my decision. I placed my order with ease, and the refrigerator was offered at a competitive price with additional discounts available.The delivery process was impressive. The item arrived before the estimated delivery date, which was a pleasant surprise. The refrigerator was well-packaged, ensuring no damage during transit. The delivery team was also courteous and professional. They handled the heavy appliance with care and even helped place it in the desired location in my home.Now, coming to the product itself, the Godrej 436 Litre refrigerator is fantastic. It offers ample storage space for a medium-to-large family and has a sleek, modern design that fits perfectly into my kitchen. The cooling is efficient and evenly distributed, keeping food fresh for longer. I particularly love the spacious freezer compartment, which offers plenty of room for frozen items.In addition, the refrigerator runs quietly and seems to be quite energy-efficient, which is a huge plus. The various compartments and shelves are well-designed, making organization easy.Overall, I am extremely happy with both Amazon’s service and the quality of the Godrej refrigerator. I highly recommend this product to anyone looking for a reliable and stylish refrigerator. Five stars all the way!\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yogeshwar\", \"rating\": \"1.0\", \"date\": \"03 Feb 2025\", \"text\": \"Would not recommend anyone to buy this refrigerator. Had purchased it on 15 Jan and I am still waiting for the installation service. Had to perforce install it myself. Frost formation in chiller section. Extremely noisy compressor and substandard quality of plastic and metal, dents and scratches are routine.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"VKVK\", \"rating\": \"5.0\", \"date\": \"11 Oct 2024\", \"text\": \"I\'m thrilled with my new Godrej fridge! After using it for a few weeks, I thought I\'d share my honest review.Design and Build:The first thing I noticed was how stunning it looks in my kitchen. The finish is very premium and looks classy. The design is very sleek, making it a perfect fit in our kitchen.Storage:We\'re a family of four, and storage was one of the reasons for upgrading. This fridge delivers that with ease. The large vegetable box is perfect for storing all our vegetables and fruits. I also love the slide shelf which is very smooth and makes accessing things at the back very easyAI Features:Had seen the ad, and it mentioned that this Fridge comes with AI technology. It adjusts the temperature based on the weather outside, tracks food inside and more, ensuring our food stays fresh. I\'ve noticed that our fruits and veggies are staying fresh for longer in this fridge in comparison to the older oneControl Panel:The control panel on the door is sleek and easy to use. I can adjust the temperature, activate different modes and even monitor the fridge\'s performance with ease.Verdict:I\'m thoroughly satisfied with my purchase. Its delivered on its promise of quality, innovation, and design.No Complaints!Honestly, I couldn\'t find any flaws. The fridge has been running smoothly, and I haven\'t encountered any issues.Recommendation:If you\'re looking for a reliable, feature-rich fridge, look no further.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pritam Baruwa\", \"rating\": \"4.0\", \"date\": \"19 Mar 2025\", \"text\": \"The product is good to use but the compressor makes a nagging sound sometimes and that’s really irritating\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"imran\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Good product\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Atish Sharma\", \"rating\": \"3.0\", \"date\": \"22 Dec 2024\", \"text\": \"I\'m extremely disappointed to find that the fruit crisper basket is missing from my refrigerator.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Vansh\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"I have bought the fridge and it is completely noise less and very value for money\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"1.0\", \"date\": \"06 Apr 2025\", \"text\": \"My family was very happy when I got this huge fridge at 35k after applying coupon and card offers. We were very excited when it was delivered. It looked awesome. But the very next day, when the technician from godrej came, we got devastated to know that we received a defective unit. A weird loud noise was coming from the compressor. We complained to Amazon right away, and now the chase began. Amazon asked godrej to send the technician to report the issue, but they never came and submitted a false report that the issue was resolved at the doorstep. We again complained to Amazon, and after waiting for 8 days, Amazon picked the fridge to start the return process since they didn\'t have another unit to replace this defective one.We are satisfied with Amazon\'s service and cooperation but are very disappointed with Godrej\'s response. A very old renowned company like Godrej can\'t treat their customers in this manner.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Vivek H.\", \"rating\": \"5.0\", \"date\": \"30 Sep 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Godrej 436 Litre refrigerator from Amazon, and I must say the experience has been flawless from start to finish!First off, the ordering process was extremely smooth. Amazon\'s interface made it easy to find exactly what I was looking for, with detailed product descriptions and user reviews helping me finalize my decision. I placed my order with ease, and the refrigerator was offered at a competitive price with additional discounts available.The delivery process was impressive. The item arrived before the estimated delivery date, which was a pleasant surprise. The refrigerator was well-packaged, ensuring no damage during transit. The delivery team was also courteous and professional. They handled the heavy appliance with care and even helped place it in the desired location in my home.Now, coming to the product itself, the Godrej 436 Litre refrigerator is fantastic. It offers ample storage space for a medium-to-large family and has a sleek, modern design that fits perfectly into my kitchen. The cooling is efficient and evenly distributed, keeping food fresh for longer. I particularly love the spacious freezer compartment, which offers plenty of room for frozen items.In addition, the refrigerator runs quietly and seems to be quite energy-efficient, which is a huge plus. The various compartments and shelves are well-designed, making organization easy.Overall, I am extremely happy with both Amazon’s service and the quality of the Godrej refrigerator. I highly recommend this product to anyone looking for a reliable and stylish refrigerator. Five stars all the way!\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yogeshwar\", \"rating\": \"1.0\", \"date\": \"03 Feb 2025\", \"text\": \"Would not recommend anyone to buy this refrigerator. Had purchased it on 15 Jan and I am still waiting for the installation service. Had to perforce install it myself. Frost formation in chiller section. Extremely noisy compressor and substandard quality of plastic and metal, dents and scratches are routine.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"VKVK\", \"rating\": \"5.0\", \"date\": \"11 Oct 2024\", \"text\": \"I\'m thrilled with my new Godrej fridge! After using it for a few weeks, I thought I\'d share my honest review.Design and Build:The first thing I noticed was how stunning it looks in my kitchen. The finish is very premium and looks classy. The design is very sleek, making it a perfect fit in our kitchen.Storage:We\'re a family of four, and storage was one of the reasons for upgrading. This fridge delivers that with ease. The large vegetable box is perfect for storing all our vegetables and fruits. I also love the slide shelf which is very smooth and makes accessing things at the back very easyAI Features:Had seen the ad, and it mentioned that this Fridge comes with AI technology. It adjusts the temperature based on the weather outside, tracks food inside and more, ensuring our food stays fresh. I\'ve noticed that our fruits and veggies are staying fresh for longer in this fridge in comparison to the older oneControl Panel:The control panel on the door is sleek and easy to use. I can adjust the temperature, activate different modes and even monitor the fridge\'s performance with ease.Verdict:I\'m thoroughly satisfied with my purchase. Its delivered on its promise of quality, innovation, and design.No Complaints!Honestly, I couldn\'t find any flaws. The fridge has been running smoothly, and I haven\'t encountered any issues.Recommendation:If you\'re looking for a reliable, feature-rich fridge, look no further.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pritam Baruwa\", \"rating\": \"4.0\", \"date\": \"19 Mar 2025\", \"text\": \"The product is good to use but the compressor makes a nagging sound sometimes and that’s really irritating\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"imran\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Good product\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Atish Sharma\", \"rating\": \"3.0\", \"date\": \"22 Dec 2024\", \"text\": \"I\'m extremely disappointed to find that the fruit crisper basket is missing from my refrigerator.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Vansh\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"I have bought the fridge and it is completely noise less and very value for money\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"1.0\", \"date\": \"06 Apr 2025\", \"text\": \"My family was very happy when I got this huge fridge at 35k after applying coupon and card offers. We were very excited when it was delivered. It looked awesome. But the very next day, when the technician from godrej came, we got devastated to know that we received a defective unit. A weird loud noise was coming from the compressor. We complained to Amazon right away, and now the chase began. Amazon asked godrej to send the technician to report the issue, but they never came and submitted a false report that the issue was resolved at the doorstep. We again complained to Amazon, and after waiting for 8 days, Amazon picked the fridge to start the return process since they didn\'t have another unit to replace this defective one.We are satisfied with Amazon\'s service and cooperation but are very disappointed with Godrej\'s response. A very old renowned company like Godrej can\'t treat their customers in this manner.\n  \nRead more\", \"product_id\": \"B0DB63CFRM\", \"link\": \"https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>oltas Beko 470 L 2 Star Inverter Frost-Free Double Door Refrigerator</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>12</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>16</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B081B9RN1C\", \"product_name\": \"Voltas Beko 470 L 2 Star Inverter Frost-Free Double Door Refrigerator, Store Fresh+ (RFF493IF, Silver)\", \"product_url\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 3.62, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"AfzelAfzel\", \"rating\": \"5.0\", \"date\": \"21 Oct 2023\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Even though i have got a 2021 MODEL instead of 2022 MODEL as described, it was a mind-blowing purchase when it comes to the quality of product (that is why i decided not to return the product). I am writing this review after one week of purchase and i found the fridge to be working in an efficient manner with very very low noise(pretty much happy with that). No complicated settings to consider about as we just needed to set the top and bottom temperatures only. Happy to have a spacious freezer........Working good so far dated 21 Apr 2024\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yosshita Poddar\", \"rating\": \"1.0\", \"date\": \"25 Aug 2024\", \"text\": \"I have never seen such a poor quality designed product from house of TATA. Shelves, glass and space are so poorly designed that lot of times your fridge door remain open due to insufficient space between shelves, tray and door. Bottom half is so awkwardly designed that you need to learn to manoeuvre it.Overall POORLY DESIGNED WITH SUB STANDARD MATERIALS.I will never recommend to buy this product.\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Subodh M.\", \"rating\": \"4.0\", \"date\": \"25 Apr 2024\", \"text\": \"Awesome product. Looks are classy, as of now performance is great,\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ankit S.\", \"rating\": \"5.0\", \"date\": \"06 Jan 2025\", \"text\": \"Good product. As described.\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mukesh Agarwal Hyd\", \"rating\": \"5.0\", \"date\": \"13 Dec 2024\", \"text\": \"Very nice gift of God via  Amazon\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Radhika\", \"rating\": \"3.0\", \"date\": \"05 Feb 2024\", \"text\": \"Freezer design is convenient\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"28 Nov 2024\", \"text\": \"Very good product\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sayed Ali\", \"rating\": \"1.0\", \"date\": \"12 Mar 2025\", \"text\": \"One of the worst Refrigerator.. that too from Voltas.. within Eight month Twice gas is been refilled, Compressor is been changed .. 6 technician visit.. still the problem exist upper part of the Fridge does not give cooling.. I don’t know what to say more.. I did not expected this From Voltas.. Horrible, Pathetic &amp; Garbage product.\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"AfzelAfzel\", \"rating\": \"5.0\", \"date\": \"21 Oct 2023\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Even though i have got a 2021 MODEL instead of 2022 MODEL as described, it was a mind-blowing purchase when it comes to the quality of product (that is why i decided not to return the product). I am writing this review after one week of purchase and i found the fridge to be working in an efficient manner with very very low noise(pretty much happy with that). No complicated settings to consider about as we just needed to set the top and bottom temperatures only. Happy to have a spacious freezer........Working good so far dated 21 Apr 2024\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yosshita Poddar\", \"rating\": \"1.0\", \"date\": \"25 Aug 2024\", \"text\": \"I have never seen such a poor quality designed product from house of TATA. Shelves, glass and space are so poorly designed that lot of times your fridge door remain open due to insufficient space between shelves, tray and door. Bottom half is so awkwardly designed that you need to learn to manoeuvre it.Overall POORLY DESIGNED WITH SUB STANDARD MATERIALS.I will never recommend to buy this product.\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Subodh M.\", \"rating\": \"4.0\", \"date\": \"25 Apr 2024\", \"text\": \"Awesome product. Looks are classy, as of now performance is great,\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ankit S.\", \"rating\": \"5.0\", \"date\": \"06 Jan 2025\", \"text\": \"Good product. As described.\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mukesh Agarwal Hyd\", \"rating\": \"5.0\", \"date\": \"13 Dec 2024\", \"text\": \"Very nice gift of God via  Amazon\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Radhika\", \"rating\": \"3.0\", \"date\": \"05 Feb 2024\", \"text\": \"Freezer design is convenient\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"28 Nov 2024\", \"text\": \"Very good product\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sayed Ali\", \"rating\": \"1.0\", \"date\": \"12 Mar 2025\", \"text\": \"One of the worst Refrigerator.. that too from Voltas.. within Eight month Twice gas is been refilled, Compressor is been changed .. 6 technician visit.. still the problem exist upper part of the Fridge does not give cooling.. I don’t know what to say more.. I did not expected this From Voltas.. Horrible, Pathetic &amp; Garbage product.\n  \nRead more\", \"product_id\": \"B081B9RN1C\", \"link\": \"https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LG 14 Place Setting Free Standing Dish Washer</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>14</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>16</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B09THF5XDX\", \"product_name\": \"LG 14 Place Setting Free Standing Dish Washer with TrueSteam, QuadWash, EasyRack Plus, Wi-Fi Enabled (DFB424FM, Matte Black, Inverter Direct Drive Motor)\", \"product_url\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"13 Sep 2019\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent Dishwasher. Little pricier compared to Bosch or other machines, but it has got lot more to offer.Pros:1, Inside fully stainless steel body, compared to Bosch.2, The Baskets are even more sturdier than Bosch, it also has a thick plastic grab rail around the baskets, which is nice.3, Top basket height adjustable. Very useful.4, Good vessel setting and can take in lot of vessels if arranged properly.5, Many wash programs are there, even the express mode/program which is only 45mins is cleaning the vessels nicely.6, Wifi connectivity, and from smartphone app, we can monitor the progress of the washing. Also it downloaded firmware when connected first time. There is a downloadable program/wash mode from smart phone, very nice. At present 4 extra programs available in app, which can be downloaded.7, Very silent operation.8, Uses very little water. Much need thing of the hour. If maid washes will need atleast 4 normal sized bucket full of water, this thing uses under 10ltrs in total per wash, that like little more than half a bucket.9, Our unit is made in South Korea around april\'19 and imported, so no complaints there.10, A steam setting is there, not very sure whats it will do, need to see further, as of now without steam itself dishes are washed sparkling clean.Cons:1, Bit pricier.2, Inlet pipe installation is a bit difficult, not as straight forward as any washing machine. This dishwasher has a inlet pipe with threaded type, so cant connect to a normal tap, need a angle tap. The inlet pipe thread size is bit odd, doesn\'t fit to a angle tap, need an adapter/bush, you can\'t even take the inlet pipe to the hardware shop and show to get an matching adapter/bush, it is attached to the machine. So took lot of photos and paper cut sizes and bought the adapter. Changed the normal pipe tap to a angle tap.3,Installation, well I did it, the LG guy called me up and said get everything ready, the pipe connection and every thing,  and he will come and show the demo. I didnt care to call him back, fitted everything and started using it. Machine works nice.Overall, a nice machine, don\'t have to be dependent on maid, need not complain to maid about dishes not clean, This machine washes the dishes to sparkling clean. Already SS vessels are starting to shine. Recommend buy.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anil\", \"rating\": \"5.0\", \"date\": \"23 Feb 2021\", \"text\": \"Bought it from cloudtail and got it delivered the very next day. It is imported from South Korea, so it needs a non-standard 3/4 inch threaded inlet (can be easily managed using an adapter on 1/2inch tap). The installation was prompt.Pros-1. I believe this is the only dishwasher in India with steam cleaning function (Bosch has only high temp upto 70°C)2. Used Finish Detergent, Salt and Rinse Aid with very good results.3. Cleaning is upto the mark and the operation is silent.4. Water consumption is low and so is power consumption unless you use the steam cycle.5. There are multiple modes and it can be connected to wifi to monitor progress on your smartphone app.Cons-1. Price is comparatively higher2. Requires non-standard 3/4inch threaded inlet3. Aluminum, Cast Iron and Non-Stick utensils cannot be used in any dishwasher due to its reactivity with the alkali detergent\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"kapil yadav\", \"rating\": \"1.0\", \"date\": \"11 Jan 2025\", \"text\": \"Washing utensils is ok but this dishwasher can\'t dry dishes well. You will find water inside it even if you select extra dry.I have been using Bosh for last 3 years never faced drying problem there... I was stupid enough to try something new this time and paid for the stupid mistake.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Piyush\", \"rating\": \"4.0\", \"date\": \"30 May 2021\", \"text\": \"Satisfied with the product, quality, cleaning and features.Best dishwasher in the market,No second thoughts, go for it !!2 Years review : no problem what so ever in terms of cleaning quality.Only issue - its cleaning cycle starts from scratch in case of power outage in between. It\'s high time - LG to bring software update immediately.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"S. M. S.\", \"rating\": \"5.0\", \"date\": \"27 Aug 2022\", \"text\": \"Initially, i was reluctant to invest in a dishwasher because of poor reviews regarding their ability to clean Indian type utensils with curry stains, oils ... etc. However due to the irritating behaviour of maids, i went ahead and bought this LG model after doing thorough research on the Internet.To cut a long story short, i have found that this particular model is exceptional in its advertised capabilities.Sparkling clean utensils etc every time.One thing to be aware of is that due to its steam and high temperature wash programs, plastic utensils of doubtful quality will warp and crack after two or three rounds of washing. This is not a bad thing actually since I now know what types of plastics to avoid purchasing in the first place.I am very satisfied with my purchase.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Simply said wow...always LG. We have 2 products like washing machine, 14 places setting dishwasher and will be looking for AC also, thanks LG and amazon.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abhiishek\", \"rating\": \"5.0\", \"date\": \"27 Jul 2023\", \"text\": \"We purchased this after a lot of research in the market. We also spent a couple of extra thousand on this black color but this is worth every rupee. The utensils will be crystal clear and you will never ever regret spending so much money on this dishwasher.It has various cleaning cycle and can also be operated with mobile using the wireless connectivity. With the steam function, there is no need of any pre cleaning / washing and you can directly put the used utensils in the dishwasher.100% recommended over any other brand of dishwasher\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"15 Nov 2024\", \"text\": \"Fantastic performance.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"13 Sep 2019\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Excellent Dishwasher. Little pricier compared to Bosch or other machines, but it has got lot more to offer.Pros:1, Inside fully stainless steel body, compared to Bosch.2, The Baskets are even more sturdier than Bosch, it also has a thick plastic grab rail around the baskets, which is nice.3, Top basket height adjustable. Very useful.4, Good vessel setting and can take in lot of vessels if arranged properly.5, Many wash programs are there, even the express mode/program which is only 45mins is cleaning the vessels nicely.6, Wifi connectivity, and from smartphone app, we can monitor the progress of the washing. Also it downloaded firmware when connected first time. There is a downloadable program/wash mode from smart phone, very nice. At present 4 extra programs available in app, which can be downloaded.7, Very silent operation.8, Uses very little water. Much need thing of the hour. If maid washes will need atleast 4 normal sized bucket full of water, this thing uses under 10ltrs in total per wash, that like little more than half a bucket.9, Our unit is made in South Korea around april\'19 and imported, so no complaints there.10, A steam setting is there, not very sure whats it will do, need to see further, as of now without steam itself dishes are washed sparkling clean.Cons:1, Bit pricier.2, Inlet pipe installation is a bit difficult, not as straight forward as any washing machine. This dishwasher has a inlet pipe with threaded type, so cant connect to a normal tap, need a angle tap. The inlet pipe thread size is bit odd, doesn\'t fit to a angle tap, need an adapter/bush, you can\'t even take the inlet pipe to the hardware shop and show to get an matching adapter/bush, it is attached to the machine. So took lot of photos and paper cut sizes and bought the adapter. Changed the normal pipe tap to a angle tap.3,Installation, well I did it, the LG guy called me up and said get everything ready, the pipe connection and every thing,  and he will come and show the demo. I didnt care to call him back, fitted everything and started using it. Machine works nice.Overall, a nice machine, don\'t have to be dependent on maid, need not complain to maid about dishes not clean, This machine washes the dishes to sparkling clean. Already SS vessels are starting to shine. Recommend buy.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anil\", \"rating\": \"5.0\", \"date\": \"23 Feb 2021\", \"text\": \"Bought it from cloudtail and got it delivered the very next day. It is imported from South Korea, so it needs a non-standard 3/4 inch threaded inlet (can be easily managed using an adapter on 1/2inch tap). The installation was prompt.Pros-1. I believe this is the only dishwasher in India with steam cleaning function (Bosch has only high temp upto 70°C)2. Used Finish Detergent, Salt and Rinse Aid with very good results.3. Cleaning is upto the mark and the operation is silent.4. Water consumption is low and so is power consumption unless you use the steam cycle.5. There are multiple modes and it can be connected to wifi to monitor progress on your smartphone app.Cons-1. Price is comparatively higher2. Requires non-standard 3/4inch threaded inlet3. Aluminum, Cast Iron and Non-Stick utensils cannot be used in any dishwasher due to its reactivity with the alkali detergent\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"kapil yadav\", \"rating\": \"1.0\", \"date\": \"11 Jan 2025\", \"text\": \"Washing utensils is ok but this dishwasher can\'t dry dishes well. You will find water inside it even if you select extra dry.I have been using Bosh for last 3 years never faced drying problem there... I was stupid enough to try something new this time and paid for the stupid mistake.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Piyush\", \"rating\": \"4.0\", \"date\": \"30 May 2021\", \"text\": \"Satisfied with the product, quality, cleaning and features.Best dishwasher in the market,No second thoughts, go for it !!2 Years review : no problem what so ever in terms of cleaning quality.Only issue - its cleaning cycle starts from scratch in case of power outage in between. It\'s high time - LG to bring software update immediately.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"S. M. S.\", \"rating\": \"5.0\", \"date\": \"27 Aug 2022\", \"text\": \"Initially, i was reluctant to invest in a dishwasher because of poor reviews regarding their ability to clean Indian type utensils with curry stains, oils ... etc. However due to the irritating behaviour of maids, i went ahead and bought this LG model after doing thorough research on the Internet.To cut a long story short, i have found that this particular model is exceptional in its advertised capabilities.Sparkling clean utensils etc every time.One thing to be aware of is that due to its steam and high temperature wash programs, plastic utensils of doubtful quality will warp and crack after two or three rounds of washing. This is not a bad thing actually since I now know what types of plastics to avoid purchasing in the first place.I am very satisfied with my purchase.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Simply said wow...always LG. We have 2 products like washing machine, 14 places setting dishwasher and will be looking for AC also, thanks LG and amazon.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abhiishek\", \"rating\": \"5.0\", \"date\": \"27 Jul 2023\", \"text\": \"We purchased this after a lot of research in the market. We also spent a couple of extra thousand on this black color but this is worth every rupee. The utensils will be crystal clear and you will never ever regret spending so much money on this dishwasher.It has various cleaning cycle and can also be operated with mobile using the wireless connectivity. With the steam function, there is no need of any pre cleaning / washing and you can directly put the used utensils in the dishwasher.100% recommended over any other brand of dishwasher\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"15 Nov 2024\", \"text\": \"Fantastic performance.\n  \nRead more\", \"product_id\": \"B09THF5XDX\", \"link\": \"https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PHILIPS Air Fryer NA352/00 with Rapid Air Technology</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>16</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>16</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D4ZCRPKL\", \"product_name\": \"PHILIPS Air Fryer NA352/00 with Rapid Air Technology, 9L capacity, Dual basket (6L &amp; 3L) for full oven tray cooking, 8 Preset Menus, Intuitive touch control, 90% less oil, 500+ Recipes, Extra Large\", \"product_url\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"SushilSushil\", \"rating\": \"5.0\", \"date\": \"18 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This philips Air Fryer is a fantastic kitchen gadget that truly elevates cooking With its 9L capacity and dual baskets it is perfect for preparing meals for large families or gatherings The Rapid Air Technology ensures that food is cooked evenly and crispy with up to 90% less oil promoting healthier eating habits The intuitive touch control and 8 preset menus make it easy to use Overall this air fryer is a game changer for anyone looking to enjoy delicious healthier meals with minimal effort Totally a value for money product\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Amulya\", \"rating\": \"5.0\", \"date\": \"18 Oct 2024\", \"text\": \"The Philips Air Fryer is a fantastic kitchen gadget that combines convenience and healthy cooking. Its rapid air technology allows for crispy and evenly cooked food with up to 90% less oil, making it a great alternative to traditional frying. The intuitive controls and multiple cooking functions—like baking, roasting, and grilling—offer versatility. It’s easy to clean with dishwasher-safe parts, making it ideal for busy kitchens. Overall, it’s a reliable choice for those looking to enjoy fried favorites with a healthier twist.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"kamari swami\", \"rating\": \"4.0\", \"date\": \"09 Apr 2025\", \"text\": \"I received a damaged product (broken from backside). It was quickly replaced with new one by amazon.I didn\'t like the overall concept of Air fryer. It is better to purchase an oven with convection feature.Otherwise, this unit works nice. Does the job. It is silent, great looking and functional.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"ChakshuChakshu\", \"rating\": \"5.0\", \"date\": \"14 Oct 2024\", \"text\": \"Quality of airfryr is very premium. Build quality is very good. This  2-compartment air fryer offers the convenience of cooking two different dishes simultaneously without mixing flavors. The baskets are usually spacious, accommodating larger portions. The air fryer delivers crispy results with minimal oil, promoting healthier eating. It heats quickly and is easy to clean, with removable, dishwasher-safe parts. Overall, it’s a versatile and time-saving appliance.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Megamisamaone\", \"rating\": \"1.0\", \"date\": \"22 Mar 2025\", \"text\": \"I am a self proclaimed great fan of Phillips innovations but this product is a disaster. Two compartments are ok but the same has resulted in 6 ltr becoming too small, try using it you will understand, 9 ltr should have been one big compartment only\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Sharvan jeetSharvan jeet\", \"rating\": \"5.0\", \"date\": \"21 Oct 2024\", \"text\": \"This fryer is very versatile functionality wise as we can cook two batches or completely two different receipes altogether as has different controls for both. I have been enjoying this for making healthy and quick receipes. Food comes perfectly crispy with minimal oul. Cleaning is also very easy and this is dishwasher safe also. Really great value for money and we also get Philips warranty and trust.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Harshith PrabhuHarshith Prabhu\", \"rating\": \"5.0\", \"date\": \"25 Jan 2025\", \"text\": \"Fantastic product!It’s my first air fryer and definitely worth the wait! Amazon was quick on delivery and the product is stunning!Tried cookies and wow it came out great!The double door is marvellous making cooking easier and quicker!The food has also been delicious!\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Anju Singla\", \"rating\": \"4.0\", \"date\": \"22 Jan 2025\", \"text\": \"Product is good , but I got to know just now that air fryer is not good for health\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"SushilSushil\", \"rating\": \"5.0\", \"date\": \"18 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This philips Air Fryer is a fantastic kitchen gadget that truly elevates cooking With its 9L capacity and dual baskets it is perfect for preparing meals for large families or gatherings The Rapid Air Technology ensures that food is cooked evenly and crispy with up to 90% less oil promoting healthier eating habits The intuitive touch control and 8 preset menus make it easy to use Overall this air fryer is a game changer for anyone looking to enjoy delicious healthier meals with minimal effort Totally a value for money product\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Amulya\", \"rating\": \"5.0\", \"date\": \"18 Oct 2024\", \"text\": \"The Philips Air Fryer is a fantastic kitchen gadget that combines convenience and healthy cooking. Its rapid air technology allows for crispy and evenly cooked food with up to 90% less oil, making it a great alternative to traditional frying. The intuitive controls and multiple cooking functions—like baking, roasting, and grilling—offer versatility. It’s easy to clean with dishwasher-safe parts, making it ideal for busy kitchens. Overall, it’s a reliable choice for those looking to enjoy fried favorites with a healthier twist.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"kamari swami\", \"rating\": \"4.0\", \"date\": \"09 Apr 2025\", \"text\": \"I received a damaged product (broken from backside). It was quickly replaced with new one by amazon.I didn\'t like the overall concept of Air fryer. It is better to purchase an oven with convection feature.Otherwise, this unit works nice. Does the job. It is silent, great looking and functional.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"ChakshuChakshu\", \"rating\": \"5.0\", \"date\": \"14 Oct 2024\", \"text\": \"Quality of airfryr is very premium. Build quality is very good. This  2-compartment air fryer offers the convenience of cooking two different dishes simultaneously without mixing flavors. The baskets are usually spacious, accommodating larger portions. The air fryer delivers crispy results with minimal oil, promoting healthier eating. It heats quickly and is easy to clean, with removable, dishwasher-safe parts. Overall, it’s a versatile and time-saving appliance.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Megamisamaone\", \"rating\": \"1.0\", \"date\": \"22 Mar 2025\", \"text\": \"I am a self proclaimed great fan of Phillips innovations but this product is a disaster. Two compartments are ok but the same has resulted in 6 ltr becoming too small, try using it you will understand, 9 ltr should have been one big compartment only\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Sharvan jeetSharvan jeet\", \"rating\": \"5.0\", \"date\": \"21 Oct 2024\", \"text\": \"This fryer is very versatile functionality wise as we can cook two batches or completely two different receipes altogether as has different controls for both. I have been enjoying this for making healthy and quick receipes. Food comes perfectly crispy with minimal oul. Cleaning is also very easy and this is dishwasher safe also. Really great value for money and we also get Philips warranty and trust.\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Harshith PrabhuHarshith Prabhu\", \"rating\": \"5.0\", \"date\": \"25 Jan 2025\", \"text\": \"Fantastic product!It’s my first air fryer and definitely worth the wait! Amazon was quick on delivery and the product is stunning!Tried cookies and wow it came out great!The double door is marvellous making cooking easier and quicker!The food has also been delicious!\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}, {\"author\": \"Anju Singla\", \"rating\": \"4.0\", \"date\": \"22 Jan 2025\", \"text\": \"Product is good , but I got to know just now that air fryer is not good for health\n  \nRead more\", \"product_id\": \"B0D4ZCRPKL\", \"link\": \"https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KENT Digital Air Fryer Oven 12L | 1800W | 360° Rapid Heat Circulation | 10 Preset Menus | Bake, Grill &amp; Roast | Digital Display &amp; Touch Control Panel | Dehydration &amp; Rotisserie Function</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>16</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DGKDWVTZ\", \"product_name\": \"KENT Digital Air Fryer Oven 12L | 1800W | 360° Rapid Heat Circulation | 10 Preset Menus | Bake, Grill &amp; Roast | Digital Display &amp; Touch Control Panel | Dehydration &amp; Rotisserie Function\", \"product_url\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 10, \"neutral\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Vanchinathan Krishnamoorthy\", \"rating\": \"5.0\", \"date\": \"31 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Air Fryer Review: A Game-Changer in the Kitchen!I recently purchased an air fryer, and it has completely transformed my cooking experience! This appliance is a must-have for anyone who loves crispy, delicious food without the excess oil.Performance &amp; Cooking QualityThe air fryer cooks food evenly and quickly, delivering a crispy texture that rivals deep-frying but with significantly less fat. Whether I’m making French fries, chicken wings, or roasted vegetables, everything turns out perfectly golden and delicious.Ease of UseOne of the best features is its user-friendly interface. With pre-set cooking options and an intuitive digital display, it’s incredibly easy to use. Simply set the temperature and time, and the air fryer does the rest. Plus, the timer and automatic shut-off feature make cooking stress-free.Design &amp; BuildThe sleek and modern design fits beautifully in my kitchen. It’s compact yet spacious enough to cook meals for the whole family. The non-stick basket makes cleanup a breeze—just a quick rinse or pop it in the dishwasher.Health BenefitsThe biggest advantage is the ability to enjoy crispy, flavorful food with up to 80% less oil. It’s perfect for those looking to eat healthier without sacrificing taste or texture.Final VerdictThis air fryer is a game-changer! It’s efficient, easy to use, and makes healthy eating more enjoyable. If you’re looking for a way to cook delicious meals with minimal effort and maximum flavor, I highly recommend investing in one.⭐ Rating: 5/5 – Absolutely Worth It! ⭐\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"manan d.\", \"rating\": \"4.0\", \"date\": \"26 Jan 2025\", \"text\": \"It\'s good buy. Does it\'s job. I am making all types of vadas, samosas, fried foods in this air fryer. Food cane out crispy and sometimes even better than oil fried version. Very easy to use, safe handling, sturdy build quality.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sahil AcharekarSahil Acharekar\", \"rating\": \"5.0\", \"date\": \"07 Apr 2025\", \"text\": \"Product was very useful to use. And price of product is affordable or worth it.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"kmvarier\", \"rating\": \"1.0\", \"date\": \"29 Apr 2025\", \"text\": \"When the item was delivered it was tested and found working ok. But after one week when we tried to use it again, it was not switching on at all. Kindly advise me as what to do to set it right. I understand that the item is under warranty for one year.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anoop Menon\", \"rating\": \"5.0\", \"date\": \"19 Apr 2025\", \"text\": \"Review after a few weeks. Sleek machine, sturdy so far, ideal for cauliflower pakoras, chicken snacks, veggie fries etc. I bought a silicone liner. Two suggestions , please provide silicone liners as add on buys ( hard to find quality liners of same size ), and the metal tray that goes in the basket has silicone bushes that keep dropping out when you remove the tray , may scratch the basket. Please redesign this.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"pri\", \"rating\": \"3.0\", \"date\": \"08 Apr 2025\", \"text\": \"Product is good it says 360° but if kept trays in layer the lower layer doesn\'t get cooked\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Asmita\", \"rating\": \"5.0\", \"date\": \"12 Dec 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    \\"I\'m absolutely delighted with my Kent 8L Air Fryer! It\'s been a game-changer in my kitchen. The large 8L capacity is perfect for cooking for my family and friends.The air fryer is incredibly easy to use, and the digital touchscreen makes it simple to navigate. The preset options for different types of food are super convenient.The results are amazing! Crispy banana chips, moist paneer , nonveg not yet tried - all with minimal oil. The cleaning process is also a breeze.I\'ve already recommended the Kent 8L Air Fryer to my friends and family. It\'s a must-have for anyone looking for a healthy and convenient cooking option.*Pros:*- Large 8L capacity- Easy to use and clean- Digital touchscreen with preset options- Healthy cooking with minimal oil- Fast cooking time*Cons:* yet not identifiedI\'m extremely satisfied with my purchase, and I\'m sure you will be too!\\"\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Harry\", \"rating\": \"4.0\", \"date\": \"19 Apr 2025\", \"text\": \"I brought Kent air oven 12l and this product cooking quality is very well and all function work properly.but for build quality i give 3 stars\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Vanchinathan Krishnamoorthy\", \"rating\": \"5.0\", \"date\": \"31 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Air Fryer Review: A Game-Changer in the Kitchen!I recently purchased an air fryer, and it has completely transformed my cooking experience! This appliance is a must-have for anyone who loves crispy, delicious food without the excess oil.Performance &amp; Cooking QualityThe air fryer cooks food evenly and quickly, delivering a crispy texture that rivals deep-frying but with significantly less fat. Whether I’m making French fries, chicken wings, or roasted vegetables, everything turns out perfectly golden and delicious.Ease of UseOne of the best features is its user-friendly interface. With pre-set cooking options and an intuitive digital display, it’s incredibly easy to use. Simply set the temperature and time, and the air fryer does the rest. Plus, the timer and automatic shut-off feature make cooking stress-free.Design &amp; BuildThe sleek and modern design fits beautifully in my kitchen. It’s compact yet spacious enough to cook meals for the whole family. The non-stick basket makes cleanup a breeze—just a quick rinse or pop it in the dishwasher.Health BenefitsThe biggest advantage is the ability to enjoy crispy, flavorful food with up to 80% less oil. It’s perfect for those looking to eat healthier without sacrificing taste or texture.Final VerdictThis air fryer is a game-changer! It’s efficient, easy to use, and makes healthy eating more enjoyable. If you’re looking for a way to cook delicious meals with minimal effort and maximum flavor, I highly recommend investing in one.⭐ Rating: 5/5 – Absolutely Worth It! ⭐\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"manan d.\", \"rating\": \"4.0\", \"date\": \"26 Jan 2025\", \"text\": \"It\'s good buy. Does it\'s job. I am making all types of vadas, samosas, fried foods in this air fryer. Food cane out crispy and sometimes even better than oil fried version. Very easy to use, safe handling, sturdy build quality.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sahil AcharekarSahil Acharekar\", \"rating\": \"5.0\", \"date\": \"07 Apr 2025\", \"text\": \"Product was very useful to use. And price of product is affordable or worth it.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"kmvarier\", \"rating\": \"1.0\", \"date\": \"29 Apr 2025\", \"text\": \"When the item was delivered it was tested and found working ok. But after one week when we tried to use it again, it was not switching on at all. Kindly advise me as what to do to set it right. I understand that the item is under warranty for one year.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anoop Menon\", \"rating\": \"5.0\", \"date\": \"19 Apr 2025\", \"text\": \"Review after a few weeks. Sleek machine, sturdy so far, ideal for cauliflower pakoras, chicken snacks, veggie fries etc. I bought a silicone liner. Two suggestions , please provide silicone liners as add on buys ( hard to find quality liners of same size ), and the metal tray that goes in the basket has silicone bushes that keep dropping out when you remove the tray , may scratch the basket. Please redesign this.\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"pri\", \"rating\": \"3.0\", \"date\": \"08 Apr 2025\", \"text\": \"Product is good it says 360° but if kept trays in layer the lower layer doesn\'t get cooked\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Asmita\", \"rating\": \"5.0\", \"date\": \"12 Dec 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    \\"I\'m absolutely delighted with my Kent 8L Air Fryer! It\'s been a game-changer in my kitchen. The large 8L capacity is perfect for cooking for my family and friends.The air fryer is incredibly easy to use, and the digital touchscreen makes it simple to navigate. The preset options for different types of food are super convenient.The results are amazing! Crispy banana chips, moist paneer , nonveg not yet tried - all with minimal oil. The cleaning process is also a breeze.I\'ve already recommended the Kent 8L Air Fryer to my friends and family. It\'s a must-have for anyone looking for a healthy and convenient cooking option.*Pros:*- Large 8L capacity- Easy to use and clean- Digital touchscreen with preset options- Healthy cooking with minimal oil- Fast cooking time*Cons:* yet not identifiedI\'m extremely satisfied with my purchase, and I\'m sure you will be too!\\"\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Harry\", \"rating\": \"4.0\", \"date\": \"19 Apr 2025\", \"text\": \"I brought Kent air oven 12l and this product cooking quality is very well and all function work properly.but for build quality i give 3 stars\n  \nRead more\", \"product_id\": \"B0DGKDWVTZ\", \"link\": \"https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Geek AiroCook Zenix 25 Litre Electric Air Fryer Oven, 18 Digital Preset Menus with Rotisserie, Airfry, Bake, Grill, Toast</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>16</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CJMJMBTZ\", \"product_name\": \"Geek AiroCook Zenix 25 Litre Electric Air Fryer Oven, 18 Digital Preset Menus with Rotisserie, Airfry, Bake, Grill, Toast, Dehydrate, Defrost &amp; Keep Warm Functions with 8 Accessories (1700W), Black\", \"product_url\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Veerakrishna\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good quality product functionality cooking was very fast\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tajdeen ATajdeen A\", \"rating\": \"4.0\", \"date\": \"27 Jul 2024\", \"text\": \"I like this AIROCOOK. But need some improvement for this product. Currently this product maximum capacity 25ltr. This is not enough for big families. Also product recipe book every recipe cook time difference between product menu timing. Please update new product recipe book. Performance good, very ease to use this product, Accessories also need cake baking tray. Value for money.\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"22 Jun 2024\", \"text\": \"The Geek AiroCook Helix Air Fryer transforms your kitchen experience, offering 12 preset menus and 8-in-1 functionality for diverse cooking needs. Prepare healthy, delicious meals with up to 85% less fat effortlessly. It\'s user-friendly, easy to clean, and a valuable addition to any kitchen, making it a worthwhile investment.\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vinutha\", \"rating\": \"1.0\", \"date\": \"03 Jan 2025\", \"text\": \"Product wise its really good and working smoothlyThe attachments are of very cheap qualityInitially it was working greatIts past one year and now there is an power fluctuations issue and there is no proper service available from the company\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AbinayaAbinaya\", \"rating\": \"5.0\", \"date\": \"25 Jul 2024\", \"text\": \"Bought this steel airfryer to replace my old philips airfryer. Calix has full steel body and enough space to bake cake bread medium pizza and grill a whole chicken. Tried making a a brownie and it came really well. The door doesn’t lock completely there are some gaps. The outside body gets heated while cooking so make sure you dont touch it. The crumb tray is really useful to clean up the mess and the rotating mesh can is very useful for making french fries. Will share more once used fully\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"NITYASREE ENTERPRISES-KRISHNAVENI RACHARLA\", \"rating\": \"4.0\", \"date\": \"20 Mar 2025\", \"text\": \"this is good for the last one monthwe will share more feedback\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Adhavan Nagarathinam\", \"rating\": \"5.0\", \"date\": \"25 Sep 2024\", \"text\": \"I purchased this 25L air fryer. It features a durable steel exterior and has ample space for baking cakes, bread, medium-sized pizzas, and even grilling an entire chicken. I tried baking cupcakes and pizza, and it turned out great. The crumb tray is a handy addition for easy cleanup, and the rotating mesh basket is excellent for making fries. In the end, excellent use it even makes our health healthier with the reduction of oil.\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nijo Joseph\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"So far so good..Tried french fries, Rotisserie Chicken, Sandwich etc. 1700 Watts... Preheat almost 500W...\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Veerakrishna\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Good quality product functionality cooking was very fast\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tajdeen ATajdeen A\", \"rating\": \"4.0\", \"date\": \"27 Jul 2024\", \"text\": \"I like this AIROCOOK. But need some improvement for this product. Currently this product maximum capacity 25ltr. This is not enough for big families. Also product recipe book every recipe cook time difference between product menu timing. Please update new product recipe book. Performance good, very ease to use this product, Accessories also need cake baking tray. Value for money.\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"22 Jun 2024\", \"text\": \"The Geek AiroCook Helix Air Fryer transforms your kitchen experience, offering 12 preset menus and 8-in-1 functionality for diverse cooking needs. Prepare healthy, delicious meals with up to 85% less fat effortlessly. It\'s user-friendly, easy to clean, and a valuable addition to any kitchen, making it a worthwhile investment.\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vinutha\", \"rating\": \"1.0\", \"date\": \"03 Jan 2025\", \"text\": \"Product wise its really good and working smoothlyThe attachments are of very cheap qualityInitially it was working greatIts past one year and now there is an power fluctuations issue and there is no proper service available from the company\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AbinayaAbinaya\", \"rating\": \"5.0\", \"date\": \"25 Jul 2024\", \"text\": \"Bought this steel airfryer to replace my old philips airfryer. Calix has full steel body and enough space to bake cake bread medium pizza and grill a whole chicken. Tried making a a brownie and it came really well. The door doesn’t lock completely there are some gaps. The outside body gets heated while cooking so make sure you dont touch it. The crumb tray is really useful to clean up the mess and the rotating mesh can is very useful for making french fries. Will share more once used fully\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"NITYASREE ENTERPRISES-KRISHNAVENI RACHARLA\", \"rating\": \"4.0\", \"date\": \"20 Mar 2025\", \"text\": \"this is good for the last one monthwe will share more feedback\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Adhavan Nagarathinam\", \"rating\": \"5.0\", \"date\": \"25 Sep 2024\", \"text\": \"I purchased this 25L air fryer. It features a durable steel exterior and has ample space for baking cakes, bread, medium-sized pizzas, and even grilling an entire chicken. I tried baking cupcakes and pizza, and it turned out great. The crumb tray is a handy addition for easy cleanup, and the rotating mesh basket is excellent for making fries. In the end, excellent use it even makes our health healthier with the reduction of oil.\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nijo Joseph\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"So far so good..Tried french fries, Rotisserie Chicken, Sandwich etc. 1700 Watts... Preheat almost 500W...\n  \nRead more\", \"product_id\": \"B0CJMJMBTZ\", \"link\": \"https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Pigeon Healthifry Digital Air Fryer</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>16</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0B8XNPQPN\", \"product_name\": \"Pigeon Healthifry Digital Air Fryer, 360° High Speed Air Circulation Technology 1200 W with Non-Stick 4.2 L Basket - Green\", \"product_url\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 3.5, \"sentiment_breakdown\": {\"positive\": 8, \"negative\": 4, \"neutral\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 50.0}, \"reviews\": [{\"author\": \"Bhavesh Jhaveri\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This is fantastic product, value for money. Aesthetics are cool. Digital display is very easy to use. Very handy machine. Gets on the task quickly. Can be cleaned quickly. Less oil and more taste. Eat with no tension as air fryer takes care of extra oil which in fact is not required.\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"souravsourav\", \"rating\": \"1.0\", \"date\": \"29 Apr 2025\", \"text\": \"Very bad product I have ordered this Air fryer just few days back and when i am using this for the first time i tried to fry some chicken where i placed 3-4 small pieces and set the temperature to 180 and timing for 15 mins , and immediately i got a error in the display showing E1 which means “ BROKEN CIRCUIT OF THE THERMAL SENSORS “ i tried to contact customer care number shown in the manual and i am not able to connect with them ( Poor Customer care support ) , very poor and frustrating experience with this product and after that i returned this product and purchased a new one where i am getting a very bad experience where the Air fryer is emitting smoke from inside and not working at all . Such a disappointing brand and Air fryer , NEVER Buy This\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"uday bhaskaruday bhaskar\", \"rating\": \"4.0\", \"date\": \"21 Jan 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    The product is morethan expected for me. Very nice and easy to cook.Design, color weight noice leve gets good marks. If u are buying for first time go for it for a try no need to go for high priced products.Quality of handle is not good. Food is not cooked equally all around. Papad of 6 small pies tried, one of the pieces burned out all the other 5 piece fried good.\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Meena Raj\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"Absolutely love this air fryer! It\'s compact yet powerful, cooks food evenly, and significantly cuts down on oil without compromising taste. Super easy to clean and the presets make it convenient for everyday use. A must-have for quick and healthy meals!\\"Even the heating quality and very easy to handle\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"JyothikaJyothika\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"Look this product is great for its price ,and works perfectly.And for the food , I tried french fries and it was pretty much great without oil + need to do much more receipe like baking , grill etc...So definitely worth buying .\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"I recently purchased the Pigeon air fryer for nearly ₹3000, expecting a quality product, but unfortunately, my experience has been quite disappointing. I’ve tried using it with different recipes and settings, but nothing seems to work as expected. Every time I attempt to use it, I receive an E1 error code, and the power shuts off every minute or so. The fryer constantly shuts down, and now, after a few uses, it has become extremely hot and refuses to turn on at all.  Given that it’s not a cheap product, I’m really frustrated with its performance and reliability. This has turned into a real hassle, and it’s concerning that a product in this price range is causing so many issues. I would appreciate any guidance on how to fix this or if anyone has experienced similar problems. I was hoping for a functional and long-lasting appliance, but right now, it’s giving me a hard time.\", \"rating\": \"1.0\", \"date\": \"17 Feb 2025\", \"text\": \"I recently purchased the Pigeon air fryer for nearly ₹3000, expecting a quality product, but unfortunately, my experience has been quite disappointing. I’ve tried using it with different recipes and settings, but nothing seems to work as expected. Every time I attempt to use it, I receive an E1 error code, and the power shuts off every minute or so. The fryer constantly shuts down, and now, after a few uses, it has become extremely hot and refuses to turn on at all.Given that it’s not a cheap product, I’m really frustrated with its performance and reliability. This has turned into a real hassle, and it’s concerning that a product in this price range is causing so many issues. I would appreciate any guidance on how to fix this or if anyone has experienced similar problems. I was hoping for a functional and long-lasting appliance, but right now, it’s giving me a hard time.\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Ch N.\", \"rating\": \"3.0\", \"date\": \"11 May 2025\", \"text\": \"After one month it\'s not working\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Ammy Saroha\", \"rating\": \"4.0\", \"date\": \"11 Mar 2025\", \"text\": \"So far okay! Quality needs to improve !\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Bhavesh Jhaveri\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This is fantastic product, value for money. Aesthetics are cool. Digital display is very easy to use. Very handy machine. Gets on the task quickly. Can be cleaned quickly. Less oil and more taste. Eat with no tension as air fryer takes care of extra oil which in fact is not required.\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"souravsourav\", \"rating\": \"1.0\", \"date\": \"29 Apr 2025\", \"text\": \"Very bad product I have ordered this Air fryer just few days back and when i am using this for the first time i tried to fry some chicken where i placed 3-4 small pieces and set the temperature to 180 and timing for 15 mins , and immediately i got a error in the display showing E1 which means “ BROKEN CIRCUIT OF THE THERMAL SENSORS “ i tried to contact customer care number shown in the manual and i am not able to connect with them ( Poor Customer care support ) , very poor and frustrating experience with this product and after that i returned this product and purchased a new one where i am getting a very bad experience where the Air fryer is emitting smoke from inside and not working at all . Such a disappointing brand and Air fryer , NEVER Buy This\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"uday bhaskaruday bhaskar\", \"rating\": \"4.0\", \"date\": \"21 Jan 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    The product is morethan expected for me. Very nice and easy to cook.Design, color weight noice leve gets good marks. If u are buying for first time go for it for a try no need to go for high priced products.Quality of handle is not good. Food is not cooked equally all around. Papad of 6 small pies tried, one of the pieces burned out all the other 5 piece fried good.\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Meena Raj\", \"rating\": \"5.0\", \"date\": \"07 May 2025\", \"text\": \"Absolutely love this air fryer! It\'s compact yet powerful, cooks food evenly, and significantly cuts down on oil without compromising taste. Super easy to clean and the presets make it convenient for everyday use. A must-have for quick and healthy meals!\\"Even the heating quality and very easy to handle\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"JyothikaJyothika\", \"rating\": \"5.0\", \"date\": \"22 May 2025\", \"text\": \"Look this product is great for its price ,and works perfectly.And for the food , I tried french fries and it was pretty much great without oil + need to do much more receipe like baking , grill etc...So definitely worth buying .\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"I recently purchased the Pigeon air fryer for nearly ₹3000, expecting a quality product, but unfortunately, my experience has been quite disappointing. I’ve tried using it with different recipes and settings, but nothing seems to work as expected. Every time I attempt to use it, I receive an E1 error code, and the power shuts off every minute or so. The fryer constantly shuts down, and now, after a few uses, it has become extremely hot and refuses to turn on at all.  Given that it’s not a cheap product, I’m really frustrated with its performance and reliability. This has turned into a real hassle, and it’s concerning that a product in this price range is causing so many issues. I would appreciate any guidance on how to fix this or if anyone has experienced similar problems. I was hoping for a functional and long-lasting appliance, but right now, it’s giving me a hard time.\", \"rating\": \"1.0\", \"date\": \"17 Feb 2025\", \"text\": \"I recently purchased the Pigeon air fryer for nearly ₹3000, expecting a quality product, but unfortunately, my experience has been quite disappointing. I’ve tried using it with different recipes and settings, but nothing seems to work as expected. Every time I attempt to use it, I receive an E1 error code, and the power shuts off every minute or so. The fryer constantly shuts down, and now, after a few uses, it has become extremely hot and refuses to turn on at all.Given that it’s not a cheap product, I’m really frustrated with its performance and reliability. This has turned into a real hassle, and it’s concerning that a product in this price range is causing so many issues. I would appreciate any guidance on how to fix this or if anyone has experienced similar problems. I was hoping for a functional and long-lasting appliance, but right now, it’s giving me a hard time.\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Ch N.\", \"rating\": \"3.0\", \"date\": \"11 May 2025\", \"text\": \"After one month it\'s not working\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Ammy Saroha\", \"rating\": \"4.0\", \"date\": \"11 Mar 2025\", \"text\": \"So far okay! Quality needs to improve !\n  \nRead more\", \"product_id\": \"B0B8XNPQPN\", \"link\": \"https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LG 1 Ton 4 Star DUAL Inverter Split AC</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>71.43%</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="n">
+        <v>14</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DQQ55C8M\", \"product_name\": \"LG 1 Ton 4 Star DUAL Inverter Split AC (Copper, AI Convertible 6-in-1 with VIRAAT Mode, Faster Cooling &amp; Energy Saving, 4 Way Swing, HD Filter with AntiVirus Protection, US-Q13JNYE, White)\", \"product_url\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"summary\": {\"total_reviews\": 14, \"average_rating\": 4.14, \"sentiment_breakdown\": {\"positive\": 10, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 71.43}, \"reviews\": [{\"author\": \"Ravi\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Amazon on time delivery and LG installation team work. Great for me. Installation team took solid 3+ hours and did very good job on installation which is the key first step.Coming LG AC, it’s very good. Cools very fast, less noisy. Outdoor unit gold coated fins looks great.Overall I would recommend LG over other brands, though it might cost 1-1.5k more, it’s worth it.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"VishnuVishnu\", \"rating\": \"4.0\", \"date\": \"18 May 2024\", \"text\": \"I have reviewed and researched many brands. Finally found LG as the best.My genuine review after purchasing 2 units and being used for more than month:I have performed real time research on various brands. Considering the ownership reviews collected from my relative and friends, concluding LG as the best.1 ton and 1.5 ton capacity ACs of all other brands available at a very low price than LG. But here comes the differentiation comparing all brands with LG:Build Quality: Excellent build quality of indoor and outdoor units.Power Savings: Electricity bill of Lg 1 ton AC after running 10 hrs a day for 30 days is just 900/- (Run on 60-80% efficiency)Cooling Performance: A room of 10x10 with medium sunlight exposure can easily be cooled within 15 minutes when run on 25°C. After 15 mins you need to wear blankets to sustain from chills 😄Airthrow: All LG ACs have 4 way swing feature, which is not available in many other brands. At fan speed F5, air throw is excellent. Covers top to bottom, left to right.***ONLY DISADVANTAGE is Swing blades does cover the area exactly under the indoor Unit. We need to sleep at least 3 ft away from indoor unit to get feel the cooling and fan air.****Last but not least- After Sales Service:LG known for the professional after sales service, when other brands doesn\'t meet LG in service. LG technicians are more professional than others.*Major cons:1. Remote doesn\'t have radium or LED buttons- during night you need switch on torch to operate the remote.2. Swing blades doesn\'t cover are under AC3. Sounds around 32 decibles - bit high.Pros:1. 4 way swing2. Extra gold fin coating protects from corrosion.3. Sleep and Timer features. You can turn on timer and sleep without any disturbance to turn off the AC during mid night.4. Auto clean feature.Conclusion: don\'t tempt to buy cheap brands which offers at a very low price. After one year you need to spend 3x more amount on repairs. Invest one time on the right brand and stay happy for ever.As per my research, ALL OTHER BRANDS fail in below aspecta:1. Provide good service2. Low cooling performance.3. Worst build quality4. Very less life of the product.Don\'t waste your hard earned money on looting brands.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ARK\", \"rating\": \"5.0\", \"date\": \"11 Nov 2024\", \"text\": \"I’ve been using the LG 1 Ton 4 Star DUAL Inverter Split AC for a couple of months, and it’s been a fantastic addition to my home. This unit is compact but powerful, providing quick and efficient cooling for my bedroom. The dual inverter technology is very effective, cooling the room in minutes while remaining quiet – ideal for nighttime use.One of my favorite features is the AI Convertible 6-in-1 Cooling. This option allows me to adjust the cooling capacity depending on the room size and the cooling needs of the moment, which has noticeably reduced my energy usage. It’s perfect for situations where I don’t need full cooling power, such as on mild days or in smaller spaces.The 4-way swing function is great for even air distribution. It reaches all corners of the room, so I don’t have to worry about uneven cooling. The HD Filter is a nice bonus too; it helps filter out dust, which is great for air quality and my allergies.The 4-star energy rating has proven effective, as my electricity bill has gone down compared to previous months. The copper condenser gives me confidence in its durability, and I expect it to last a long time without major issues.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pooja\", \"rating\": \"1.0\", \"date\": \"16 May 2025\", \"text\": \"Product is good. Missing copper pipe in box. I have purches the pipe from technician he charges 4200 and amzone reimburse me only 3200 rs. Very much disappointed from amzone. I have kindly suggest please check the itom before packing.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"LG 1 Ton 4 Star AC – Highly Recommended!I’ve been using it for a few days and I’m really happy with its performance. Power consumption is manageable, which is a big plus.However, do keep in mind that the installation cost can be quite high if you purchase all the accessories from the company. Overall, a great product!Installation Poor take all accessories from outside.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajit SAjit S\", \"rating\": \"5.0\", \"date\": \"17 Apr 2024\", \"text\": \"we have been waiting for installation to happen since 5 days. The support center does not respond. LG says we have escalated. After buying product from Amazon this is the situation. Should have gone to the shop and purchased, probably should have got the installation done quickly. Very disanointed the way LG treats its customer..AFter prolonged wait the installation was done, requested the service engineer to come with Vaccum Pump, he simply refused that he will not carry Vacuum Pump. LG clearly states on installation the Outdoor unit needs to be Vacuum Pumped. I insisted with the Service Center that I will not allow an installation. Also raised this issue with LG Support Center and finally the Service Engineer was forced to come with the vacuum pump. People who does not know how important is a vacuum pump in a split AC, please search for the same in You Tube and Internet.The AC itself is very quiet and cools OK. Cooling however is slow compared to a non-inverter AC. My non inverter AC cools very quickly and keeps the room cool for longer time.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Srinivas\", \"rating\": \"4.0\", \"date\": \"30 Mar 2025\", \"text\": \"Good product and quick cooling. Running very smooth with minimal noice.Would have been excellent if they provided smart ac option in this segment.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ravi\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Amazon on time delivery and LG installation team work. Great for me. Installation team took solid 3+ hours and did very good job on installation which is the key first step.Coming LG AC, it’s very good. Cools very fast, less noisy. Outdoor unit gold coated fins looks great.Overall I would recommend LG over other brands, though it might cost 1-1.5k more, it’s worth it.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"VishnuVishnu\", \"rating\": \"4.0\", \"date\": \"18 May 2024\", \"text\": \"I have reviewed and researched many brands. Finally found LG as the best.My genuine review after purchasing 2 units and being used for more than month:I have performed real time research on various brands. Considering the ownership reviews collected from my relative and friends, concluding LG as the best.1 ton and 1.5 ton capacity ACs of all other brands available at a very low price than LG. But here comes the differentiation comparing all brands with LG:Build Quality: Excellent build quality of indoor and outdoor units.Power Savings: Electricity bill of Lg 1 ton AC after running 10 hrs a day for 30 days is just 900/- (Run on 60-80% efficiency)Cooling Performance: A room of 10x10 with medium sunlight exposure can easily be cooled within 15 minutes when run on 25°C. After 15 mins you need to wear blankets to sustain from chills 😄Airthrow: All LG ACs have 4 way swing feature, which is not available in many other brands. At fan speed F5, air throw is excellent. Covers top to bottom, left to right.***ONLY DISADVANTAGE is Swing blades does cover the area exactly under the indoor Unit. We need to sleep at least 3 ft away from indoor unit to get feel the cooling and fan air.****Last but not least- After Sales Service:LG known for the professional after sales service, when other brands doesn\'t meet LG in service. LG technicians are more professional than others.*Major cons:1. Remote doesn\'t have radium or LED buttons- during night you need switch on torch to operate the remote.2. Swing blades doesn\'t cover are under AC3. Sounds around 32 decibles - bit high.Pros:1. 4 way swing2. Extra gold fin coating protects from corrosion.3. Sleep and Timer features. You can turn on timer and sleep without any disturbance to turn off the AC during mid night.4. Auto clean feature.Conclusion: don\'t tempt to buy cheap brands which offers at a very low price. After one year you need to spend 3x more amount on repairs. Invest one time on the right brand and stay happy for ever.As per my research, ALL OTHER BRANDS fail in below aspecta:1. Provide good service2. Low cooling performance.3. Worst build quality4. Very less life of the product.Don\'t waste your hard earned money on looting brands.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ARK\", \"rating\": \"5.0\", \"date\": \"11 Nov 2024\", \"text\": \"I’ve been using the LG 1 Ton 4 Star DUAL Inverter Split AC for a couple of months, and it’s been a fantastic addition to my home. This unit is compact but powerful, providing quick and efficient cooling for my bedroom. The dual inverter technology is very effective, cooling the room in minutes while remaining quiet – ideal for nighttime use.One of my favorite features is the AI Convertible 6-in-1 Cooling. This option allows me to adjust the cooling capacity depending on the room size and the cooling needs of the moment, which has noticeably reduced my energy usage. It’s perfect for situations where I don’t need full cooling power, such as on mild days or in smaller spaces.The 4-way swing function is great for even air distribution. It reaches all corners of the room, so I don’t have to worry about uneven cooling. The HD Filter is a nice bonus too; it helps filter out dust, which is great for air quality and my allergies.The 4-star energy rating has proven effective, as my electricity bill has gone down compared to previous months. The copper condenser gives me confidence in its durability, and I expect it to last a long time without major issues.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pooja\", \"rating\": \"1.0\", \"date\": \"16 May 2025\", \"text\": \"Product is good. Missing copper pipe in box. I have purches the pipe from technician he charges 4200 and amzone reimburse me only 3200 rs. Very much disappointed from amzone. I have kindly suggest please check the itom before packing.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"LG 1 Ton 4 Star AC – Highly Recommended!I’ve been using it for a few days and I’m really happy with its performance. Power consumption is manageable, which is a big plus.However, do keep in mind that the installation cost can be quite high if you purchase all the accessories from the company. Overall, a great product!Installation Poor take all accessories from outside.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajit SAjit S\", \"rating\": \"5.0\", \"date\": \"17 Apr 2024\", \"text\": \"we have been waiting for installation to happen since 5 days. The support center does not respond. LG says we have escalated. After buying product from Amazon this is the situation. Should have gone to the shop and purchased, probably should have got the installation done quickly. Very disanointed the way LG treats its customer..AFter prolonged wait the installation was done, requested the service engineer to come with Vaccum Pump, he simply refused that he will not carry Vacuum Pump. LG clearly states on installation the Outdoor unit needs to be Vacuum Pumped. I insisted with the Service Center that I will not allow an installation. Also raised this issue with LG Support Center and finally the Service Engineer was forced to come with the vacuum pump. People who does not know how important is a vacuum pump in a split AC, please search for the same in You Tube and Internet.The AC itself is very quiet and cools OK. Cooling however is slow compared to a non-inverter AC. My non inverter AC cools very quickly and keeps the room cool for longer time.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Srinivas\", \"rating\": \"4.0\", \"date\": \"30 Mar 2025\", \"text\": \"Good product and quick cooling. Running very smooth with minimal noice.Would have been excellent if they provided smart ac option in this segment.\n  \nRead more\", \"product_id\": \"B0DQQ55C8M\", \"link\": \"https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Winix Premium 4 Stage Air Purifier,Kills Virus&amp;Bacteria</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
         <v>4.88</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>14</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>16</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B01D8DAYBA\", \"product_name\": \"Winix Premium 4 Stage Air Purifier,Kills Virus&amp;Bacteria - Only Guaranteed Tripple Certified Uk Allergy,Ecarf (Cadr 390M3)&amp;Aham (360Sqft) Upto 1065 Sqft,2 Year Warranty,Korean Brand (5300-2),Gray\", \"product_url\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.88, \"sentiment_breakdown\": {\"positive\": 14, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"TKS\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Very nice product. They man consider one more version which shows the AQI reading on the device. This model shows red, orange &amp; blue color indications instead of showing the reading\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shamim A.\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"Very quiet, effective in controlling air quality, value for money, easy to use, can be used for just 4 hours daily in the city like Bangalore\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rohan\", \"rating\": \"5.0\", \"date\": \"29 Jan 2025\", \"text\": \"Works silently. Seems to have strong air delivery. Comes with extra filters. Auto turns off panel lights when it’s dark. Perfect for bedroom.\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"RamSainiRamSaini\", \"rating\": \"4.0\", \"date\": \"05 Jan 2025\", \"text\": \"प्रोडक्ट ठीक-ठाक है बस एक कमी है कि इसमें डिजिटल मीटर नहीं है, जिससे कि पता चल सके रूम के अंदर AQI कितना है.The product is fine, just one drawback is that it does not have a digital meter to know how much AQI is inside the room.\n  \n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"sandeep\", \"rating\": \"5.0\", \"date\": \"02 Feb 2025\", \"text\": \"Excellent, it made difference in our air purification\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"PUNJAB NATIONAL BANK, REGIONAL STAFF COLLEGE\", \"rating\": \"5.0\", \"date\": \"26 Oct 2024\", \"text\": \"The product is as claimed in the description.\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Prakhar Bhardwaj\", \"rating\": \"5.0\", \"date\": \"26 Oct 2024\", \"text\": \"Awesome 👍\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"B SHARVESHB SHARVESH\", \"rating\": \"5.0\", \"date\": \"21 Aug 2024\", \"text\": \"Good quality, easy to use and changing filters. Money worth. Useful for pet allergic in home.\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"TKS\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Very nice product. They man consider one more version which shows the AQI reading on the device. This model shows red, orange &amp; blue color indications instead of showing the reading\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shamim A.\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"Very quiet, effective in controlling air quality, value for money, easy to use, can be used for just 4 hours daily in the city like Bangalore\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rohan\", \"rating\": \"5.0\", \"date\": \"29 Jan 2025\", \"text\": \"Works silently. Seems to have strong air delivery. Comes with extra filters. Auto turns off panel lights when it’s dark. Perfect for bedroom.\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"RamSainiRamSaini\", \"rating\": \"4.0\", \"date\": \"05 Jan 2025\", \"text\": \"प्रोडक्ट ठीक-ठाक है बस एक कमी है कि इसमें डिजिटल मीटर नहीं है, जिससे कि पता चल सके रूम के अंदर AQI कितना है.The product is fine, just one drawback is that it does not have a digital meter to know how much AQI is inside the room.\n  \n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"sandeep\", \"rating\": \"5.0\", \"date\": \"02 Feb 2025\", \"text\": \"Excellent, it made difference in our air purification\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"PUNJAB NATIONAL BANK, REGIONAL STAFF COLLEGE\", \"rating\": \"5.0\", \"date\": \"26 Oct 2024\", \"text\": \"The product is as claimed in the description.\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Prakhar Bhardwaj\", \"rating\": \"5.0\", \"date\": \"26 Oct 2024\", \"text\": \"Awesome 👍\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"B SHARVESHB SHARVESH\", \"rating\": \"5.0\", \"date\": \"21 Aug 2024\", \"text\": \"Good quality, easy to use and changing filters. Money worth. Useful for pet allergic in home.\n  \nRead more\", \"product_id\": \"B01D8DAYBA\", \"link\": \"https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Carrier 1.5 Ton 5 Star Wi-Fi Smart Flexicool Inverter Split AC</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>16</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{\"product_id\": \"B0CY5QW186\", \"product_name\": \"Sony PlayStation®5 Digital Edition (slim) Console Video Game\", \"product_url\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.88, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Shivshankar\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    First time getting a PS5 as GTA VI soon, and honestly the console experience is nice. You pick up the controller and just play. Overall amazing experience, that’s coming from a long time PC gamer.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajay\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"It is perfect and got it for a great price. Playstation plus membership is highly recommended with it.PS: It may not work on inverter if there is a power outage as its wattage is over 100 watts. So don\'t worry, once the power comes back on, you are good to go 😎\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhanashree\", \"rating\": \"5.0\", \"date\": \"12 May 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"ADI\", \"rating\": \"5.0\", \"date\": \"23 Aug 2024\", \"text\": \"I finally got my hands on the Sony PlayStation®5 Digital Edition, and it has exceeded all my expectations! The only downside was the delayed delivery, which was frustrating, but once it arrived, it was absolutely worth the wait.Performance:The PS5 is a powerhouse. The speed and performance are on another level, with games loading almost instantly thanks to the SSD. The graphics are stunning, bringing an immersive experience that I’ve never felt before. Playing games in 4K with ray tracing truly makes a difference, and everything runs incredibly smoothly.Design:The design of the PS5 Digital Edition is sleek and modern. It looks great in my entertainment setup and feels like a premium piece of technology. Even though it’s a bit large, the futuristic design makes it a centerpiece rather than just a console.Digital Experience:I was initially concerned about going all-digital, but the PS5 Digital Edition has made me a believer. The PlayStation Store is easy to navigate, and downloading games is quick and hassle-free. Plus, without the need for discs, everything feels more streamlined and clutter-free.DualSense Controller:The new DualSense controller is a game-changer. The haptic feedback and adaptive triggers add a whole new dimension to gaming, making it feel more immersive and responsive. It’s comfortable to hold, and the battery life is impressive.Overall:Despite the delayed delivery, I couldn’t be happier with my PS5 Digital Edition. The performance, design, and overall gaming experience are phenomenal. If you’re considering making the leap to next-gen gaming, the PS5 Digital Edition is definitely the way to go.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Mayank Saluja\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"Really worth it at the cost I have got this gaming console . Playing it digital is also fun . Playstation Plus subscription is suggested to take to enjoy online gaming fun too . Graphics and gaming experience is really worth it . If anyone has a 4K smart tv then it will be more fun to enjoy. Wish if could have got 2 remotes instead of only 1 wid dis gaming console oderwise the its fun to enjoy .\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhrubajyoti Baishya\", \"rating\": \"4.0\", \"date\": \"19 Apr 2025\", \"text\": \"Got delivered in one day. Excellent service, excellent packaging. But the product built quality could be better. I have a feeling that the hdmi port will break if you keep putting it on and off. Plastic quality feels like something you get in a non branded console apart from the side panel and the front side. The main unit doesn\'t feel that good as compared to the controller. It feels cheap. But the performance is top notch. Power consumption is low if you compare it to a gaming pc setup with that much performance.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"30 Apr 2025\", \"text\": \"The item was delivered in appropriate packaging. Functions as expected, no issues at all.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Navdeep k.\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"A really good product for gamers.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Shivshankar\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    First time getting a PS5 as GTA VI soon, and honestly the console experience is nice. You pick up the controller and just play. Overall amazing experience, that’s coming from a long time PC gamer.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Ajay\", \"rating\": \"5.0\", \"date\": \"18 Apr 2025\", \"text\": \"It is perfect and got it for a great price. Playstation plus membership is highly recommended with it.PS: It may not work on inverter if there is a power outage as its wattage is over 100 watts. So don\'t worry, once the power comes back on, you are good to go 😎\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhanashree\", \"rating\": \"5.0\", \"date\": \"12 May 2025\", \"text\": \"Good\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"ADI\", \"rating\": \"5.0\", \"date\": \"23 Aug 2024\", \"text\": \"I finally got my hands on the Sony PlayStation®5 Digital Edition, and it has exceeded all my expectations! The only downside was the delayed delivery, which was frustrating, but once it arrived, it was absolutely worth the wait.Performance:The PS5 is a powerhouse. The speed and performance are on another level, with games loading almost instantly thanks to the SSD. The graphics are stunning, bringing an immersive experience that I’ve never felt before. Playing games in 4K with ray tracing truly makes a difference, and everything runs incredibly smoothly.Design:The design of the PS5 Digital Edition is sleek and modern. It looks great in my entertainment setup and feels like a premium piece of technology. Even though it’s a bit large, the futuristic design makes it a centerpiece rather than just a console.Digital Experience:I was initially concerned about going all-digital, but the PS5 Digital Edition has made me a believer. The PlayStation Store is easy to navigate, and downloading games is quick and hassle-free. Plus, without the need for discs, everything feels more streamlined and clutter-free.DualSense Controller:The new DualSense controller is a game-changer. The haptic feedback and adaptive triggers add a whole new dimension to gaming, making it feel more immersive and responsive. It’s comfortable to hold, and the battery life is impressive.Overall:Despite the delayed delivery, I couldn’t be happier with my PS5 Digital Edition. The performance, design, and overall gaming experience are phenomenal. If you’re considering making the leap to next-gen gaming, the PS5 Digital Edition is definitely the way to go.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Mayank Saluja\", \"rating\": \"5.0\", \"date\": \"14 May 2025\", \"text\": \"Really worth it at the cost I have got this gaming console . Playing it digital is also fun . Playstation Plus subscription is suggested to take to enjoy online gaming fun too . Graphics and gaming experience is really worth it . If anyone has a 4K smart tv then it will be more fun to enjoy. Wish if could have got 2 remotes instead of only 1 wid dis gaming console oderwise the its fun to enjoy .\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Dhrubajyoti Baishya\", \"rating\": \"4.0\", \"date\": \"19 Apr 2025\", \"text\": \"Got delivered in one day. Excellent service, excellent packaging. But the product built quality could be better. I have a feeling that the hdmi port will break if you keep putting it on and off. Plastic quality feels like something you get in a non branded console apart from the side panel and the front side. The main unit doesn\'t feel that good as compared to the controller. It feels cheap. But the performance is top notch. Power consumption is low if you compare it to a gaming pc setup with that much performance.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"30 Apr 2025\", \"text\": \"The item was delivered in appropriate packaging. Functions as expected, no issues at all.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Navdeep k.\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"A really good product for gamers.\n  \nRead more\", \"product_id\": \"B0CY5QW186\", \"link\": \"https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1\", \"sentiment\": \"positive\"}]}</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1</t>
+      <c r="E53" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>16</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DSXJFF5H\", \"product_name\": \"Carrier 1.5 Ton 5 Star Wi-Fi Smart Flexicool Inverter Split AC (Copper, Convertible 6-in-1 Cooling,Smart Energy Display,HD &amp; PM 2.5 Filter, ESTER EDGE FXi (Wi-Fi), CAI19EE5R35W0,White)\", \"product_url\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.75, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"PiyaliPiyali\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Carrier AC and installation is a good choice. I received my installation on the same day as the delivery, in the evening. The delivery time was pretty quick, and I\'m glad I went with Carrier.Two people came to do the installation, and they did a good job with no problems. However, one of the helpers seemed a little arrogant. Otherwise, the installation was done in just three hours. The AC itself is very good. My room is 120 square feet, and the AC keeps it cool enough even when set to 25 degrees.After having used it for a month, I’d say Carrier made a good air conditioner, and they do excellent installations. I definitely have no complaints.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Working fine.\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"Product is very good at this price and performance is excellent till now. Installation technician is also very good and polite.He has installed it very well.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jaydeep Basani\", \"rating\": \"4.0\", \"date\": \"15 May 2025\", \"text\": \"Excellent machine, super cooling ability, latest model.Excellent installation team.Only thing they need to upgrade WiFi compatibility with IOS . It does not work with  latest mobile OS\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"K S RayK S Ray\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Thanks to Amazon for prompt delivery and thanks to company for quick installation within 24 hours.Product is good, several features, good cooling capacity with affordable price from Carier\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abhishek Chandel\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"Good AC, works just as intended.It chilles 800 Sqrft of my house, from living room kitchen and 1 bedroom.Initially I thought the front has led light strip but only plastic trim is there.Cooling is good even when the outer unit is in small duct space.The water dripping issue is something I am facing which looks like installation issue.My request to installation is that they should reach out to me and get it corrected.I had to pay 3300₹ for installation.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tapas Kumar Pal\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Nice product also work smoothly, service also good, allover cooling, air flow, features, installation good 👍\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"priyanga\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Good product and it is value for money. Cooling is very good.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ramesh\", \"rating\": \"4.0\", \"date\": \"08 May 2025\", \"text\": \"Good Product..... delivered on time, installation ontime... AC is working Amazingly...worth for money... Thanks Amazon....\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"PiyaliPiyali\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Carrier AC and installation is a good choice. I received my installation on the same day as the delivery, in the evening. The delivery time was pretty quick, and I\'m glad I went with Carrier.Two people came to do the installation, and they did a good job with no problems. However, one of the helpers seemed a little arrogant. Otherwise, the installation was done in just three hours. The AC itself is very good. My room is 120 square feet, and the AC keeps it cool enough even when set to 25 degrees.After having used it for a month, I’d say Carrier made a good air conditioner, and they do excellent installations. I definitely have no complaints.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Working fine.\", \"rating\": \"5.0\", \"date\": \"20 May 2025\", \"text\": \"Product is very good at this price and performance is excellent till now. Installation technician is also very good and polite.He has installed it very well.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jaydeep Basani\", \"rating\": \"4.0\", \"date\": \"15 May 2025\", \"text\": \"Excellent machine, super cooling ability, latest model.Excellent installation team.Only thing they need to upgrade WiFi compatibility with IOS . It does not work with  latest mobile OS\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"K S RayK S Ray\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Thanks to Amazon for prompt delivery and thanks to company for quick installation within 24 hours.Product is good, several features, good cooling capacity with affordable price from Carier\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abhishek Chandel\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"Good AC, works just as intended.It chilles 800 Sqrft of my house, from living room kitchen and 1 bedroom.Initially I thought the front has led light strip but only plastic trim is there.Cooling is good even when the outer unit is in small duct space.The water dripping issue is something I am facing which looks like installation issue.My request to installation is that they should reach out to me and get it corrected.I had to pay 3300₹ for installation.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tapas Kumar Pal\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"Nice product also work smoothly, service also good, allover cooling, air flow, features, installation good 👍\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"priyanga\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"Good product and it is value for money. Cooling is very good.\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ramesh\", \"rating\": \"4.0\", \"date\": \"08 May 2025\", \"text\": \"Good Product..... delivered on time, installation ontime... AC is working Amazingly...worth for money... Thanks Amazon....\n  \nRead more\", \"product_id\": \"B0DSXJFF5H\", \"link\": \"https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Daikin 1.5 Ton 3 Star Inverter Split AC</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>12</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0BK1KS6ZD\", \"product_name\": \"Daikin 1.5 Ton 3 Star Inverter Split AC (Copper, PM 2.5 Filter, Triple Display, Dew Clean Technology, Coanda Airflow, 2024 Model, MTKL50U, White)\", \"product_url\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"summary\": {\"total_reviews\": 12, \"average_rating\": 4.17, \"sentiment_breakdown\": {\"positive\": 12}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Nitish SinghNitish Singh\", \"rating\": \"5.0\", \"date\": \"06 Apr 2019\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    If you are looking for a complete package, then look nowhere other than Daikin.I purchased the 1.5 Ton 4 Star AC 10-days ago, and until now I am impressed with what it has to offer. To give you guys a better idea, let me go through the whole experience.Installation: Installation went super smooth. The installation guys called me even before the AC arrived. I told them that it had not arrived yet. They insisted on letting them know once it does. So, once the AC arrived, I called them, and to my surprise, they said that they are coming right away.The installation process started, and it was done in 3 hours max.Also, for those people who are saying that they are charging money even when installation is free, you guys have no idea about how AC installation is done.According to the offer when I purchased the AC, the installation charges are free. This means that the engineers won\'t take labor charges for installing the AC. But, that doesn\'t mean that you also don\'t have to pay for the extra materials that are required to install the AC!Also, the extra charges can vary heavily depending on the amount of material needed including pipe, tape and so on. In my case, it cost me 2500 INR, and I am super happy with it.Build Quality and DesignThe build quality of the AC is excellent. The internal unit looks sleek and modern. However, I do have a complaint here.The bottom part of the internal unit slightly bugles during installation. According to engineer, it cannot be fixed (or removed) due to the backplate that is fixed on the wall. The AC resets on the backplate. Anyway, it is not a big issue, and hard to notice for visitors..so I agreed to not do anything else.Functionality and RemoteThe AC functions as advertised. It cools and cools very nicely.However, I was not expecting that the AC remote would be so awesome!It has almost every functionality that you would need.Few of my key features that can be controlled through remote include Coanda mode which works in conjunction with a fan. You just turn it on and put a fan on the slowest speed. Your room will be filled with a cold ambiance unlike direct cold air in case of swing fans.I also love the display at the remote. It shows all the possible icons and notification that makes handling AC a charm!I also loved Good Slepe mode, Econo mode, and horizontal and vertical swing!ManualThe manual is also nicely crafted. I used it to learn about the AC which the engineers fail to tell me. I told the installation guys to give me a demo, but they couldn\'t. I don\'t blame them as they just basic stuff. I would request everyone who buys the AC to read the manual at least once to understand the true functionality of the AC.Overall ValueThe overall value of the AC is just excellent. It is affordable and enables you to enjoy with minimal electricity bills(I am skeptical here as I am yet to receive the first electric bill, but I think it will be fine)!Summary1. Excellent build quality.2. Out of the world AC remote.3. Great feature-set4. No display on the AC unit(CON)5. Excellent manualOverall rating: 9.5/10About the service, I am not sure as I am yet to take advantage of it. However, from my friend circle and peers, they are well known for their service(at least in the Kolkata region.)\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yash Majithiya\", \"rating\": \"4.0\", \"date\": \"16 Apr 2025\", \"text\": \"- Noise levels are balanced. Not too high not too low- cooling capacity is good- Material quality is good- remote functions and product reliability is goodWhen to consider this AC:- your room is under 150sqft and no direct sunlight exposure- properly air sealed room- do not place outdoor unit near to your room. Or behind same wall. It makes too much noiseInstallation was avarage 4/5Features are decent 4/5Value for money 4/5Comfort 4/5\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ANJANA JYOTHY\", \"rating\": \"1.0\", \"date\": \"11 Mar 2024\", \"text\": \"Bought it for my Kerala home and thought Daikin is a know brand and I would like it. But, I was wrong. From day 1, the cooling of the AC is abominable. It starts slowly and reaches at around 90-97% compressor capacity and after a little time starts reducing its capacity and stays at 45-55% then after. Reported the issue to the company and they sent technician from some Giant Air System and they say that ambient temperature is high and that’s why it’s like that. I wonder that if 34 degrees ambient temperature is high for this AC, what would happen to people who buy it for Delhi or places like that? It’s been more than 25 days since I’ve registered the complaint and have called Giant Air Systems multiple times but till date they have not attended it.My suggestion would is people, don’t buy this brand. Their service is poor and you will regret your decision like I am right now.Update 14/03/24 - The guy (I think he is some senior tech guy from service team) visited on 13/02/24 and checked the system with gas pressure monitor and found nothing wrong with the gas pressure. It was around 140 when operating and he told me that it’s fine. Then apparently he flushed the gas a little bit and told me that sometimes it’s needed to do so to let the trapped air release from the system and it can help. He did check rest of the operations. He explained a lot of things and some key takeaways are-1. The display room temperature is always adjusted 2-3 degrees higher than the actual room temperature so that the machine could keep on working on keeping the room temperature to a comfortable levels when people open the doors or windows of that room for something.2. He taught me how without any equipment one can test and find that the AC gas pressure and other functions are ok. The method is - just go to the outdoor unit and check the pipe temperature of both in and out pipes and if they are somewhat similar in temperature, that means the rotation of the gas is perfect and there is no need to worry. On the other hand if there is a big variation in temperature of in and out pipes, one should ask the technician to come and check.3. Even if we set 18 degree as the required temperature for the room, it will never really reach that level in practical conditions. So, we must be ok with that as well and I think that’s fair enough.4. He asked me to keep the AC at 24 degrees preferably and that would give you the most comfortable room condition and I agree with him.5. These are smart ACs and they are designed to operate with minimal power consumption and hence you may find the load on compressor varying at times.He said sometimes the trapped air in the system can cause a bit issue with cooling but I am not sure how and if that air can be removed from the system when it is already mixed with the gas in compressor.First day of use after flushing it was better compared to previous days. The system didn’t drop performance and did some work to cool the room. At 24 degrees, it felt cool enough and I think it’s improved.Will share more after a few days of checking it. Increasing the rating from 1 star to 3 star for the well behaved technician from Giant air systems ( actually every technician who visited from Giant was well behaved and gentleman, it’s just my frustration with the delay in their response which got be cribbing about them ;) ha ha haa…)\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"abdulmuheet shaikh\", \"rating\": \"5.0\", \"date\": \"24 May 2025\", \"text\": \"It\'s working as expected, keeping the room chill, good quality and best brand value.\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Manikandan\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Very Fast cooling In a sheet house.  Noise is low. Good one. worth for buying👍. Installation was good but charges was little bit high. Ac features are oki.\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shambhu Chowdhary\", \"rating\": \"5.0\", \"date\": \"08 Mar 2025\", \"text\": \"I recently purchased the Daikin 1.5 Ton 3 Star Inverter Split AC, and I couldn\'t be happier with my decision. This AC is a game-changer for several reasons:Efficient Cooling: The cooling performance is outstanding. It cools my room quickly and maintains a consistent temperature, even during the hottest days.Energy Saving: The inverter technology ensures that the AC runs efficiently, saving on electricity bills without compromising on performance.Quiet Operation: The AC operates quietly, making it perfect for a peaceful night\'s sleep.Durable Build: The copper condenser coil enhances durability and ensures long-lasting performance.User-Friendly Features: The remote control is easy to use, and features like the sleep mode and timer add to the convenience.Overall, I highly recommend the Daikin 1.5 Ton 3 Star Inverter Split AC for anyone looking for a reliable and efficient cooling solution. It\'s worth every penny!\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nitish SinghNitish Singh\", \"rating\": \"5.0\", \"date\": \"06 Apr 2019\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    If you are looking for a complete package, then look nowhere other than Daikin.I purchased the 1.5 Ton 4 Star AC 10-days ago, and until now I am impressed with what it has to offer. To give you guys a better idea, let me go through the whole experience.Installation: Installation went super smooth. The installation guys called me even before the AC arrived. I told them that it had not arrived yet. They insisted on letting them know once it does. So, once the AC arrived, I called them, and to my surprise, they said that they are coming right away.The installation process started, and it was done in 3 hours max.Also, for those people who are saying that they are charging money even when installation is free, you guys have no idea about how AC installation is done.According to the offer when I purchased the AC, the installation charges are free. This means that the engineers won\'t take labor charges for installing the AC. But, that doesn\'t mean that you also don\'t have to pay for the extra materials that are required to install the AC!Also, the extra charges can vary heavily depending on the amount of material needed including pipe, tape and so on. In my case, it cost me 2500 INR, and I am super happy with it.Build Quality and DesignThe build quality of the AC is excellent. The internal unit looks sleek and modern. However, I do have a complaint here.The bottom part of the internal unit slightly bugles during installation. According to engineer, it cannot be fixed (or removed) due to the backplate that is fixed on the wall. The AC resets on the backplate. Anyway, it is not a big issue, and hard to notice for visitors..so I agreed to not do anything else.Functionality and RemoteThe AC functions as advertised. It cools and cools very nicely.However, I was not expecting that the AC remote would be so awesome!It has almost every functionality that you would need.Few of my key features that can be controlled through remote include Coanda mode which works in conjunction with a fan. You just turn it on and put a fan on the slowest speed. Your room will be filled with a cold ambiance unlike direct cold air in case of swing fans.I also love the display at the remote. It shows all the possible icons and notification that makes handling AC a charm!I also loved Good Slepe mode, Econo mode, and horizontal and vertical swing!ManualThe manual is also nicely crafted. I used it to learn about the AC which the engineers fail to tell me. I told the installation guys to give me a demo, but they couldn\'t. I don\'t blame them as they just basic stuff. I would request everyone who buys the AC to read the manual at least once to understand the true functionality of the AC.Overall ValueThe overall value of the AC is just excellent. It is affordable and enables you to enjoy with minimal electricity bills(I am skeptical here as I am yet to receive the first electric bill, but I think it will be fine)!Summary1. Excellent build quality.2. Out of the world AC remote.3. Great feature-set4. No display on the AC unit(CON)5. Excellent manualOverall rating: 9.5/10About the service, I am not sure as I am yet to take advantage of it. However, from my friend circle and peers, they are well known for their service(at least in the Kolkata region.)\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yash Majithiya\", \"rating\": \"4.0\", \"date\": \"16 Apr 2025\", \"text\": \"- Noise levels are balanced. Not too high not too low- cooling capacity is good- Material quality is good- remote functions and product reliability is goodWhen to consider this AC:- your room is under 150sqft and no direct sunlight exposure- properly air sealed room- do not place outdoor unit near to your room. Or behind same wall. It makes too much noiseInstallation was avarage 4/5Features are decent 4/5Value for money 4/5Comfort 4/5\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ANJANA JYOTHY\", \"rating\": \"1.0\", \"date\": \"11 Mar 2024\", \"text\": \"Bought it for my Kerala home and thought Daikin is a know brand and I would like it. But, I was wrong. From day 1, the cooling of the AC is abominable. It starts slowly and reaches at around 90-97% compressor capacity and after a little time starts reducing its capacity and stays at 45-55% then after. Reported the issue to the company and they sent technician from some Giant Air System and they say that ambient temperature is high and that’s why it’s like that. I wonder that if 34 degrees ambient temperature is high for this AC, what would happen to people who buy it for Delhi or places like that? It’s been more than 25 days since I’ve registered the complaint and have called Giant Air Systems multiple times but till date they have not attended it.My suggestion would is people, don’t buy this brand. Their service is poor and you will regret your decision like I am right now.Update 14/03/24 - The guy (I think he is some senior tech guy from service team) visited on 13/02/24 and checked the system with gas pressure monitor and found nothing wrong with the gas pressure. It was around 140 when operating and he told me that it’s fine. Then apparently he flushed the gas a little bit and told me that sometimes it’s needed to do so to let the trapped air release from the system and it can help. He did check rest of the operations. He explained a lot of things and some key takeaways are-1. The display room temperature is always adjusted 2-3 degrees higher than the actual room temperature so that the machine could keep on working on keeping the room temperature to a comfortable levels when people open the doors or windows of that room for something.2. He taught me how without any equipment one can test and find that the AC gas pressure and other functions are ok. The method is - just go to the outdoor unit and check the pipe temperature of both in and out pipes and if they are somewhat similar in temperature, that means the rotation of the gas is perfect and there is no need to worry. On the other hand if there is a big variation in temperature of in and out pipes, one should ask the technician to come and check.3. Even if we set 18 degree as the required temperature for the room, it will never really reach that level in practical conditions. So, we must be ok with that as well and I think that’s fair enough.4. He asked me to keep the AC at 24 degrees preferably and that would give you the most comfortable room condition and I agree with him.5. These are smart ACs and they are designed to operate with minimal power consumption and hence you may find the load on compressor varying at times.He said sometimes the trapped air in the system can cause a bit issue with cooling but I am not sure how and if that air can be removed from the system when it is already mixed with the gas in compressor.First day of use after flushing it was better compared to previous days. The system didn’t drop performance and did some work to cool the room. At 24 degrees, it felt cool enough and I think it’s improved.Will share more after a few days of checking it. Increasing the rating from 1 star to 3 star for the well behaved technician from Giant air systems ( actually every technician who visited from Giant was well behaved and gentleman, it’s just my frustration with the delay in their response which got be cribbing about them ;) ha ha haa…)\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"abdulmuheet shaikh\", \"rating\": \"5.0\", \"date\": \"24 May 2025\", \"text\": \"It\'s working as expected, keeping the room chill, good quality and best brand value.\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Manikandan\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Very Fast cooling In a sheet house.  Noise is low. Good one. worth for buying👍. Installation was good but charges was little bit high. Ac features are oki.\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shambhu Chowdhary\", \"rating\": \"5.0\", \"date\": \"08 Mar 2025\", \"text\": \"I recently purchased the Daikin 1.5 Ton 3 Star Inverter Split AC, and I couldn\'t be happier with my decision. This AC is a game-changer for several reasons:Efficient Cooling: The cooling performance is outstanding. It cools my room quickly and maintains a consistent temperature, even during the hottest days.Energy Saving: The inverter technology ensures that the AC runs efficiently, saving on electricity bills without compromising on performance.Quiet Operation: The AC operates quietly, making it perfect for a peaceful night\'s sleep.Durable Build: The copper condenser coil enhances durability and ensures long-lasting performance.User-Friendly Features: The remote control is easy to use, and features like the sleep mode and timer add to the convenience.Overall, I highly recommend the Daikin 1.5 Ton 3 Star Inverter Split AC for anyone looking for a reliable and efficient cooling solution. It\'s worth every penny!\n  \nRead more\", \"product_id\": \"B0BK1KS6ZD\", \"link\": \"https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TCL 248 cm (98 inches) 4K Ultra HD Smart QD-Mini LED Google TV 98C755 (Black)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CMDB7D11\", \"product_name\": \"TCL 248 cm (98 inches) 4K Ultra HD Smart QD-Mini LED Google TV 98C755 (Black)\", \"product_url\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"summary\": {\"total_reviews\": 8, \"average_rating\": 3.75, \"sentiment_breakdown\": {\"positive\": 8}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"SKL\", \"rating\": \"5.0\", \"date\": \"06 Jan 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Bought the 85 inch version.The TV did not come with the center stand and they said that the stand is out of stock and I\'ll have to wait for 4-5 days to get it in stock. Got it installed in 4 days since TCL did not provide the service team with a stand.From a TV perspective, it\'s a brilliant TV for it\'s price.The HDR performance is great, I have a dark theater setup and the black levels of the TV is very close to OLED levels with a bit of blooming.Not sure about the number of dimming zones, but should be around 800 for the 85 inch TV.The sound is decent and the audio performance is comparable to a mid priced soundbar.The colour accuracy is decent and the TV gets super bright in highlight areas in the HDR mode without much blooming.SDR upscaling is not great and you may not enjoy anything less than 1080p in such a large TV, but 1080p and 4k looks fantastic.This TV is worth it\'s price and will not disappoint. 5 star for the performance, given the price. I reduced 1 star for not including stand in the box, delaying the TV setupEdit : Spent a day more with the TV and it\'s actually amazing. Deep blacks, HDR+ content looks stunning and I\'m reverting to 5 starsI also see people complaining about the speed and responsiveness of the android TV interface, but it\'s pretty fluid. Very fast and never hangs.\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tropicalstorm\", \"rating\": \"1.0\", \"date\": \"05 Aug 2023\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    What impressed me most: Sound quality. Sound is crisp, clear with good bass and almost perfectly balanced mids, highs and lows. The front firing speakers have excellent channel separation and the tv renders dolby atmos and dolby digital content flawlessly.Due to the tvs high peak brightness and good mini-led calibration, objects in low light HDR don\'t look like black blobs. Shadow details, compared to most mid-range LED tvs are excellent and there is no blooming.What was not so good: Flouting Mini-Led technology as the holy grail of tv technology. This mini-led tv has a fairly good panel, however color calibration is not as accurate as expected - there is a greenish baseline hue in the picture. Generally, the picture tends to lean on the cooler side even if you have set the adjustment to warm.Picture processing : It\'s adequate but not perfect. Even though this is a 120 hz TV, I do notice motion judder every now and then. Even in slow panning shots judder is not uncommon. I think it is due to the older (Gen 2) picture processor used in this tv. In any case this is not expected of a flagship tv.Operating system /UI: unfortunately, I have to concur with many other reviewers that the UI is buggy. Occasionally, the tv hangs and while watching a series on OTT, google voice search gets activated on its own! In such cases you have to power off the TV and restart it.I have also noticed some screen fluctuation while watching 4K content. This issue has been flagged by one other reviewer here on amazon. I hope this goes away on a future software update.On opening the box I was surprised to find that my tcl tv had a lot of accumulated dust and scratches on the back. This tv was definitely not factory packed. This delivery was fulfilled by Amazon and I was least expecting this.UPDATE ONE YEAR AND SIX MONTHS LATER:Due to frequent glitchs in TV software like TV not starting for hours together, shutting off on its own and picture freezing etc I contacted TCL India via their email many times during the warranty period but I received no response. Now the situation has gotten out of hand and the TV has stopped working. I called up TCL India customer care number where a chap told me that TCL technical team would contact me within 2-4 hours. He also asked me to rate him by giving him 5 stars since \'he had solved my problem\'. Nobody called me from TCL in the specified time line. After two days I received a call from them and they (TCL) informed me that a technician will be sent to my home to look into the problem.I will update the progress regarding this so that customers at amazon are made aware about TCL service post purchase.For now, this tv is lying useless and just occupying space :(Further update 10 days after placing service request : Nobody from TCL has contacted me via email or phone. No technician has visited my home till now.I will update this review with my final experience 20 days from now ( 20 days after filling the service request).Finally update on 24/2/25: I checked my service request via case id number on TCL website and it shows that my TV has already been repaired and a part has been replaced! The service request has been closed by TCL now.I\'m sharing this bad experience regarding loss of my hard earned money so that consumers are made aware that Chinese products are as bad as they used to be when we were kids. Nothing\'s changed!\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sumit\", \"rating\": \"5.0\", \"date\": \"24 Jan 2025\", \"text\": \"I recently purchased the TCL C755 65-Inch TV, and it has exceeded all my expectations! The QD Mini LED technology truly brings 4K content to life with vibrant, accurate colors and incredible clarity. The sound quality is equally impressive, delivering punchy bass that eliminates the need for external speakers. The deep blacks enhance the overall viewing experience, making it feel more immersive and cinematic. Additionally, the Google TV operating system adds great convenience and seamless access to a wide range of apps and content. Gaming at 144Hz on this TV is an absolute game-changer, offering ultra-smooth performance that elevates the experience to a whole new level. A fantastic purchase all around!\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sheldon\", \"rating\": \"4.0\", \"date\": \"14 Jan 2024\", \"text\": \"Update: After a week of going back and forth with the customer care. Two technicians visiting my house and telling me they have no idea how to fix the tv. I have fixed the issue myself through a lot of troubleshooting,  trial and error.I am now finally happy with my purchase but really unhappy that the TCL service.The TV is great now, works well in all settings. The local dimming is amazing and hdr is vibrant. Compatibility with my gaming pc is also great.I would have rated the product 5 stars but considering the service engineers couldn’t even diagnose my issue let alone fix it. I will deduct 1 starOriginal Review: I was really looking forward to using this. Went through all the reviews I could find if it’s sister model c805 that’s sold abroad.There were no complaints according to the review. But I’m facing the issue of lag/frame stutters.I have no idea of how to fix it.\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SKL\", \"rating\": \"5.0\", \"date\": \"06 Jan 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Bought the 85 inch version.The TV did not come with the center stand and they said that the stand is out of stock and I\'ll have to wait for 4-5 days to get it in stock. Got it installed in 4 days since TCL did not provide the service team with a stand.From a TV perspective, it\'s a brilliant TV for it\'s price.The HDR performance is great, I have a dark theater setup and the black levels of the TV is very close to OLED levels with a bit of blooming.Not sure about the number of dimming zones, but should be around 800 for the 85 inch TV.The sound is decent and the audio performance is comparable to a mid priced soundbar.The colour accuracy is decent and the TV gets super bright in highlight areas in the HDR mode without much blooming.SDR upscaling is not great and you may not enjoy anything less than 1080p in such a large TV, but 1080p and 4k looks fantastic.This TV is worth it\'s price and will not disappoint. 5 star for the performance, given the price. I reduced 1 star for not including stand in the box, delaying the TV setupEdit : Spent a day more with the TV and it\'s actually amazing. Deep blacks, HDR+ content looks stunning and I\'m reverting to 5 starsI also see people complaining about the speed and responsiveness of the android TV interface, but it\'s pretty fluid. Very fast and never hangs.\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tropicalstorm\", \"rating\": \"1.0\", \"date\": \"05 Aug 2023\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    What impressed me most: Sound quality. Sound is crisp, clear with good bass and almost perfectly balanced mids, highs and lows. The front firing speakers have excellent channel separation and the tv renders dolby atmos and dolby digital content flawlessly.Due to the tvs high peak brightness and good mini-led calibration, objects in low light HDR don\'t look like black blobs. Shadow details, compared to most mid-range LED tvs are excellent and there is no blooming.What was not so good: Flouting Mini-Led technology as the holy grail of tv technology. This mini-led tv has a fairly good panel, however color calibration is not as accurate as expected - there is a greenish baseline hue in the picture. Generally, the picture tends to lean on the cooler side even if you have set the adjustment to warm.Picture processing : It\'s adequate but not perfect. Even though this is a 120 hz TV, I do notice motion judder every now and then. Even in slow panning shots judder is not uncommon. I think it is due to the older (Gen 2) picture processor used in this tv. In any case this is not expected of a flagship tv.Operating system /UI: unfortunately, I have to concur with many other reviewers that the UI is buggy. Occasionally, the tv hangs and while watching a series on OTT, google voice search gets activated on its own! In such cases you have to power off the TV and restart it.I have also noticed some screen fluctuation while watching 4K content. This issue has been flagged by one other reviewer here on amazon. I hope this goes away on a future software update.On opening the box I was surprised to find that my tcl tv had a lot of accumulated dust and scratches on the back. This tv was definitely not factory packed. This delivery was fulfilled by Amazon and I was least expecting this.UPDATE ONE YEAR AND SIX MONTHS LATER:Due to frequent glitchs in TV software like TV not starting for hours together, shutting off on its own and picture freezing etc I contacted TCL India via their email many times during the warranty period but I received no response. Now the situation has gotten out of hand and the TV has stopped working. I called up TCL India customer care number where a chap told me that TCL technical team would contact me within 2-4 hours. He also asked me to rate him by giving him 5 stars since \'he had solved my problem\'. Nobody called me from TCL in the specified time line. After two days I received a call from them and they (TCL) informed me that a technician will be sent to my home to look into the problem.I will update the progress regarding this so that customers at amazon are made aware about TCL service post purchase.For now, this tv is lying useless and just occupying space :(Further update 10 days after placing service request : Nobody from TCL has contacted me via email or phone. No technician has visited my home till now.I will update this review with my final experience 20 days from now ( 20 days after filling the service request).Finally update on 24/2/25: I checked my service request via case id number on TCL website and it shows that my TV has already been repaired and a part has been replaced! The service request has been closed by TCL now.I\'m sharing this bad experience regarding loss of my hard earned money so that consumers are made aware that Chinese products are as bad as they used to be when we were kids. Nothing\'s changed!\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sumit\", \"rating\": \"5.0\", \"date\": \"24 Jan 2025\", \"text\": \"I recently purchased the TCL C755 65-Inch TV, and it has exceeded all my expectations! The QD Mini LED technology truly brings 4K content to life with vibrant, accurate colors and incredible clarity. The sound quality is equally impressive, delivering punchy bass that eliminates the need for external speakers. The deep blacks enhance the overall viewing experience, making it feel more immersive and cinematic. Additionally, the Google TV operating system adds great convenience and seamless access to a wide range of apps and content. Gaming at 144Hz on this TV is an absolute game-changer, offering ultra-smooth performance that elevates the experience to a whole new level. A fantastic purchase all around!\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sheldon\", \"rating\": \"4.0\", \"date\": \"14 Jan 2024\", \"text\": \"Update: After a week of going back and forth with the customer care. Two technicians visiting my house and telling me they have no idea how to fix the tv. I have fixed the issue myself through a lot of troubleshooting,  trial and error.I am now finally happy with my purchase but really unhappy that the TCL service.The TV is great now, works well in all settings. The local dimming is amazing and hdr is vibrant. Compatibility with my gaming pc is also great.I would have rated the product 5 stars but considering the service engineers couldn’t even diagnose my issue let alone fix it. I will deduct 1 starOriginal Review: I was really looking forward to using this. Went through all the reviews I could find if it’s sister model c805 that’s sold abroad.There were no complaints according to the review. But I’m facing the issue of lag/frame stutters.I have no idea of how to fix it.\n  \nRead more\", \"product_id\": \"B0CMDB7D11\", \"link\": \"https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sony BRAVIA 3 Series 215 cm (85 inches</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>16</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D3DVZ9YD\", \"product_name\": \"Sony BRAVIA 3 Series 215 cm (85 inches) 4K Utra HD AI Smart LED Google TV K-85S30 (Black)\", \"product_url\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.88, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"08 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Installation on time.. productvis excellent condition.. picture quantity is great..technician is of good knowledge Abt the product..\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tejal Musale\", \"rating\": \"5.0\", \"date\": \"19 Apr 2025\", \"text\": \"Excellent TV. Good installation support.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KJE\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Product is excellent, the installation was also done by professionals who took care of everything. I would recommend this your home.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"hemalatha\", \"rating\": \"5.0\", \"date\": \"25 Mar 2025\", \"text\": \"Sound quality , picture quality very good, excellent service and installation.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ROCHE J.\", \"rating\": \"4.0\", \"date\": \"14 Mar 2025\", \"text\": \"The product was good and installation was done with proper explanation.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Puspham\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"Product is great. Good clarity and great features. Installation was done professionally.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AryamanAryaman\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"Best product you can find under this range  value for money.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nandagopal Nandagopal\", \"rating\": \"5.0\", \"date\": \"19 Jan 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I ordered this tv on 13 th january.Eventhough I am a prime user they provided a shedule delivery at 18th january(i.e product was dispatched 4days after the order placed).But The installation was really impressive they made it on the very next day of delivery(On Sunday also they work🥳)Picture quality is impressive,sound is awesome,color quality natural as much as possibleIn the entire journey my favorite was installation part🤩🤩\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"08 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Installation on time.. productvis excellent condition.. picture quantity is great..technician is of good knowledge Abt the product..\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tejal Musale\", \"rating\": \"5.0\", \"date\": \"19 Apr 2025\", \"text\": \"Excellent TV. Good installation support.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KJE\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"Product is excellent, the installation was also done by professionals who took care of everything. I would recommend this your home.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"hemalatha\", \"rating\": \"5.0\", \"date\": \"25 Mar 2025\", \"text\": \"Sound quality , picture quality very good, excellent service and installation.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ROCHE J.\", \"rating\": \"4.0\", \"date\": \"14 Mar 2025\", \"text\": \"The product was good and installation was done with proper explanation.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Puspham\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"Product is great. Good clarity and great features. Installation was done professionally.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"AryamanAryaman\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"Best product you can find under this range  value for money.\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nandagopal Nandagopal\", \"rating\": \"5.0\", \"date\": \"19 Jan 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I ordered this tv on 13 th january.Eventhough I am a prime user they provided a shedule delivery at 18th january(i.e product was dispatched 4days after the order placed).But The installation was really impressive they made it on the very next day of delivery(On Sunday also they work🥳)Picture quality is impressive,sound is awesome,color quality natural as much as possibleIn the entire journey my favorite was installation part🤩🤩\n  \nRead more\", \"product_id\": \"B0D3DVZ9YD\", \"link\": \"https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Hisense 215 cm (85 inches) Q7N Series 4K Ultra HD Smart QLED TV 85Q7N</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>14</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>16</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D3X8H9PD\", \"product_name\": \"Hisense 215 cm (85 inches) Q7N Series 4K Ultra HD Smart QLED TV 85Q7N (Dark Grey)\", \"product_url\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.25, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"SrinidhiSrinidhi\", \"rating\": \"5.0\", \"date\": \"26 Dec 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Q7N sound Clarity is top notch and the Display is Very good for the Asking Price. Color Accuracy is on point, There are options to even choose the different color management profiles from Adobe RGB to DCI-P3 and more.Not upto OLED leves but an exceptional quality for a QLED. The UI is very smooth compared to the other TV brands, The TV comes pre installed with apps like Jio Cinema, Sony Liv, Sun Nxt, Amazon Prime, Disney Hotstar, Youtube. The app store is just basic and connot be compared to Google TV.Display 7.8/10Sound 8/10Build Quality 7/10Color Accuracy 7.8/10UI Smoothness 9/10App Store/Apps 5/10Overall 7.8/10\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yuvrajsinh Chauhan\", \"rating\": \"4.0\", \"date\": \"13 Jan 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I have been using this tv since last 3 months and its the best tv anyone can consider at this price range with best 4k gaming features and quality output. It provides great colour and audio quality is also perfect over all sound effects- consist with good function and all expected and used ports- vidaa os is very smooth and with updates i think will provide better options- brightness over 70% feels very adequate and perfectoverall can be considered as the best 4k gaming tv with good refresh rate in budget range of 50-60k\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vipul H.\", \"rating\": \"5.0\", \"date\": \"03 Jan 2025\", \"text\": \"This TV offers excellent picture quality with vibrant colors and sharp 4K resolution. Sound is also clear .The smart features are intuitive, with a responsive interface but a limited app store due to the OS. Its sleek design and ample connectivity options are also strong points. it\'s a solid choice for those seeking a high-quality TV at a reasonable price. Would recommend, especially for casual viewers.\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amit kothiyal\", \"rating\": \"5.0\", \"date\": \"21 Feb 2025\", \"text\": \"Excellent sound quality, design and picture quality is good. Service was pathetic from dealer but product is good. Kindly note there is no wall mount which comes with package. Also, I use this TV for console gaming (PS5), it gives excellent gaming experience with sound and 4K 120 FPS (depends on games).\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"1.0\", \"date\": \"12 Nov 2024\", \"text\": \"Edit: 02-05-2025I am experiencing a nightmare day after day. I complained on 21-04-2025 that all HDMI ports stopped working. To date, not only has it not been fixed, there has not even been an attempt to fix it.  I keep calling customer care and the local service center (Reliance Resq) every day, receiving only false assurances that technicians will be sent.  A good product with zero customer support is pathetic. I am downgrading the five-star rating to one star, though it deserves less than one star. ....My initial review: The seller and Amazon have been reported for misleading customers by advertising that a wall mount is included with the purchase of a television, when in fact it is not. Both the seller\'s and Amazon\'s customer service teams have been contacted, yet their responses have left customers feeling dismissed and trivialized. Additionally, the delivery of the product took an excessive amount of time, approximately 18 days. (Edit: Just a couple of days ago, Company (not the seller) sent the wallmount after more than two month of delivery, strange!)The process of installing a large 85-inch TV through Amazon demonstrates a lack of control over the installation services, which compromises the customer experience. The scheduling of installation appointments is inefficient, often requiring customers to persistently contact customer care to arrange a suitable time, which can extend to a week or more. This lack of efficiency can significantly inconvenience the customer.Despite these issues, the television itself performs exceptionally well. Initial skepticism regarding the brand\'s quality was unfounded as the TV delivers outstanding visual performance. The 4K resolution, HDR, and Dolby Vision content provide an enjoyable viewing experience. Concerns about potential blooming effects were alleviated upon use, as the TV displayed precise black levels and vibrant, natural colors. The audio quality is robust, with a moderate woofer included, though an external sound bar with a subwoofer is recommended for an enhanced audio experience.The operating system of the TV, VIDAA, offers a satisfactory number of streaming applications. However, to maximize entertainment options, the addition of an Android box or Fire TV is advised.In summary, despite the initial obstacles with misleading advertisement, delivery delays, and installation challenges, the quality and performance of the television itself are commendable, making it a worthy choice for consumers.\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"PlaceholderPlaceholder\", \"rating\": \"5.0\", \"date\": \"04 Jan 2025\", \"text\": \"I owned a Hisense Television which I was really happy with, and that encouraged me to choose Hisense while I was looking for a bigger size. And with all honesty, I can say that this one\'s even better. Picture, Sound, Built, even the viewing angles are excellent. Perfect TV at justifyable price\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anumeha\", \"rating\": \"4.0\", \"date\": \"07 Feb 2025\", \"text\": \"Review: Excellent Quality at a Budget-Friendly Price!I recently purchased this TV, and I must say, it exceeded my expectations! The picture quality is crisp and vibrant, making every viewing experience enjoyable. The sound quality is also impressive, delivering clear and immersive audio without the need for external speakers.One of the best things about this TV is its affordability. It offers premium features at a budget-friendly price, making it a great value for money. Whether for movies, gaming, or casual watching, this TV delivers a fantastic experience without breaking the bank.Highly recommended for anyone looking for a quality TV at an affordable price!\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Parijat Das\", \"rating\": \"5.0\", \"date\": \"10 Feb 2025\", \"text\": \"Excellent picture and sound quality..Good interface…Great for gamers as the refresh rate is good…The affordability is the greatest aspect…Highly Recommend!\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SrinidhiSrinidhi\", \"rating\": \"5.0\", \"date\": \"26 Dec 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Q7N sound Clarity is top notch and the Display is Very good for the Asking Price. Color Accuracy is on point, There are options to even choose the different color management profiles from Adobe RGB to DCI-P3 and more.Not upto OLED leves but an exceptional quality for a QLED. The UI is very smooth compared to the other TV brands, The TV comes pre installed with apps like Jio Cinema, Sony Liv, Sun Nxt, Amazon Prime, Disney Hotstar, Youtube. The app store is just basic and connot be compared to Google TV.Display 7.8/10Sound 8/10Build Quality 7/10Color Accuracy 7.8/10UI Smoothness 9/10App Store/Apps 5/10Overall 7.8/10\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Yuvrajsinh Chauhan\", \"rating\": \"4.0\", \"date\": \"13 Jan 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I have been using this tv since last 3 months and its the best tv anyone can consider at this price range with best 4k gaming features and quality output. It provides great colour and audio quality is also perfect over all sound effects- consist with good function and all expected and used ports- vidaa os is very smooth and with updates i think will provide better options- brightness over 70% feels very adequate and perfectoverall can be considered as the best 4k gaming tv with good refresh rate in budget range of 50-60k\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vipul H.\", \"rating\": \"5.0\", \"date\": \"03 Jan 2025\", \"text\": \"This TV offers excellent picture quality with vibrant colors and sharp 4K resolution. Sound is also clear .The smart features are intuitive, with a responsive interface but a limited app store due to the OS. Its sleek design and ample connectivity options are also strong points. it\'s a solid choice for those seeking a high-quality TV at a reasonable price. Would recommend, especially for casual viewers.\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amit kothiyal\", \"rating\": \"5.0\", \"date\": \"21 Feb 2025\", \"text\": \"Excellent sound quality, design and picture quality is good. Service was pathetic from dealer but product is good. Kindly note there is no wall mount which comes with package. Also, I use this TV for console gaming (PS5), it gives excellent gaming experience with sound and 4K 120 FPS (depends on games).\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"1.0\", \"date\": \"12 Nov 2024\", \"text\": \"Edit: 02-05-2025I am experiencing a nightmare day after day. I complained on 21-04-2025 that all HDMI ports stopped working. To date, not only has it not been fixed, there has not even been an attempt to fix it.  I keep calling customer care and the local service center (Reliance Resq) every day, receiving only false assurances that technicians will be sent.  A good product with zero customer support is pathetic. I am downgrading the five-star rating to one star, though it deserves less than one star. ....My initial review: The seller and Amazon have been reported for misleading customers by advertising that a wall mount is included with the purchase of a television, when in fact it is not. Both the seller\'s and Amazon\'s customer service teams have been contacted, yet their responses have left customers feeling dismissed and trivialized. Additionally, the delivery of the product took an excessive amount of time, approximately 18 days. (Edit: Just a couple of days ago, Company (not the seller) sent the wallmount after more than two month of delivery, strange!)The process of installing a large 85-inch TV through Amazon demonstrates a lack of control over the installation services, which compromises the customer experience. The scheduling of installation appointments is inefficient, often requiring customers to persistently contact customer care to arrange a suitable time, which can extend to a week or more. This lack of efficiency can significantly inconvenience the customer.Despite these issues, the television itself performs exceptionally well. Initial skepticism regarding the brand\'s quality was unfounded as the TV delivers outstanding visual performance. The 4K resolution, HDR, and Dolby Vision content provide an enjoyable viewing experience. Concerns about potential blooming effects were alleviated upon use, as the TV displayed precise black levels and vibrant, natural colors. The audio quality is robust, with a moderate woofer included, though an external sound bar with a subwoofer is recommended for an enhanced audio experience.The operating system of the TV, VIDAA, offers a satisfactory number of streaming applications. However, to maximize entertainment options, the addition of an Android box or Fire TV is advised.In summary, despite the initial obstacles with misleading advertisement, delivery delays, and installation challenges, the quality and performance of the television itself are commendable, making it a worthy choice for consumers.\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"PlaceholderPlaceholder\", \"rating\": \"5.0\", \"date\": \"04 Jan 2025\", \"text\": \"I owned a Hisense Television which I was really happy with, and that encouraged me to choose Hisense while I was looking for a bigger size. And with all honesty, I can say that this one\'s even better. Picture, Sound, Built, even the viewing angles are excellent. Perfect TV at justifyable price\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anumeha\", \"rating\": \"4.0\", \"date\": \"07 Feb 2025\", \"text\": \"Review: Excellent Quality at a Budget-Friendly Price!I recently purchased this TV, and I must say, it exceeded my expectations! The picture quality is crisp and vibrant, making every viewing experience enjoyable. The sound quality is also impressive, delivering clear and immersive audio without the need for external speakers.One of the best things about this TV is its affordability. It offers premium features at a budget-friendly price, making it a great value for money. Whether for movies, gaming, or casual watching, this TV delivers a fantastic experience without breaking the bank.Highly recommended for anyone looking for a quality TV at an affordable price!\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Parijat Das\", \"rating\": \"5.0\", \"date\": \"10 Feb 2025\", \"text\": \"Excellent picture and sound quality..Good interface…Great for gamers as the refresh rate is good…The affordability is the greatest aspect…Highly Recommend!\n  \nRead more\", \"product_id\": \"B0D3X8H9PD\", \"link\": \"https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>E GATE Duster 7X 100% Dust Proof Automatic Android Projector</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>10</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"product_name\": \"E GATE Duster 7X 100% Dust Proof Automatic Android Projector, 700 ISO Lumens, FHD 1080p Native &amp; 4K HDR, AI Auto (Keystone+Focus+Obstacle+Tilt), 2GB-32GB, 2XHDMI-ARC, WiFi 6, Bluetooth, EGate\", \"product_url\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"summary\": {\"total_reviews\": 10, \"average_rating\": 3.6, \"sentiment_breakdown\": {\"positive\": 10}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"jimmy kotwal\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Its been 1.5 year\'s , this product is awesome,1080p clarity, bluetooth,n many features, its worth every penny, this company is also good when i had dust problem in projector they picked up from my home and they gave it back in 1 week time and its all free....Generally all projector have dust issue u can\'t do anything about it...\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"4.0\", \"date\": \"27 Oct 2022\", \"text\": \"This review is for the native FHD projector.Yes, it is a native 1080p led projector. connected this to my desktop computer and tested also.Dont bother trying to play videos from USB. Quality is bad.But when connected to right streaming or display source thru hdmi, it is actually quite good. I mean picture quality, colours, brightness etc for a sub 10k projector. In this department this projector can easily compete with many projectors in sub 15k ranges.Sound is also pretty much okay, loud enough more like boat 5w speakers, may be a bit more louder not good quality wise. Quitr workable as portable solution, but not for a permanent setup.Audio output to my studio headphones are pretty decent quality wise and loud also. Meaning 2.1 speakers can be connected to it, for a higher setup, person has to figure out to seperate the audio at the source itself.From 9ft and 3-4 inches distance of lens to wall, we can get exactly 100 inch(87 inch x 49 inch) projection. So, it can be called as short throw projector, albiet may be border level. There is an option to reduce the screen size upto 75% of original size electronically once connected to HDMI.Keystone correction is not usuable at all. That wheel has to be exatly in middle position to get a good focus on whole screen.That means one has to setup the projector or screen at a fixed location. Can not lilt the projector to move screen up or down and then adjust with keystone correction. I. e if you want to keep the projector screen at lower levels, projector also has to fixed at lower levels only. Best focus can be get, when projecting exactly oppsite to the projector probably 5 to 6 inch above, so if we flip the projector upside down, we get best focus opposite to center a few inches down.For mysetup, where projecting only 1.5 feet above from the floor, going to use a wall mount to setup the projector upside down, this way i can fix the projector a bit more above/behind the sofa. I will post the pics later, once it is setup properly.Now the verdict - this projector with a combination of reflective projector screen( look it up on amazon xelectron or minago brand) is one of most vfm combo for approx 11k for experiencing a very bright 100 inch screen experience of good quality for 1 or 2 person.  But now that im considering buying one of those expensive fixed frame alr projector screens costing upward of 15k to 30k, im thinikg it would have been better if i could have invested a bit more on a brighter projector(look only ANSI value). This buy was more of an impulse purchase, but it is more then good enough for me now to make me consider much costlier projector screens and then later upgrade to a high end projector.Edit: the biggest drawback of this projector is that dust gets inside on lcd panel, which impacts the clarity also after a few days. I had to clean the panel myselg just after 1.5 month.  New lesson learnt, apart from high ansi lumen projector, this is also an important factor for future purchase. Planning to get a custom cloth cover made, so that i dont have to clean it often. Though, Lcd cleaning can be done pretty easily without much opening and its easier compared to youtube videos i have seen for previous model. Somehow lens did not get any dust inside yet. Only the lcd has very very fine dust particles inside.\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KHURSHEED KHAN\", \"rating\": \"1.0\", \"date\": \"23 Aug 2023\", \"text\": \"This is my second Egate Projector (I had Egate I9 Pro before this). I bought it at INR 22k after doing a lot of research and comparing many brands. My requirements are a projector that we can watch even during the day because we do not own a TV.Pros:1. Easy Setup - There is nothing to setup to be honest as this is not an Android projector. The only thing to be setup was the Keystone correction, which is pretty easy with the remote2. Excellent brightness - It has the best brightness of any projector I have used so far. So much so that we could watch it during daytime with curtains drawn, with as much light in the room that you could eat or the kids can play3. Picture Quality - It could have been better but it is OK, quite comparable to the cheaper models like i9 pro4. Digital Keystone correction - It works well, something it\'s predecessors missedCons:1. Bulky - It is big in size, i.e. not quite portable as it will not fit in your usual laptop bag2. Interface - It\'s boring, they haven\'t upgraded much since I bought the i9 pro in 2017. Other brand projectors such as Wanbo have a better interface which looks more professional3. Keystone Correction - The physical keystone correction has the same problems that its predecessors like i9 had, the corners get blurred if you use physical correction4. Sound - Could have been better. It\'s better than the cheaper eGate projectors but not enough to watch a movie in hall, it\'s only sufficient for a small room5. USB Play - It did not play a lot of formats, even most 1080 MP4s and gave unsupported format error, which reminded me of the irritating same problem with the i9. I expected better from L9To be honest, I expected more from a projector costing 22k. The only marginal advantage I got was the brightness so that I can watch it during daytime. The worse part is it will always need a physical input because it is not Android and doesn\'t support Miracast/screen-share, not even a damn bluetooth so you need another output for sound; so hanging this from the ceiling is another pain. I bought i9 for INR5500 and it gave me 1080 picture, with the drawback that it needed complete darkness for good experience, however as a projector it did what it should for that amount; though it had a shoddy build quality and its polarization filter got burnt in an area within an year, and Egate customer care did not respond in time, by then my warranty had run out. I ordered a Wanbo X1 pro (INR12k) before this and it had better interface, with Miracast and Bluetooth so using it was a charm compared to this.So, buy this only if you have a requirement of using it in daytime, if you plan on watching few movies etc in a dark room, buy a cheaper one because that will do the job.Update after 11 months of Use: It has started showing a dark spot on screen, which is visible in low light scenes. The same problem happened with their earlier projector Egate i9, but it was a much cheaper item and it happened after 2-3 years of use, and Egate was relatively a small company then, so it was somewhat acceptable. But given the giant it has become in the field of projectors, such performance is not acceptable at all.Update on Customer Support: They have a PATHETIC AFTER SALES SUPPORT, with no one even responding to complaints, even though I was coaxed into getting a Useless Extended 2 Year Warranty!!!! It\'s been more than a year and they have not responded to my query or suggested any resolution. Trust me you cannot do without tech support in case of a projector because you cannot get it repaired at a normal electronic repair shop, at least not an Indian projector whose parts are not easily available.Update after 15 months of Use: Because of the poor casing, as is the case with all Egate projectors, a lot of dust has accumulate on the side of the screen which is visible during light scenes, it looks really bad and there is no way to fix it as I don\'t have the knowhow to open and clean it, and the Useless Customer Support Of Egate doesn\'t respond.Please avoid this and buy a Chinese made projector in same price range, they offer much better quality for this price. Or you can try WANBO Projectors, they offer much better build and component quality, a better Android interface and Responsive Customer Support.\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Samanvya D. Dwivedi\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Writing after using for more than 2 months\'. The projector is actually good and among those few that actually work in dim light conditions as well. This is an indoor projector, doesn\'t emit heat and has decent sound. It\'s better to connect it to external speakers for quality sound however the inbuilt speakers are decent enough to watch movies on low sound. Don\'t expect home theatre sound.Coming to video, if the room is dark, the video quality and brightness is exceptionally good. However if there is a tubelight (switched on) then it becomes a problem and the visuals get too dim. That being said it is good enough to watch with open windows and doors and some ambient light.\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Prime Madan\", \"rating\": \"3.0\", \"date\": \"08 May 2025\", \"text\": \"I am writing this review after 6 months of usage, we have purchased 4 egate projectors due to their brand and trust, this projector is good in performance but got focus problem after 5 months of usage. we have to send the projector to their service center in Noida only, they don\'t have any service center in India other than that place. But their service center staff is very prompt and helpful to understand and coordinate. They have fixed the issue and sent back through courier service,now the projector is back and working fine. I found slightly fitting issues I.e the board inside the projector is loose fit and the output connection jacks are slightly displaced .\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"jimmy kotwal\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Its been 1.5 year\'s , this product is awesome,1080p clarity, bluetooth,n many features, its worth every penny, this company is also good when i had dust problem in projector they picked up from my home and they gave it back in 1 week time and its all free....Generally all projector have dust issue u can\'t do anything about it...\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"4.0\", \"date\": \"27 Oct 2022\", \"text\": \"This review is for the native FHD projector.Yes, it is a native 1080p led projector. connected this to my desktop computer and tested also.Dont bother trying to play videos from USB. Quality is bad.But when connected to right streaming or display source thru hdmi, it is actually quite good. I mean picture quality, colours, brightness etc for a sub 10k projector. In this department this projector can easily compete with many projectors in sub 15k ranges.Sound is also pretty much okay, loud enough more like boat 5w speakers, may be a bit more louder not good quality wise. Quitr workable as portable solution, but not for a permanent setup.Audio output to my studio headphones are pretty decent quality wise and loud also. Meaning 2.1 speakers can be connected to it, for a higher setup, person has to figure out to seperate the audio at the source itself.From 9ft and 3-4 inches distance of lens to wall, we can get exactly 100 inch(87 inch x 49 inch) projection. So, it can be called as short throw projector, albiet may be border level. There is an option to reduce the screen size upto 75% of original size electronically once connected to HDMI.Keystone correction is not usuable at all. That wheel has to be exatly in middle position to get a good focus on whole screen.That means one has to setup the projector or screen at a fixed location. Can not lilt the projector to move screen up or down and then adjust with keystone correction. I. e if you want to keep the projector screen at lower levels, projector also has to fixed at lower levels only. Best focus can be get, when projecting exactly oppsite to the projector probably 5 to 6 inch above, so if we flip the projector upside down, we get best focus opposite to center a few inches down.For mysetup, where projecting only 1.5 feet above from the floor, going to use a wall mount to setup the projector upside down, this way i can fix the projector a bit more above/behind the sofa. I will post the pics later, once it is setup properly.Now the verdict - this projector with a combination of reflective projector screen( look it up on amazon xelectron or minago brand) is one of most vfm combo for approx 11k for experiencing a very bright 100 inch screen experience of good quality for 1 or 2 person.  But now that im considering buying one of those expensive fixed frame alr projector screens costing upward of 15k to 30k, im thinikg it would have been better if i could have invested a bit more on a brighter projector(look only ANSI value). This buy was more of an impulse purchase, but it is more then good enough for me now to make me consider much costlier projector screens and then later upgrade to a high end projector.Edit: the biggest drawback of this projector is that dust gets inside on lcd panel, which impacts the clarity also after a few days. I had to clean the panel myselg just after 1.5 month.  New lesson learnt, apart from high ansi lumen projector, this is also an important factor for future purchase. Planning to get a custom cloth cover made, so that i dont have to clean it often. Though, Lcd cleaning can be done pretty easily without much opening and its easier compared to youtube videos i have seen for previous model. Somehow lens did not get any dust inside yet. Only the lcd has very very fine dust particles inside.\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"KHURSHEED KHAN\", \"rating\": \"1.0\", \"date\": \"23 Aug 2023\", \"text\": \"This is my second Egate Projector (I had Egate I9 Pro before this). I bought it at INR 22k after doing a lot of research and comparing many brands. My requirements are a projector that we can watch even during the day because we do not own a TV.Pros:1. Easy Setup - There is nothing to setup to be honest as this is not an Android projector. The only thing to be setup was the Keystone correction, which is pretty easy with the remote2. Excellent brightness - It has the best brightness of any projector I have used so far. So much so that we could watch it during daytime with curtains drawn, with as much light in the room that you could eat or the kids can play3. Picture Quality - It could have been better but it is OK, quite comparable to the cheaper models like i9 pro4. Digital Keystone correction - It works well, something it\'s predecessors missedCons:1. Bulky - It is big in size, i.e. not quite portable as it will not fit in your usual laptop bag2. Interface - It\'s boring, they haven\'t upgraded much since I bought the i9 pro in 2017. Other brand projectors such as Wanbo have a better interface which looks more professional3. Keystone Correction - The physical keystone correction has the same problems that its predecessors like i9 had, the corners get blurred if you use physical correction4. Sound - Could have been better. It\'s better than the cheaper eGate projectors but not enough to watch a movie in hall, it\'s only sufficient for a small room5. USB Play - It did not play a lot of formats, even most 1080 MP4s and gave unsupported format error, which reminded me of the irritating same problem with the i9. I expected better from L9To be honest, I expected more from a projector costing 22k. The only marginal advantage I got was the brightness so that I can watch it during daytime. The worse part is it will always need a physical input because it is not Android and doesn\'t support Miracast/screen-share, not even a damn bluetooth so you need another output for sound; so hanging this from the ceiling is another pain. I bought i9 for INR5500 and it gave me 1080 picture, with the drawback that it needed complete darkness for good experience, however as a projector it did what it should for that amount; though it had a shoddy build quality and its polarization filter got burnt in an area within an year, and Egate customer care did not respond in time, by then my warranty had run out. I ordered a Wanbo X1 pro (INR12k) before this and it had better interface, with Miracast and Bluetooth so using it was a charm compared to this.So, buy this only if you have a requirement of using it in daytime, if you plan on watching few movies etc in a dark room, buy a cheaper one because that will do the job.Update after 11 months of Use: It has started showing a dark spot on screen, which is visible in low light scenes. The same problem happened with their earlier projector Egate i9, but it was a much cheaper item and it happened after 2-3 years of use, and Egate was relatively a small company then, so it was somewhat acceptable. But given the giant it has become in the field of projectors, such performance is not acceptable at all.Update on Customer Support: They have a PATHETIC AFTER SALES SUPPORT, with no one even responding to complaints, even though I was coaxed into getting a Useless Extended 2 Year Warranty!!!! It\'s been more than a year and they have not responded to my query or suggested any resolution. Trust me you cannot do without tech support in case of a projector because you cannot get it repaired at a normal electronic repair shop, at least not an Indian projector whose parts are not easily available.Update after 15 months of Use: Because of the poor casing, as is the case with all Egate projectors, a lot of dust has accumulate on the side of the screen which is visible during light scenes, it looks really bad and there is no way to fix it as I don\'t have the knowhow to open and clean it, and the Useless Customer Support Of Egate doesn\'t respond.Please avoid this and buy a Chinese made projector in same price range, they offer much better quality for this price. Or you can try WANBO Projectors, they offer much better build and component quality, a better Android interface and Responsive Customer Support.\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Samanvya D. Dwivedi\", \"rating\": \"5.0\", \"date\": \"11 May 2025\", \"text\": \"Writing after using for more than 2 months\'. The projector is actually good and among those few that actually work in dim light conditions as well. This is an indoor projector, doesn\'t emit heat and has decent sound. It\'s better to connect it to external speakers for quality sound however the inbuilt speakers are decent enough to watch movies on low sound. Don\'t expect home theatre sound.Coming to video, if the room is dark, the video quality and brightness is exceptionally good. However if there is a tubelight (switched on) then it becomes a problem and the visuals get too dim. That being said it is good enough to watch with open windows and doors and some ambient light.\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Prime Madan\", \"rating\": \"3.0\", \"date\": \"08 May 2025\", \"text\": \"I am writing this review after 6 months of usage, we have purchased 4 egate projectors due to their brand and trust, this projector is good in performance but got focus problem after 5 months of usage. we have to send the projector to their service center in Noida only, they don\'t have any service center in India other than that place. But their service center staff is very prompt and helpful to understand and coordinate. They have fixed the issue and sent back through courier service,now the projector is back and working fine. I found slightly fitting issues I.e the board inside the projector is loose fit and the output connection jacks are slightly displaced .\n  \nRead more\", \"product_id\": \"B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"link\": \"https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025 BORSSO Pixel Power | Certified Android 13 Projector</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>8</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B07XH4X69F\", \"product_name\": \"2025 BORSSO Pixel Power | Certified Android 13 Projector 1080p Native 550 ANSI, Fully Automatic, Dolby,4k HDR, HDMI ARC &amp; CEC, 2.4G &amp; 5G WiFi &amp; 5.2 BT, 3D Support | Upgraded\", \"product_url\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 8, \"average_rating\": 3.75, \"sentiment_breakdown\": {\"positive\": 8}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Afroz shaikh\", \"rating\": \"5.0\", \"date\": \"29 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I was little nervous about the outcome of product. Because, the TV and Projectors work differently. If the projector is not that brighter in ambient light / bright room it will be not worth. But, when I tested the projector I was completely amazed by the quality of the image it is producing and how much bright it is. I was completely pleased and satisfied with product after I connected internet and played few videos . And people who are thinking will it be able to show clear videos in fully light 💡 room. 100% visibility is there. The inbuilt speaker is also awesome the video I uploaded here is only on 30-40 % volume. Still its loud and clear. On 100% it\'s just awesome.I was not able to upload that video cause, in review we can upload only one video. So I chose the best one with best out put. And post purchase the seller was very nice and response and helped in clearing many doubts I asked and is responding patiently and calmy. I suggest who are looking for bright projector. Can definitely go for it. It\'s a very good deal.\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ANUP SRIVASTAVAANUP SRIVASTAVA\", \"rating\": \"4.0\", \"date\": \"04 Nov 2023\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    After comparing it with different brands, for a budget Android projector, I recently purchased the Borsso Ultima, and I have been using it for the last week.Overall, my experience with the Borsso Ultima Android projector has been positive. Given that it is a budget projector, I wasn\'t expecting top-notch performance, but it has exceeded my expectations.I will try to give a fair review, which can help other buyers. Mind it, though it\'s marketed as an Indian brand, almost every brand gets it manufactured and imported from China, just like mobile phones, whose same manufacturer gives projectors to different importers, branding them in their names.Points to Notice.1. Firstly, the projector\'s high resolution and brightness provide an immersive viewing experience. Whether I\'m watching movies, sports, or playing video games, the image clarity is exceptional. The vibrant colors and sharp details truly enhance the visual enjoyment. Even in a well-lit room, the projector manages to deliver crisp and clear images without compromising on contrast. Realise 1080 Native Resolution\'s potential. Uncertain about its 1150 lumens—the majority of projectors make higher brightness claims, but there\'s no scientific method to verify these.2. It allows me to stream content directly from applications such as Netflix,YouTube, and Amazon Prime but At 1080p it looks good but not great.I  recommend to buy Mi TV stick to get better colours and depth, enhance experience with all OTT platform, youcan watch 4k you tube.3. No heating issues - Lastly, the projector\'s durability is worth mentioning. It has a sturdy build and has shown no signs of overheating or malfunctioning, even after prolonged use. Tested watching match for 8 hrs.4. The built-in speakers are decent, but I would recommend using external speakers for a better audio experience. The projector has various connectivity options, including HDMI, USB, and AV, ARC, which allows me to connect it to my Home Theater.Sound in Video is from Atmos Home Theater.5. Speakers are stereo not Dolby.6. No dust observerd till date.7. Support HDD - connected my 4Tb external drive.8. Plays 4k content smoothly.9. The seller is approachable and kind; they assisted me by showing me how to utilise the ARC feature.In conclusion - Considering its mid segment and price range, the Borsso Ultima Android projector offers good value for money. While it may not have all the bells and whistles of high-end projectors, it does a decent job for casual home entertainment or small office presentations.\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"saini\", \"rating\": \"5.0\", \"date\": \"24 Feb 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    After digging through a lot of reviews, i finally arrived at this product and to my surprise, this product is absolutely amazing. The picture quality is truly good loving upto its claims. The inbuilt speakers are of high quality stereo audio and delivers great sound compared to the other budget projectors out there. I think they stand no where near this.The best part:It supports dolby audio (check the video attached) via HDMI arc (HDMI port 1 of the projector) connected to the soundbar. This is truly amazing as no other projector (to the best i know) does this. This adds to the immersive movie experience.Support:Mr Parul, great at his side in clearing all of my doubts and being technically soooo sound one can expect a solution at finger tips. Never experienced such great support especially in the projectors category. Great work Mr Parul.\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SridharSridhar\", \"rating\": \"1.0\", \"date\": \"15 Mar 2025\", \"text\": \"Projector is good but problem is in hdmi it doesn’t support 4 video and usb also it doesn’t support … so better buy AUn projector it support\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Afroz shaikh\", \"rating\": \"5.0\", \"date\": \"29 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I was little nervous about the outcome of product. Because, the TV and Projectors work differently. If the projector is not that brighter in ambient light / bright room it will be not worth. But, when I tested the projector I was completely amazed by the quality of the image it is producing and how much bright it is. I was completely pleased and satisfied with product after I connected internet and played few videos . And people who are thinking will it be able to show clear videos in fully light 💡 room. 100% visibility is there. The inbuilt speaker is also awesome the video I uploaded here is only on 30-40 % volume. Still its loud and clear. On 100% it\'s just awesome.I was not able to upload that video cause, in review we can upload only one video. So I chose the best one with best out put. And post purchase the seller was very nice and response and helped in clearing many doubts I asked and is responding patiently and calmy. I suggest who are looking for bright projector. Can definitely go for it. It\'s a very good deal.\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"ANUP SRIVASTAVAANUP SRIVASTAVA\", \"rating\": \"4.0\", \"date\": \"04 Nov 2023\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    After comparing it with different brands, for a budget Android projector, I recently purchased the Borsso Ultima, and I have been using it for the last week.Overall, my experience with the Borsso Ultima Android projector has been positive. Given that it is a budget projector, I wasn\'t expecting top-notch performance, but it has exceeded my expectations.I will try to give a fair review, which can help other buyers. Mind it, though it\'s marketed as an Indian brand, almost every brand gets it manufactured and imported from China, just like mobile phones, whose same manufacturer gives projectors to different importers, branding them in their names.Points to Notice.1. Firstly, the projector\'s high resolution and brightness provide an immersive viewing experience. Whether I\'m watching movies, sports, or playing video games, the image clarity is exceptional. The vibrant colors and sharp details truly enhance the visual enjoyment. Even in a well-lit room, the projector manages to deliver crisp and clear images without compromising on contrast. Realise 1080 Native Resolution\'s potential. Uncertain about its 1150 lumens—the majority of projectors make higher brightness claims, but there\'s no scientific method to verify these.2. It allows me to stream content directly from applications such as Netflix,YouTube, and Amazon Prime but At 1080p it looks good but not great.I  recommend to buy Mi TV stick to get better colours and depth, enhance experience with all OTT platform, youcan watch 4k you tube.3. No heating issues - Lastly, the projector\'s durability is worth mentioning. It has a sturdy build and has shown no signs of overheating or malfunctioning, even after prolonged use. Tested watching match for 8 hrs.4. The built-in speakers are decent, but I would recommend using external speakers for a better audio experience. The projector has various connectivity options, including HDMI, USB, and AV, ARC, which allows me to connect it to my Home Theater.Sound in Video is from Atmos Home Theater.5. Speakers are stereo not Dolby.6. No dust observerd till date.7. Support HDD - connected my 4Tb external drive.8. Plays 4k content smoothly.9. The seller is approachable and kind; they assisted me by showing me how to utilise the ARC feature.In conclusion - Considering its mid segment and price range, the Borsso Ultima Android projector offers good value for money. While it may not have all the bells and whistles of high-end projectors, it does a decent job for casual home entertainment or small office presentations.\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"saini\", \"rating\": \"5.0\", \"date\": \"24 Feb 2025\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    After digging through a lot of reviews, i finally arrived at this product and to my surprise, this product is absolutely amazing. The picture quality is truly good loving upto its claims. The inbuilt speakers are of high quality stereo audio and delivers great sound compared to the other budget projectors out there. I think they stand no where near this.The best part:It supports dolby audio (check the video attached) via HDMI arc (HDMI port 1 of the projector) connected to the soundbar. This is truly amazing as no other projector (to the best i know) does this. This adds to the immersive movie experience.Support:Mr Parul, great at his side in clearing all of my doubts and being technically soooo sound one can expect a solution at finger tips. Never experienced such great support especially in the projectors category. Great work Mr Parul.\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"SridharSridhar\", \"rating\": \"1.0\", \"date\": \"15 Mar 2025\", \"text\": \"Projector is good but problem is in hdmi it doesn’t support 4 video and usb also it doesn’t support … so better buy AUn projector it support\n  \nRead more\", \"product_id\": \"B07XH4X69F\", \"link\": \"https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon Fire TV Stick 4K </t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>14</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>16</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CJLMSPXH\", \"product_name\": \"Amazon Fire TV Stick 4K streaming device (newest model), ultra-cinematic 4K streaming, supports Wi-Fi 6, Dolby Vision/Atmos, HDR10+\", \"product_url\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.12, \"sentiment_breakdown\": {\"positive\": 14, \"neutral\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Ishita\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Likes:1. Supports Dolby Atmos decoding on Netflix, JioHotstar, Apple TV and Zee5 in pass through mode(connected to my LG Soundbar).2. UI is very snappy and RAM management is great. Apps remain in memory.3. Picture quality and contrast ratio is much better than LG WebOS4. Navigation is decent, nothing to complain about.5. Runs on the latest FireTV OS v8.6. Alexa works very well and is able to process everything quickly.7. Wifi 6 performance is pretty great with a Wifi 6 compatible router.Dislikes:1. Setup is complicated and time consuming2. Remote’s build quality could have been better.3. Should come with a USB C port instead of micro USB.4. A lot of Ads on the home screen which feels a little cluttered.Overall a VFM product. Does the job and is a huge upgrade from LG WebOS. Both Picture and Sound Quality improved after I switched to Firestick.Please note that this is not a 2025 model, it’s manufactured in 2024 and is a Firestick 4K 2nd Gen model.It has got 2GB of ram and 8GB of storage which is sufficient.Make sure to play around with the picture and audio settings to get a fine tuned output.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"ASHISH BAHUKHANDIASHISH BAHUKHANDI\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"https://youtu.be/Hd34KHrkgXIFantastic streaming experience! The new Fire TV Stick 4K delivers ultra-clear 4K quality with Dolby Vision and Atmos — the picture and sound are truly cinematic. Fast connectivity with Wi-Fi 6 ensures smooth performance. Easy setup, great interface, and HDR10+ support make it a top-notch device. Totally worth it!\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"EShopper\", \"rating\": \"4.0\", \"date\": \"18 Aug 2024\", \"text\": \"Recently bought during the sale period and got it for 4499. So far performing well without any glitches and setup was easy with existing Amazon account. I am using a Samsung crystal 4k tv and LG sound bar, both can be controlled by firetv stick remote. Tv power on and soundbar volume adjustment can be controlled by single remote itself which is really convenient. Booting also quick, not taking much time around whence tv powered on firetv opens.Pros- Quick bootup and performance- Single remote to control tv power on off and soundbar volume- Remote with dedicated forward and rewind buttons.Cons- Battery was not working which came with the package, replaced with new one and started working.- Remote button click is bit hard, comparing to my Samsung tv remote which is smooth.- Operating system UI is bit outdated when comparing with new google tv os.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"TM\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Very strangely, while other apps work, it doesn\'t allow me to see movies on Amazon Prime Video. It says number of devices exceeded when I all I am doing is replacing my existing smart TV\'s inbuilt functions (where I was using prime video earlier) with this Firestick as I thought it would be faster. But sadly, instead of performing faster Prime Video is not working at all!Apart from that, the device itself with its remaining functions is superb.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"I loved it... Super fast performance no doubt.. just go and purchase.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"jitendra singh\", \"rating\": \"5.0\", \"date\": \"13 Apr 2025\", \"text\": \"Close your eyes and purchase,  worth expenditure and excellent experience\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rudra NarayanRudra Narayan\", \"rating\": \"5.0\", \"date\": \"12 Feb 2025\", \"text\": \"Best in the Segment!!!So I have been using the Amazon Fire tv stick 4k for more than 15 days now and here is my experience of itI bought this for ₹4500. There are many streaming devices that are available in the market but not many offer 4k functionality. I use this fire tv on my LG 4K 55’ television all because the User interface of LG (web os) was flimsy and not easy to use and really complicated for children and elders of the family to operate so I decided to buy a streaming stick this is majorly a jio and airtel dominated market as they offer smart boxes with their subscription model but trust me this fire tv actually lives up to it’s name of “Fire” because it’s not just easy to use but very user friendly and simple to operate by anyone it also comes with Dolby vision and Dolby audio which enhances the audio and video quality of your existing tv this also comes with 16gb storage so no worries about installing streaming services and news apps. Lastly alexa is a joy to use because of the integration into the UI.Summary of review - this is the best 4k tv stick you can buy. It is truly value for money and and comes with great functionality and easy to useRecommended buy.Regards\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amol Chikurdekar\", \"rating\": \"3.0\", \"date\": \"15 Mar 2025\", \"text\": \"Volume Up and down, Power On Off Not Working with haier tv\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Ishita\", \"rating\": \"5.0\", \"date\": \"19 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Likes:1. Supports Dolby Atmos decoding on Netflix, JioHotstar, Apple TV and Zee5 in pass through mode(connected to my LG Soundbar).2. UI is very snappy and RAM management is great. Apps remain in memory.3. Picture quality and contrast ratio is much better than LG WebOS4. Navigation is decent, nothing to complain about.5. Runs on the latest FireTV OS v8.6. Alexa works very well and is able to process everything quickly.7. Wifi 6 performance is pretty great with a Wifi 6 compatible router.Dislikes:1. Setup is complicated and time consuming2. Remote’s build quality could have been better.3. Should come with a USB C port instead of micro USB.4. A lot of Ads on the home screen which feels a little cluttered.Overall a VFM product. Does the job and is a huge upgrade from LG WebOS. Both Picture and Sound Quality improved after I switched to Firestick.Please note that this is not a 2025 model, it’s manufactured in 2024 and is a Firestick 4K 2nd Gen model.It has got 2GB of ram and 8GB of storage which is sufficient.Make sure to play around with the picture and audio settings to get a fine tuned output.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"ASHISH BAHUKHANDIASHISH BAHUKHANDI\", \"rating\": \"5.0\", \"date\": \"17 May 2025\", \"text\": \"https://youtu.be/Hd34KHrkgXIFantastic streaming experience! The new Fire TV Stick 4K delivers ultra-clear 4K quality with Dolby Vision and Atmos — the picture and sound are truly cinematic. Fast connectivity with Wi-Fi 6 ensures smooth performance. Easy setup, great interface, and HDR10+ support make it a top-notch device. Totally worth it!\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"EShopper\", \"rating\": \"4.0\", \"date\": \"18 Aug 2024\", \"text\": \"Recently bought during the sale period and got it for 4499. So far performing well without any glitches and setup was easy with existing Amazon account. I am using a Samsung crystal 4k tv and LG sound bar, both can be controlled by firetv stick remote. Tv power on and soundbar volume adjustment can be controlled by single remote itself which is really convenient. Booting also quick, not taking much time around whence tv powered on firetv opens.Pros- Quick bootup and performance- Single remote to control tv power on off and soundbar volume- Remote with dedicated forward and rewind buttons.Cons- Battery was not working which came with the package, replaced with new one and started working.- Remote button click is bit hard, comparing to my Samsung tv remote which is smooth.- Operating system UI is bit outdated when comparing with new google tv os.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"TM\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Very strangely, while other apps work, it doesn\'t allow me to see movies on Amazon Prime Video. It says number of devices exceeded when I all I am doing is replacing my existing smart TV\'s inbuilt functions (where I was using prime video earlier) with this Firestick as I thought it would be faster. But sadly, instead of performing faster Prime Video is not working at all!Apart from that, the device itself with its remaining functions is superb.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amazon Customer\", \"rating\": \"5.0\", \"date\": \"05 May 2025\", \"text\": \"I loved it... Super fast performance no doubt.. just go and purchase.\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"jitendra singh\", \"rating\": \"5.0\", \"date\": \"13 Apr 2025\", \"text\": \"Close your eyes and purchase,  worth expenditure and excellent experience\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rudra NarayanRudra Narayan\", \"rating\": \"5.0\", \"date\": \"12 Feb 2025\", \"text\": \"Best in the Segment!!!So I have been using the Amazon Fire tv stick 4k for more than 15 days now and here is my experience of itI bought this for ₹4500. There are many streaming devices that are available in the market but not many offer 4k functionality. I use this fire tv on my LG 4K 55’ television all because the User interface of LG (web os) was flimsy and not easy to use and really complicated for children and elders of the family to operate so I decided to buy a streaming stick this is majorly a jio and airtel dominated market as they offer smart boxes with their subscription model but trust me this fire tv actually lives up to it’s name of “Fire” because it’s not just easy to use but very user friendly and simple to operate by anyone it also comes with Dolby vision and Dolby audio which enhances the audio and video quality of your existing tv this also comes with 16gb storage so no worries about installing streaming services and news apps. Lastly alexa is a joy to use because of the integration into the UI.Summary of review - this is the best 4k tv stick you can buy. It is truly value for money and and comes with great functionality and easy to useRecommended buy.Regards\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amol Chikurdekar\", \"rating\": \"3.0\", \"date\": \"15 Mar 2025\", \"text\": \"Volume Up and down, Power On Off Not Working with haier tv\n  \nRead more\", \"product_id\": \"B0CJLMSPXH\", \"link\": \"https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1\", \"sentiment\": \"neutral\"}]}</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Amazon Echo (4th Gen) | Premium sound powered by Dolby and Alexa (Black)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>16</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>16</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B085FY9NK8\", \"product_name\": \"Amazon Echo (4th Gen) | Premium sound powered by Dolby and Alexa (Black)\", \"product_url\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.75, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Santhosh kumar\", \"rating\": \"5.0\", \"date\": \"17 Jul 2023\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Review:The Amazon Echo 4th Gen has truly revolutionized my smart home experience. This sleek and stylish device offers an impressive range of features that make it an absolute must-have for any tech-savvy individual.First and foremost, the sound quality is outstanding. The 4th Gen Echo delivers crisp, clear, and immersive audio that fills the room effortlessly. Whether I\'m enjoying my favorite playlist or listening to a podcast, the sound is rich and vibrant, adding an extra layer of enjoyment to my daily routine.The voice assistant capabilities of this device are unparalleled. Alexa\'s intelligence and responsiveness are truly remarkable. From setting reminders and timers to controlling my smart home devices, Alexa flawlessly executes my commands, making my life easier and more convenient.The design of the Amazon Echo 4th Gen is another standout feature. Its modern, fabric-covered look seamlessly blends with any home decor. The compact size ensures that it doesn\'t take up much space, while the LED light ring adds a touch of elegance. It\'s a true aesthetic addition to my living room.What impresses me the most is the comprehensive ecosystem Amazon has built around the Echo. With a wide range of compatible smart devices, I can control my lights, thermostat, security cameras, and more, all with a simple voice command. It truly feels like living in the future!Setting up the Echo 4th Gen was a breeze. The intuitive installation process guided me through every step, and I was up and running within minutes. The device seamlessly connects to my Wi-Fi network, ensuring a stable and reliable connection.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Manjeet Singh\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"I have used all Echo since Gen 1, 2 and recently I purchased this one. It is really awesome and value for money, Setup is also fine if you follow the given instructions. Operating it really easy, this one understand your commands at very easy. A must buy.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pulkit MehtaPulkit Mehta\", \"rating\": \"4.0\", \"date\": \"11 May 2022\", \"text\": \"About Stereo Pair:I got 2 of them to try stereo pair. Unfortunately stereo pair only works with Amazon music or linked music application with Alexa app. Which means you cannot use stereo pair for watching content (unless you do it through firestick). Also I could sense uneven audio balance with L and R channel and no option to correct that.Sound quality:Me being an audio nerd, I would say not best but great according to the form factor and Dolby Atmos refined. Comparing 1 echo device with another speaker I use JBL charge 4. Charge 4 can go much loud without any bass distortion and sound quality compromise but echo cannot which is understandable as it is half the price. But both sound signatures are really different and sound is very subjective and preference widely varies from person to person. I am not comparing this with my Home theatre from Obage which i use as well as home theaters cannot be matched obviously.Voice Recognition and automation:I saw there has been speculation regarding that. To be honest I did not face any issue with that rather it is able to detect feeble trigger phrases in noisy environment as well. Works well with all my smart lights and connected tech. And not to forget tons of routines,  skills and games you can make you device learn. Consider buying Smart lights , sockets (I recommend from wipro) and Smart Blinds for windows.Design and built:Amazing built quality, fabric looks very elegant and sphere shape gives it a futuristic look.Conclusion:I will divide this into parts- This might not be for you ifYou are looking for excellent sound quality with Alexa AI. Consider buying a good sound system and Echo Flex device (or an old smartphone with Alexa app also does decent job).- This is for you ifYou want a small and elegant package bundled with Alexa AI and reasonably good Dolby sound.Thanks.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nagin Patel\", \"rating\": \"5.0\", \"date\": \"24 Sep 2024\", \"text\": \"The Echo 4th Gen is an excellent smart speaker, offering solid audio quality with enhanced bass and clear vocals, thanks to its 3-inch woofer and dual tweeters. It comes with Alexa, Amazon\'s voice assistant, which can control smart home devices, play music, set reminders, answer questions, and more. It also features Zigbee and Bluetooth Low Energy for easier smart home integration, making it a hub for compatible devices. With its spherical design, it\'s compact and stylish. Overall, it provides great value for those looking for a smart speaker with robust sound and smart home capabilities.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Spersh\", \"rating\": \"5.0\", \"date\": \"21 Apr 2025\", \"text\": \"Works so well, sounds superb. Integrates well with everything and commands are very customizable.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vinayak\", \"rating\": \"5.0\", \"date\": \"24 Mar 2025\", \"text\": \"Excellent Quality Sound\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pooja\", \"rating\": \"4.0\", \"date\": \"22 Jul 2023\", \"text\": \"Wanted to purchase this for a long time, but the reviews regarding Alexa’s voice recognition held me back. Not going to lie, I am facing just what I was scared of. Alexa refuses to listen and carry out tasks at times. But since it happens on rare occasions, I am not bothered as much. I think Alexa’s pretty decent, so if you want an affordable smart speaker, Echo is the one to go for. Sound quality and body design satisfies my expectations. I use it for music and controlling smart bulbs and tube lights . :)\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"arvind k.\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"Me perfect music companion for office. Exvellent sound quality and plays almost every song i ask for. Highly recommended.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Santhosh kumar\", \"rating\": \"5.0\", \"date\": \"17 Jul 2023\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Review:The Amazon Echo 4th Gen has truly revolutionized my smart home experience. This sleek and stylish device offers an impressive range of features that make it an absolute must-have for any tech-savvy individual.First and foremost, the sound quality is outstanding. The 4th Gen Echo delivers crisp, clear, and immersive audio that fills the room effortlessly. Whether I\'m enjoying my favorite playlist or listening to a podcast, the sound is rich and vibrant, adding an extra layer of enjoyment to my daily routine.The voice assistant capabilities of this device are unparalleled. Alexa\'s intelligence and responsiveness are truly remarkable. From setting reminders and timers to controlling my smart home devices, Alexa flawlessly executes my commands, making my life easier and more convenient.The design of the Amazon Echo 4th Gen is another standout feature. Its modern, fabric-covered look seamlessly blends with any home decor. The compact size ensures that it doesn\'t take up much space, while the LED light ring adds a touch of elegance. It\'s a true aesthetic addition to my living room.What impresses me the most is the comprehensive ecosystem Amazon has built around the Echo. With a wide range of compatible smart devices, I can control my lights, thermostat, security cameras, and more, all with a simple voice command. It truly feels like living in the future!Setting up the Echo 4th Gen was a breeze. The intuitive installation process guided me through every step, and I was up and running within minutes. The device seamlessly connects to my Wi-Fi network, ensuring a stable and reliable connection.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Manjeet Singh\", \"rating\": \"5.0\", \"date\": \"01 May 2025\", \"text\": \"I have used all Echo since Gen 1, 2 and recently I purchased this one. It is really awesome and value for money, Setup is also fine if you follow the given instructions. Operating it really easy, this one understand your commands at very easy. A must buy.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pulkit MehtaPulkit Mehta\", \"rating\": \"4.0\", \"date\": \"11 May 2022\", \"text\": \"About Stereo Pair:I got 2 of them to try stereo pair. Unfortunately stereo pair only works with Amazon music or linked music application with Alexa app. Which means you cannot use stereo pair for watching content (unless you do it through firestick). Also I could sense uneven audio balance with L and R channel and no option to correct that.Sound quality:Me being an audio nerd, I would say not best but great according to the form factor and Dolby Atmos refined. Comparing 1 echo device with another speaker I use JBL charge 4. Charge 4 can go much loud without any bass distortion and sound quality compromise but echo cannot which is understandable as it is half the price. But both sound signatures are really different and sound is very subjective and preference widely varies from person to person. I am not comparing this with my Home theatre from Obage which i use as well as home theaters cannot be matched obviously.Voice Recognition and automation:I saw there has been speculation regarding that. To be honest I did not face any issue with that rather it is able to detect feeble trigger phrases in noisy environment as well. Works well with all my smart lights and connected tech. And not to forget tons of routines,  skills and games you can make you device learn. Consider buying Smart lights , sockets (I recommend from wipro) and Smart Blinds for windows.Design and built:Amazing built quality, fabric looks very elegant and sphere shape gives it a futuristic look.Conclusion:I will divide this into parts- This might not be for you ifYou are looking for excellent sound quality with Alexa AI. Consider buying a good sound system and Echo Flex device (or an old smartphone with Alexa app also does decent job).- This is for you ifYou want a small and elegant package bundled with Alexa AI and reasonably good Dolby sound.Thanks.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nagin Patel\", \"rating\": \"5.0\", \"date\": \"24 Sep 2024\", \"text\": \"The Echo 4th Gen is an excellent smart speaker, offering solid audio quality with enhanced bass and clear vocals, thanks to its 3-inch woofer and dual tweeters. It comes with Alexa, Amazon\'s voice assistant, which can control smart home devices, play music, set reminders, answer questions, and more. It also features Zigbee and Bluetooth Low Energy for easier smart home integration, making it a hub for compatible devices. With its spherical design, it\'s compact and stylish. Overall, it provides great value for those looking for a smart speaker with robust sound and smart home capabilities.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Spersh\", \"rating\": \"5.0\", \"date\": \"21 Apr 2025\", \"text\": \"Works so well, sounds superb. Integrates well with everything and commands are very customizable.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vinayak\", \"rating\": \"5.0\", \"date\": \"24 Mar 2025\", \"text\": \"Excellent Quality Sound\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Pooja\", \"rating\": \"4.0\", \"date\": \"22 Jul 2023\", \"text\": \"Wanted to purchase this for a long time, but the reviews regarding Alexa’s voice recognition held me back. Not going to lie, I am facing just what I was scared of. Alexa refuses to listen and carry out tasks at times. But since it happens on rare occasions, I am not bothered as much. I think Alexa’s pretty decent, so if you want an affordable smart speaker, Echo is the one to go for. Sound quality and body design satisfies my expectations. I use it for music and controlling smart bulbs and tube lights . :)\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"arvind k.\", \"rating\": \"5.0\", \"date\": \"25 Apr 2025\", \"text\": \"Me perfect music companion for office. Exvellent sound quality and plays almost every song i ask for. Highly recommended.\n  \nRead more\", \"product_id\": \"B085FY9NK8\", \"link\": \"https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Luminous Inverlast ILTT28060 Battery for Home</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>12</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>16</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B09KV8JYXH\", \"product_name\": \"Luminous Inverlast ILTT28060 Battery for Home, Office &amp; Shops | 250 Ah Tall Tubular | Easy Installation | Durable and Reliable Inverter Battery | Minimum Maintenance | with 60 Months Warranty\", \"product_url\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.12, \"sentiment_breakdown\": {\"neutral\": 2, \"positive\": 12, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"RITESH KUMAR VERMA\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Yes definitely\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Sukhendra Singh S/O Sheshmani SinghSukhendra Singh S/O Sheshmani Singh\", \"rating\": \"5.0\", \"date\": \"11 Mar 2025\", \"text\": \"Very good product. But water leakage on battrey head\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shivam Sheth\", \"rating\": \"1.0\", \"date\": \"10 Apr 2025\", \"text\": \"Buy on 22 Separate 2024Now Battery charging issue started, Before 10 days full day battery charging happened, but now Battery Low indication.Having Luminous Rappid Charge 1650 Inverter available, but Battery is not responding.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Placeholder\", \"rating\": \"4.0\", \"date\": \"19 Nov 2024\", \"text\": \"Everything is fine and have been year now working with good backup life and was value for money. Just when it was in transit water come out so it was wet little bit.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Injamul Haque Sardar\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"Amazing backup and fast charging. Very low maintenance\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Deepak Kumar\", \"rating\": \"3.0\", \"date\": \"30 Jul 2024\", \"text\": \"Product value for money\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jes L Pulamte\", \"rating\": \"5.0\", \"date\": \"07 Nov 2024\", \"text\": \"It take a bit of time to get delivered but its worth the price and wait for does the job well and it last for a good enough time, one of the best inverter battery.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Prophet\", \"rating\": \"5.0\", \"date\": \"16 Jun 2023\", \"text\": \"I bought this battery 2 months ago and paired it with a 1000VA inverter, I run my gaming PC(650 Watts), 2 fans, 3 tubelights on it and so far no issues. I can\'t notice when the power goes out or returns.It lasts for about 10 hours with all devices on and normal usage on PC and about 5 hours with heavy loads/gaming. Initally the battery came with 50% charged and took about 5 1/2 hours to be fully charged(Charging current of 25A).If it fits your budget go for it.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"RITESH KUMAR VERMA\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Yes definitely\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Sukhendra Singh S/O Sheshmani SinghSukhendra Singh S/O Sheshmani Singh\", \"rating\": \"5.0\", \"date\": \"11 Mar 2025\", \"text\": \"Very good product. But water leakage on battrey head\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shivam Sheth\", \"rating\": \"1.0\", \"date\": \"10 Apr 2025\", \"text\": \"Buy on 22 Separate 2024Now Battery charging issue started, Before 10 days full day battery charging happened, but now Battery Low indication.Having Luminous Rappid Charge 1650 Inverter available, but Battery is not responding.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Placeholder\", \"rating\": \"4.0\", \"date\": \"19 Nov 2024\", \"text\": \"Everything is fine and have been year now working with good backup life and was value for money. Just when it was in transit water come out so it was wet little bit.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Injamul Haque Sardar\", \"rating\": \"5.0\", \"date\": \"22 Feb 2025\", \"text\": \"Amazing backup and fast charging. Very low maintenance\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Deepak Kumar\", \"rating\": \"3.0\", \"date\": \"30 Jul 2024\", \"text\": \"Product value for money\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jes L Pulamte\", \"rating\": \"5.0\", \"date\": \"07 Nov 2024\", \"text\": \"It take a bit of time to get delivered but its worth the price and wait for does the job well and it last for a good enough time, one of the best inverter battery.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Prophet\", \"rating\": \"5.0\", \"date\": \"16 Jun 2023\", \"text\": \"I bought this battery 2 months ago and paired it with a 1000VA inverter, I run my gaming PC(650 Watts), 2 fans, 3 tubelights on it and so far no issues. I can\'t notice when the power goes out or returns.It lasts for about 10 hours with all devices on and normal usage on PC and about 5 hours with heavy loads/gaming. Initally the battery came with 50% charged and took about 5 1/2 hours to be fully charged(Charging current of 25A).If it fits your budget go for it.\n  \nRead more\", \"product_id\": \"B09KV8JYXH\", \"link\": \"https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EZVIZ by Hikvision|3k H9C Dual-Lens (5MP+5MP) Pan &amp; Tilt Wi-Fi Camera</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>14</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>16</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D7MM2CF4\", \"product_name\": \"EZVIZ by Hikvision|3k H9C Dual-Lens (5MP+5MP) Pan &amp; Tilt Wi-Fi Camera|Two-Way Talk|AI-Powered Human/Vehicle Detection|Active Defense with Siren and Strobe Light|Weatherproof Design|Upto 512GB Support\", \"product_url\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Ankit Singh\", \"rating\": \"5.0\", \"date\": \"07 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This device is awesome, both the cameras are working fine has clear picture quality, zoom is fine ..better than 3 mp cameras...light and siren are perfect..self auto patrolling mode is awesome..Also, I hope this devices survives and last long as I using this brand for first time..\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jar Jar\", \"rating\": \"4.0\", \"date\": \"21 May 2025\", \"text\": \"Easy to install, easily paired to my wifi connection and easy to use... The software specially for the Computer leaves more to be desired, especially things like zooming in on a particular area but the app for your phone works well... Auto detection works very well, but I wish there was auto detection for Animals because cats and dogs keep coming and pooping on my lawn... I also wish the camera pixels were a little higher because picture becomes hazy when you zoom in specially at night. Sound is loud and clear... I have been using this camera for a year now and have had no issues till now...\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Y P Y P\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Good Camer Good picture Quality And Good camera Mic or Speaker very Clear And loud Over All Good Quality Product but Buy Only WiFi Camera H8c 4mp Support WiFi And Lan Also Don\'t buy 4g sim Camera\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"RAJ KUMAR BOLLAM\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Over all camera good but sometimes problem.. 15 days work after problem start.. network issues 15 days good work.. every time restart\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Bhagath Kumar Vittal\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"Quality of recording is very good and human sensors activeness and alerts are quick. Perfect security guard camera.\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Razi\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"Nice good clarity good performance 🔥audio perfect. Hd performance very good\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rohith Pillalamarri\", \"rating\": \"3.0\", \"date\": \"29 Mar 2025\", \"text\": \"Best in classBest video and Audio and App is so much better and easy accessible.The worst thing is Camera have serious connection problems with 4G Sim Card, it always Goes offline even with a proper sim card,However it works good with LAN connection.\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"MohiT\", \"rating\": \"4.0\", \"date\": \"08 May 2025\", \"text\": \"Overall good product. Build quality is perfect. App quality and ease of use is perfect . Night vision is also perfect .Only con in the camera is its picture quality and zoom quality . Doesn’t seems to be more than 2 MP quality.\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ankit Singh\", \"rating\": \"5.0\", \"date\": \"07 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This device is awesome, both the cameras are working fine has clear picture quality, zoom is fine ..better than 3 mp cameras...light and siren are perfect..self auto patrolling mode is awesome..Also, I hope this devices survives and last long as I using this brand for first time..\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Jar Jar\", \"rating\": \"4.0\", \"date\": \"21 May 2025\", \"text\": \"Easy to install, easily paired to my wifi connection and easy to use... The software specially for the Computer leaves more to be desired, especially things like zooming in on a particular area but the app for your phone works well... Auto detection works very well, but I wish there was auto detection for Animals because cats and dogs keep coming and pooping on my lawn... I also wish the camera pixels were a little higher because picture becomes hazy when you zoom in specially at night. Sound is loud and clear... I have been using this camera for a year now and have had no issues till now...\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Y P Y P\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Good Camer Good picture Quality And Good camera Mic or Speaker very Clear And loud Over All Good Quality Product but Buy Only WiFi Camera H8c 4mp Support WiFi And Lan Also Don\'t buy 4g sim Camera\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"RAJ KUMAR BOLLAM\", \"rating\": \"1.0\", \"date\": \"27 May 2025\", \"text\": \"Over all camera good but sometimes problem.. 15 days work after problem start.. network issues 15 days good work.. every time restart\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Bhagath Kumar Vittal\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"Quality of recording is very good and human sensors activeness and alerts are quick. Perfect security guard camera.\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Razi\", \"rating\": \"5.0\", \"date\": \"29 Apr 2025\", \"text\": \"Nice good clarity good performance 🔥audio perfect. Hd performance very good\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Rohith Pillalamarri\", \"rating\": \"3.0\", \"date\": \"29 Mar 2025\", \"text\": \"Best in classBest video and Audio and App is so much better and easy accessible.The worst thing is Camera have serious connection problems with 4G Sim Card, it always Goes offline even with a proper sim card,However it works good with LAN connection.\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"MohiT\", \"rating\": \"4.0\", \"date\": \"08 May 2025\", \"text\": \"Overall good product. Build quality is perfect. App quality and ease of use is perfect . Night vision is also perfect .Only con in the camera is its picture quality and zoom quality . Doesn’t seems to be more than 2 MP quality.\n  \nRead more\", \"product_id\": \"B0D7MM2CF4\", \"link\": \"https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Imou 3MP Smart CCTV Security WiFi Camera for Home, 360° Coverage, AI Human Detection, Siren Alarm, Night Vision</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>12</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4</v>
+      </c>
+      <c r="H64" t="n">
+        <v>16</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"unknown\", \"product_name\": \"Imou 3MP Smart CCTV Security WiFi Camera for Home, 360° Coverage, AI Human Detection, Siren Alarm, Night Vision 10M, 2-Way Talk, Supports 256GB SD Card, WiFi &amp; Ethernet Connection\", \"product_url\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Amol\", \"rating\": \"5.0\", \"date\": \"17 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This is the brand I am using for last four to five years. I have added one more into my system. Nice camera 3MP . Quick and easy setup.Every home user must purchase and use it for home security. Specially when you are going out. Keep the camera ON with motion sensor on and alarm message set up . You can watch the home ...\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sanjay Verma\", \"rating\": \"4.0\", \"date\": \"14 May 2025\", \"text\": \"A nice product &amp; video quantity/ function is great, value for money.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"marvelousmaniraj\", \"rating\": \"5.0\", \"date\": \"02 Apr 2025\", \"text\": \"SMALL AND SWEET CAMERA WITH ALL FEATURES EXCEPT SPOTLIGHT,FUCNCTIONALITY IS SUPER SMOOTH,CONNECTIVITY SHOULD BE HIGH IN RANGE,RECORDING QUALITY IS COMPLETELY AWESOME,EASE OF INSTALLATION,AND THE SUBSCRIPTION OF THE CLOUD STORAGE PER MONTH IS 600 WHICH IS SO SAD TO PAY,AND THE WORST AND BAD FEATURE IS THERE IS NO UPI PAYMENT OPTION THERE IS ONLY CARD PAYMENT,APART FROM THAT THIS IS CAMERA IS CRAZY AND COOL,I HAVE MORE THAN 4 CAMERAS IN MY HOME SO NO NEED TO WORRY YOU CAN COMPLETELY TRUST THE PRODUCT BLINDLY🥳🥳🥳🥳🥳🔥🔥🔥😍😍😍👌👌\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Shanwaz Ali\", \"rating\": \"1.0\", \"date\": \"28 Apr 2025\", \"text\": \"Camera is good but imou service is bad I\'m clam warranty but customer helpline number asking to sent the adapter via courier to imou service center mumbai to self money using to sent after sending the adapter the can forward to replacement clearly the service to cheap and bad solve problams😡\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"I have order 90m but seller to gived me only 70m cable . I am not satisfied\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"Good product . Easy to use and human detection is very fast and mic is super\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Arun kumar\", \"rating\": \"3.0\", \"date\": \"24 Jan 2025\", \"text\": \"It is good in this price range. Only problem is about service.i had purchased one before 6 months. But it has recording problem. When I contacted the company, they said that they have no responsibility.Then I contacted Amazon team. I had made a lot of calls on this. Atlast I got refund through gift card and I returned the product.when I am going through the reviews,a lot of people are facing this recording problem.So please keep in mind that, it is a good product and only problem is about service.  Again the same problem,the same recording problem.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anubhav sood\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Nice product . Excellent clarity\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nadim. N. Chauhan\", \"rating\": \"4.0\", \"date\": \"17 Apr 2025\", \"text\": \"value for money\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Amol\", \"rating\": \"5.0\", \"date\": \"17 Apr 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This is the brand I am using for last four to five years. I have added one more into my system. Nice camera 3MP . Quick and easy setup.Every home user must purchase and use it for home security. Specially when you are going out. Keep the camera ON with motion sensor on and alarm message set up . You can watch the home ...\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sanjay Verma\", \"rating\": \"4.0\", \"date\": \"14 May 2025\", \"text\": \"A nice product &amp; video quantity/ function is great, value for money.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"marvelousmaniraj\", \"rating\": \"5.0\", \"date\": \"02 Apr 2025\", \"text\": \"SMALL AND SWEET CAMERA WITH ALL FEATURES EXCEPT SPOTLIGHT,FUCNCTIONALITY IS SUPER SMOOTH,CONNECTIVITY SHOULD BE HIGH IN RANGE,RECORDING QUALITY IS COMPLETELY AWESOME,EASE OF INSTALLATION,AND THE SUBSCRIPTION OF THE CLOUD STORAGE PER MONTH IS 600 WHICH IS SO SAD TO PAY,AND THE WORST AND BAD FEATURE IS THERE IS NO UPI PAYMENT OPTION THERE IS ONLY CARD PAYMENT,APART FROM THAT THIS IS CAMERA IS CRAZY AND COOL,I HAVE MORE THAN 4 CAMERAS IN MY HOME SO NO NEED TO WORRY YOU CAN COMPLETELY TRUST THE PRODUCT BLINDLY🥳🥳🥳🥳🥳🔥🔥🔥😍😍😍👌👌\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Shanwaz Ali\", \"rating\": \"1.0\", \"date\": \"28 Apr 2025\", \"text\": \"Camera is good but imou service is bad I\'m clam warranty but customer helpline number asking to sent the adapter via courier to imou service center mumbai to self money using to sent after sending the adapter the can forward to replacement clearly the service to cheap and bad solve problams😡\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"I have order 90m but seller to gived me only 70m cable . I am not satisfied\", \"rating\": \"5.0\", \"date\": \"23 Apr 2025\", \"text\": \"Good product . Easy to use and human detection is very fast and mic is super\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Arun kumar\", \"rating\": \"3.0\", \"date\": \"24 Jan 2025\", \"text\": \"It is good in this price range. Only problem is about service.i had purchased one before 6 months. But it has recording problem. When I contacted the company, they said that they have no responsibility.Then I contacted Amazon team. I had made a lot of calls on this. Atlast I got refund through gift card and I returned the product.when I am going through the reviews,a lot of people are facing this recording problem.So please keep in mind that, it is a good product and only problem is about service.  Again the same problem,the same recording problem.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anubhav sood\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"Nice product . Excellent clarity\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Nadim. N. Chauhan\", \"rating\": \"4.0\", \"date\": \"17 Apr 2025\", \"text\": \"value for money\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Imou 5MP CCTV Camera for Home Outdoor, 360° Security WiFi Camera</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>12</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4</v>
+      </c>
+      <c r="H65" t="n">
+        <v>16</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D7BYH8J7\", \"product_name\": \"Imou 5MP CCTV Camera for Home Outdoor, 360° Security WiFi Camera, Full Color Night Vision 30M, Human Detection, 2-Way Talk, Siren Alarm, Compatible with Alexa, Supports 512GB SD Card, IP66, DK7\", \"product_url\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Santosh Mohanty\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Best camera only problem is subscription pack price ... They just have option for 3-7-30days.... Rest value of money to purchase\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ron\", \"rating\": \"4.0\", \"date\": \"15 May 2025\", \"text\": \"Offers clear footage with effective night vision detection. Weatherproof design ensures durability.\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kalind Rathod\", \"rating\": \"1.0\", \"date\": \"05 Sep 2022\", \"text\": \"i wanted to use this camera where there is hardly Internet possibility and power goes down often.. places like farms and villages .. so keep this in mind when reading this review..but this review still relevant when someone\'s internet goes off.. or power goes off ..I don\'t want to say this camera as worst because hardware is good but the firmware and the application software are more than worst. very thanks to programmer.camera has inbuilt hotspot but that can be used to connect only to activate internet connection. as you connect to internet, inbuilt hotspot becomes inactive forever and no way to start it back on. so in any case your internet connection goes off there is no way to connect to camera directly through any Wi-Fi device.if you need to record in SD card that everyone needs.. you have to have internet connection because when you connect camera to the internet .. then only one can see the settings through which local SD card recording can be activated.now imagine the situation where you started SD card recording through internet .. leter internet goes off.. now you have got recordings in the camera sd card but there is no way to connect to camera through Wi-Fi device ( forever disabled Hotspot of camera )and no way to access sd card recording until your internet comes back on.yes, you can reset the camera to its original default settings to activate hotspot again .. and connect it to access old recordings..  but as recording to sd card is disabled by default so now you have no further recordings. now again you have to wait for internet to start SD card recording and then you find again that hotspot is disabled now.so if you want to use this camera to record in SD card and use it without internet then this is not for you.now other important case for me ..  that is if Power goes off.. you will find that when power comes back on the camera internal date reverted to 1st January 2000 .. now all your next recordings will have this wrong date. if power load shedding happens multiple time during week or month.. you have multiple recordings having same date and time.okay any how accepted this. real enjoyment starts now !! to access recordings of year 2000 there is no way in the Application so that you can change the year directly from 2022 to 2000 to access it\'s recording.. the fastest one can go back is month by month .. so total you have to press back button of month atleast for 22 year x 12 month= 264 times..  okay accepted..!!  but you cannot do this fast.. you have to wait for a second after each back month pressed..  yeehh..!!if some manufacturer force to be online for any reason.. that means they might do some suspicious background activity .. believe me..!!many of its services are depends on their premium plans so application begs you repeatedly to activate it.then some other issues but I don\'t have more time now.. I am returning it back.\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Sakthivel\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"I bought two cameras. Initially (one week) it was not working properly, it was very slow in the mobile application and worked like a still camera. Then there was a software version update symbol showed under each camera in the mobile app, and I updated it to latest version. It is working awesome now. :-). But still i like \\"Imou 5MP+5MP Dual Lens CCTV Camera Home Outdoor\\". costly.. but worth.\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anand Ganesan\", \"rating\": \"5.0\", \"date\": \"22 Apr 2025\", \"text\": \"Good quality easy to install crystal clear vedio and audio\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"S A\", \"rating\": \"3.0\", \"date\": \"26 Dec 2024\", \"text\": \"good product, but not real value addition over the Full HD / 2MP variant\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Venkat Parasuram\", \"rating\": \"4.0\", \"date\": \"05 May 2025\", \"text\": \"Good clarity and easy operation\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Faizal\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Very nice thing, usefull, no damage, i tryed this one.... No damage is there\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Santosh Mohanty\", \"rating\": \"5.0\", \"date\": \"10 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Best camera only problem is subscription pack price ... They just have option for 3-7-30days.... Rest value of money to purchase\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ron\", \"rating\": \"4.0\", \"date\": \"15 May 2025\", \"text\": \"Offers clear footage with effective night vision detection. Weatherproof design ensures durability.\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kalind Rathod\", \"rating\": \"1.0\", \"date\": \"05 Sep 2022\", \"text\": \"i wanted to use this camera where there is hardly Internet possibility and power goes down often.. places like farms and villages .. so keep this in mind when reading this review..but this review still relevant when someone\'s internet goes off.. or power goes off ..I don\'t want to say this camera as worst because hardware is good but the firmware and the application software are more than worst. very thanks to programmer.camera has inbuilt hotspot but that can be used to connect only to activate internet connection. as you connect to internet, inbuilt hotspot becomes inactive forever and no way to start it back on. so in any case your internet connection goes off there is no way to connect to camera directly through any Wi-Fi device.if you need to record in SD card that everyone needs.. you have to have internet connection because when you connect camera to the internet .. then only one can see the settings through which local SD card recording can be activated.now imagine the situation where you started SD card recording through internet .. leter internet goes off.. now you have got recordings in the camera sd card but there is no way to connect to camera through Wi-Fi device ( forever disabled Hotspot of camera )and no way to access sd card recording until your internet comes back on.yes, you can reset the camera to its original default settings to activate hotspot again .. and connect it to access old recordings..  but as recording to sd card is disabled by default so now you have no further recordings. now again you have to wait for internet to start SD card recording and then you find again that hotspot is disabled now.so if you want to use this camera to record in SD card and use it without internet then this is not for you.now other important case for me ..  that is if Power goes off.. you will find that when power comes back on the camera internal date reverted to 1st January 2000 .. now all your next recordings will have this wrong date. if power load shedding happens multiple time during week or month.. you have multiple recordings having same date and time.okay any how accepted this. real enjoyment starts now !! to access recordings of year 2000 there is no way in the Application so that you can change the year directly from 2022 to 2000 to access it\'s recording.. the fastest one can go back is month by month .. so total you have to press back button of month atleast for 22 year x 12 month= 264 times..  okay accepted..!!  but you cannot do this fast.. you have to wait for a second after each back month pressed..  yeehh..!!if some manufacturer force to be online for any reason.. that means they might do some suspicious background activity .. believe me..!!many of its services are depends on their premium plans so application begs you repeatedly to activate it.then some other issues but I don\'t have more time now.. I am returning it back.\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Sakthivel\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"I bought two cameras. Initially (one week) it was not working properly, it was very slow in the mobile application and worked like a still camera. Then there was a software version update symbol showed under each camera in the mobile app, and I updated it to latest version. It is working awesome now. :-). But still i like \\"Imou 5MP+5MP Dual Lens CCTV Camera Home Outdoor\\". costly.. but worth.\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anand Ganesan\", \"rating\": \"5.0\", \"date\": \"22 Apr 2025\", \"text\": \"Good quality easy to install crystal clear vedio and audio\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"S A\", \"rating\": \"3.0\", \"date\": \"26 Dec 2024\", \"text\": \"good product, but not real value addition over the Full HD / 2MP variant\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Venkat Parasuram\", \"rating\": \"4.0\", \"date\": \"05 May 2025\", \"text\": \"Good clarity and easy operation\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Faizal\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Very nice thing, usefull, no damage, i tryed this one.... No damage is there\n  \nRead more\", \"product_id\": \"B0D7BYH8J7\", \"link\": \"https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cmf By Nothing Wireless Earbuds (Orange) - In Ear</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>12</v>
+      </c>
+      <c r="H66" t="n">
+        <v>16</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CJ8S7XHQ\", \"product_name\": \"Cmf By Nothing Wireless Earbuds (Orange) - In Ear\", \"product_url\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 2.38, \"sentiment_breakdown\": {\"neutral\": 2, \"positive\": 2, \"negative\": 12}, \"overall_sentiment\": \"negative\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Nice\", \"rating\": \"5.0\", \"date\": \"11 Apr 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I like the colour and quality\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Remove😊Remove😊\", \"rating\": \"5.0\", \"date\": \"03 Mar 2024\", \"text\": \"Voice clear, battery back up, sound adjustnent superb 💥👌🎉Nothing buds are bestAnd it\'s fit in ears very nice\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Atharva\", \"rating\": \"1.0\", \"date\": \"11 Jul 2024\", \"text\": \"Do not buy very uncomfortable seriously I mean it’s the worst quality you can find\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Friends OTT\", \"rating\": \"3.0\", \"date\": \"10 Jul 2024\", \"text\": \"Product is fine. But i face difficulty connecting to the other android devices with bluetooth and without the app. Do i need to reset the earbuds everytime ??\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"GAURAV KUMAR MEENA\", \"rating\": \"1.0\", \"date\": \"12 May 2025\", \"text\": \"very bad connecting problam face  connectivity problam face only one blootooth connect in ear the very bad total money loss 3rd class earbuds loss of money\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Anonymous1\", \"rating\": \"2.0\", \"date\": \"23 Jul 2024\", \"text\": \"Left sided bud has sound issues already within 5 months of usage. They keep falling out of ear during workouts.\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Amisha\", \"rating\": \"1.0\", \"date\": \"11 Apr 2025\", \"text\": \"Did’nt last even a year. Earbuds stopped charging, battery started draining no reply over mail as well….not good quality at all\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Avnish kumar\", \"rating\": \"1.0\", \"date\": \"18 Mar 2024\", \"text\": \"first of all its sound quality for listening music  is good but for  calling 😬😬 it burst your mind and annoying  i cant express what i feel ... after wasting such a amount for this buds...... very very bad experience of calling.......... not recommended strictly...even i suggest  oneplus nord buds 2  or oppo enco buds 2.instead of this worst productnot meet the quality clame by company...\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Nice\", \"rating\": \"5.0\", \"date\": \"11 Apr 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I like the colour and quality\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Remove😊Remove😊\", \"rating\": \"5.0\", \"date\": \"03 Mar 2024\", \"text\": \"Voice clear, battery back up, sound adjustnent superb 💥👌🎉Nothing buds are bestAnd it\'s fit in ears very nice\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Atharva\", \"rating\": \"1.0\", \"date\": \"11 Jul 2024\", \"text\": \"Do not buy very uncomfortable seriously I mean it’s the worst quality you can find\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Friends OTT\", \"rating\": \"3.0\", \"date\": \"10 Jul 2024\", \"text\": \"Product is fine. But i face difficulty connecting to the other android devices with bluetooth and without the app. Do i need to reset the earbuds everytime ??\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"GAURAV KUMAR MEENA\", \"rating\": \"1.0\", \"date\": \"12 May 2025\", \"text\": \"very bad connecting problam face  connectivity problam face only one blootooth connect in ear the very bad total money loss 3rd class earbuds loss of money\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Anonymous1\", \"rating\": \"2.0\", \"date\": \"23 Jul 2024\", \"text\": \"Left sided bud has sound issues already within 5 months of usage. They keep falling out of ear during workouts.\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Amisha\", \"rating\": \"1.0\", \"date\": \"11 Apr 2025\", \"text\": \"Did’nt last even a year. Earbuds stopped charging, battery started draining no reply over mail as well….not good quality at all\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Avnish kumar\", \"rating\": \"1.0\", \"date\": \"18 Mar 2024\", \"text\": \"first of all its sound quality for listening music  is good but for  calling 😬😬 it burst your mind and annoying  i cant express what i feel ... after wasting such a amount for this buds...... very very bad experience of calling.......... not recommended strictly...even i suggest  oneplus nord buds 2  or oppo enco buds 2.instead of this worst productnot meet the quality clame by company...\n  \nRead more\", \"product_id\": \"B0CJ8S7XHQ\", \"link\": \"https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>soundcore By Anker Liberty 4 Nc Wireless Noise Cancelling In Ear Earbud,98.5% Noise Reduction</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0BZV7M23Q\", \"product_name\": \"soundcore By Anker Liberty 4 Nc Wireless Noise Cancelling In Ear Earbud,98.5% Noise Reduction,Adaptive Noise Cancelling To Ear And Environment,Hi-Res Sound,50H Battery,Wireless Charging,Bluetooth 5.3\", \"product_url\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 8, \"average_rating\": 3.75, \"sentiment_breakdown\": {\"positive\": 6, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"HEMANT JAIN\", \"rating\": \"5.0\", \"date\": \"25 Feb 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Introduction The Anker Soundcore Liberty 4 NC are true wireless in-ear earbuds that offer advanced features and impressive performance at a competitive price.Build Quality and Design The earbuds are made of high-quality materials, making them durable and comfortable for long listening sessions. They fit securely in the ears and come with a compact charging case for easy portability.Sound Quality The sound quality is excellent, with clear and detailed vocals. The bass, mids, and treble are well-balanced, delivering a rich and immersive listening experience. The noise cancellation is effective, blocking out a significant amount of external noise.Features and Functionality The Soundcore Liberty 4 NC offers a stable Bluetooth connection and impressive battery life, lasting up to 8 hours on a single charge with an additional 32 hours from the charging case. The touch controls are intuitive, and the earbuds come with a companion app for customizing the sound profile.Performance in Different Scenarios These earbuds perform well in daily use, providing excellent sound quality and noise cancellation during commutes and office work. They are also suitable for gaming, with accurate sound cues and minimal latency. For exercise, the earbuds are sweat-resistant and secure, making them ideal for workouts.Pros and Cons Pros:Excellent sound qualityEffective noise cancellationComfortable and secure fitLong battery lifeAffordable priceCons:Touch controls can be sensitiveConclusion and Recommendation Overall, the Anker Soundcore Liberty 4 NC are an excellent choice for anyone seeking high-quality true wireless earbuds with noise cancellation at an affordable price. Their performance and features make them a great value for money.\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"K. Vikram\", \"rating\": \"1.0\", \"date\": \"27 Mar 2025\", \"text\": \"The earphones themselves are reasonably good. The fit isn\'t very comfortable, and can hurt your ears after a few hours. But the sound clarity is great, connectivity is good enough.My primary issue (and the reason for the 1 star rating) is that around 11 months after purchase, the battery life became awful - it would last less than 60 minutes on full charge. When I approached the company under warranty, they informed me that my Liberty 4 earbuds were not repairable; they then offered me cheap 2000-3000rs \'refurbished\' earbuds as replacement - because they did not have my model in stock. This has been ongoing for more than 30 days, and I ended up buying a new pair of earbuds from a more reputable company. Hopefully, some day they will resolve this issue and I will update my rating accordingly.Update (31/3/25): They offered me INR 625 as refund - as the product was purchased 11 months ago. So, they are quite clear on the fact that the product loses nearly 90% of its value in under a year. Purchase from a reputed brand, folks. Save yourself a ton of grief.Update 2 (4/4/25): I requested that they return my defective device instead of this pathetic refund; but unfortunately, they have \'misplaced\' it. Do not bother buying from this scam company.\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Misbah Ul HasanMisbah Ul Hasan\", \"rating\": \"4.0\", \"date\": \"08 Oct 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'ve been using the Soundcore Liberty 4NC earbuds with my iPhone 13 Pro for a few weeks now, and I\'m generally impressed with them. The sound quality is excellent, with rich bass, clear mids, and crisp highs. The Active Noise Cancellation (ANC) isn\'t groundbreaking, but it does a decent job of blocking out ambient noise, especially on buses or trains.One of the standout features is the seamless connectivity with two devices simultaneously. I can easily switch between my iPhone and laptop without any hassle. The battery life is also impressive, lasting well over a week on a single charge.However, there\'s one area where these earbuds fall short: call quality. Despite the claimed 6 microphones, I haven\'t noticed any significant improvement in clarity during calls. There\'s still some background noise and muffled voices.Overall, the Soundcore Liberty 4NC earbuds are a solid purchase, offering great sound quality, decent ANC, and convenient multi-device connectivity. If you\'re looking for earbuds with excellent audio performance and don\'t prioritise crystal-clear phone calls, these are a great option.\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"DivyDivy\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"I was sceptical because the seal was actually reapplied by the seller. Not to find that the product wouldn’t work but tbh used products which we have to put onto ourselves should be hygienic.But the content inside seemed to be intact and as new. The extra ear buds especially were in mint condition, since the seal for the buds within weren’t removed. So I felt reassured.The earbuds built quality overall is very good; sound quality is also impressive with a well balanced sound signature with clear highs and minds, and non tinny lows. I wouldn’t say it has a neutral sound profile but it’s well balanced and really enjoyable.I use it with my IPhone 14 and there doesn’t seem to be any issues with the connection or quality. The ambient sound is the another impressive attribute which lets a very natural sound into the ears wild walking or jogging. The sound is no different than not having it on and listening to the street noises with your bare ears.Noise cancellation is also admirable.The app is really handy.Overall, I really like it since the sound quality seems close to my Sony WH 1000 m3 headphones for an inear earbuds (on wireless connection).\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"HEMANT JAIN\", \"rating\": \"5.0\", \"date\": \"25 Feb 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Introduction The Anker Soundcore Liberty 4 NC are true wireless in-ear earbuds that offer advanced features and impressive performance at a competitive price.Build Quality and Design The earbuds are made of high-quality materials, making them durable and comfortable for long listening sessions. They fit securely in the ears and come with a compact charging case for easy portability.Sound Quality The sound quality is excellent, with clear and detailed vocals. The bass, mids, and treble are well-balanced, delivering a rich and immersive listening experience. The noise cancellation is effective, blocking out a significant amount of external noise.Features and Functionality The Soundcore Liberty 4 NC offers a stable Bluetooth connection and impressive battery life, lasting up to 8 hours on a single charge with an additional 32 hours from the charging case. The touch controls are intuitive, and the earbuds come with a companion app for customizing the sound profile.Performance in Different Scenarios These earbuds perform well in daily use, providing excellent sound quality and noise cancellation during commutes and office work. They are also suitable for gaming, with accurate sound cues and minimal latency. For exercise, the earbuds are sweat-resistant and secure, making them ideal for workouts.Pros and Cons Pros:Excellent sound qualityEffective noise cancellationComfortable and secure fitLong battery lifeAffordable priceCons:Touch controls can be sensitiveConclusion and Recommendation Overall, the Anker Soundcore Liberty 4 NC are an excellent choice for anyone seeking high-quality true wireless earbuds with noise cancellation at an affordable price. Their performance and features make them a great value for money.\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"K. Vikram\", \"rating\": \"1.0\", \"date\": \"27 Mar 2025\", \"text\": \"The earphones themselves are reasonably good. The fit isn\'t very comfortable, and can hurt your ears after a few hours. But the sound clarity is great, connectivity is good enough.My primary issue (and the reason for the 1 star rating) is that around 11 months after purchase, the battery life became awful - it would last less than 60 minutes on full charge. When I approached the company under warranty, they informed me that my Liberty 4 earbuds were not repairable; they then offered me cheap 2000-3000rs \'refurbished\' earbuds as replacement - because they did not have my model in stock. This has been ongoing for more than 30 days, and I ended up buying a new pair of earbuds from a more reputable company. Hopefully, some day they will resolve this issue and I will update my rating accordingly.Update (31/3/25): They offered me INR 625 as refund - as the product was purchased 11 months ago. So, they are quite clear on the fact that the product loses nearly 90% of its value in under a year. Purchase from a reputed brand, folks. Save yourself a ton of grief.Update 2 (4/4/25): I requested that they return my defective device instead of this pathetic refund; but unfortunately, they have \'misplaced\' it. Do not bother buying from this scam company.\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Misbah Ul HasanMisbah Ul Hasan\", \"rating\": \"4.0\", \"date\": \"08 Oct 2024\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    I\'ve been using the Soundcore Liberty 4NC earbuds with my iPhone 13 Pro for a few weeks now, and I\'m generally impressed with them. The sound quality is excellent, with rich bass, clear mids, and crisp highs. The Active Noise Cancellation (ANC) isn\'t groundbreaking, but it does a decent job of blocking out ambient noise, especially on buses or trains.One of the standout features is the seamless connectivity with two devices simultaneously. I can easily switch between my iPhone and laptop without any hassle. The battery life is also impressive, lasting well over a week on a single charge.However, there\'s one area where these earbuds fall short: call quality. Despite the claimed 6 microphones, I haven\'t noticed any significant improvement in clarity during calls. There\'s still some background noise and muffled voices.Overall, the Soundcore Liberty 4NC earbuds are a solid purchase, offering great sound quality, decent ANC, and convenient multi-device connectivity. If you\'re looking for earbuds with excellent audio performance and don\'t prioritise crystal-clear phone calls, these are a great option.\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"DivyDivy\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"I was sceptical because the seal was actually reapplied by the seller. Not to find that the product wouldn’t work but tbh used products which we have to put onto ourselves should be hygienic.But the content inside seemed to be intact and as new. The extra ear buds especially were in mint condition, since the seal for the buds within weren’t removed. So I felt reassured.The earbuds built quality overall is very good; sound quality is also impressive with a well balanced sound signature with clear highs and minds, and non tinny lows. I wouldn’t say it has a neutral sound profile but it’s well balanced and really enjoyable.I use it with my IPhone 14 and there doesn’t seem to be any issues with the connection or quality. The ambient sound is the another impressive attribute which lets a very natural sound into the ears wild walking or jogging. The sound is no different than not having it on and listening to the street noises with your bare ears.Noise cancellation is also admirable.The app is really handy.Overall, I really like it since the sound quality seems close to my Sony WH 1000 m3 headphones for an inear earbuds (on wireless connection).\n  \nRead more\", \"product_id\": \"B0BZV7M23Q\", \"link\": \"https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>JLab JBuds LUX ANC Smart Active Noise Cancelling Headphones</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>16</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>16</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0CRM4Q1W1\", \"product_name\": \"JLab JBuds LUX ANC Smart Active Noise Cancelling Headphones - Over Ear Wireless Headphones with Microphone, 70+ H Playtime Foldable Bluetooth Earphones with Multipoint &amp; Customisable Sound, Graphite\", \"product_url\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.62, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Shyam\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Best in class in this budget segment . ANC does fine. Superior sound quality. One can compare the clarity to jbl live 770  NC which I use along side. Needs little tweaking through jlabs app. I found sound clarity to be nice with a good soundstage too for this price. App supports updates too and got an update immediately after connecting for the first time. Ear cuffs are designed uniquely than any other over the ear headphones. One little issue with the ear cuffs though, it gets really hot around ears after some time and we sweat heavily. That issue may be because the muffs provided covers entire ear with a very snug fit. Earmuffs are soft and durable. Battery life is amazing. Haven’t charged even once since started burning in. It’s been more than 30 hours playing on 70% volume with ANC on and still the battery shows 60 %. Over all good built quality is good even though made of plastic and doesn’t feel cheap. Bluetooth connection is great and supports google fast pair. Haven’t noticed any lag or disconnection ever. Just go for it if you are in budget and you won’t be disappointed.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"05 Dec 2024\", \"text\": \"JLab headphones stand out with their excellent build quality, ensuring durability and comfort for daily use. The sound quality is impressive, offering rich bass, clear mids, and detailed highs. Their effective voice cancellation minimizes background noise, enhancing call clarity and immersive listening. The sleek design and lightweight feel make them ideal for extended wear. Overall, JLab delivers great value with a perfect blend of durability, performance, and affordability.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anjali G\", \"rating\": \"5.0\", \"date\": \"26 Dec 2024\", \"text\": \"Beautiful color - 10/10Build - 10/10Value for money- bit expensive but worth it..Surround soundANCMasssst headphones 👌\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Supratim\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Soft ear pads, comforting sound. it doesn’t ache your ears on long run.good for calls  ,ANC works very well.  dual pairings works well too.  Battery life is pretty good .must say.found it to be disconnecting after almost every team calls thru laptop (when u r connected with Bluetooth) if you use it with the cable provided, no complaints .  overall good buy! recommend.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"03 Dec 2024\", \"text\": \"The build quality and sound output are impressive. Works well and loved how it fits and noise cancellation is also good. Seems value for money and stand out as compared to other brands\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Karthik\", \"rating\": \"5.0\", \"date\": \"27 May 2025\", \"text\": \"Exceptional Value and Performance – A Month InAfter using these headphones for a month, I can confidently say they are outstanding in every aspect. The sound quality, comfort, and battery life are top-notch—truly one of the best products I\'ve come across in recent times.A couple of minor observations: a carrying pouch in the box would’ve been a thoughtful addition, and your ears may feel a bit warm during extended use. That said, these are small trade-offs for what you get.Overall, this is an absolute value-for-money purchase. Highly recommended!\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ronnie\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Worth beyond its value!\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sathish\", \"rating\": \"3.0\", \"date\": \"28 Jan 2025\", \"text\": \"Simple bass and low sound with full volume.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shyam\", \"rating\": \"5.0\", \"date\": \"19 Mar 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Best in class in this budget segment . ANC does fine. Superior sound quality. One can compare the clarity to jbl live 770  NC which I use along side. Needs little tweaking through jlabs app. I found sound clarity to be nice with a good soundstage too for this price. App supports updates too and got an update immediately after connecting for the first time. Ear cuffs are designed uniquely than any other over the ear headphones. One little issue with the ear cuffs though, it gets really hot around ears after some time and we sweat heavily. That issue may be because the muffs provided covers entire ear with a very snug fit. Earmuffs are soft and durable. Battery life is amazing. Haven’t charged even once since started burning in. It’s been more than 30 hours playing on 70% volume with ANC on and still the battery shows 60 %. Over all good built quality is good even though made of plastic and doesn’t feel cheap. Bluetooth connection is great and supports google fast pair. Haven’t noticed any lag or disconnection ever. Just go for it if you are in budget and you won’t be disappointed.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"05 Dec 2024\", \"text\": \"JLab headphones stand out with their excellent build quality, ensuring durability and comfort for daily use. The sound quality is impressive, offering rich bass, clear mids, and detailed highs. Their effective voice cancellation minimizes background noise, enhancing call clarity and immersive listening. The sleek design and lightweight feel make them ideal for extended wear. Overall, JLab delivers great value with a perfect blend of durability, performance, and affordability.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Anjali G\", \"rating\": \"5.0\", \"date\": \"26 Dec 2024\", \"text\": \"Beautiful color - 10/10Build - 10/10Value for money- bit expensive but worth it..Surround soundANCMasssst headphones 👌\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Supratim\", \"rating\": \"4.0\", \"date\": \"18 May 2025\", \"text\": \"Soft ear pads, comforting sound. it doesn’t ache your ears on long run.good for calls  ,ANC works very well.  dual pairings works well too.  Battery life is pretty good .must say.found it to be disconnecting after almost every team calls thru laptop (when u r connected with Bluetooth) if you use it with the cable provided, no complaints .  overall good buy! recommend.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"03 Dec 2024\", \"text\": \"The build quality and sound output are impressive. Works well and loved how it fits and noise cancellation is also good. Seems value for money and stand out as compared to other brands\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Karthik\", \"rating\": \"5.0\", \"date\": \"27 May 2025\", \"text\": \"Exceptional Value and Performance – A Month InAfter using these headphones for a month, I can confidently say they are outstanding in every aspect. The sound quality, comfort, and battery life are top-notch—truly one of the best products I\'ve come across in recent times.A couple of minor observations: a carrying pouch in the box would’ve been a thoughtful addition, and your ears may feel a bit warm during extended use. That said, these are small trade-offs for what you get.Overall, this is an absolute value-for-money purchase. Highly recommended!\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ronnie\", \"rating\": \"5.0\", \"date\": \"14 Apr 2025\", \"text\": \"Worth beyond its value!\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Sathish\", \"rating\": \"3.0\", \"date\": \"28 Jan 2025\", \"text\": \"Simple bass and low sound with full volume.\n  \nRead more\", \"product_id\": \"B0CRM4Q1W1\", \"link\": \"https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SHOKZ OpenRun Pro 2 Bone Conduction Sports Headphones</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>16</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>16</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"unknown\", \"product_name\": \"SHOKZ OpenRun Pro 2 Bone Conduction Sports Headphones, Open-Ear Wireless Earphones with Bluetooth 5.3, Noise Cancelling Mics, IP55 Waterproof, 12h Playtime for Running, USB-C Qiuck Charge (Black)\", \"product_url\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.88, \"sentiment_breakdown\": {\"positive\": 16}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Dr.Ralte\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This is my first ever Bone Conduction headphones I have used or purchase.Having gone through multiple reviews, finally decided to purchase these.As all reviewers have emphasized do not have expectations for it to perform like a normal Headphone/Earphone.With that in mind ordered Openrun Pro 2 after eliminating all the others.On opening the box, it comes with a nice case, the headphones, USB cable (A to C), warranty card with serial and reflective stickersAfter downloading the app, I pared it with my phone and the registration was done on the fly along with a firmware upgrade.App allows you to multi-pair and adjust EQ to your liking.The build quality is very good and robust.The band sits comfortably on both ear and found no issues with it. I can probably wear this much longer than any headphones/earphones I have owned till date.Coming to the audio, I started with 50% volume on standard EQ, I was pleasantly surprised to hear the audio almost similar to having a headphone/earphone on.Only thing was the bass wont be able to compare to standard ear/headphones, but it was not such that you could not appreciate the bass. In fact it sounds much much better than any mobile phone speakers and better than most portable bluetooth speakers, regarding bass (only way to give an easy comparative description)Picking and answering calls is easy and the mic noise cancellation is awesome, such that the person on the other side will not realize you are on a wireless.Going on a walk or jog the headphones perform 100% to what they are specified for.Have not given a full run for its battery life but will update on it soon.Conclusion: Very happy and satisfied with the purchase abet the price kinds pinches on the pockets. At the time I bought this the similar bone conducting Bose was selling lower than this by 1k+Would definitely to people who completely understand what they are signing up for.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"MRG\", \"rating\": \"5.0\", \"date\": \"21 Mar 2025\", \"text\": \"Amazingly snug , sits lightly around the ears without pulls or tags , took it for a jog spin - flawless , immersive , amazing quality of sound ,Music and voice call -\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"customerfromindia\", \"rating\": \"5.0\", \"date\": \"26 Dec 2024\", \"text\": \"This is an excellent running/walking/gym companion. While sound quality is decent it\'s very liberating to not poke your ear or cover ear while you are doing high adrenaline workout. This also has pretty good phone functionality to take calls on the go. You can easily control music from \\"multi function\\" button conveniently located. Overall this is best money can buy for listening to music/podecast or talking on phone while working out.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Puneet P\", \"rating\": \"4.0\", \"date\": \"26 Apr 2025\", \"text\": \"Pros:1. If you have sensitive ears and get discomfort or ear fatigue on prolonged use of Headphones or In-earphones, then this Revolutionary Headphones is for you.2. You can use it for 5-6 hours in one stretch without any ear fatigue issues.3. The weight is literally negligible. Fits well on your ears.4. The sound quality is top notch (only for quiet environments, not for crowded/places places)5. Battery life is really good.6. Calling quality is greatCons:1. It\'s of NO use when you use it in Public/crowded spaces2. You\'ll not hear anything below 50% volume levels.3. The only EQ mode that works the best in all scenes is Vocal.4. works great only when in Indoors mostly in quiet spaces. It doesn\'t work well when the environment is noisy..\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"John Joshua\", \"rating\": \"5.0\", \"date\": \"20 Jan 2025\", \"text\": \"I am using this after using Shokz Pro version 1. This is the best Open Ear in the market today. The placement of the button and its lightweightness make it more comfortable to wear.I wish it had been adjustable so it does not hit my collar when I look up. However, the sound quality and noise cancellation are good. Sometimes, I have to speak a little loud, but it is a good-quality open-ear headset overall.Battery: 4.9/5.Build: 4.8/5Sound Quality: 4.5/5Ergonomics: 4.9/5\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tanu m.\", \"rating\": \"5.0\", \"date\": \"12 Dec 2024\", \"text\": \"It’s a very nice and lite, no stress on ears the dual pitch tech is great, sound quality is very good.I am wearing it all day without any hassles the product is very suitable in a normal quiet environment but in noisy conditions with an open ear you will find it hard to listenOverall Its value for money .\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"This have good amount of bass and the volume is also good\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Satyanarayana Iragattapu\", \"rating\": \"5.0\", \"date\": \"16 Apr 2025\", \"text\": \"The app to manage the headphones makes life easy, help you stay connected with the world around you while you are on calls, no fear of dropping your headphones, no ear pain like in or over ear headphones.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Dr.Ralte\", \"rating\": \"5.0\", \"date\": \"18 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    This is my first ever Bone Conduction headphones I have used or purchase.Having gone through multiple reviews, finally decided to purchase these.As all reviewers have emphasized do not have expectations for it to perform like a normal Headphone/Earphone.With that in mind ordered Openrun Pro 2 after eliminating all the others.On opening the box, it comes with a nice case, the headphones, USB cable (A to C), warranty card with serial and reflective stickersAfter downloading the app, I pared it with my phone and the registration was done on the fly along with a firmware upgrade.App allows you to multi-pair and adjust EQ to your liking.The build quality is very good and robust.The band sits comfortably on both ear and found no issues with it. I can probably wear this much longer than any headphones/earphones I have owned till date.Coming to the audio, I started with 50% volume on standard EQ, I was pleasantly surprised to hear the audio almost similar to having a headphone/earphone on.Only thing was the bass wont be able to compare to standard ear/headphones, but it was not such that you could not appreciate the bass. In fact it sounds much much better than any mobile phone speakers and better than most portable bluetooth speakers, regarding bass (only way to give an easy comparative description)Picking and answering calls is easy and the mic noise cancellation is awesome, such that the person on the other side will not realize you are on a wireless.Going on a walk or jog the headphones perform 100% to what they are specified for.Have not given a full run for its battery life but will update on it soon.Conclusion: Very happy and satisfied with the purchase abet the price kinds pinches on the pockets. At the time I bought this the similar bone conducting Bose was selling lower than this by 1k+Would definitely to people who completely understand what they are signing up for.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"MRG\", \"rating\": \"5.0\", \"date\": \"21 Mar 2025\", \"text\": \"Amazingly snug , sits lightly around the ears without pulls or tags , took it for a jog spin - flawless , immersive , amazing quality of sound ,Music and voice call -\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"customerfromindia\", \"rating\": \"5.0\", \"date\": \"26 Dec 2024\", \"text\": \"This is an excellent running/walking/gym companion. While sound quality is decent it\'s very liberating to not poke your ear or cover ear while you are doing high adrenaline workout. This also has pretty good phone functionality to take calls on the go. You can easily control music from \\"multi function\\" button conveniently located. Overall this is best money can buy for listening to music/podecast or talking on phone while working out.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Puneet P\", \"rating\": \"4.0\", \"date\": \"26 Apr 2025\", \"text\": \"Pros:1. If you have sensitive ears and get discomfort or ear fatigue on prolonged use of Headphones or In-earphones, then this Revolutionary Headphones is for you.2. You can use it for 5-6 hours in one stretch without any ear fatigue issues.3. The weight is literally negligible. Fits well on your ears.4. The sound quality is top notch (only for quiet environments, not for crowded/places places)5. Battery life is really good.6. Calling quality is greatCons:1. It\'s of NO use when you use it in Public/crowded spaces2. You\'ll not hear anything below 50% volume levels.3. The only EQ mode that works the best in all scenes is Vocal.4. works great only when in Indoors mostly in quiet spaces. It doesn\'t work well when the environment is noisy..\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"John Joshua\", \"rating\": \"5.0\", \"date\": \"20 Jan 2025\", \"text\": \"I am using this after using Shokz Pro version 1. This is the best Open Ear in the market today. The placement of the button and its lightweightness make it more comfortable to wear.I wish it had been adjustable so it does not hit my collar when I look up. However, the sound quality and noise cancellation are good. Sometimes, I have to speak a little loud, but it is a good-quality open-ear headset overall.Battery: 4.9/5.Build: 4.8/5Sound Quality: 4.5/5Ergonomics: 4.9/5\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tanu m.\", \"rating\": \"5.0\", \"date\": \"12 Dec 2024\", \"text\": \"It’s a very nice and lite, no stress on ears the dual pitch tech is great, sound quality is very good.I am wearing it all day without any hassles the product is very suitable in a normal quiet environment but in noisy conditions with an open ear you will find it hard to listenOverall Its value for money .\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"09 May 2025\", \"text\": \"This have good amount of bass and the volume is also good\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Satyanarayana Iragattapu\", \"rating\": \"5.0\", \"date\": \"16 Apr 2025\", \"text\": \"The app to manage the headphones makes life easy, help you stay connected with the world around you while you are on calls, no fear of dropping your headphones, no ear pain like in or over ear headphones.\n  \nRead more\", \"product_id\": \"unknown\", \"link\": \"https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ZEBRONICS 1100 Watts Powerful Soundbar, 7.2.4 Home Theatre, Wireless (Dual Satellites + Dual Driver Subwoofer)</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>12</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>16</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DV3R2QM6\", \"product_name\": \"ZEBRONICS 1100 Watts Powerful Soundbar, 7.2.4 Home Theatre, Wireless (Dual Satellites + Dual Driver Subwoofer) Dual Radiators, DTS X, Dolby Atmos, Karaoke UHF Mic, HDMI eARC, Optical (Juke BAR 10000)\", \"product_url\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"30 Aug 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Seedhi baat no extra stuffI have a multiple number of soundbars and hence m saying this from experience.I was too sceptical to buy it for my 55 inches led tv but took the decision reading and watching reviews on YouTubeSo summary of points as below1.60W is enough for a normal user in family or bachelor house for loud music😀 and tv movie viewing.2.the size is too cute and perfect for tight spaces and that the main reason of me buying this.dont think it\'s not big enough..it\'s aptU won\'t feel any issue with the size and stuff3.power is great.trust me it\'s great.the bass at 0 level mid level with just Equalizer presets is awesome.clarity of vocals and those English movie special effects bass sounds bgm all sound just perfect.dialogues are great.if ur smart tv has dialogue enhance option u can change that reather than changing the soundbar settings always.4.the bass is enough, punchy for a tv viewing and movies.this soundbar is NOT for loud music lovers and bass boom boom party people this is for music lovers.may it be living room tv or bedroom tv or music listening while working with desktop laptop and even on casual music constant this is enough.basically its a soundbar for every indian...may it be house hold may it be shop showroom or small garages and the list is endless...this will not occupy space yet serve the purpose 99%5.no wall mount given but u can always fix those small photos frames hooks behind with screw and the body is sturdy enough for that.mine is a table top tv setup and it looks amazing6.the hdmi arc audio is awesome at 50 percent synced volume only I am reducing sound of English movie channels of action and sci fi.7.external power adapter which ensures the soundbar doesn\'t get hot and the best part is u can always get an aftermarket adapter if this one goes damaged.8.the subwoofer is compact and small but don\'t go by the size when u place it properly in the wall room corner and give a distance of 10cm approx from the wall as the air vent is at the back u will definitely get a good bass.for best bass u need to check placement videos on YouTube and how to keep furniture and other stuff for a great living room sound.9.the price is good at 3499 so beyond that u can avoind buying and don\'t buy 3902 model as the output is marginally same but the led indicator is a big turn off on 3902.10.i have always used zebronics brand and never ever used boat trust me boat is all hype but this brand zebronics is pure quality and no compromise.Buy this soundbar for a budget and you will not at all regret your decision to buy...5 star super dhamaka product ..\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Katam Akil Gnana Paul\", \"rating\": \"4.0\", \"date\": \"26 May 2025\", \"text\": \"Solid for even biggest room. Built Premium, Value for Money. Remote could be better. App integration is something missing at this price.\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kalindi\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"The product is very good and has a very nice and powerfull sound. For the performance of the product I am giving five star for the product. The product is very nice and full marks to zebronics for bringing such product in the market.\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"22 Mar 2025\", \"text\": \"Superb Soundhar. I was lot of confusion of selecting Home theater. Fortunately my grand son impressed upon me to buy  soudbarr instead of Home theater. Finally on his selections I purchased this Zerbonics soundhar 100 A with 60 watts. This soundhar is very very supero superb. Easy to install. The sound is very much appreciated and shocking on the whole room So must buy. Cheap and best. I am giving this reiw after 10 days of use\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"shyam Chouhanshyam Chouhan\", \"rating\": \"1.0\", \"date\": \"11 Apr 2025\", \"text\": \"Read more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Danish InamdarDanish Inamdar\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"One of The immersive sound quality of this soundbar truly elevates the home theater experience.  Its sleek design seamlessly integrates with any entertainment setup.  The deep bass and crisp dialogue create a rich audio landscape.  Setting up the soundbar was remarkably straightforward and user-friendly.  This device significantly enhances movie nights and music listening.the best soundbar\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tukaram Kadam\", \"rating\": \"3.0\", \"date\": \"28 Mar 2025\", \"text\": \"It\'s ok for this price.....Subuufer not for satisfaction base\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Bharath\", \"rating\": \"4.0\", \"date\": \"12 Dec 2024\", \"text\": \"Writting this review after using the product for 1 week.Subwoofer is too small but Producing Good bass.Only led indicator provided. No displayEasy to pair with bluetooth.Glassy finish gives you good look to the speaker Bar.No wall mount option.\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"30 Aug 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Seedhi baat no extra stuffI have a multiple number of soundbars and hence m saying this from experience.I was too sceptical to buy it for my 55 inches led tv but took the decision reading and watching reviews on YouTubeSo summary of points as below1.60W is enough for a normal user in family or bachelor house for loud music😀 and tv movie viewing.2.the size is too cute and perfect for tight spaces and that the main reason of me buying this.dont think it\'s not big enough..it\'s aptU won\'t feel any issue with the size and stuff3.power is great.trust me it\'s great.the bass at 0 level mid level with just Equalizer presets is awesome.clarity of vocals and those English movie special effects bass sounds bgm all sound just perfect.dialogues are great.if ur smart tv has dialogue enhance option u can change that reather than changing the soundbar settings always.4.the bass is enough, punchy for a tv viewing and movies.this soundbar is NOT for loud music lovers and bass boom boom party people this is for music lovers.may it be living room tv or bedroom tv or music listening while working with desktop laptop and even on casual music constant this is enough.basically its a soundbar for every indian...may it be house hold may it be shop showroom or small garages and the list is endless...this will not occupy space yet serve the purpose 99%5.no wall mount given but u can always fix those small photos frames hooks behind with screw and the body is sturdy enough for that.mine is a table top tv setup and it looks amazing6.the hdmi arc audio is awesome at 50 percent synced volume only I am reducing sound of English movie channels of action and sci fi.7.external power adapter which ensures the soundbar doesn\'t get hot and the best part is u can always get an aftermarket adapter if this one goes damaged.8.the subwoofer is compact and small but don\'t go by the size when u place it properly in the wall room corner and give a distance of 10cm approx from the wall as the air vent is at the back u will definitely get a good bass.for best bass u need to check placement videos on YouTube and how to keep furniture and other stuff for a great living room sound.9.the price is good at 3499 so beyond that u can avoind buying and don\'t buy 3902 model as the output is marginally same but the led indicator is a big turn off on 3902.10.i have always used zebronics brand and never ever used boat trust me boat is all hype but this brand zebronics is pure quality and no compromise.Buy this soundbar for a budget and you will not at all regret your decision to buy...5 star super dhamaka product ..\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Katam Akil Gnana Paul\", \"rating\": \"4.0\", \"date\": \"26 May 2025\", \"text\": \"Solid for even biggest room. Built Premium, Value for Money. Remote could be better. App integration is something missing at this price.\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Kalindi\", \"rating\": \"5.0\", \"date\": \"13 May 2025\", \"text\": \"The product is very good and has a very nice and powerfull sound. For the performance of the product I am giving five star for the product. The product is very nice and full marks to zebronics for bringing such product in the market.\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"22 Mar 2025\", \"text\": \"Superb Soundhar. I was lot of confusion of selecting Home theater. Fortunately my grand son impressed upon me to buy  soudbarr instead of Home theater. Finally on his selections I purchased this Zerbonics soundhar 100 A with 60 watts. This soundhar is very very supero superb. Easy to install. The sound is very much appreciated and shocking on the whole room So must buy. Cheap and best. I am giving this reiw after 10 days of use\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"shyam Chouhanshyam Chouhan\", \"rating\": \"1.0\", \"date\": \"11 Apr 2025\", \"text\": \"Read more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Danish InamdarDanish Inamdar\", \"rating\": \"5.0\", \"date\": \"23 May 2025\", \"text\": \"One of The immersive sound quality of this soundbar truly elevates the home theater experience.  Its sleek design seamlessly integrates with any entertainment setup.  The deep bass and crisp dialogue create a rich audio landscape.  Setting up the soundbar was remarkably straightforward and user-friendly.  This device significantly enhances movie nights and music listening.the best soundbar\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Tukaram Kadam\", \"rating\": \"3.0\", \"date\": \"28 Mar 2025\", \"text\": \"It\'s ok for this price.....Subuufer not for satisfaction base\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Bharath\", \"rating\": \"4.0\", \"date\": \"12 Dec 2024\", \"text\": \"Writting this review after using the product for 1 week.Subwoofer is too small but Producing Good bass.Only led indicator provided. No displayEasy to pair with bluetooth.Glassy finish gives you good look to the speaker Bar.No wall mount option.\n  \nRead more\", \"product_id\": \"B0DV3R2QM6\", \"link\": \"https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>JBL Cinema SB271, Dolby Digital Soundbar with Wireless Subwoofer for Extra Deep Bass, 2.1 Channel Home Theatre</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>6</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0B6441RNK\", \"product_name\": \"JBL Cinema SB271, Dolby Digital Soundbar with Wireless Subwoofer for Extra Deep Bass, 2.1 Channel Home Theatre with Remote, HDMI ARC, Bluetooth &amp; Optical Connectivity (220W)\", \"product_url\": \"https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4\", \"summary\": {\"total_reviews\": 6, \"average_rating\": 4.67, \"sentiment_breakdown\": {\"positive\": 6}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Sasikala\", \"rating\": \"5.0\", \"date\": \"05 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    JBL speaker is the best for the people who likes low bass with crystal clear sound qualityJBL speaker made at high qualityIt comes for longer life span of you use correctlyThis speaker is suitable for the people who like soft bass for music and also for moviesUsually it feels low bass but it\'s deep and crystal clear audioBut based on the room size you should buyIf you buy high watt for small room it causing irritation and headacheAnd if you buy low watt for big hall it feels disappointmentI used this 220w speaker for my 100square feet under 40%or 30% it\'s very good for hearing melody and other songs I felt irritate when I used high sound for long time as my room size is smallerFor both hall and room I planned and purchasedIam trusting that this speaker comes for many yearsIt\'s value for money you can go for itIt\'s also perform excellent for movies with low and deep bass but powerfulBut you should buy the speaker from Amazon carefully as they given only service replacement for 7 daysTake videoes and photos when you open the boxCheck whether the box is already opened or sealed packageI got perfect package from AmazonBut it\'s cost is too high even though it has made at high quality you can go for itSony is best for movies with high bassJBL is best for movies and music lover with perfect sound clarityJBL is best in sound clarity compare to Sony. Thank you\n  \nRead more\", \"product_id\": \"B0B6441RNK\", \"link\": \"https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4\", \"sentiment\": \"positive\"}, {\"author\": \"Pravin P.Pravin P.\", \"rating\": \"4.0\", \"date\": \"08 Oct 2023\", \"text\": \"*Read Edit at the bottom*--Original review:Very balanced &amp; melodious sound signature! Set it on movie mode and forget playing with its settings - oh well there isn\'t anything to do on remote as you can\'t adjust bass treble. I don\'t mind that! The soundbar is tuned so well for balanced sound that it won\'t irritate you and you will actually enjoy listening for long hours.Note: My observations below are based on \'Movie\' mode which I think is best mode. Music mode is like 60-65% voice and rest is of instruments - perfect for those who can\'t tolerate noise (loud music). When you set on Music mode the overall volume sounds lower.*Trebles* - Clear trebles - you will hear many music instruments which you miss completely in bass heavy speakers.*Bass* - Detailed bass - all lower bass and not much mid &amp; upper bass. No boomy and vibrating bass - its clean high quality bass, absolutely no distortion. Also no artificial beats, boomy effects.Bass in quantity vs bass in quality - you have to experience it to understand!This soundbar produces the quality one.*Dialogues/Vocals* -  Vocals are great and sounds natural!Perfect for pairing with TV, you will enjoy OTT movies and shows. You don\'t have to adjust volume levels frequently as with other soundbars! This cinema series is specifically designed for movies and tv shows binging - in which it excels!My first budget soundbar from quality brand, a level above zebronics, moto, boats, govos etc products under 10k. Got it at 9k, sounds like worth it for how it performs.*Cons* -- If you like bass a lot, you won\'t like it. Note that this soundbar does give good bass whose quality is far better than cheap soundbars but its less in quantity specially when you increase volume you\'d expect bit more bass which feel lacking.- I noticed this soundbar has in-built volume normalizer. When there is very loud sound the soundbar reduces volume lower than what the actual volume level is playing at. The volume should normalize to current volume level and not reduce it lower. For example, if volume level is set at 50% and when normalizer kicks in it will reduce volume to 20% Note that it happens to very specific frequencies that product high volume and I didn\'t face it with all content. Still I wish they could fix it with firmware update. Since its a bit older product now I don\'t expect any update on firmware.- No led display- Bluetooth sound performance not good enough, stick to HDMI Arc or at least OpticalConclusion:If you consumption is mostly on TV Shows, Movies side then Highly recommended for TV!Music experience is also very sweet but it\'s NOT for loud/party music. At high volume bass will be quite less and with volume normalizer feature it is kind of not great experience.*Edit (November 2024)*While what I wrote above holds true but I have moved away from soundbars! Ever since I heard bookshelf speakers - they outperform soundbars by quite a distance - it\'s like experiencing whole new world. Don\'t buy soundbars - buy at least active bookshelf speakers something like JBL Nako K4 pair around 11-12k, Swans D1080-IVB at 12k Or you can get old passive speakers of Sony, Onkyo, Philips, Aiwa, Samsung etc. under 5k and connect them with cheap class D amplifiers like Aiyima T9, Fosi BT20A Pro, Aiyima A07 Max, Fosi BT20A. This will perform better than even expensive soundbars.\n  \nRead more\", \"product_id\": \"B0B6441RNK\", \"link\": \"https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4\", \"sentiment\": \"positive\"}, {\"author\": \"Sahil\", \"rating\": \"5.0\", \"date\": \"18 Jul 2023\", \"text\": \"I recently purchased the JBL Cinema SB271 Dolby Digital Soundbar, and I\'m quite pleased with my purchase. Overall, I would rate it 4 out of 5 stars. This soundbar may be an entry-level product, but it delivers higher-quality sound than expected, making it a worthy addition to your home theater setup.The package arrived promptly and in good condition, thanks to Amazon\'s packaging and delivery standards. Setting up the soundbar was a breeze, thanks to the detailed and easy-to-follow instruction handbook. It includes the soundbar, a wireless subwoofer, and an HDMI (ARC) cable, as well as fixtures for wall mounting.The product appearance is stylish and appealing, adding a touch of elegance to any living room. The sound quality is impressive, providing a greater audio experience compared to standard TV speakers. It\'s suitable for various uses, from watching sports and movies to enjoying music with family and friends.Connecting the soundbar to the TV is simple, just plug in the HDMI cord, and it works flawlessly. However, the Bluetooth connectivity could have been better. Sometimes, the connection between the soundbar and subwoofer can be a bit tricky, and the back light indicator is confusing. Turning on the subwoofer before the soundbar might take some getting used to, but it\'s a minor inconvenience.The soundbar lacks variable equalizer settings, except for News, Music, and Movie modes. Despite this limitation, the sound quality remains promising and provides excellent value for money. If you\'re looking to enhance your sound experience without spending a fortune on elaborate sound configurations, this soundbar is more than sufficient.However, it may not be the best choice for heavy metal enthusiasts or those with specific tweeter quality and bass requirements. Also, keep in mind that it doesn\'t support advanced audio formats like Atmos or Dolby.In conclusion, the JBL Cinema SB271 Dolby Digital Soundbar is an excellent option for anyone seeking an affordable and stylish sound upgrade. With its impressive sound quality, easy setup, and overall performance, it represents excellent value for money. If you\'re in the market for a reliable and feature-packed soundbar, the JBL Cinema SB271 is worth considering.\n  \nRead more\", \"product_id\": \"B0B6441RNK\", \"link\": \"https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4\", \"sentiment\": \"positive\"}, {\"author\": \"Sasikala\", \"rating\": \"5.0\", \"date\": \"05 Jan 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n\n    \n        \n\n        \n        \n            \n        \n\n        \n            \n            \n                \n                        \n                \n                \n                    The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    JBL speaker is the best for the people who likes low bass with crystal clear sound qualityJBL speaker made at high qualityIt comes for longer life span of you use correctlyThis speaker is suitable for the people who like soft bass for music and also for moviesUsually it feels low bass but it\'s deep and crystal clear audioBut based on the room size you should buyIf you buy high watt for small room it causing irritation and headacheAnd if you buy low watt for big hall it feels disappointmentI used this 220w speaker for my 100square feet under 40%or 30% it\'s very good for hearing melody and other songs I felt irritate when I used high sound for long time as my room size is smallerFor both hall and room I planned and purchasedIam trusting that this speaker comes for many yearsIt\'s value for money you can go for itIt\'s also perform excellent for movies with low and deep bass but powerfulBut you should buy the speaker from Amazon carefully as they given only service replacement for 7 daysTake videoes and photos when you open the boxCheck whether the box is already opened or sealed packageI got perfect package from AmazonBut it\'s cost is too high even though it has made at high quality you can go for itSony is best for movies with high bassJBL is best for movies and music lover with perfect sound clarityJBL is best in sound clarity compare to Sony. Thank you\n  \nRead more\", \"product_id\": \"B0B6441RNK\", \"link\": \"https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4\", \"sentiment\": \"positive\"}, {\"author\": \"Pravin P.Pravin P.\", \"rating\": \"4.0\", \"date\": \"08 Oct 2023\", \"text\": \"*Read Edit at the bottom*--Original review:Very balanced &amp; melodious sound signature! Set it on movie mode and forget playing with its settings - oh well there isn\'t anything to do on remote as you can\'t adjust bass treble. I don\'t mind that! The soundbar is tuned so well for balanced sound that it won\'t irritate you and you will actually enjoy listening for long hours.Note: My observations below are based on \'Movie\' mode which I think is best mode. Music mode is like 60-65% voice and rest is of instruments - perfect for those who can\'t tolerate noise (loud music). When you set on Music mode the overall volume sounds lower.*Trebles* - Clear trebles - you will hear many music instruments which you miss completely in bass heavy speakers.*Bass* - Detailed bass - all lower bass and not much mid &amp; upper bass. No boomy and vibrating bass - its clean high quality bass, absolutely no distortion. Also no artificial beats, boomy effects.Bass in quantity vs bass in quality - you have to experience it to understand!This soundbar produces the quality one.*Dialogues/Vocals* -  Vocals are great and sounds natural!Perfect for pairing with TV, you will enjoy OTT movies and shows. You don\'t have to adjust volume levels frequently as with other soundbars! This cinema series is specifically designed for movies and tv shows binging - in which it excels!My first budget soundbar from quality brand, a level above zebronics, moto, boats, govos etc products under 10k. Got it at 9k, sounds like worth it for how it performs.*Cons* -- If you like bass a lot, you won\'t like it. Note that this soundbar does give good bass whose quality is far better than cheap soundbars but its less in quantity specially when you increase volume you\'d expect bit more bass which feel lacking.- I noticed this soundbar has in-built volume normalizer. When there is very loud sound the soundbar reduces volume lower than what the actual volume level is playing at. The volume should normalize to current volume level and not reduce it lower. For example, if volume level is set at 50% and when normalizer kicks in it will reduce volume to 20% Note that it happens to very specific frequencies that product high volume and I didn\'t face it with all content. Still I wish they could fix it with firmware update. Since its a bit older product now I don\'t expect any update on firmware.- No led display- Bluetooth sound performance not good enough, stick to HDMI Arc or at least OpticalConclusion:If you consumption is mostly on TV Shows, Movies side then Highly recommended for TV!Music experience is also very sweet but it\'s NOT for loud/party music. At high volume bass will be quite less and with volume normalizer feature it is kind of not great experience.*Edit (November 2024)*While what I wrote above holds true but I have moved away from soundbars! Ever since I heard bookshelf speakers - they outperform soundbars by quite a distance - it\'s like experiencing whole new world. Don\'t buy soundbars - buy at least active bookshelf speakers something like JBL Nako K4 pair around 11-12k, Swans D1080-IVB at 12k Or you can get old passive speakers of Sony, Onkyo, Philips, Aiwa, Samsung etc. under 5k and connect them with cheap class D amplifiers like Aiyima T9, Fosi BT20A Pro, Aiyima A07 Max, Fosi BT20A. This will perform better than even expensive soundbars.\n  \nRead more\", \"product_id\": \"B0B6441RNK\", \"link\": \"https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4\", \"sentiment\": \"positive\"}, {\"author\": \"Sahil\", \"rating\": \"5.0\", \"date\": \"18 Jul 2023\", \"text\": \"I recently purchased the JBL Cinema SB271 Dolby Digital Soundbar, and I\'m quite pleased with my purchase. Overall, I would rate it 4 out of 5 stars. This soundbar may be an entry-level product, but it delivers higher-quality sound than expected, making it a worthy addition to your home theater setup.The package arrived promptly and in good condition, thanks to Amazon\'s packaging and delivery standards. Setting up the soundbar was a breeze, thanks to the detailed and easy-to-follow instruction handbook. It includes the soundbar, a wireless subwoofer, and an HDMI (ARC) cable, as well as fixtures for wall mounting.The product appearance is stylish and appealing, adding a touch of elegance to any living room. The sound quality is impressive, providing a greater audio experience compared to standard TV speakers. It\'s suitable for various uses, from watching sports and movies to enjoying music with family and friends.Connecting the soundbar to the TV is simple, just plug in the HDMI cord, and it works flawlessly. However, the Bluetooth connectivity could have been better. Sometimes, the connection between the soundbar and subwoofer can be a bit tricky, and the back light indicator is confusing. Turning on the subwoofer before the soundbar might take some getting used to, but it\'s a minor inconvenience.The soundbar lacks variable equalizer settings, except for News, Music, and Movie modes. Despite this limitation, the sound quality remains promising and provides excellent value for money. If you\'re looking to enhance your sound experience without spending a fortune on elaborate sound configurations, this soundbar is more than sufficient.However, it may not be the best choice for heavy metal enthusiasts or those with specific tweeter quality and bass requirements. Also, keep in mind that it doesn\'t support advanced audio formats like Atmos or Dolby.In conclusion, the JBL Cinema SB271 Dolby Digital Soundbar is an excellent option for anyone seeking an affordable and stylish sound upgrade. With its impressive sound quality, easy setup, and overall performance, it represents excellent value for money. If you\'re in the market for a reliable and feature-packed soundbar, the JBL Cinema SB271 is worth considering.\n  \nRead more\", \"product_id\": \"B0B6441RNK\", \"link\": \"https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sennheiser AMBEO Soundbar Max - 500 Watts Sound Bar for TV with Built in Subwoofer </t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4</v>
+      </c>
+      <c r="H72" t="n">
+        <v>16</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B07ZRTLK8Z\", \"product_name\": \"Sennheiser AMBEO Soundbar Max - 500 Watts Sound Bar for TV with Built in Subwoofer (13 Speakers) - 5.1.4 Channel with Dolby Atmos &amp; Alexa Built-in, Designed in Germany, 2 Yr Warranty\", \"product_url\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 10, \"neutral\": 2, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 62.5}, \"reviews\": [{\"author\": \"Sachin BhatiaSachin Bhatia\", \"rating\": \"5.0\", \"date\": \"30 May 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Sennheiser AMBEO Soundbar Mini, and it has truly transformed my audio experience. For such a compact device, it delivers impressive sound quality, featuring clear highs, rich mids, and deep bass.The 3D audio effect brings movies and music to life in a remarkable way.Review on DesignSleek and Stylish: Fits perfectly with my TV setup. The premium build quality is evident.Hassle-Free Installation:The setup was a breeze with the detailed manual. It offers various connectivity options, including HDMI, Bluetooth, and Wi-Fi.FeaturesVersatile Customization: The Smart Control app is fantastic for adjusting sound profiles to my liking.Convenient Voice Assistants:Built-in voice control makes operation easy.Automatic Room Calibration: Adjusts sound based on my room’s layout, ensuring the best audio quality.Regarding PerformanceImpressive Audio: Handles movies and music with excellence, delivering clear dialogue and deep bass.Boosted with Subwoofer: Pairing it with a Sennheiser subwoofer makes the sound even richer and more powerful.Perfect for Bedroom: Ideal for my bedroom, providing rich sound without being overpowering.ValueWorth Every Penny: Although it\'s on the pricier side, the sound quality and performance justify the investment.Overall ⭐️⭐️⭐️⭐️⭐️ Exceeded my expectations!\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ali\", \"rating\": \"5.0\", \"date\": \"17 Dec 2024\", \"text\": \"This is a good product for all occasions. Be it for turning your room into a mini theatre or playing light music while you work, it has a great quality sound\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"VENKATA RAMANA\", \"rating\": \"5.0\", \"date\": \"07 Dec 2023\", \"text\": \"Audio &amp; music listen this sound bar very clear.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Priyank Shahi\", \"rating\": \"1.0\", \"date\": \"12 Jan 2025\", \"text\": \"Lacks crystal sound. Definately not for music, There is only midrange, middy sound, no highs, may be suitable for movies, Sennheiser should improve their for the music.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"D10z\", \"rating\": \"4.0\", \"date\": \"02 Mar 2025\", \"text\": \"The sound quality is excellent.But attaching to tv,ps5 and airtel xtream black box is confusing.The remote is on the heavier side and twisting the cover to fix the coin battery ended up breaking it.The battery cover should be customer friendly like other tv remote.Now that the remote is not functioning and cannotbe replaced,it a total waste of money and time.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"AnkushAnkush\", \"rating\": \"5.0\", \"date\": \"12 May 2024\", \"text\": \"Sennheiser\'s Ambeo Plus is absolutely top-notch! The sound quality is fantastic, especially with the Ambeo function. Surprisingly, even without a subwoofer, the bass is just right but once paired with the sub, the bass is strong enough to enhance the experience without overpowering it.It\'s like the bass knows exactly when to make an appearance. Perfect for movies, the bass is clear, precise, and never overwhelms the audio. Plus, the app is super user-friendly, putting all the settings you need right at your fingertips. No need to go searching around—it\'s all there, making customization a breeze. Overall, I\'m thoroughly impressed!\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"karthikeyankarthikeyan\", \"rating\": \"5.0\", \"date\": \"19 May 2024\", \"text\": \"I recently purchased the Ambeo Plus Soundbar and couldnt be more thrilled with my initial impressionlet me tell you, it has exceeded all my expectations.Self-Calibration:One of the standout features of the Ambeo Plus Soundbar is its self-calibration capability. The soundbar intelligently tunes itself to the room, ensuring optimal sound quality tailored to my living space. The difference in sound quality before and after calibration was noticeable, with a richer, more immersive audio experience.Performance with Dolby Atmos and DTS:X:The Dolby Atmos and DTS:X support truly elevated the audio experience to new heights. Whether I\'m watching movies, playing games, or listening to music. With a living room spanning 350 square feet, I was impressed by how well the soundbar fills the space.Overall Impressions:In conclusion, the Ambeo Plus Soundbar has completely transformed my home audio experience. I would highly recommend it to anyone looking for immersive, high-quality sound. It\'s truly a game-changer one of the best out there with 2 Yrs Warranty which is an unique offering from sennheiser.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mohit Shah\", \"rating\": \"2.0\", \"date\": \"18 Jul 2024\", \"text\": \"The calibration mic is very delicate and gets broken. also the sub woofer vibrates a lot while playing at high volumes.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"Sachin BhatiaSachin Bhatia\", \"rating\": \"5.0\", \"date\": \"30 May 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    I recently purchased the Sennheiser AMBEO Soundbar Mini, and it has truly transformed my audio experience. For such a compact device, it delivers impressive sound quality, featuring clear highs, rich mids, and deep bass.The 3D audio effect brings movies and music to life in a remarkable way.Review on DesignSleek and Stylish: Fits perfectly with my TV setup. The premium build quality is evident.Hassle-Free Installation:The setup was a breeze with the detailed manual. It offers various connectivity options, including HDMI, Bluetooth, and Wi-Fi.FeaturesVersatile Customization: The Smart Control app is fantastic for adjusting sound profiles to my liking.Convenient Voice Assistants:Built-in voice control makes operation easy.Automatic Room Calibration: Adjusts sound based on my room’s layout, ensuring the best audio quality.Regarding PerformanceImpressive Audio: Handles movies and music with excellence, delivering clear dialogue and deep bass.Boosted with Subwoofer: Pairing it with a Sennheiser subwoofer makes the sound even richer and more powerful.Perfect for Bedroom: Ideal for my bedroom, providing rich sound without being overpowering.ValueWorth Every Penny: Although it\'s on the pricier side, the sound quality and performance justify the investment.Overall ⭐️⭐️⭐️⭐️⭐️ Exceeded my expectations!\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ali\", \"rating\": \"5.0\", \"date\": \"17 Dec 2024\", \"text\": \"This is a good product for all occasions. Be it for turning your room into a mini theatre or playing light music while you work, it has a great quality sound\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"VENKATA RAMANA\", \"rating\": \"5.0\", \"date\": \"07 Dec 2023\", \"text\": \"Audio &amp; music listen this sound bar very clear.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Priyank Shahi\", \"rating\": \"1.0\", \"date\": \"12 Jan 2025\", \"text\": \"Lacks crystal sound. Definately not for music, There is only midrange, middy sound, no highs, may be suitable for movies, Sennheiser should improve their for the music.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"D10z\", \"rating\": \"4.0\", \"date\": \"02 Mar 2025\", \"text\": \"The sound quality is excellent.But attaching to tv,ps5 and airtel xtream black box is confusing.The remote is on the heavier side and twisting the cover to fix the coin battery ended up breaking it.The battery cover should be customer friendly like other tv remote.Now that the remote is not functioning and cannotbe replaced,it a total waste of money and time.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"AnkushAnkush\", \"rating\": \"5.0\", \"date\": \"12 May 2024\", \"text\": \"Sennheiser\'s Ambeo Plus is absolutely top-notch! The sound quality is fantastic, especially with the Ambeo function. Surprisingly, even without a subwoofer, the bass is just right but once paired with the sub, the bass is strong enough to enhance the experience without overpowering it.It\'s like the bass knows exactly when to make an appearance. Perfect for movies, the bass is clear, precise, and never overwhelms the audio. Plus, the app is super user-friendly, putting all the settings you need right at your fingertips. No need to go searching around—it\'s all there, making customization a breeze. Overall, I\'m thoroughly impressed!\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"karthikeyankarthikeyan\", \"rating\": \"5.0\", \"date\": \"19 May 2024\", \"text\": \"I recently purchased the Ambeo Plus Soundbar and couldnt be more thrilled with my initial impressionlet me tell you, it has exceeded all my expectations.Self-Calibration:One of the standout features of the Ambeo Plus Soundbar is its self-calibration capability. The soundbar intelligently tunes itself to the room, ensuring optimal sound quality tailored to my living space. The difference in sound quality before and after calibration was noticeable, with a richer, more immersive audio experience.Performance with Dolby Atmos and DTS:X:The Dolby Atmos and DTS:X support truly elevated the audio experience to new heights. Whether I\'m watching movies, playing games, or listening to music. With a living room spanning 350 square feet, I was impressed by how well the soundbar fills the space.Overall Impressions:In conclusion, the Ambeo Plus Soundbar has completely transformed my home audio experience. I would highly recommend it to anyone looking for immersive, high-quality sound. It\'s truly a game-changer one of the best out there with 2 Yrs Warranty which is an unique offering from sennheiser.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Mohit Shah\", \"rating\": \"2.0\", \"date\": \"18 Jul 2024\", \"text\": \"The calibration mic is very delicate and gets broken. also the sub woofer vibrates a lot while playing at high volumes.\n  \nRead more\", \"product_id\": \"B07ZRTLK8Z\", \"link\": \"https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1\", \"sentiment\": \"negative\"}]}</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sony HT-A3000 5.1.ch 360 SSM and Dolby Atmos Soundbar Home Theatre System with Wireless subwoofer</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>12</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>16</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DH5217H7\", \"product_name\": \"Sony HT-A3000 5.1.ch 360 SSM and Dolby Atmos Soundbar Home Theatre System with Wireless subwoofer SA-SW3 and Rear Speaker SA-RS3S(Hi Res &amp; 360 Reality Audio, Bluetooth,Google/Alexa)\", \"product_url\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.38, \"sentiment_breakdown\": {\"positive\": 12, \"neutral\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"JAI MEDICALS ARNI\", \"rating\": \"5.0\", \"date\": \"12 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    best qt best sound best 360 sony vvvv best h\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"suraj niprul\", \"rating\": \"5.0\", \"date\": \"23 Oct 2023\", \"text\": \"engineer followup for installation and installed the product within 1 day of deliverygood service from sony (Javed Shaikh)\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Sam Mathew\", \"rating\": \"5.0\", \"date\": \"13 May 2023\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    The sound signature is High definition ,sweet, sublime sony sound with great stereo dynamics.It is a compact system that offers nice stereo sound.You can customise the sound after connecting to TV.Especially the decibel dB adjustment and distance adjustment after going into manual speaker settings,after disabling 360 sound. You get best sound. Please turn 360 sound on which will lock the settings. Without calibration itself if you have the components it will offer good sound.But To say the truth the A series of sony is better than all other brands but calibration can be a problem to many..Cons about the 3000.1. The most important con is this bar is highly priced .2.Sound feild is little narrow but for the price paid we expect little more big feild. 3.components are must for the sony brand sound we are expecting for all A series sound bars.4, even though The stereo dynamics is good it is not as versatile as the 5000..in 5000 when you do db adjustment it becomes the best sony system currently available and blows out most other premium brand like bose and jbl out of the Park..My Score with all components for movies 7.0/10,for music 7.5/10. Overall 5000 may be little better,more open ,more versatile but not compact..height and direction adjustment also makes sound more effective.If you love the sublime sony stereo sound you can Go for 3000 but if you want something more go for the more versatile 5000.Hope you found this review useful and helpful! thanks\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"25 Oct 2023\", \"text\": \"It is a good product, but as far as sound is concerned i feel only bar is not sufficient if you plan only to go for bar opt for 5000 or 7000 model only bar won’t give that performance as much as it is hyped on youtube review or internet still i would say the product is a quality product sound is crisp and it is fun to watch movies or tv on this but sometimes on amazon prime or netflix or any other platforms the volume of the bar need to be raised to 100% so if you have a bigger room than 200 sq. Ft. You will need to go for 5000\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"harshanand Popalwar\", \"rating\": \"4.0\", \"date\": \"13 Mar 2024\", \"text\": \"Sound is very nice. Service installation is very fast.\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Gautam kumarGautam kumar\", \"rating\": \"5.0\", \"date\": \"11 Sep 2024\", \"text\": \"Well product\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Madhu Gourelly\", \"rating\": \"1.0\", \"date\": \"09 Oct 2023\", \"text\": \"It’s sound quality worest go other brands it’s not worthy 50kIt should be 10 to 15 k around.**** Don’t Waste ur money*******\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"PRITHIJIT CHAUDHURY\", \"rating\": \"5.0\", \"date\": \"10 Oct 2023\", \"text\": \"Very good soundbar and very good installation done by Mr Shamim from Sony.\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"JAI MEDICALS ARNI\", \"rating\": \"5.0\", \"date\": \"12 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    best qt best sound best 360 sony vvvv best h\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"suraj niprul\", \"rating\": \"5.0\", \"date\": \"23 Oct 2023\", \"text\": \"engineer followup for installation and installed the product within 1 day of deliverygood service from sony (Javed Shaikh)\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Sam Mathew\", \"rating\": \"5.0\", \"date\": \"13 May 2023\", \"text\": \"The media could not be loaded.\n                \n            \n                \n            \n        \n    \n    \n\n\n\n\n\n\n\n\n  \n  \n    The sound signature is High definition ,sweet, sublime sony sound with great stereo dynamics.It is a compact system that offers nice stereo sound.You can customise the sound after connecting to TV.Especially the decibel dB adjustment and distance adjustment after going into manual speaker settings,after disabling 360 sound. You get best sound. Please turn 360 sound on which will lock the settings. Without calibration itself if you have the components it will offer good sound.But To say the truth the A series of sony is better than all other brands but calibration can be a problem to many..Cons about the 3000.1. The most important con is this bar is highly priced .2.Sound feild is little narrow but for the price paid we expect little more big feild. 3.components are must for the sony brand sound we are expecting for all A series sound bars.4, even though The stereo dynamics is good it is not as versatile as the 5000..in 5000 when you do db adjustment it becomes the best sony system currently available and blows out most other premium brand like bose and jbl out of the Park..My Score with all components for movies 7.0/10,for music 7.5/10. Overall 5000 may be little better,more open ,more versatile but not compact..height and direction adjustment also makes sound more effective.If you love the sublime sony stereo sound you can Go for 3000 but if you want something more go for the more versatile 5000.Hope you found this review useful and helpful! thanks\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Placeholder\", \"rating\": \"5.0\", \"date\": \"25 Oct 2023\", \"text\": \"It is a good product, but as far as sound is concerned i feel only bar is not sufficient if you plan only to go for bar opt for 5000 or 7000 model only bar won’t give that performance as much as it is hyped on youtube review or internet still i would say the product is a quality product sound is crisp and it is fun to watch movies or tv on this but sometimes on amazon prime or netflix or any other platforms the volume of the bar need to be raised to 100% so if you have a bigger room than 200 sq. Ft. You will need to go for 5000\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"harshanand Popalwar\", \"rating\": \"4.0\", \"date\": \"13 Mar 2024\", \"text\": \"Sound is very nice. Service installation is very fast.\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Gautam kumarGautam kumar\", \"rating\": \"5.0\", \"date\": \"11 Sep 2024\", \"text\": \"Well product\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"neutral\"}, {\"author\": \"Madhu Gourelly\", \"rating\": \"1.0\", \"date\": \"09 Oct 2023\", \"text\": \"It’s sound quality worest go other brands it’s not worthy 50kIt should be 10 to 15 k around.**** Don’t Waste ur money*******\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"PRITHIJIT CHAUDHURY\", \"rating\": \"5.0\", \"date\": \"10 Oct 2023\", \"text\": \"Very good soundbar and very good installation done by Mr Shamim from Sony.\n  \nRead more\", \"product_id\": \"B0DH5217H7\", \"link\": \"https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Fastrack Astor FR2 Pro 1.43" AMOLED Stainless Steel Smart Watch with SpO2, Heart Rate, BT Calling, Adaptive AOD, Functional Crown, AI Voice Assistant – Smartwatch for Stylish Professionals (Black)</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>12</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>16</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0DGGVHMDS\", \"product_name\": \"Fastrack Astor FR2 Pro 1.43\\" AMOLED Stainless Steel Smart Watch with SpO2, Heart Rate, BT Calling, Adaptive AOD, Functional Crown, AI Voice Assistant – Smartwatch for Stylish Professionals (Black)\", \"product_url\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 12, \"negative\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 75.0}, \"reviews\": [{\"author\": \"SOMAKEERTHI B\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Very nice watch but the battery backup comes only three days and battery bar is not available on ye desktop screen  itself\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"srikanthsrikanth\", \"rating\": \"4.0\", \"date\": \"22 Apr 2025\", \"text\": \"Good product good quality aqurete foot steps,hartrate,spo2,stress levels, speed connectivity,call quality also good, display quality also good, battery backup also good value for money I\'ll using this product past 11days charging still remening 27 %.\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"aishwarya desaiaishwarya desai\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Watch is very nice and mainly the display is good. Overall nice product\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Priti Rawat\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Dont Buy..Battery hardly lasts a day..I had noise smatwatch earlier and it used to last 10 days.. But with this watch within 15 min you will see the battery drop by 1%and all this while i have disabled all the settings on the watch.Even the step counter doesnt work properly.1 * only for the looks, but whts the use if its going to be off moat of the times.\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"negative\"}, {\"author\": \"Theressa Binu\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Very bad product..no quality. Please Don\'t buy this..\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"negative\"}, {\"author\": \"Subin Bhaskaran\", \"rating\": \"3.0\", \"date\": \"11 May 2025\", \"text\": \"Overall, it is a good product. The display is good. Lookwise, it is cool. The battery backup is something to mention. It lasts for a week on a single charge. The only drawback I felt was that the black coating of the strap started to flake off before a month.\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Manish kumarManish kumar\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Good packing and good qoulity\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ranjeet Jadhav\", \"rating\": \"4.0\", \"date\": \"27 May 2025\", \"text\": \"Good and affordable\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"SOMAKEERTHI B\", \"rating\": \"5.0\", \"date\": \"21 May 2025\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Very nice watch but the battery backup comes only three days and battery bar is not available on ye desktop screen  itself\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"srikanthsrikanth\", \"rating\": \"4.0\", \"date\": \"22 Apr 2025\", \"text\": \"Good product good quality aqurete foot steps,hartrate,spo2,stress levels, speed connectivity,call quality also good, display quality also good, battery backup also good value for money I\'ll using this product past 11days charging still remening 27 %.\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"aishwarya desaiaishwarya desai\", \"rating\": \"5.0\", \"date\": \"26 May 2025\", \"text\": \"Watch is very nice and mainly the display is good. Overall nice product\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Priti Rawat\", \"rating\": \"1.0\", \"date\": \"13 May 2025\", \"text\": \"Dont Buy..Battery hardly lasts a day..I had noise smatwatch earlier and it used to last 10 days.. But with this watch within 15 min you will see the battery drop by 1%and all this while i have disabled all the settings on the watch.Even the step counter doesnt work properly.1 * only for the looks, but whts the use if its going to be off moat of the times.\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"negative\"}, {\"author\": \"Theressa Binu\", \"rating\": \"5.0\", \"date\": \"06 May 2025\", \"text\": \"Very bad product..no quality. Please Don\'t buy this..\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"negative\"}, {\"author\": \"Subin Bhaskaran\", \"rating\": \"3.0\", \"date\": \"11 May 2025\", \"text\": \"Overall, it is a good product. The display is good. Lookwise, it is cool. The battery backup is something to mention. It lasts for a week on a single charge. The only drawback I felt was that the black coating of the strap started to flake off before a month.\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Manish kumarManish kumar\", \"rating\": \"5.0\", \"date\": \"16 May 2025\", \"text\": \"Good packing and good qoulity\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}, {\"author\": \"Ranjeet Jadhav\", \"rating\": \"4.0\", \"date\": \"27 May 2025\", \"text\": \"Good and affordable\n  \nRead more\", \"product_id\": \"B0DGGVHMDS\", \"link\": \"https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Fastrack Radiant FX2 2.04" AMOLED Smart Watch with BT Calling, Voice Assistant, Functional Crown, Metal Alloy Case, 100+ Sports Modes, SpO2, AOD – Smartwatch for Men and Women (Black)</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>16</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B0D7MFV54Q\", \"product_name\": \"Fastrack Radiant FX2 2.04\\" AMOLED Smart Watch with BT Calling, Voice Assistant, Functional Crown, Metal Alloy Case, 100+ Sports Modes, SpO2, AOD – Smartwatch for Men and Women (Black)\", \"product_url\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"summary\": {\"total_reviews\": 16, \"average_rating\": 4.0, \"sentiment_breakdown\": {\"positive\": 14, \"negative\": 2}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 87.5}, \"reviews\": [{\"author\": \"Navneet Singh Sirohi\", \"rating\": \"5.0\", \"date\": \"12 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Fastrack Reflex Beat+ 1.69\\" UltraVU Display smartwatch is a testament to the brand\'s reliability and innovative design. With its sleek and modern aesthetics, this watch is not only a stylish accessory but also a powerhouse of features. The 1.69\\" UltraVU display boasts an impressive 500 nits brightness, ensuring optimal visibility even in direct sunlight. Moreover, the watch offers an array of 60 sports modes, catering to a wide range of fitness enthusiasts.One of the standout features of the Reflex Beat+ is its impressive battery backup, allowing you to enjoy its functionalities without frequent charging interruptions. Additionally, the IP68 water resistance rating means you can fearlessly take a dip in the pool or engage in water-based activities without worrying about damaging the watch.Fastrack has also incorporated essential health monitoring features, including a 24/7 heart rate monitor and an SpO2 monitor, ensuring you can keep track of your vitals conveniently. The sleep tracker further enhances the watch\'s capabilities, providing valuable insights into your sleep patterns.Beyond fitness and health tracking, the Reflex Beat+ offers convenient features like music and camera control, making it a versatile companion for your daily activities.With its reliable performance, feature-packed capabilities, and sleek design, the Fastrack Reflex Beat+ 1.69\\" UltraVU Display smartwatch is undoubtedly a great investment for those seeking a trustworthy and stylish wearable that seamlessly integrates into their active lifestyles.\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Gandavarapu siva maniGandavarapu siva mani\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good 👍\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shyama Sharma\", \"rating\": \"5.0\", \"date\": \"02 Apr 2025\", \"text\": \"I am wearing it from 2 years. This product is really amazing. Worth it. It can be connected with phone Which makes it easy to change walpaper, it keeps reminding of water, clock setting and other settings is also amazing. I have already bought two one for my mother and one for myself. Going to buy another product of Fastrack\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Janardhan.c\", \"rating\": \"1.0\", \"date\": \"24 May 2025\", \"text\": \"waste product please don\'t buy anyone there is a no return also in this product\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"sarath\", \"rating\": \"3.0\", \"date\": \"15 Feb 2025\", \"text\": \"Solid built quality and excellent looking watch. But charging cable stopped working within 3 months\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vinay Vishwakarma\", \"rating\": \"5.0\", \"date\": \"06 Apr 2025\", \"text\": \"Good quality\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abinesh.T\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Good Product. Nice performance.\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Soumik palSoumik pal\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"Calling feature very good sound, touch smooth, charging speed average, product quality awesome, Super amoled Display.\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Navneet Singh Sirohi\", \"rating\": \"5.0\", \"date\": \"12 Oct 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    The Fastrack Reflex Beat+ 1.69\\" UltraVU Display smartwatch is a testament to the brand\'s reliability and innovative design. With its sleek and modern aesthetics, this watch is not only a stylish accessory but also a powerhouse of features. The 1.69\\" UltraVU display boasts an impressive 500 nits brightness, ensuring optimal visibility even in direct sunlight. Moreover, the watch offers an array of 60 sports modes, catering to a wide range of fitness enthusiasts.One of the standout features of the Reflex Beat+ is its impressive battery backup, allowing you to enjoy its functionalities without frequent charging interruptions. Additionally, the IP68 water resistance rating means you can fearlessly take a dip in the pool or engage in water-based activities without worrying about damaging the watch.Fastrack has also incorporated essential health monitoring features, including a 24/7 heart rate monitor and an SpO2 monitor, ensuring you can keep track of your vitals conveniently. The sleep tracker further enhances the watch\'s capabilities, providing valuable insights into your sleep patterns.Beyond fitness and health tracking, the Reflex Beat+ offers convenient features like music and camera control, making it a versatile companion for your daily activities.With its reliable performance, feature-packed capabilities, and sleek design, the Fastrack Reflex Beat+ 1.69\\" UltraVU Display smartwatch is undoubtedly a great investment for those seeking a trustworthy and stylish wearable that seamlessly integrates into their active lifestyles.\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Gandavarapu siva maniGandavarapu siva mani\", \"rating\": \"4.0\", \"date\": \"22 May 2025\", \"text\": \"Good 👍\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Shyama Sharma\", \"rating\": \"5.0\", \"date\": \"02 Apr 2025\", \"text\": \"I am wearing it from 2 years. This product is really amazing. Worth it. It can be connected with phone Which makes it easy to change walpaper, it keeps reminding of water, clock setting and other settings is also amazing. I have already bought two one for my mother and one for myself. Going to buy another product of Fastrack\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Janardhan.c\", \"rating\": \"1.0\", \"date\": \"24 May 2025\", \"text\": \"waste product please don\'t buy anyone there is a no return also in this product\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"negative\"}, {\"author\": \"sarath\", \"rating\": \"3.0\", \"date\": \"15 Feb 2025\", \"text\": \"Solid built quality and excellent looking watch. But charging cable stopped working within 3 months\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Vinay Vishwakarma\", \"rating\": \"5.0\", \"date\": \"06 Apr 2025\", \"text\": \"Good quality\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Abinesh.T\", \"rating\": \"4.0\", \"date\": \"13 Apr 2025\", \"text\": \"Good Product. Nice performance.\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}, {\"author\": \"Soumik palSoumik pal\", \"rating\": \"5.0\", \"date\": \"18 May 2025\", \"text\": \"Calling feature very good sound, touch smooth, charging speed average, product quality awesome, Super amoled Display.\n  \nRead more\", \"product_id\": \"B0D7MFV54Q\", \"link\": \"https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1\", \"sentiment\": \"positive\"}]}</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Hamilton Khaki Watch, Analog Watch</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>5</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>{\"product_id\": \"B09HMJ6NXS\", \"product_name\": \"Hamilton Khaki Watch, Analog Watch\", \"product_url\": \"https://www.amazon.in/Hamilton-Khaki-Watch-Analog/dp/B09HMJ6NXS/ref=sr_1_1?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.vpNmFA-2m3imGj3Ydt2TqINuNKcgVMtDYOgdVnK4nb4tnBUEQQ-Oe-6VQVA_bTxULY4ofb5qWHS1ZPqcktAaWZUXNLOnoeksm6RLzGQLUKMCQuwWfko76r3Lpj61xDtqD96dxMMiakR0qnxTDu9QKKAaYatoR05mz7G0jBqCAMc4h11J1bU3Yy93V5YvGhIkQRDWNFcuJTrlZbc4bZ1OeT7MO-DO8TYnYwKJu-46H_w8SOhk7lqNM8ijJmuW6Pg3eADwzckxlcHRYIIGjALMJaKejnxOuuuhWLx9o81VOHc.cU-Lqskud3Yv4R-CYCga_k_Nuvpq6gnIvCe3Z7RWmew&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582120&amp;sprefix=watches%2Caps%2C335&amp;sr=8-1\", \"summary\": {\"total_reviews\": 4, \"average_rating\": 5.0, \"sentiment_breakdown\": {\"positive\": 4}, \"overall_sentiment\": \"positive\", \"accuracy_score\": 100.0}, \"reviews\": [{\"author\": \"Saravanan\", \"rating\": \"5.0\", \"date\": \"23 Dec 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Wow nice watch maybe for those who are able to buy and the watch is like a gift for my failure in exam\n  \nRead more\", \"product_id\": \"B09HMJ6NXS\", \"link\": \"https://www.amazon.in/Hamilton-Khaki-Watch-Analog/dp/B09HMJ6NXS/ref=sr_1_1?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.vpNmFA-2m3imGj3Ydt2TqINuNKcgVMtDYOgdVnK4nb4tnBUEQQ-Oe-6VQVA_bTxULY4ofb5qWHS1ZPqcktAaWZUXNLOnoeksm6RLzGQLUKMCQuwWfko76r3Lpj61xDtqD96dxMMiakR0qnxTDu9QKKAaYatoR05mz7G0jBqCAMc4h11J1bU3Yy93V5YvGhIkQRDWNFcuJTrlZbc4bZ1OeT7MO-DO8TYnYwKJu-46H_w8SOhk7lqNM8ijJmuW6Pg3eADwzckxlcHRYIIGjALMJaKejnxOuuuhWLx9o81VOHc.cU-Lqskud3Yv4R-CYCga_k_Nuvpq6gnIvCe3Z7RWmew&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582120&amp;sprefix=watches%2Caps%2C335&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Karthik D.\", \"rating\": \"5.0\", \"date\": \"30 Oct 2024\", \"text\": \"THis watch is everything. Solid swiss made chrono. Buy it if you can, but note that it\'s actually worth less than HALF of the INR listed price here on Amazon. But I still went and bought it because I am effing rich!\n  \nRead more\", \"product_id\": \"B09HMJ6NXS\", \"link\": \"https://www.amazon.in/Hamilton-Khaki-Watch-Analog/dp/B09HMJ6NXS/ref=sr_1_1?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.vpNmFA-2m3imGj3Ydt2TqINuNKcgVMtDYOgdVnK4nb4tnBUEQQ-Oe-6VQVA_bTxULY4ofb5qWHS1ZPqcktAaWZUXNLOnoeksm6RLzGQLUKMCQuwWfko76r3Lpj61xDtqD96dxMMiakR0qnxTDu9QKKAaYatoR05mz7G0jBqCAMc4h11J1bU3Yy93V5YvGhIkQRDWNFcuJTrlZbc4bZ1OeT7MO-DO8TYnYwKJu-46H_w8SOhk7lqNM8ijJmuW6Pg3eADwzckxlcHRYIIGjALMJaKejnxOuuuhWLx9o81VOHc.cU-Lqskud3Yv4R-CYCga_k_Nuvpq6gnIvCe3Z7RWmew&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582120&amp;sprefix=watches%2Caps%2C335&amp;sr=8-1\", \"sentiment\": \"positive\"}, {\"author\": \"Saravanan\", \"rating\": \"5.0\", \"date\": \"23 Dec 2024\", \"text\": \"(function() {\n            P.when(\'cr-A\', \'ready\').execute(function(A) {\n                if(typeof A.toggleExpanderAriaLabel === \'function\') {\n                    A.toggleExpanderAriaLabel(\'review_text_read_more\', \'Read more of this review\', \'Read less of this review\');\n                }\n            });\n        })();\n    \n    \n        .review-text-read-more-expander:focus-visible {\n            outline: 2px solid #2162a1;\n            outline-offset: 2px;\n            border-radius: 5px;\n        }\n    \n\n\n\n\n\n\n\n\n  \n  \n    Wow nice watch maybe for those who are able to buy and the watch is like a gift for my failure in exam\n  \nRead more\", \"product_id\": \"B09HMJ6NXS\", \"link\": \"https://www.amazon.in/Hamilton-Khaki-Watch-Analog/dp/B09HMJ6NXS/ref=sr_1_1?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.vpNmFA-2m3imGj3Ydt2TqINuNKcgVMtDYOgdVnK4nb4tnBUEQQ-Oe-6VQVA_bTxULY4ofb5qWHS1ZPqcktAaWZUXNLOnoeksm6RLzGQLUKMCQuwWfko76r3Lpj61xDtqD96dxM